--- a/internal_doc/03.开发设计/OM_web接口.xlsx
+++ b/internal_doc/03.开发设计/OM_web接口.xlsx
@@ -332,7 +332,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="231">
   <si>
     <t>需求</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1241,6 +1241,30 @@
   </si>
   <si>
     <t>business_type=sequoiadb&amp;business_name=db1&amp;cluster_type=cluster&amp;cluster_name=cls1&amp;coord={[host_name, dbpath, svcname…]}&amp;catalog={[host_name, dbpath, svcname…]}&amp;data_group={[group_name, [host_name, dbpath, svcname…]]}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{errno,local}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>返回跳转页面命令</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>网页跳转响应(CMD)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>网页跳转响应(GETFILE)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>返回跳转页面代码</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>网页代码 &lt;!DOCTYPE html&gt;&lt;html&gt;&lt;head&gt;&lt;meta http-equiv="refresh" content="0;url=xxxx.html"&gt;&lt;/head&gt;&lt;/html&gt;</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1475,6 +1499,15 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1493,89 +1526,12 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -1587,7 +1543,7 @@
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="C7EDCC"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -1912,7 +1868,7 @@
       </c>
     </row>
     <row r="3" spans="1:8">
-      <c r="A3" s="22" t="s">
+      <c r="A3" s="25" t="s">
         <v>12</v>
       </c>
       <c r="B3" s="4" t="s">
@@ -1930,7 +1886,7 @@
       <c r="H3" s="4"/>
     </row>
     <row r="4" spans="1:8" ht="13.5">
-      <c r="A4" s="23"/>
+      <c r="A4" s="26"/>
       <c r="B4" s="4" t="s">
         <v>5</v>
       </c>
@@ -1946,7 +1902,7 @@
       <c r="H4" s="4"/>
     </row>
     <row r="5" spans="1:8" ht="13.5">
-      <c r="A5" s="23"/>
+      <c r="A5" s="26"/>
       <c r="B5" s="4" t="s">
         <v>8</v>
       </c>
@@ -1962,7 +1918,7 @@
       <c r="H5" s="4"/>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" s="24"/>
+      <c r="A6" s="27"/>
       <c r="B6" s="4" t="s">
         <v>13</v>
       </c>
@@ -1978,7 +1934,7 @@
       <c r="H6" s="4"/>
     </row>
     <row r="7" spans="1:8" ht="24">
-      <c r="A7" s="25" t="s">
+      <c r="A7" s="28" t="s">
         <v>24</v>
       </c>
       <c r="B7" s="4" t="s">
@@ -1996,7 +1952,7 @@
       <c r="H7" s="4"/>
     </row>
     <row r="8" spans="1:8" ht="36">
-      <c r="A8" s="26"/>
+      <c r="A8" s="29"/>
       <c r="B8" s="4" t="s">
         <v>17</v>
       </c>
@@ -2014,7 +1970,7 @@
       <c r="H8" s="4"/>
     </row>
     <row r="9" spans="1:8" ht="72">
-      <c r="A9" s="26"/>
+      <c r="A9" s="29"/>
       <c r="B9" s="4" t="s">
         <v>18</v>
       </c>
@@ -2032,7 +1988,7 @@
       <c r="H9" s="4"/>
     </row>
     <row r="10" spans="1:8" ht="24">
-      <c r="A10" s="27"/>
+      <c r="A10" s="30"/>
       <c r="B10" s="4" t="s">
         <v>21</v>
       </c>
@@ -2070,7 +2026,7 @@
       <c r="H11" s="4"/>
     </row>
     <row r="12" spans="1:8" ht="24">
-      <c r="A12" s="25" t="s">
+      <c r="A12" s="28" t="s">
         <v>26</v>
       </c>
       <c r="B12" s="4" t="s">
@@ -2088,7 +2044,7 @@
       <c r="H12" s="4"/>
     </row>
     <row r="13" spans="1:8">
-      <c r="A13" s="26"/>
+      <c r="A13" s="29"/>
       <c r="B13" s="4" t="s">
         <v>32</v>
       </c>
@@ -2104,7 +2060,7 @@
       <c r="H13" s="4"/>
     </row>
     <row r="14" spans="1:8" ht="24">
-      <c r="A14" s="26"/>
+      <c r="A14" s="29"/>
       <c r="B14" s="4" t="s">
         <v>33</v>
       </c>
@@ -2122,7 +2078,7 @@
       <c r="H14" s="4"/>
     </row>
     <row r="15" spans="1:8">
-      <c r="A15" s="26"/>
+      <c r="A15" s="29"/>
       <c r="B15" s="4" t="s">
         <v>35</v>
       </c>
@@ -2138,7 +2094,7 @@
       <c r="H15" s="4"/>
     </row>
     <row r="16" spans="1:8">
-      <c r="A16" s="26"/>
+      <c r="A16" s="29"/>
       <c r="B16" s="4" t="s">
         <v>57</v>
       </c>
@@ -2150,7 +2106,7 @@
       <c r="H16" s="4"/>
     </row>
     <row r="17" spans="1:8" ht="48">
-      <c r="A17" s="26"/>
+      <c r="A17" s="29"/>
       <c r="B17" s="4" t="s">
         <v>30</v>
       </c>
@@ -2168,7 +2124,7 @@
       <c r="H17" s="4"/>
     </row>
     <row r="18" spans="1:8">
-      <c r="A18" s="26"/>
+      <c r="A18" s="29"/>
       <c r="B18" s="4" t="s">
         <v>38</v>
       </c>
@@ -2184,7 +2140,7 @@
       <c r="H18" s="4"/>
     </row>
     <row r="19" spans="1:8">
-      <c r="A19" s="26"/>
+      <c r="A19" s="29"/>
       <c r="B19" s="4" t="s">
         <v>41</v>
       </c>
@@ -2200,7 +2156,7 @@
       <c r="H19" s="4"/>
     </row>
     <row r="20" spans="1:8">
-      <c r="A20" s="26"/>
+      <c r="A20" s="29"/>
       <c r="B20" s="4" t="s">
         <v>40</v>
       </c>
@@ -2216,7 +2172,7 @@
       <c r="H20" s="4"/>
     </row>
     <row r="21" spans="1:8" ht="24">
-      <c r="A21" s="26"/>
+      <c r="A21" s="29"/>
       <c r="B21" s="4" t="s">
         <v>44</v>
       </c>
@@ -2234,7 +2190,7 @@
       <c r="H21" s="4"/>
     </row>
     <row r="22" spans="1:8" ht="24">
-      <c r="A22" s="26"/>
+      <c r="A22" s="29"/>
       <c r="B22" s="4" t="s">
         <v>47</v>
       </c>
@@ -2250,7 +2206,7 @@
       <c r="H22" s="4"/>
     </row>
     <row r="23" spans="1:8" ht="24">
-      <c r="A23" s="26"/>
+      <c r="A23" s="29"/>
       <c r="B23" s="4" t="s">
         <v>49</v>
       </c>
@@ -3278,13 +3234,13 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G36"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="18.625" style="3" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="28.75" style="3" customWidth="1"/>
     <col min="3" max="3" width="45.125" style="10" customWidth="1"/>
-    <col min="4" max="4" width="54.375" style="30" customWidth="1"/>
+    <col min="4" max="4" width="54.375" style="24" customWidth="1"/>
     <col min="5" max="5" width="43.375" style="10" bestFit="1" customWidth="1"/>
     <col min="6" max="16384" width="9" style="3"/>
   </cols>
@@ -3295,7 +3251,7 @@
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="9"/>
-      <c r="D1" s="28"/>
+      <c r="D1" s="22"/>
       <c r="E1" s="9"/>
       <c r="F1" s="4"/>
       <c r="G1" s="4"/>
@@ -3310,7 +3266,7 @@
       <c r="C2" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="D2" s="29" t="s">
+      <c r="D2" s="23" t="s">
         <v>201</v>
       </c>
       <c r="E2" s="5" t="s">
@@ -3329,7 +3285,7 @@
       <c r="C3" s="9" t="s">
         <v>165</v>
       </c>
-      <c r="D3" s="28" t="s">
+      <c r="D3" s="22" t="s">
         <v>202</v>
       </c>
       <c r="E3" s="9"/>
@@ -3346,7 +3302,7 @@
       <c r="C4" s="9" t="s">
         <v>166</v>
       </c>
-      <c r="D4" s="28" t="s">
+      <c r="D4" s="22" t="s">
         <v>203</v>
       </c>
       <c r="E4" s="9" t="s">
@@ -3361,7 +3317,7 @@
         <v>155</v>
       </c>
       <c r="C5" s="9"/>
-      <c r="D5" s="28"/>
+      <c r="D5" s="22"/>
       <c r="E5" s="9"/>
       <c r="F5" s="4"/>
       <c r="G5" s="4"/>
@@ -3376,7 +3332,7 @@
       <c r="C6" s="9" t="s">
         <v>167</v>
       </c>
-      <c r="D6" s="28" t="s">
+      <c r="D6" s="22" t="s">
         <v>204</v>
       </c>
       <c r="E6" s="9"/>
@@ -3393,7 +3349,7 @@
       <c r="C7" s="9" t="s">
         <v>168</v>
       </c>
-      <c r="D7" s="28" t="s">
+      <c r="D7" s="22" t="s">
         <v>205</v>
       </c>
       <c r="E7" s="9" t="s">
@@ -3408,7 +3364,7 @@
         <v>155</v>
       </c>
       <c r="C8" s="9"/>
-      <c r="D8" s="28"/>
+      <c r="D8" s="22"/>
       <c r="E8" s="9"/>
       <c r="F8" s="4"/>
       <c r="G8" s="4"/>
@@ -3423,7 +3379,7 @@
       <c r="C9" s="9" t="s">
         <v>170</v>
       </c>
-      <c r="D9" s="28" t="s">
+      <c r="D9" s="22" t="s">
         <v>206</v>
       </c>
       <c r="E9" s="9"/>
@@ -3440,7 +3396,7 @@
       <c r="C10" s="9" t="s">
         <v>169</v>
       </c>
-      <c r="D10" s="28" t="s">
+      <c r="D10" s="22" t="s">
         <v>207</v>
       </c>
       <c r="E10" s="9"/>
@@ -3453,7 +3409,7 @@
         <v>155</v>
       </c>
       <c r="C11" s="9"/>
-      <c r="D11" s="28"/>
+      <c r="D11" s="22"/>
       <c r="E11" s="9"/>
       <c r="F11" s="4"/>
       <c r="G11" s="4"/>
@@ -3468,7 +3424,7 @@
       <c r="C12" s="9" t="s">
         <v>171</v>
       </c>
-      <c r="D12" s="28" t="s">
+      <c r="D12" s="22" t="s">
         <v>208</v>
       </c>
       <c r="E12" s="9"/>
@@ -3485,7 +3441,7 @@
       <c r="C13" s="9" t="s">
         <v>166</v>
       </c>
-      <c r="D13" s="28" t="s">
+      <c r="D13" s="22" t="s">
         <v>203</v>
       </c>
       <c r="E13" s="9"/>
@@ -3498,7 +3454,7 @@
         <v>155</v>
       </c>
       <c r="C14" s="9"/>
-      <c r="D14" s="28"/>
+      <c r="D14" s="22"/>
       <c r="E14" s="9"/>
       <c r="F14" s="4"/>
       <c r="G14" s="4"/>
@@ -3513,7 +3469,7 @@
       <c r="C15" s="9" t="s">
         <v>165</v>
       </c>
-      <c r="D15" s="28" t="s">
+      <c r="D15" s="22" t="s">
         <v>202</v>
       </c>
       <c r="E15" s="9"/>
@@ -3530,7 +3486,7 @@
       <c r="C16" s="9" t="s">
         <v>172</v>
       </c>
-      <c r="D16" s="28" t="s">
+      <c r="D16" s="22" t="s">
         <v>209</v>
       </c>
       <c r="E16" s="9"/>
@@ -3543,7 +3499,7 @@
         <v>155</v>
       </c>
       <c r="C17" s="9"/>
-      <c r="D17" s="28"/>
+      <c r="D17" s="22"/>
       <c r="E17" s="9"/>
       <c r="F17" s="4"/>
       <c r="G17" s="4"/>
@@ -3556,7 +3512,7 @@
         <v>175</v>
       </c>
       <c r="C18" s="9"/>
-      <c r="D18" s="28" t="s">
+      <c r="D18" s="22" t="s">
         <v>210</v>
       </c>
       <c r="E18" s="9"/>
@@ -3573,7 +3529,7 @@
       <c r="C19" s="9" t="s">
         <v>195</v>
       </c>
-      <c r="D19" s="28" t="s">
+      <c r="D19" s="22" t="s">
         <v>211</v>
       </c>
       <c r="E19" s="9" t="s">
@@ -3588,7 +3544,7 @@
         <v>155</v>
       </c>
       <c r="C20" s="9"/>
-      <c r="D20" s="28"/>
+      <c r="D20" s="22"/>
       <c r="E20" s="9"/>
       <c r="F20" s="4"/>
       <c r="G20" s="4"/>
@@ -3603,7 +3559,7 @@
       <c r="C21" s="9" t="s">
         <v>219</v>
       </c>
-      <c r="D21" s="28" t="s">
+      <c r="D21" s="22" t="s">
         <v>212</v>
       </c>
       <c r="E21" s="9"/>
@@ -3620,7 +3576,7 @@
       <c r="C22" s="9" t="s">
         <v>220</v>
       </c>
-      <c r="D22" s="28" t="s">
+      <c r="D22" s="22" t="s">
         <v>213</v>
       </c>
       <c r="E22" s="9" t="s">
@@ -3635,7 +3591,7 @@
         <v>155</v>
       </c>
       <c r="C23" s="9"/>
-      <c r="D23" s="28"/>
+      <c r="D23" s="22"/>
       <c r="E23" s="9"/>
       <c r="F23" s="4"/>
       <c r="G23" s="4"/>
@@ -3650,7 +3606,7 @@
       <c r="C24" s="9" t="s">
         <v>222</v>
       </c>
-      <c r="D24" s="28" t="s">
+      <c r="D24" s="22" t="s">
         <v>221</v>
       </c>
       <c r="E24" s="9"/>
@@ -3667,7 +3623,7 @@
       <c r="C25" s="9" t="s">
         <v>223</v>
       </c>
-      <c r="D25" s="28" t="s">
+      <c r="D25" s="22" t="s">
         <v>214</v>
       </c>
       <c r="E25" s="9"/>
@@ -3680,7 +3636,7 @@
         <v>155</v>
       </c>
       <c r="C26" s="9"/>
-      <c r="D26" s="28"/>
+      <c r="D26" s="22"/>
       <c r="E26" s="9"/>
       <c r="F26" s="4"/>
       <c r="G26" s="4"/>
@@ -3695,7 +3651,7 @@
       <c r="C27" s="9" t="s">
         <v>224</v>
       </c>
-      <c r="D27" s="28" t="s">
+      <c r="D27" s="22" t="s">
         <v>214</v>
       </c>
       <c r="E27" s="9"/>
@@ -3712,7 +3668,7 @@
       <c r="C28" s="11" t="s">
         <v>197</v>
       </c>
-      <c r="D28" s="28" t="s">
+      <c r="D28" s="22" t="s">
         <v>215</v>
       </c>
       <c r="E28" s="9" t="s">
@@ -3727,7 +3683,7 @@
         <v>155</v>
       </c>
       <c r="C29" s="9"/>
-      <c r="D29" s="28"/>
+      <c r="D29" s="22"/>
       <c r="E29" s="9"/>
       <c r="F29" s="4"/>
       <c r="G29" s="4"/>
@@ -3742,7 +3698,7 @@
       <c r="C30" s="9" t="s">
         <v>224</v>
       </c>
-      <c r="D30" s="28" t="s">
+      <c r="D30" s="22" t="s">
         <v>214</v>
       </c>
       <c r="E30" s="9"/>
@@ -3759,7 +3715,7 @@
       <c r="C31" s="9" t="s">
         <v>197</v>
       </c>
-      <c r="D31" s="28" t="s">
+      <c r="D31" s="22" t="s">
         <v>216</v>
       </c>
       <c r="E31" s="9" t="s">
@@ -3774,7 +3730,7 @@
         <v>155</v>
       </c>
       <c r="C32" s="9"/>
-      <c r="D32" s="28"/>
+      <c r="D32" s="22"/>
       <c r="E32" s="9"/>
       <c r="F32" s="4"/>
       <c r="G32" s="4"/>
@@ -3789,7 +3745,7 @@
       <c r="C33" s="9" t="s">
         <v>198</v>
       </c>
-      <c r="D33" s="28" t="s">
+      <c r="D33" s="22" t="s">
         <v>217</v>
       </c>
       <c r="E33" s="9"/>
@@ -3806,7 +3762,7 @@
       <c r="C34" s="9" t="s">
         <v>199</v>
       </c>
-      <c r="D34" s="28" t="s">
+      <c r="D34" s="22" t="s">
         <v>218</v>
       </c>
       <c r="E34" s="9"/>
@@ -3817,19 +3773,40 @@
       <c r="A35" s="4"/>
       <c r="B35" s="4"/>
       <c r="C35" s="9"/>
-      <c r="D35" s="28"/>
+      <c r="D35" s="22"/>
       <c r="E35" s="9"/>
       <c r="F35" s="4"/>
       <c r="G35" s="4"/>
     </row>
     <row r="36" spans="1:7">
-      <c r="A36" s="4"/>
+      <c r="A36" s="4" t="s">
+        <v>227</v>
+      </c>
       <c r="B36" s="4"/>
       <c r="C36" s="9"/>
-      <c r="D36" s="28"/>
-      <c r="E36" s="9"/>
+      <c r="D36" s="22" t="s">
+        <v>225</v>
+      </c>
+      <c r="E36" s="9" t="s">
+        <v>226</v>
+      </c>
       <c r="F36" s="4"/>
       <c r="G36" s="4"/>
+    </row>
+    <row r="37" spans="1:7" ht="24">
+      <c r="A37" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="B37" s="4"/>
+      <c r="C37" s="9"/>
+      <c r="D37" s="22" t="s">
+        <v>230</v>
+      </c>
+      <c r="E37" s="9" t="s">
+        <v>229</v>
+      </c>
+      <c r="F37" s="4"/>
+      <c r="G37" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/internal_doc/03.开发设计/OM_web接口.xlsx
+++ b/internal_doc/03.开发设计/OM_web接口.xlsx
@@ -332,7 +332,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="231">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="234">
   <si>
     <t>需求</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -941,12 +941,6 @@
   <si>
     <t>创建cs, cl</t>
     <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>create_cluster_req</t>
-  </si>
-  <si>
-    <t>create_cluster_res</t>
   </si>
   <si>
     <t/>
@@ -1144,10 +1138,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>rest参数</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>命令参数</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1244,10 +1234,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>{errno,local}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>返回跳转页面命令</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1265,6 +1251,34 @@
   </si>
   <si>
     <t>网页代码 &lt;!DOCTYPE html&gt;&lt;html&gt;&lt;head&gt;&lt;meta http-equiv="refresh" content="0;url=xxxx.html"&gt;&lt;/head&gt;&lt;/html&gt;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rest参数(响应最外层统一加上rc)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{rc,local}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cmd=xxx&amp;cluster_name=cls1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>create_cluster_req</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>create_cluster_res</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>命令错误</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{rc,detail}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1532,6 +1546,74 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -1543,7 +1625,7 @@
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:sysClr val="window" lastClr="C7EDCC"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -3234,7 +3316,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="18.625" style="3" bestFit="1" customWidth="1"/>
@@ -3261,13 +3343,13 @@
         <v>134</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>200</v>
+        <v>227</v>
       </c>
       <c r="D2" s="23" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="E2" s="5" t="s">
         <v>1</v>
@@ -3280,13 +3362,13 @@
         <v>28</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>153</v>
+        <v>230</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>165</v>
+        <v>229</v>
       </c>
       <c r="D3" s="22" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="E3" s="9"/>
       <c r="F3" s="4"/>
@@ -3297,13 +3379,13 @@
         <v>140</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>154</v>
+        <v>231</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D4" s="22" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="E4" s="9" t="s">
         <v>150</v>
@@ -3314,7 +3396,7 @@
     <row r="5" spans="1:7">
       <c r="A5" s="4"/>
       <c r="B5" s="4" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C5" s="9"/>
       <c r="D5" s="22"/>
@@ -3327,13 +3409,13 @@
         <v>141</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="D6" s="22" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="E6" s="9"/>
       <c r="F6" s="4"/>
@@ -3344,13 +3426,13 @@
         <v>142</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D7" s="22" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>143</v>
@@ -3361,7 +3443,7 @@
     <row r="8" spans="1:7">
       <c r="A8" s="4"/>
       <c r="B8" s="4" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C8" s="9"/>
       <c r="D8" s="22"/>
@@ -3374,13 +3456,13 @@
         <v>144</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D9" s="22" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="E9" s="9"/>
       <c r="F9" s="4"/>
@@ -3391,13 +3473,13 @@
         <v>145</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D10" s="22" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="E10" s="9"/>
       <c r="F10" s="4"/>
@@ -3406,7 +3488,7 @@
     <row r="11" spans="1:7">
       <c r="A11" s="4"/>
       <c r="B11" s="4" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C11" s="9"/>
       <c r="D11" s="22"/>
@@ -3419,13 +3501,13 @@
         <v>146</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D12" s="22" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="E12" s="9"/>
       <c r="F12" s="4"/>
@@ -3436,13 +3518,13 @@
         <v>147</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D13" s="22" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="E13" s="9"/>
       <c r="F13" s="4"/>
@@ -3451,7 +3533,7 @@
     <row r="14" spans="1:7">
       <c r="A14" s="4"/>
       <c r="B14" s="4" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C14" s="9"/>
       <c r="D14" s="22"/>
@@ -3464,13 +3546,13 @@
         <v>148</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D15" s="22" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="E15" s="9"/>
       <c r="F15" s="4"/>
@@ -3481,13 +3563,13 @@
         <v>149</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D16" s="22" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="E16" s="9"/>
       <c r="F16" s="4"/>
@@ -3496,7 +3578,7 @@
     <row r="17" spans="1:7">
       <c r="A17" s="4"/>
       <c r="B17" s="4" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C17" s="9"/>
       <c r="D17" s="22"/>
@@ -3506,14 +3588,14 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="B18" s="4" t="s">
         <v>173</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>175</v>
       </c>
       <c r="C18" s="9"/>
       <c r="D18" s="22" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="E18" s="9"/>
       <c r="F18" s="4"/>
@@ -3521,16 +3603,16 @@
     </row>
     <row r="19" spans="1:7" ht="24">
       <c r="A19" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="B19" s="4" t="s">
         <v>174</v>
       </c>
-      <c r="B19" s="4" t="s">
-        <v>176</v>
-      </c>
       <c r="C19" s="9" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="D19" s="22" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>135</v>
@@ -3541,7 +3623,7 @@
     <row r="20" spans="1:7">
       <c r="A20" s="4"/>
       <c r="B20" s="4" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C20" s="9"/>
       <c r="D20" s="22"/>
@@ -3551,16 +3633,16 @@
     </row>
     <row r="21" spans="1:7" ht="24">
       <c r="A21" s="4" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="D21" s="22" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="E21" s="9"/>
       <c r="F21" s="4"/>
@@ -3568,19 +3650,19 @@
     </row>
     <row r="22" spans="1:7" ht="48">
       <c r="A22" s="4" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="D22" s="22" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="E22" s="9" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="F22" s="4"/>
       <c r="G22" s="4"/>
@@ -3588,7 +3670,7 @@
     <row r="23" spans="1:7">
       <c r="A23" s="4"/>
       <c r="B23" s="4" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C23" s="9"/>
       <c r="D23" s="22"/>
@@ -3598,16 +3680,16 @@
     </row>
     <row r="24" spans="1:7" ht="60">
       <c r="A24" s="4" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="D24" s="22" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="E24" s="9"/>
       <c r="F24" s="4"/>
@@ -3615,16 +3697,16 @@
     </row>
     <row r="25" spans="1:7" ht="72">
       <c r="A25" s="4" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="D25" s="22" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="E25" s="9"/>
       <c r="F25" s="4"/>
@@ -3633,7 +3715,7 @@
     <row r="26" spans="1:7">
       <c r="A26" s="4"/>
       <c r="B26" s="4" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C26" s="9"/>
       <c r="D26" s="22"/>
@@ -3646,13 +3728,13 @@
         <v>136</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="D27" s="22" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="E27" s="9"/>
       <c r="F27" s="4"/>
@@ -3663,13 +3745,13 @@
         <v>137</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="D28" s="22" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="E28" s="9" t="s">
         <v>138</v>
@@ -3680,7 +3762,7 @@
     <row r="29" spans="1:7">
       <c r="A29" s="4"/>
       <c r="B29" s="4" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C29" s="9"/>
       <c r="D29" s="22"/>
@@ -3690,16 +3772,16 @@
     </row>
     <row r="30" spans="1:7" ht="60">
       <c r="A30" s="4" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="D30" s="22" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="E30" s="9"/>
       <c r="F30" s="4"/>
@@ -3707,16 +3789,16 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31" s="4" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="D31" s="22" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>139</v>
@@ -3727,7 +3809,7 @@
     <row r="32" spans="1:7">
       <c r="A32" s="4"/>
       <c r="B32" s="4" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C32" s="9"/>
       <c r="D32" s="22"/>
@@ -3737,16 +3819,16 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33" s="4" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D33" s="22" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="E33" s="9"/>
       <c r="F33" s="4"/>
@@ -3754,16 +3836,16 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34" s="4" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="D34" s="22" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="E34" s="9"/>
       <c r="F34" s="4"/>
@@ -3780,33 +3862,46 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36" s="4" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="B36" s="4"/>
       <c r="C36" s="9"/>
       <c r="D36" s="22" t="s">
-        <v>225</v>
-      </c>
-      <c r="E36" s="9" t="s">
-        <v>226</v>
-      </c>
+        <v>233</v>
+      </c>
+      <c r="E36" s="9"/>
       <c r="F36" s="4"/>
       <c r="G36" s="4"/>
     </row>
-    <row r="37" spans="1:7" ht="24">
+    <row r="37" spans="1:7">
       <c r="A37" s="4" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="B37" s="4"/>
       <c r="C37" s="9"/>
       <c r="D37" s="22" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="F37" s="4"/>
       <c r="G37" s="4"/>
+    </row>
+    <row r="38" spans="1:7" ht="24">
+      <c r="A38" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="B38" s="4"/>
+      <c r="C38" s="9"/>
+      <c r="D38" s="22" t="s">
+        <v>226</v>
+      </c>
+      <c r="E38" s="9" t="s">
+        <v>225</v>
+      </c>
+      <c r="F38" s="4"/>
+      <c r="G38" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/internal_doc/03.开发设计/OM_web接口.xlsx
+++ b/internal_doc/03.开发设计/OM_web接口.xlsx
@@ -332,7 +332,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="234">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="240">
   <si>
     <t>需求</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1242,10 +1242,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>网页跳转响应(GETFILE)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>返回跳转页面代码</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1279,6 +1275,34 @@
   </si>
   <si>
     <t>{rc,detail}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>网页跳转响应(GETFILE)(废除)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>网页session校验</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>check_session_req</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>网页session校验响应</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cmd=check_session_req</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{rc,local}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>local是跳转地址(例如:"/index.html")</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1546,74 +1570,6 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -1625,7 +1581,7 @@
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="C7EDCC"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -3316,7 +3272,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G38"/>
+  <dimension ref="A1:G40"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="18.625" style="3" bestFit="1" customWidth="1"/>
@@ -3346,7 +3302,7 @@
         <v>162</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D2" s="23" t="s">
         <v>198</v>
@@ -3362,10 +3318,10 @@
         <v>28</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D3" s="22" t="s">
         <v>199</v>
@@ -3379,7 +3335,7 @@
         <v>140</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>164</v>
@@ -3862,12 +3818,12 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36" s="4" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B36" s="4"/>
       <c r="C36" s="9"/>
       <c r="D36" s="22" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E36" s="9"/>
       <c r="F36" s="4"/>
@@ -3880,7 +3836,7 @@
       <c r="B37" s="4"/>
       <c r="C37" s="9"/>
       <c r="D37" s="22" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>222</v>
@@ -3890,18 +3846,40 @@
     </row>
     <row r="38" spans="1:7" ht="24">
       <c r="A38" s="4" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="B38" s="4"/>
       <c r="C38" s="9"/>
       <c r="D38" s="22" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E38" s="9" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F38" s="4"/>
       <c r="G38" s="4"/>
+    </row>
+    <row r="39" spans="1:7">
+      <c r="A39" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="C39" s="10" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="D40" s="24" t="s">
+        <v>238</v>
+      </c>
+      <c r="E40" s="10" t="s">
+        <v>239</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/internal_doc/03.开发设计/OM_web接口.xlsx
+++ b/internal_doc/03.开发设计/OM_web接口.xlsx
@@ -332,7 +332,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="240">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="242">
   <si>
     <t>需求</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -946,363 +946,351 @@
     <t/>
   </si>
   <si>
+    <t>scan_host_res</t>
+  </si>
+  <si>
+    <t>check_host_req</t>
+  </si>
+  <si>
+    <t>check_host_res</t>
+  </si>
+  <si>
+    <t>config_host_req</t>
+  </si>
+  <si>
+    <t>config_host_res</t>
+  </si>
+  <si>
+    <t>get_host_req</t>
+  </si>
+  <si>
+    <t>get_host_res</t>
+  </si>
+  <si>
+    <t>命令字(cmd=??)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cluster_name=cls1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cluster_name=cls1&amp;host_info={[host_ip, host_name, username, passwd, firework, [disk],[cpu]...]}&amp;username=usr1&amp;passwd=passwd1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>获取business列表</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>获取business列表响应</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>get_business_list_req</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>get_business_list_res</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>获取business模板配置</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>获取business模板配置响应</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>配置business</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>配置business响应</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>添加business</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>添加business响应</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>删除business</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>删除business响应</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>config_business_req</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>get_business_config_template_req</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>get_business_config_template_res</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>config_business_res</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>check_business_config_req</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>check_business_config_res</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>add_business_req</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>add_business_res</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>remove_business_req</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>remove_business_res</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>business_user_group, business_user_passwd(sdbadmin:sdbadmin)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>business_name=xxx&amp;cluster_name=xxx</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NA</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{business_type, business_name, cluster_type, cluster_name, [host_name, disk_name, dbpath, svcname…], [host_name, disk_name, dbpath, svcname…], [group_name, [host_name, disk_name, dbpath, svcname…]]}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{rc, [???]}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{rc, ???}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>business_type=xxx&amp;business_name=xxx&amp;cluster_type=xxx</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>business_type=xxx&amp;business_name=xxx&amp;cluster_type=xxx&amp;cluster_name=xxx&amp;rep_num=xxx&amp;rep_group_num=xxx&amp;catalog_num=xxx&amp;coord_num=xxx&amp;business_user_group=xxx&amp;business_user_passwd=xxx&amp;host_info={[host_name, disk_name]}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>business_type=sequoiadb&amp;business_name=db1&amp;cluster_type=cluster&amp;cluster_name=cls1&amp;coord={[host_name, dbpath, svcname…]}&amp;catalog={[host_name, dbpath, svcname…]}&amp;data_group={[group_name, [host_name, dbpath, svcname…]]}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>返回跳转页面命令</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>返回跳转页面代码</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rest参数(响应最外层统一加上rc)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>create_cluster_req</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>create_cluster_res</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>网页跳转响应(GETFILE)(废除)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>网页session校验</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>check_session_req</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>网页session校验响应</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>local是跳转地址(例如:"/index.html")</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>创建cluster</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>获取文件命令</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>通过接口获取（pAdptor-&gt;recvRequestBody( this, httpCommon, &amp;pFilePath, bodySize )）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{cluster_name, rc}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{[host_ip, host_name, rc]}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{cluster_name, rc, [host_ip, host_name, firework, [disk],[cpu]...]}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{[business_type, business_desc, [cluster_type]]}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{business_type, business_name, cluster_type, rep_num, rep_group_num, catalog_num, coord_num, business_user_group, business_user_passwd}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{business_name, cluster_name, rc}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{rc,detail}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{rc,local}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>命令错误响应1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>命令错误响应2（未登陆等需要网页跳转的情况)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>获取文件命令响应1(html)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NA</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>获取文件命令响应1(非html)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>读取文件失败时：_restAdaptor-&gt;sendResponse( _restSession, HTTP_NOTFOUND ) ;
+正常时：将内容appendHttpBody进去，调用sendResponse填HTTP_OK</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>读取html文件失败时：先调用 appendHttpBody, 把跳转命令append进去, 然后调用 sendResponse,  参数 HTTP_RESPONSE_CODE 应该用 HTTP_OK
+html正常时：将内容appendHttpBody进去，调用sendResponse填HTTP_OK</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>跳转命令：&lt;!DOCTYPE html&gt;&lt;html&gt;&lt;head&gt;&lt;meta http-equiv="refresh" content="0;url=xxxx.html"&gt;&lt;/head&gt;&lt;/html&gt;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>登陆命令</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>login_req</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>check_session_res</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>user=xx&amp;passwd=xx&amp;timestamp=xx</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>登陆命令响应</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>login_res</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>成功时：{rc}
+校验失败时：{rc,local} local为跳转文件login.html</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>获取cluster信息</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>query_cluster_req</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>获取cluster信息响应</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>query_cluster_res</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cmd=xxx</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>scan_host_req</t>
-  </si>
-  <si>
-    <t>scan_host_res</t>
-  </si>
-  <si>
-    <t>check_host_req</t>
-  </si>
-  <si>
-    <t>check_host_res</t>
-  </si>
-  <si>
-    <t>config_host_req</t>
-  </si>
-  <si>
-    <t>config_host_res</t>
-  </si>
-  <si>
-    <t>get_host_req</t>
-  </si>
-  <si>
-    <t>get_host_res</t>
-  </si>
-  <si>
-    <t>命令字(cmd=??)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>cluster_name=cls1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>cluster_name=cls1&amp;rc=-1&amp;detail=??</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>host_info={[host_ip/host_name, username, passwd]}&amp;username=usr1&amp;passwd=passwd1&amp;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>timestamp</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>=11</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>host_info={[host_ip, host_name, rc]}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>cluster_name=cls1&amp;host_info=[host_ip, host_name, rc, firework, [disk],[cpu]...]}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>cluster_name=cls1&amp;host_info={[host_ip, host_name, username, passwd]}&amp;username=usr1&amp;passwd=passwd1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>cluster_name=cls1&amp;host_info={[host_ip, host_name, username, passwd, firework, [disk],[cpu]...]}&amp;username=usr1&amp;passwd=passwd1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>cluster_name=cls1&amp;rc=0&amp;detail={[host_ip, host_name, firework, [disk],[cpu]...]}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>获取business列表</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>获取business列表响应</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>get_business_list_req</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>get_business_list_res</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>获取business模板配置</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>获取business模板配置响应</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>配置business</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>配置business响应</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>添加business</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>添加business响应</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>删除business</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>删除business响应</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>config_business_req</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>get_business_config_template_req</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>get_business_config_template_res</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>config_business_res</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>check_business_config_req</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>check_business_config_res</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>add_business_req</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>add_business_res</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>remove_business_req</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>remove_business_res</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>business_list={[business_type, business_desc, [cluster_type]]}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>business_user_group, business_user_passwd(sdbadmin:sdbadmin)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>rc=-1&amp;detail=???</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>business_name=xxx&amp;cluster_name=xxx</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>business_name=xxx&amp;cluster_name=xxx&amp;rc=xxx</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>命令参数</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{cluster_name}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{cluster_name, rc}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{[host_ip/host_name, username, passwd], username, passwd}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{[host_ip, host_name, rc]}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{cluster_name, [host_ip, host_name, username, passwd], username, passwd}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{cluster_name, [host_ip, host_name, rc, firework, [disk],[cpu]...]}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{cluster_name, [host_ip, host_name, username, passwd, firework, [disk],[cpu]...], username, passwd}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{cluster_name, rc, [host_ip, host_name, firework, [disk],[cpu]...]}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>NA</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{[business_type, business_desc, [cluster_type]]}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{business_type, business_name, cluster_type}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{business_type, business_name, cluster_type, rep_num, rep_group_num, catalog_num, coord_num, business_user_group, business_user_passwd}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{business_type, business_name, cluster_type, cluster_name, [host_name, disk_name, dbpath, svcname…], [host_name, disk_name, dbpath, svcname…], [group_name, [host_name, disk_name, dbpath, svcname…]]}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{rc, [???]}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{rc, ???}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>business_name, cluster_name</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>business_name, cluster_name, rc</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>business_type=xxx&amp;business_name=xxx&amp;cluster_type=xxx</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>business_type=xxx&amp;business_name=xxx&amp;cluster_type=xxx&amp;rep_num=xxx&amp;rep_group_num=xxx&amp;catalog_num=xxx&amp;coord_num=xxx&amp;business_user_group=xxx&amp;business_user_passwd=xxx</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{business_type, business_name, cluster_type, cluster_name, rep_num, rep_group_num, catalog_num, coord_num, business_user_group, business_user_passwd, [host_name, disk_name]}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>business_type=xxx&amp;business_name=xxx&amp;cluster_type=xxx&amp;cluster_name=xxx&amp;rep_num=xxx&amp;rep_group_num=xxx&amp;catalog_num=xxx&amp;coord_num=xxx&amp;business_user_group=xxx&amp;business_user_passwd=xxx&amp;host_info={[host_name, disk_name]}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>business_type=sequoiadb&amp;business_name=db1&amp;cluster_type=cluster&amp;cluster_name=cls1&amp;coord={[host_name, disk_name, dbpath, svcname…]}&amp;catalog={[host_name, disk_name, dbpath, svcname…]}&amp;data_group={[group_name, [host_name, dbpath, svcname…]]}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>business_type=sequoiadb&amp;business_name=db1&amp;cluster_type=cluster&amp;cluster_name=cls1&amp;coord={[host_name, dbpath, svcname…]}&amp;catalog={[host_name, dbpath, svcname…]}&amp;data_group={[group_name, [host_name, dbpath, svcname…]]}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>返回跳转页面命令</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>网页跳转响应(CMD)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>返回跳转页面代码</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>网页代码 &lt;!DOCTYPE html&gt;&lt;html&gt;&lt;head&gt;&lt;meta http-equiv="refresh" content="0;url=xxxx.html"&gt;&lt;/head&gt;&lt;/html&gt;</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>rest参数(响应最外层统一加上rc)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{rc,local}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>cmd=xxx&amp;cluster_name=cls1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>create_cluster_req</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>create_cluster_res</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>命令错误</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{rc,detail}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>网页跳转响应(GETFILE)(废除)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>网页session校验</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>check_session_req</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>网页session校验响应</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>cmd=check_session_req</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{rc,local}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>local是跳转地址(例如:"/index.html")</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{cluster_name:xxx, desc:xxx}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cluster_info={cluster_name=cls1, desc=xxx}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>host_info={[host_ip/host_name:xxx, username:xxx, passwd:xxx],username:usr1,passwd:passwd1}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>host_info={cluster_name:cls1, host_info:[{host_ip, host_name, username, passwd},...], username:usr1, passwd:passwd1}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{cluster_name, [{host_ip, host_name, rc, firework, [disk],[cpu]…}, ...]}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1403,7 +1391,7 @@
     </font>
     <font>
       <sz val="10"/>
-      <color theme="1" tint="0.499984740745262"/>
+      <color theme="2" tint="-0.499984740745262"/>
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
@@ -1536,14 +1524,12 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1570,6 +1556,74 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -1581,7 +1635,7 @@
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:sysClr val="window" lastClr="C7EDCC"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -3272,614 +3326,769 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G40"/>
+  <dimension ref="A1:F64"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
-    <col min="1" max="1" width="18.625" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="26" style="10" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="28.75" style="3" customWidth="1"/>
     <col min="3" max="3" width="45.125" style="10" customWidth="1"/>
-    <col min="4" max="4" width="54.375" style="24" customWidth="1"/>
-    <col min="5" max="5" width="43.375" style="10" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="9" style="3"/>
+    <col min="4" max="4" width="43.375" style="10" bestFit="1" customWidth="1"/>
+    <col min="5" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
-      <c r="A1" s="21" t="s">
+    <row r="1" spans="1:6">
+      <c r="A1" s="24" t="s">
         <v>133</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="9"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="4"/>
       <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-    </row>
-    <row r="2" spans="1:7">
-      <c r="A2" s="2" t="s">
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="5" t="s">
         <v>134</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>226</v>
-      </c>
-      <c r="D2" s="23" t="s">
+        <v>197</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="9" t="s">
+        <v>205</v>
+      </c>
+      <c r="B3" s="4" t="s">
         <v>198</v>
       </c>
-      <c r="E2" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>229</v>
-      </c>
       <c r="C3" s="9" t="s">
-        <v>228</v>
-      </c>
-      <c r="D3" s="22" t="s">
+        <v>238</v>
+      </c>
+      <c r="D3" s="9"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>199</v>
       </c>
-      <c r="E3" s="9"/>
-      <c r="F3" s="4"/>
-      <c r="G3" s="4"/>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>230</v>
-      </c>
       <c r="C4" s="9" t="s">
-        <v>164</v>
-      </c>
-      <c r="D4" s="22" t="s">
-        <v>200</v>
-      </c>
-      <c r="E4" s="9" t="s">
+        <v>208</v>
+      </c>
+      <c r="D4" s="9" t="s">
         <v>150</v>
       </c>
+      <c r="E4" s="4"/>
       <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5" s="4"/>
-      <c r="B5" s="4" t="s">
-        <v>153</v>
-      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="9"/>
+      <c r="B5" s="4"/>
       <c r="C5" s="9"/>
-      <c r="D5" s="22"/>
-      <c r="E5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="4"/>
       <c r="F5" s="4"/>
-      <c r="G5" s="4"/>
-    </row>
-    <row r="6" spans="1:7" ht="24">
-      <c r="A6" s="4" t="s">
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="9" t="s">
+        <v>231</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>235</v>
+      </c>
+      <c r="D6" s="9"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="9" t="s">
+        <v>233</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>237</v>
+      </c>
+      <c r="D7" s="9"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="9"/>
+      <c r="B8" s="4"/>
+      <c r="C8" s="9"/>
+      <c r="D8" s="9"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
+    </row>
+    <row r="9" spans="1:6" ht="24">
+      <c r="A9" s="9" t="s">
         <v>141</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B9" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="D9" s="9"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4"/>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="B10" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="C6" s="9" t="s">
-        <v>165</v>
-      </c>
-      <c r="D6" s="22" t="s">
-        <v>201</v>
-      </c>
-      <c r="E6" s="9"/>
-      <c r="F6" s="4"/>
-      <c r="G6" s="4"/>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>166</v>
-      </c>
-      <c r="D7" s="22" t="s">
-        <v>202</v>
-      </c>
-      <c r="E7" s="9" t="s">
+      <c r="C10" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="D10" s="9" t="s">
         <v>143</v>
       </c>
-      <c r="F7" s="4"/>
-      <c r="G7" s="4"/>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8" s="4"/>
-      <c r="B8" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="C8" s="9"/>
-      <c r="D8" s="22"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="4"/>
-      <c r="G8" s="4"/>
-    </row>
-    <row r="9" spans="1:7" ht="24">
-      <c r="A9" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>156</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>168</v>
-      </c>
-      <c r="D9" s="22" t="s">
-        <v>203</v>
-      </c>
-      <c r="E9" s="9"/>
-      <c r="F9" s="4"/>
-      <c r="G9" s="4"/>
-    </row>
-    <row r="10" spans="1:7" ht="24">
-      <c r="A10" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="C10" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="D10" s="22" t="s">
-        <v>204</v>
-      </c>
-      <c r="E10" s="9"/>
+      <c r="E10" s="4"/>
       <c r="F10" s="4"/>
-      <c r="G10" s="4"/>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11" s="4"/>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="9"/>
       <c r="B11" s="4" t="s">
         <v>153</v>
       </c>
       <c r="C11" s="9"/>
-      <c r="D11" s="22"/>
-      <c r="E11" s="9"/>
+      <c r="D11" s="9"/>
+      <c r="E11" s="4"/>
       <c r="F11" s="4"/>
-      <c r="G11" s="4"/>
-    </row>
-    <row r="12" spans="1:7" ht="36">
-      <c r="A12" s="4" t="s">
-        <v>146</v>
+    </row>
+    <row r="12" spans="1:6" ht="36">
+      <c r="A12" s="9" t="s">
+        <v>144</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="D12" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="E12" s="9"/>
+        <v>240</v>
+      </c>
+      <c r="D12" s="9"/>
+      <c r="E12" s="4"/>
       <c r="F12" s="4"/>
-      <c r="G12" s="4"/>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13" s="4" t="s">
-        <v>147</v>
+    </row>
+    <row r="13" spans="1:6" ht="24">
+      <c r="A13" s="9" t="s">
+        <v>145</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>164</v>
-      </c>
-      <c r="D13" s="22" t="s">
-        <v>200</v>
-      </c>
-      <c r="E13" s="9"/>
+        <v>241</v>
+      </c>
+      <c r="D13" s="9"/>
+      <c r="E13" s="4"/>
       <c r="F13" s="4"/>
-      <c r="G13" s="4"/>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14" s="4"/>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="9"/>
       <c r="B14" s="4" t="s">
         <v>153</v>
       </c>
       <c r="C14" s="9"/>
-      <c r="D14" s="22"/>
-      <c r="E14" s="9"/>
+      <c r="D14" s="9"/>
+      <c r="E14" s="4"/>
       <c r="F14" s="4"/>
-      <c r="G14" s="4"/>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15" s="4" t="s">
-        <v>148</v>
+    </row>
+    <row r="15" spans="1:6" ht="36">
+      <c r="A15" s="9" t="s">
+        <v>146</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="C15" s="9" t="s">
         <v>163</v>
       </c>
-      <c r="D15" s="22" t="s">
-        <v>199</v>
-      </c>
-      <c r="E15" s="9"/>
+      <c r="D15" s="9"/>
+      <c r="E15" s="4"/>
       <c r="F15" s="4"/>
-      <c r="G15" s="4"/>
-    </row>
-    <row r="16" spans="1:7" ht="24">
-      <c r="A16" s="4" t="s">
-        <v>149</v>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="9" t="s">
+        <v>147</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>170</v>
-      </c>
-      <c r="D16" s="22" t="s">
-        <v>206</v>
-      </c>
-      <c r="E16" s="9"/>
+        <v>208</v>
+      </c>
+      <c r="D16" s="9"/>
+      <c r="E16" s="4"/>
       <c r="F16" s="4"/>
-      <c r="G16" s="4"/>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17" s="4"/>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" s="9"/>
       <c r="B17" s="4" t="s">
         <v>153</v>
       </c>
       <c r="C17" s="9"/>
-      <c r="D17" s="22"/>
-      <c r="E17" s="9"/>
+      <c r="D17" s="9"/>
+      <c r="E17" s="4"/>
       <c r="F17" s="4"/>
-      <c r="G17" s="4"/>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18" s="4" t="s">
-        <v>171</v>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" s="9" t="s">
+        <v>148</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>173</v>
-      </c>
-      <c r="C18" s="9"/>
-      <c r="D18" s="22" t="s">
-        <v>207</v>
-      </c>
-      <c r="E18" s="9"/>
+        <v>159</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="D18" s="9"/>
+      <c r="E18" s="4"/>
       <c r="F18" s="4"/>
-      <c r="G18" s="4"/>
-    </row>
-    <row r="19" spans="1:7" ht="24">
-      <c r="A19" s="4" t="s">
-        <v>172</v>
+    </row>
+    <row r="19" spans="1:6" ht="24">
+      <c r="A19" s="9" t="s">
+        <v>149</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>174</v>
+        <v>160</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>193</v>
-      </c>
-      <c r="D19" s="22" t="s">
-        <v>208</v>
-      </c>
-      <c r="E19" s="9" t="s">
-        <v>135</v>
-      </c>
+        <v>210</v>
+      </c>
+      <c r="D19" s="9"/>
+      <c r="E19" s="4"/>
       <c r="F19" s="4"/>
-      <c r="G19" s="4"/>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20" s="4"/>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20" s="9"/>
       <c r="B20" s="4" t="s">
         <v>153</v>
       </c>
       <c r="C20" s="9"/>
-      <c r="D20" s="22"/>
-      <c r="E20" s="9"/>
+      <c r="D20" s="9"/>
+      <c r="E20" s="4"/>
       <c r="F20" s="4"/>
-      <c r="G20" s="4"/>
-    </row>
-    <row r="21" spans="1:7" ht="24">
-      <c r="A21" s="4" t="s">
-        <v>175</v>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21" s="9" t="s">
+        <v>164</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>184</v>
-      </c>
-      <c r="C21" s="9" t="s">
-        <v>216</v>
-      </c>
-      <c r="D21" s="22" t="s">
-        <v>209</v>
-      </c>
-      <c r="E21" s="9"/>
+        <v>166</v>
+      </c>
+      <c r="C21" s="9"/>
+      <c r="D21" s="9"/>
+      <c r="E21" s="4"/>
       <c r="F21" s="4"/>
-      <c r="G21" s="4"/>
-    </row>
-    <row r="22" spans="1:7" ht="48">
-      <c r="A22" s="4" t="s">
-        <v>176</v>
+    </row>
+    <row r="22" spans="1:6">
+      <c r="A22" s="9" t="s">
+        <v>165</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>217</v>
-      </c>
-      <c r="D22" s="22" t="s">
-        <v>210</v>
-      </c>
-      <c r="E22" s="9" t="s">
-        <v>194</v>
-      </c>
+        <v>211</v>
+      </c>
+      <c r="D22" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="E22" s="4"/>
       <c r="F22" s="4"/>
-      <c r="G22" s="4"/>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23" s="4"/>
+    </row>
+    <row r="23" spans="1:6">
+      <c r="A23" s="9"/>
       <c r="B23" s="4" t="s">
         <v>153</v>
       </c>
       <c r="C23" s="9"/>
-      <c r="D23" s="22"/>
-      <c r="E23" s="9"/>
+      <c r="D23" s="9"/>
+      <c r="E23" s="4"/>
       <c r="F23" s="4"/>
-      <c r="G23" s="4"/>
-    </row>
-    <row r="24" spans="1:7" ht="60">
-      <c r="A24" s="4" t="s">
+    </row>
+    <row r="24" spans="1:6" ht="24">
+      <c r="A24" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="B24" s="4" t="s">
         <v>177</v>
       </c>
-      <c r="B24" s="4" t="s">
-        <v>183</v>
-      </c>
       <c r="C24" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="D24" s="22" t="s">
-        <v>218</v>
-      </c>
-      <c r="E24" s="9"/>
+        <v>192</v>
+      </c>
+      <c r="D24" s="9"/>
+      <c r="E24" s="4"/>
       <c r="F24" s="4"/>
-      <c r="G24" s="4"/>
-    </row>
-    <row r="25" spans="1:7" ht="72">
-      <c r="A25" s="4" t="s">
+    </row>
+    <row r="25" spans="1:6" ht="36">
+      <c r="A25" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="B25" s="4" t="s">
         <v>178</v>
       </c>
-      <c r="B25" s="4" t="s">
+      <c r="C25" s="9" t="s">
+        <v>212</v>
+      </c>
+      <c r="D25" s="9" t="s">
         <v>186</v>
       </c>
-      <c r="C25" s="9" t="s">
-        <v>220</v>
-      </c>
-      <c r="D25" s="22" t="s">
-        <v>211</v>
-      </c>
-      <c r="E25" s="9"/>
+      <c r="E25" s="4"/>
       <c r="F25" s="4"/>
-      <c r="G25" s="4"/>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26" s="4"/>
+    </row>
+    <row r="26" spans="1:6">
+      <c r="A26" s="9"/>
       <c r="B26" s="4" t="s">
         <v>153</v>
       </c>
       <c r="C26" s="9"/>
-      <c r="D26" s="22"/>
-      <c r="E26" s="9"/>
+      <c r="D26" s="9"/>
+      <c r="E26" s="4"/>
       <c r="F26" s="4"/>
-      <c r="G26" s="4"/>
-    </row>
-    <row r="27" spans="1:7" ht="60">
-      <c r="A27" s="4" t="s">
-        <v>136</v>
+    </row>
+    <row r="27" spans="1:6" ht="60">
+      <c r="A27" s="9" t="s">
+        <v>170</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>187</v>
+        <v>176</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>221</v>
-      </c>
-      <c r="D27" s="22" t="s">
-        <v>211</v>
-      </c>
-      <c r="E27" s="9"/>
+        <v>193</v>
+      </c>
+      <c r="D27" s="9"/>
+      <c r="E27" s="4"/>
       <c r="F27" s="4"/>
-      <c r="G27" s="4"/>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="A28" s="4" t="s">
-        <v>137</v>
+    </row>
+    <row r="28" spans="1:6" ht="60">
+      <c r="A28" s="9" t="s">
+        <v>171</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>188</v>
-      </c>
-      <c r="C28" s="11" t="s">
-        <v>195</v>
-      </c>
-      <c r="D28" s="22" t="s">
-        <v>212</v>
-      </c>
-      <c r="E28" s="9" t="s">
-        <v>138</v>
-      </c>
+        <v>179</v>
+      </c>
+      <c r="C28" s="9" t="s">
+        <v>189</v>
+      </c>
+      <c r="D28" s="9"/>
+      <c r="E28" s="4"/>
       <c r="F28" s="4"/>
-      <c r="G28" s="4"/>
-    </row>
-    <row r="29" spans="1:7">
-      <c r="A29" s="4"/>
+    </row>
+    <row r="29" spans="1:6">
+      <c r="A29" s="9"/>
       <c r="B29" s="4" t="s">
         <v>153</v>
       </c>
       <c r="C29" s="9"/>
-      <c r="D29" s="22"/>
-      <c r="E29" s="9"/>
+      <c r="D29" s="9"/>
+      <c r="E29" s="4"/>
       <c r="F29" s="4"/>
-      <c r="G29" s="4"/>
-    </row>
-    <row r="30" spans="1:7" ht="60">
-      <c r="A30" s="4" t="s">
-        <v>179</v>
+    </row>
+    <row r="30" spans="1:6" ht="60">
+      <c r="A30" s="9" t="s">
+        <v>136</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>221</v>
-      </c>
-      <c r="D30" s="22" t="s">
-        <v>211</v>
-      </c>
-      <c r="E30" s="9"/>
+        <v>194</v>
+      </c>
+      <c r="D30" s="9"/>
+      <c r="E30" s="4"/>
       <c r="F30" s="4"/>
-      <c r="G30" s="4"/>
-    </row>
-    <row r="31" spans="1:7">
-      <c r="A31" s="4" t="s">
-        <v>180</v>
+    </row>
+    <row r="31" spans="1:6">
+      <c r="A31" s="9" t="s">
+        <v>137</v>
       </c>
       <c r="B31" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="C31" s="11" t="s">
         <v>190</v>
       </c>
-      <c r="C31" s="9" t="s">
-        <v>195</v>
-      </c>
-      <c r="D31" s="22" t="s">
-        <v>213</v>
-      </c>
-      <c r="E31" s="9" t="s">
-        <v>139</v>
-      </c>
+      <c r="D31" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="E31" s="4"/>
       <c r="F31" s="4"/>
-      <c r="G31" s="4"/>
-    </row>
-    <row r="32" spans="1:7">
-      <c r="A32" s="4"/>
+    </row>
+    <row r="32" spans="1:6">
+      <c r="A32" s="9"/>
       <c r="B32" s="4" t="s">
         <v>153</v>
       </c>
       <c r="C32" s="9"/>
-      <c r="D32" s="22"/>
-      <c r="E32" s="9"/>
+      <c r="D32" s="9"/>
+      <c r="E32" s="4"/>
       <c r="F32" s="4"/>
-      <c r="G32" s="4"/>
-    </row>
-    <row r="33" spans="1:7">
-      <c r="A33" s="4" t="s">
-        <v>181</v>
+    </row>
+    <row r="33" spans="1:6" ht="60">
+      <c r="A33" s="9" t="s">
+        <v>172</v>
       </c>
       <c r="B33" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="C33" s="9" t="s">
+        <v>194</v>
+      </c>
+      <c r="D33" s="9"/>
+      <c r="E33" s="4"/>
+      <c r="F33" s="4"/>
+    </row>
+    <row r="34" spans="1:6">
+      <c r="A34" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="C34" s="9" t="s">
         <v>191</v>
       </c>
-      <c r="C33" s="9" t="s">
-        <v>196</v>
-      </c>
-      <c r="D33" s="22" t="s">
-        <v>214</v>
-      </c>
-      <c r="E33" s="9"/>
-      <c r="F33" s="4"/>
-      <c r="G33" s="4"/>
-    </row>
-    <row r="34" spans="1:7">
-      <c r="A34" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="B34" s="4" t="s">
-        <v>192</v>
-      </c>
-      <c r="C34" s="9" t="s">
-        <v>197</v>
-      </c>
-      <c r="D34" s="22" t="s">
-        <v>215</v>
-      </c>
-      <c r="E34" s="9"/>
+      <c r="D34" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="E34" s="4"/>
       <c r="F34" s="4"/>
-      <c r="G34" s="4"/>
-    </row>
-    <row r="35" spans="1:7">
-      <c r="A35" s="4"/>
-      <c r="B35" s="4"/>
+    </row>
+    <row r="35" spans="1:6">
+      <c r="A35" s="9"/>
+      <c r="B35" s="4" t="s">
+        <v>153</v>
+      </c>
       <c r="C35" s="9"/>
-      <c r="D35" s="22"/>
-      <c r="E35" s="9"/>
+      <c r="D35" s="9"/>
+      <c r="E35" s="4"/>
       <c r="F35" s="4"/>
-      <c r="G35" s="4"/>
-    </row>
-    <row r="36" spans="1:7">
-      <c r="A36" s="4" t="s">
-        <v>231</v>
-      </c>
-      <c r="B36" s="4"/>
-      <c r="C36" s="9"/>
-      <c r="D36" s="22" t="s">
-        <v>232</v>
-      </c>
-      <c r="E36" s="9"/>
+    </row>
+    <row r="36" spans="1:6">
+      <c r="A36" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="C36" s="9" t="s">
+        <v>187</v>
+      </c>
+      <c r="D36" s="9"/>
+      <c r="E36" s="4"/>
       <c r="F36" s="4"/>
-      <c r="G36" s="4"/>
-    </row>
-    <row r="37" spans="1:7">
-      <c r="A37" s="4" t="s">
-        <v>223</v>
-      </c>
-      <c r="B37" s="4"/>
-      <c r="C37" s="9"/>
-      <c r="D37" s="22" t="s">
-        <v>227</v>
-      </c>
-      <c r="E37" s="9" t="s">
-        <v>222</v>
-      </c>
+    </row>
+    <row r="37" spans="1:6">
+      <c r="A37" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="C37" s="9" t="s">
+        <v>213</v>
+      </c>
+      <c r="D37" s="9"/>
+      <c r="E37" s="4"/>
       <c r="F37" s="4"/>
-      <c r="G37" s="4"/>
-    </row>
-    <row r="38" spans="1:7" ht="24">
-      <c r="A38" s="4" t="s">
-        <v>233</v>
-      </c>
+    </row>
+    <row r="38" spans="1:6">
+      <c r="A38" s="9"/>
       <c r="B38" s="4"/>
       <c r="C38" s="9"/>
-      <c r="D38" s="22" t="s">
+      <c r="D38" s="9"/>
+      <c r="E38" s="4"/>
+      <c r="F38" s="4"/>
+    </row>
+    <row r="39" spans="1:6">
+      <c r="A39" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="B39" s="4"/>
+      <c r="C39" s="9" t="s">
+        <v>214</v>
+      </c>
+      <c r="D39" s="9"/>
+      <c r="E39" s="4"/>
+      <c r="F39" s="4"/>
+    </row>
+    <row r="40" spans="1:6" ht="24">
+      <c r="A40" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="B40" s="4"/>
+      <c r="C40" s="9" t="s">
+        <v>215</v>
+      </c>
+      <c r="D40" s="9" t="s">
+        <v>195</v>
+      </c>
+      <c r="E40" s="4"/>
+      <c r="F40" s="4"/>
+    </row>
+    <row r="41" spans="1:6" ht="24">
+      <c r="A41" s="9" t="s">
+        <v>206</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="C41" s="9" t="s">
+        <v>207</v>
+      </c>
+      <c r="D41" s="9"/>
+      <c r="E41" s="4"/>
+      <c r="F41" s="4"/>
+    </row>
+    <row r="42" spans="1:6" ht="60">
+      <c r="A42" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="C42" s="9" t="s">
+        <v>222</v>
+      </c>
+      <c r="D42" s="9" t="s">
+        <v>223</v>
+      </c>
+      <c r="E42" s="4"/>
+      <c r="F42" s="4"/>
+    </row>
+    <row r="43" spans="1:6" ht="48">
+      <c r="A43" s="9" t="s">
+        <v>220</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="C43" s="9" t="s">
+        <v>221</v>
+      </c>
+      <c r="D43" s="9"/>
+      <c r="E43" s="4"/>
+      <c r="F43" s="4"/>
+    </row>
+    <row r="44" spans="1:6" s="23" customFormat="1">
+      <c r="A44" s="22" t="s">
+        <v>200</v>
+      </c>
+      <c r="B44" s="21"/>
+      <c r="C44" s="22"/>
+      <c r="D44" s="22" t="s">
+        <v>196</v>
+      </c>
+      <c r="E44" s="21"/>
+      <c r="F44" s="21"/>
+    </row>
+    <row r="45" spans="1:6">
+      <c r="A45" s="9" t="s">
+        <v>201</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="C45" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="D45" s="9"/>
+      <c r="E45" s="4"/>
+      <c r="F45" s="4"/>
+    </row>
+    <row r="46" spans="1:6" ht="24">
+      <c r="A46" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="C46" s="9" t="s">
+        <v>230</v>
+      </c>
+      <c r="D46" s="9" t="s">
+        <v>204</v>
+      </c>
+      <c r="E46" s="4"/>
+      <c r="F46" s="4"/>
+    </row>
+    <row r="47" spans="1:6">
+      <c r="A47" s="9"/>
+      <c r="B47" s="4"/>
+      <c r="C47" s="9"/>
+      <c r="D47" s="9"/>
+      <c r="E47" s="4"/>
+      <c r="F47" s="4"/>
+    </row>
+    <row r="48" spans="1:6">
+      <c r="A48" s="9" t="s">
+        <v>224</v>
+      </c>
+      <c r="B48" s="4" t="s">
         <v>225</v>
       </c>
-      <c r="E38" s="9" t="s">
-        <v>224</v>
-      </c>
-      <c r="F38" s="4"/>
-      <c r="G38" s="4"/>
-    </row>
-    <row r="39" spans="1:7">
-      <c r="A39" s="3" t="s">
-        <v>234</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>235</v>
-      </c>
-      <c r="C39" s="10" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7">
-      <c r="A40" s="3" t="s">
-        <v>236</v>
-      </c>
-      <c r="D40" s="24" t="s">
-        <v>238</v>
-      </c>
-      <c r="E40" s="10" t="s">
-        <v>239</v>
-      </c>
+      <c r="C48" s="9" t="s">
+        <v>227</v>
+      </c>
+      <c r="D48" s="9"/>
+      <c r="E48" s="4"/>
+      <c r="F48" s="4"/>
+    </row>
+    <row r="49" spans="1:6">
+      <c r="A49" s="9" t="s">
+        <v>228</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="C49" s="9" t="s">
+        <v>215</v>
+      </c>
+      <c r="D49" s="9"/>
+      <c r="E49" s="4"/>
+      <c r="F49" s="4"/>
+    </row>
+    <row r="50" spans="1:6">
+      <c r="A50" s="9"/>
+      <c r="B50" s="4"/>
+      <c r="C50" s="9"/>
+      <c r="D50" s="9"/>
+      <c r="E50" s="4"/>
+      <c r="F50" s="4"/>
+    </row>
+    <row r="51" spans="1:6">
+      <c r="A51" s="9"/>
+      <c r="B51" s="4"/>
+      <c r="C51" s="9"/>
+      <c r="D51" s="9"/>
+      <c r="E51" s="4"/>
+      <c r="F51" s="4"/>
+    </row>
+    <row r="52" spans="1:6">
+      <c r="A52" s="9"/>
+      <c r="B52" s="4"/>
+      <c r="C52" s="9"/>
+      <c r="D52" s="9"/>
+      <c r="E52" s="4"/>
+      <c r="F52" s="4"/>
+    </row>
+    <row r="53" spans="1:6">
+      <c r="A53" s="9"/>
+      <c r="B53" s="4"/>
+      <c r="C53" s="9"/>
+      <c r="D53" s="9"/>
+      <c r="E53" s="4"/>
+      <c r="F53" s="4"/>
+    </row>
+    <row r="54" spans="1:6">
+      <c r="A54" s="9"/>
+      <c r="B54" s="4"/>
+      <c r="C54" s="9"/>
+      <c r="D54" s="9"/>
+      <c r="E54" s="4"/>
+      <c r="F54" s="4"/>
+    </row>
+    <row r="55" spans="1:6">
+      <c r="A55" s="9"/>
+      <c r="B55" s="4"/>
+      <c r="C55" s="9"/>
+      <c r="D55" s="9"/>
+      <c r="E55" s="4"/>
+      <c r="F55" s="4"/>
+    </row>
+    <row r="56" spans="1:6">
+      <c r="A56" s="9"/>
+      <c r="B56" s="4"/>
+      <c r="C56" s="9"/>
+      <c r="D56" s="9"/>
+      <c r="E56" s="4"/>
+      <c r="F56" s="4"/>
+    </row>
+    <row r="57" spans="1:6">
+      <c r="A57" s="9"/>
+      <c r="B57" s="4"/>
+      <c r="C57" s="9"/>
+      <c r="D57" s="9"/>
+      <c r="E57" s="4"/>
+      <c r="F57" s="4"/>
+    </row>
+    <row r="58" spans="1:6">
+      <c r="A58" s="9"/>
+      <c r="B58" s="4"/>
+      <c r="C58" s="9"/>
+      <c r="D58" s="9"/>
+      <c r="E58" s="4"/>
+      <c r="F58" s="4"/>
+    </row>
+    <row r="59" spans="1:6">
+      <c r="A59" s="9"/>
+      <c r="B59" s="4"/>
+      <c r="C59" s="9"/>
+      <c r="D59" s="9"/>
+      <c r="E59" s="4"/>
+      <c r="F59" s="4"/>
+    </row>
+    <row r="60" spans="1:6">
+      <c r="A60" s="9"/>
+      <c r="B60" s="4"/>
+      <c r="C60" s="9"/>
+      <c r="D60" s="9"/>
+      <c r="E60" s="4"/>
+      <c r="F60" s="4"/>
+    </row>
+    <row r="61" spans="1:6">
+      <c r="A61" s="9"/>
+      <c r="B61" s="4"/>
+      <c r="C61" s="9"/>
+      <c r="D61" s="9"/>
+      <c r="E61" s="4"/>
+      <c r="F61" s="4"/>
+    </row>
+    <row r="62" spans="1:6">
+      <c r="A62" s="9"/>
+      <c r="B62" s="4"/>
+      <c r="C62" s="9"/>
+      <c r="D62" s="9"/>
+      <c r="E62" s="4"/>
+      <c r="F62" s="4"/>
+    </row>
+    <row r="63" spans="1:6">
+      <c r="A63" s="9"/>
+      <c r="B63" s="4"/>
+      <c r="C63" s="9"/>
+      <c r="D63" s="9"/>
+      <c r="E63" s="4"/>
+      <c r="F63" s="4"/>
+    </row>
+    <row r="64" spans="1:6">
+      <c r="A64" s="9"/>
+      <c r="B64" s="4"/>
+      <c r="C64" s="9"/>
+      <c r="D64" s="9"/>
+      <c r="E64" s="4"/>
+      <c r="F64" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/internal_doc/03.开发设计/OM_web接口.xlsx
+++ b/internal_doc/03.开发设计/OM_web接口.xlsx
@@ -332,7 +332,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="242">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="244">
   <si>
     <t>需求</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -955,12 +955,6 @@
     <t>check_host_res</t>
   </si>
   <si>
-    <t>config_host_req</t>
-  </si>
-  <si>
-    <t>config_host_res</t>
-  </si>
-  <si>
     <t>get_host_req</t>
   </si>
   <si>
@@ -975,10 +969,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>cluster_name=cls1&amp;host_info={[host_ip, host_name, username, passwd, firework, [disk],[cpu]...]}&amp;username=usr1&amp;passwd=passwd1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>获取business列表</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1156,10 +1146,6 @@
   </si>
   <si>
     <t>{cluster_name, rc}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{[host_ip, host_name, rc]}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1282,15 +1268,39 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>host_info={cluster_name:cls1, host_info:[{host_ip, host_name, username, passwd},...], username:usr1, passwd:passwd1}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>host_info={cluster_name:cls1, host_info:[{host_ip, host_name, username, passwd, firework, [disk],[cpu]…}, ...], username:xxx, passwd:xxx}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{host_ip, host_name, rc}, ...]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>msgBuildQueryMsg( &amp;pContent, &amp;contentSize, OM_BASIC_CHECK_REQ, 0, 0, 0, -1, &amp;bsonRequest, NULL, NULL, NULL )</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pContent在什么情况下可以释放</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{[{host_ip, host_name, rc, firework, [disk],[cpu]…}, ...]}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>host_info={[host_ip/host_name:xxx, username:xxx, passwd:xxx],username:usr1,passwd:passwd1}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>host_info={cluster_name:cls1, host_info:[{host_ip, host_name, username, passwd},...], username:usr1, passwd:passwd1}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{cluster_name, [{host_ip, host_name, rc, firework, [disk],[cpu]…}, ...]}</t>
+    <t>add_host_req</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>add_host_res</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1298,7 +1308,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="13">
+  <fonts count="14">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1397,6 +1407,14 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -1473,10 +1491,13 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1550,9 +1571,14 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Warning Text" xfId="1" builtinId="11"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -3351,10 +3377,10 @@
         <v>134</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="D2" s="5" t="s">
         <v>1</v>
@@ -3364,13 +3390,13 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="9" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="D3" s="9"/>
       <c r="E3" s="4"/>
@@ -3381,10 +3407,10 @@
         <v>140</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="D4" s="9" t="s">
         <v>150</v>
@@ -3402,13 +3428,13 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="9" t="s">
+        <v>227</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="C6" s="9" t="s">
         <v>231</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>232</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>235</v>
       </c>
       <c r="D6" s="9"/>
       <c r="E6" s="4"/>
@@ -3416,13 +3442,13 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="9" t="s">
+        <v>229</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="C7" s="9" t="s">
         <v>233</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>234</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>237</v>
       </c>
       <c r="D7" s="9"/>
       <c r="E7" s="4"/>
@@ -3441,10 +3467,10 @@
         <v>141</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="D9" s="9"/>
       <c r="E9" s="4"/>
@@ -3458,7 +3484,7 @@
         <v>154</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>209</v>
+        <v>237</v>
       </c>
       <c r="D10" s="9" t="s">
         <v>143</v>
@@ -3484,7 +3510,7 @@
         <v>155</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="D12" s="9"/>
       <c r="E12" s="4"/>
@@ -3498,7 +3524,7 @@
         <v>156</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D13" s="9"/>
       <c r="E13" s="4"/>
@@ -3519,10 +3545,10 @@
         <v>146</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>157</v>
+        <v>242</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>163</v>
+        <v>236</v>
       </c>
       <c r="D15" s="9"/>
       <c r="E15" s="4"/>
@@ -3533,10 +3559,10 @@
         <v>147</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>158</v>
+        <v>243</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="D16" s="9"/>
       <c r="E16" s="4"/>
@@ -3557,10 +3583,10 @@
         <v>148</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D18" s="9"/>
       <c r="E18" s="4"/>
@@ -3571,10 +3597,10 @@
         <v>149</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="D19" s="9"/>
       <c r="E19" s="4"/>
@@ -3592,10 +3618,10 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="9" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="C21" s="9"/>
       <c r="D21" s="9"/>
@@ -3604,13 +3630,13 @@
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="9" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="D22" s="9" t="s">
         <v>135</v>
@@ -3630,13 +3656,13 @@
     </row>
     <row r="24" spans="1:6" ht="24">
       <c r="A24" s="9" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="D24" s="9"/>
       <c r="E24" s="4"/>
@@ -3644,16 +3670,16 @@
     </row>
     <row r="25" spans="1:6" ht="36">
       <c r="A25" s="9" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="E25" s="4"/>
       <c r="F25" s="4"/>
@@ -3670,13 +3696,13 @@
     </row>
     <row r="27" spans="1:6" ht="60">
       <c r="A27" s="9" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="D27" s="9"/>
       <c r="E27" s="4"/>
@@ -3684,13 +3710,13 @@
     </row>
     <row r="28" spans="1:6" ht="60">
       <c r="A28" s="9" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="D28" s="9"/>
       <c r="E28" s="4"/>
@@ -3711,10 +3737,10 @@
         <v>136</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="D30" s="9"/>
       <c r="E30" s="4"/>
@@ -3725,10 +3751,10 @@
         <v>137</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="D31" s="9" t="s">
         <v>138</v>
@@ -3748,13 +3774,13 @@
     </row>
     <row r="33" spans="1:6" ht="60">
       <c r="A33" s="9" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="D33" s="9"/>
       <c r="E33" s="4"/>
@@ -3762,13 +3788,13 @@
     </row>
     <row r="34" spans="1:6">
       <c r="A34" s="9" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="D34" s="9" t="s">
         <v>139</v>
@@ -3788,13 +3814,13 @@
     </row>
     <row r="36" spans="1:6">
       <c r="A36" s="9" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="B36" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="C36" s="9" t="s">
         <v>184</v>
-      </c>
-      <c r="C36" s="9" t="s">
-        <v>187</v>
       </c>
       <c r="D36" s="9"/>
       <c r="E36" s="4"/>
@@ -3802,13 +3828,13 @@
     </row>
     <row r="37" spans="1:6">
       <c r="A37" s="9" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="D37" s="9"/>
       <c r="E37" s="4"/>
@@ -3824,11 +3850,11 @@
     </row>
     <row r="39" spans="1:6">
       <c r="A39" s="9" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="B39" s="4"/>
       <c r="C39" s="9" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="D39" s="9"/>
       <c r="E39" s="4"/>
@@ -3836,27 +3862,27 @@
     </row>
     <row r="40" spans="1:6" ht="24">
       <c r="A40" s="9" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="B40" s="4"/>
       <c r="C40" s="9" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="D40" s="9" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="E40" s="4"/>
       <c r="F40" s="4"/>
     </row>
     <row r="41" spans="1:6" ht="24">
       <c r="A41" s="9" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="C41" s="9" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="D41" s="9"/>
       <c r="E41" s="4"/>
@@ -3864,29 +3890,29 @@
     </row>
     <row r="42" spans="1:6" ht="60">
       <c r="A42" s="9" t="s">
+        <v>214</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="C42" s="9" t="s">
         <v>218</v>
       </c>
-      <c r="B42" s="4" t="s">
+      <c r="D42" s="9" t="s">
         <v>219</v>
-      </c>
-      <c r="C42" s="9" t="s">
-        <v>222</v>
-      </c>
-      <c r="D42" s="9" t="s">
-        <v>223</v>
       </c>
       <c r="E42" s="4"/>
       <c r="F42" s="4"/>
     </row>
     <row r="43" spans="1:6" ht="48">
       <c r="A43" s="9" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="C43" s="9" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="D43" s="9"/>
       <c r="E43" s="4"/>
@@ -3894,25 +3920,25 @@
     </row>
     <row r="44" spans="1:6" s="23" customFormat="1">
       <c r="A44" s="22" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="B44" s="21"/>
       <c r="C44" s="22"/>
       <c r="D44" s="22" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="E44" s="21"/>
       <c r="F44" s="21"/>
     </row>
     <row r="45" spans="1:6">
       <c r="A45" s="9" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="C45" s="9" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="D45" s="9"/>
       <c r="E45" s="4"/>
@@ -3920,16 +3946,16 @@
     </row>
     <row r="46" spans="1:6" ht="24">
       <c r="A46" s="9" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="B46" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="C46" s="9" t="s">
         <v>226</v>
       </c>
-      <c r="C46" s="9" t="s">
-        <v>230</v>
-      </c>
       <c r="D46" s="9" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="E46" s="4"/>
       <c r="F46" s="4"/>
@@ -3944,13 +3970,13 @@
     </row>
     <row r="48" spans="1:6">
       <c r="A48" s="9" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="C48" s="9" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="D48" s="9"/>
       <c r="E48" s="4"/>
@@ -3958,13 +3984,13 @@
     </row>
     <row r="49" spans="1:6">
       <c r="A49" s="9" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="C49" s="9" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="D49" s="9"/>
       <c r="E49" s="4"/>
@@ -4099,19 +4125,28 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="11.375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="47.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="30.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:3">
       <c r="A1" t="s">
         <v>152</v>
       </c>
       <c r="B1" t="s">
         <v>151</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="40.5">
+      <c r="B8" s="31" t="s">
+        <v>238</v>
+      </c>
+      <c r="C8" s="32" t="s">
+        <v>239</v>
       </c>
     </row>
   </sheetData>

--- a/internal_doc/03.开发设计/OM_web接口.xlsx
+++ b/internal_doc/03.开发设计/OM_web接口.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="6510" activeTab="3"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="6510" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="需求" sheetId="1" r:id="rId1"/>
@@ -68,60 +68,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B26" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Author:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-catalog</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="宋体"/>
-            <family val="3"/>
-            <charset val="134"/>
-          </rPr>
-          <t>和</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>data</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="宋体"/>
-            <family val="3"/>
-            <charset val="134"/>
-          </rPr>
-          <t>需要</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="C36" authorId="0">
+    <comment ref="C35" authorId="0">
       <text>
         <r>
           <rPr>
@@ -332,7 +279,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="244">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="233">
   <si>
     <t>需求</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -762,21 +709,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>replname</t>
-  </si>
-  <si>
-    <t>shardname</t>
-  </si>
-  <si>
-    <t>catalogname</t>
-  </si>
-  <si>
-    <t>httpname</t>
-  </si>
-  <si>
-    <t>diaglevel</t>
-  </si>
-  <si>
     <t>单选</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -789,38 +721,14 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>role</t>
-  </si>
-  <si>
     <t>字符串</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>standalone</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>logfilesz</t>
-  </si>
-  <si>
-    <t>[64,2048]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>logfilenum</t>
-  </si>
-  <si>
-    <t>transactionon</t>
-  </si>
-  <si>
     <t>false</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>[1,11800]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>[true, false]</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -829,12 +737,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>numpagecleaners</t>
-  </si>
-  <si>
-    <t>pagecleaninterval</t>
-  </si>
-  <si>
     <t>A</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -855,10 +757,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>catalogaddr</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>[host_name, [coord, disk_name, [dbpath,svcname...]]]</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -871,10 +769,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>cluster_type:cluster/standalone</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>校验配置</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -946,29 +840,10 @@
     <t/>
   </si>
   <si>
-    <t>scan_host_res</t>
-  </si>
-  <si>
-    <t>check_host_req</t>
-  </si>
-  <si>
-    <t>check_host_res</t>
-  </si>
-  <si>
-    <t>get_host_req</t>
-  </si>
-  <si>
-    <t>get_host_res</t>
-  </si>
-  <si>
     <t>命令字(cmd=??)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>cluster_name=cls1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>获取business列表</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -977,14 +852,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>get_business_list_req</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>get_business_list_res</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>获取business模板配置</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1017,22 +884,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>config_business_req</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>get_business_config_template_req</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>get_business_config_template_res</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>config_business_res</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>check_business_config_req</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1057,22 +908,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>business_user_group, business_user_passwd(sdbadmin:sdbadmin)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>business_name=xxx&amp;cluster_name=xxx</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>NA</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>{business_type, business_name, cluster_type, cluster_name, [host_name, disk_name, dbpath, svcname…], [host_name, disk_name, dbpath, svcname…], [group_name, [host_name, disk_name, dbpath, svcname…]]}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>{rc, [???]}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1081,18 +920,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>business_type=xxx&amp;business_name=xxx&amp;cluster_type=xxx</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>business_type=xxx&amp;business_name=xxx&amp;cluster_type=xxx&amp;cluster_name=xxx&amp;rep_num=xxx&amp;rep_group_num=xxx&amp;catalog_num=xxx&amp;coord_num=xxx&amp;business_user_group=xxx&amp;business_user_passwd=xxx&amp;host_info={[host_name, disk_name]}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>business_type=sequoiadb&amp;business_name=db1&amp;cluster_type=cluster&amp;cluster_name=cls1&amp;coord={[host_name, dbpath, svcname…]}&amp;catalog={[host_name, dbpath, svcname…]}&amp;data_group={[group_name, [host_name, dbpath, svcname…]]}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>返回跳转页面命令</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1105,14 +932,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>create_cluster_req</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>create_cluster_res</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>网页跳转响应(GETFILE)(废除)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1121,10 +940,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>check_session_req</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>网页session校验响应</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1142,26 +957,6 @@
   </si>
   <si>
     <t>通过接口获取（pAdptor-&gt;recvRequestBody( this, httpCommon, &amp;pFilePath, bodySize )）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{cluster_name, rc}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{cluster_name, rc, [host_ip, host_name, firework, [disk],[cpu]...]}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{[business_type, business_desc, [cluster_type]]}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{business_type, business_name, cluster_type, rep_num, rep_group_num, catalog_num, coord_num, business_user_group, business_user_passwd}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{business_name, cluster_name, rc}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1211,15 +1006,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>login_req</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>check_session_res</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>user=xx&amp;passwd=xx&amp;timestamp=xx</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1240,46 +1027,14 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>query_cluster_req</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>获取cluster信息响应</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>query_cluster_res</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>cmd=xxx</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>scan_host_req</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{cluster_name:xxx, desc:xxx}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>cluster_info={cluster_name=cls1, desc=xxx}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>host_info={cluster_name:cls1, host_info:[{host_ip, host_name, username, passwd},...], username:usr1, passwd:passwd1}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>host_info={cluster_name:cls1, host_info:[{host_ip, host_name, username, passwd, firework, [disk],[cpu]…}, ...], username:xxx, passwd:xxx}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[{host_ip, host_name, rc}, ...]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>msgBuildQueryMsg( &amp;pContent, &amp;contentSize, OM_BASIC_CHECK_REQ, 0, 0, 0, -1, &amp;bsonRequest, NULL, NULL, NULL )</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1288,19 +1043,236 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>{[{host_ip, host_name, rc, firework, [disk],[cpu]…}, ...]}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>host_info={[host_ip/host_name:xxx, username:xxx, passwd:xxx],username:usr1,passwd:passwd1}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>add_host_req</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>add_host_res</t>
+    <t>[64-2048]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[1-11800]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CreateClusterReq</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ClusterInfo={ClusterName=cls1, Desc=xxx}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{ClusterName, rc}</t>
+  </si>
+  <si>
+    <t>{ClusterName, rc}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>QueryClusterReq</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LoginReq</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>User=xx&amp;Passwd=xx&amp;Timestamp=xx</t>
+  </si>
+  <si>
+    <t>CheckSessionReq</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ScanHostReq</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{IP, HostName, rc}, ...]</t>
+  </si>
+  <si>
+    <t>HostInfo={ClusterName:cls1,HostInfo:[{IP/HostName:xxx, User:xxx, Passwd:xxx, SshPort:xxx, AgentPort:xxx}, ...],User:usr1,Passwd:Passwd1, SshPort:xxx, AgentPort:xxx}</t>
+  </si>
+  <si>
+    <t>CheckHostReq</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{[{IP, HostName, rc, Firework, [Disk],[CPU]…}, ...]}</t>
+  </si>
+  <si>
+    <t>AddHostReq</t>
+  </si>
+  <si>
+    <t>{ClusterName:xxx, desc:xxx}</t>
+  </si>
+  <si>
+    <t>host_info={ClusterName:cls1, host_info:[{IP, HostName, User, Passwd, SshPort:xxx, AgentPort:xxx},...], User:usr1, Passwd:Passwd1, SshPort:xxx, AgentPort:xxx}</t>
+  </si>
+  <si>
+    <t>host_info={ClusterName:cls1, host_info:[{IP, HostName, User, Passwd, SshPort:xxx, AgentPort:xxx, InstallPath:xxx, Firework, [Disk],[CPU]…}, ...], User:xxx, Passwd:xxx, SshPort:xxx, AgentPort:xxx, InstallPath:xxx}</t>
+  </si>
+  <si>
+    <t>ClusterName=cls1</t>
+  </si>
+  <si>
+    <t>{ClusterName, rc, [IP, HostName, Firework, [Disk],[CPU]...]}</t>
+  </si>
+  <si>
+    <t>business_name=xxx&amp;ClusterName=xxx</t>
+  </si>
+  <si>
+    <t>{business_name, ClusterName, rc}</t>
+  </si>
+  <si>
+    <t>QueryHostReq</t>
+  </si>
+  <si>
+    <t>QueryBusinessListReq</t>
+  </si>
+  <si>
+    <t>{BusinessType, business_name, cluster_type, ClusterName, [HostName, Disk_name, dbpath, svcname…], [HostName, Disk_name, dbpath, svcname…], [group_name, [HostName, Disk_name, dbpath, svcname…]]}</t>
+  </si>
+  <si>
+    <t>BusinessType=sequoiadb&amp;business_name=db1&amp;cluster_type=cluster&amp;ClusterName=cls1&amp;coord={[HostName, dbpath, svcname…]}&amp;catalog={[HostName, dbpath, svcname…]}&amp;data_group={[group_name, [HostName, dbpath, svcname…]]}</t>
+  </si>
+  <si>
+    <t>{BusinessList:[{BusinessType, BusinessDesc},...]}</t>
+  </si>
+  <si>
+    <t>QueryBusinessTemplateReq</t>
+  </si>
+  <si>
+    <t>BusinessType=xxx</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"BusinessType":"sequoiadb", "ClusterType": "standalone", "Property": [ { "Name": "replica_num", "Type": "int", "Default": "1", "Valid": "1", "Display": "edit box", "Edit": "false" }, ...] }  
+{"ClusterType": "cluster", "Property":[...]}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ConfigBusinessReq</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ClusterType:cluster/standalone
+下拉列表，选中则切换配置</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>{"BusinessType":"sequoiadb", "ClusterType": "standalone", "Property": [ { "Name": "replica_num", "Type": "int", "Default": "1", "Valid": "1", "Display": "edit box", "Edit": "false",</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="3"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>"Value":""</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">}, ...], </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>"HostInfo":[{"IP":"192.168.1.1", "HostName":"host1", Disk["Name":"", "Mount":"", "Size":""]}, ...]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>}</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>replname</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>shardname</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>catalogname</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>httpname</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>diaglevel</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>role</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>logfilesz</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>logfilenum</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>transactionon</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>numpagecleaners</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pagecleaninterval</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1308,7 +1280,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="14">
+  <fonts count="17">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1412,6 +1384,31 @@
       <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF00B0F0"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF00B0F0"/>
+      <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -2519,7 +2516,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L53"/>
+  <dimension ref="A1:L52"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="15.125" style="13" bestFit="1" customWidth="1"/>
@@ -2703,7 +2700,7 @@
     </row>
     <row r="11" spans="1:12" ht="36">
       <c r="A11" s="20" t="s">
-        <v>130</v>
+        <v>116</v>
       </c>
       <c r="B11" s="14" t="s">
         <v>61</v>
@@ -2737,7 +2734,7 @@
         <v>99</v>
       </c>
       <c r="C12" s="16" t="s">
-        <v>129</v>
+        <v>115</v>
       </c>
       <c r="D12" s="14"/>
       <c r="E12" s="14" t="s">
@@ -2778,7 +2775,7 @@
     <row r="14" spans="1:12">
       <c r="A14" s="14"/>
       <c r="B14" s="14" t="s">
-        <v>105</v>
+        <v>222</v>
       </c>
       <c r="C14" s="14">
         <v>11811</v>
@@ -2800,7 +2797,7 @@
     <row r="15" spans="1:12">
       <c r="A15" s="14"/>
       <c r="B15" s="14" t="s">
-        <v>106</v>
+        <v>223</v>
       </c>
       <c r="C15" s="14">
         <v>11812</v>
@@ -2822,7 +2819,7 @@
     <row r="16" spans="1:12">
       <c r="A16" s="14"/>
       <c r="B16" s="14" t="s">
-        <v>107</v>
+        <v>224</v>
       </c>
       <c r="C16" s="14">
         <v>11813</v>
@@ -2844,7 +2841,7 @@
     <row r="17" spans="1:12">
       <c r="A17" s="14"/>
       <c r="B17" s="14" t="s">
-        <v>108</v>
+        <v>225</v>
       </c>
       <c r="C17" s="14">
         <v>11814</v>
@@ -2866,7 +2863,7 @@
     <row r="18" spans="1:12">
       <c r="A18" s="14"/>
       <c r="B18" s="14" t="s">
-        <v>109</v>
+        <v>226</v>
       </c>
       <c r="C18" s="14">
         <v>3</v>
@@ -2876,10 +2873,10 @@
         <v>104</v>
       </c>
       <c r="F18" s="14" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="G18" s="14" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="H18" s="14"/>
       <c r="I18" s="14"/>
@@ -2890,20 +2887,20 @@
     <row r="19" spans="1:12">
       <c r="A19" s="14"/>
       <c r="B19" s="14" t="s">
-        <v>113</v>
+        <v>227</v>
       </c>
       <c r="C19" s="14" t="s">
         <v>95</v>
       </c>
       <c r="D19" s="14"/>
       <c r="E19" s="14" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="F19" s="14" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="G19" s="14" t="s">
-        <v>115</v>
+        <v>95</v>
       </c>
       <c r="H19" s="14"/>
       <c r="I19" s="14"/>
@@ -2914,7 +2911,7 @@
     <row r="20" spans="1:12">
       <c r="A20" s="14"/>
       <c r="B20" s="14" t="s">
-        <v>116</v>
+        <v>228</v>
       </c>
       <c r="C20" s="14">
         <v>64</v>
@@ -2927,7 +2924,7 @@
         <v>102</v>
       </c>
       <c r="G20" s="14" t="s">
-        <v>117</v>
+        <v>188</v>
       </c>
       <c r="H20" s="14"/>
       <c r="I20" s="14"/>
@@ -2938,7 +2935,7 @@
     <row r="21" spans="1:12">
       <c r="A21" s="14"/>
       <c r="B21" s="14" t="s">
-        <v>118</v>
+        <v>229</v>
       </c>
       <c r="C21" s="14">
         <v>20</v>
@@ -2951,7 +2948,7 @@
         <v>102</v>
       </c>
       <c r="G21" s="14" t="s">
-        <v>121</v>
+        <v>189</v>
       </c>
       <c r="H21" s="14"/>
       <c r="I21" s="14"/>
@@ -2962,20 +2959,20 @@
     <row r="22" spans="1:12">
       <c r="A22" s="14"/>
       <c r="B22" s="14" t="s">
-        <v>119</v>
+        <v>230</v>
       </c>
       <c r="C22" s="17" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="D22" s="14"/>
       <c r="E22" s="14" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="F22" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="G22" s="14" t="s">
         <v>110</v>
-      </c>
-      <c r="G22" s="14" t="s">
-        <v>122</v>
       </c>
       <c r="H22" s="14"/>
       <c r="I22" s="14"/>
@@ -2986,20 +2983,20 @@
     <row r="23" spans="1:12">
       <c r="A23" s="14"/>
       <c r="B23" s="14" t="s">
-        <v>123</v>
+        <v>111</v>
       </c>
       <c r="C23" s="14" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="D23" s="14"/>
       <c r="E23" s="14" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="F23" s="14" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="G23" s="14" t="s">
-        <v>127</v>
+        <v>113</v>
       </c>
       <c r="H23" s="14"/>
       <c r="I23" s="14"/>
@@ -3010,7 +3007,7 @@
     <row r="24" spans="1:12">
       <c r="A24" s="14"/>
       <c r="B24" s="16" t="s">
-        <v>124</v>
+        <v>231</v>
       </c>
       <c r="C24" s="11">
         <v>1</v>
@@ -3032,7 +3029,7 @@
     <row r="25" spans="1:12" s="19" customFormat="1">
       <c r="A25" s="16"/>
       <c r="B25" s="16" t="s">
-        <v>125</v>
+        <v>232</v>
       </c>
       <c r="C25" s="11">
         <v>10000</v>
@@ -3045,7 +3042,7 @@
         <v>102</v>
       </c>
       <c r="G25" s="11" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="H25" s="11"/>
       <c r="I25" s="11"/>
@@ -3055,9 +3052,7 @@
     </row>
     <row r="26" spans="1:12">
       <c r="A26" s="14"/>
-      <c r="B26" s="14" t="s">
-        <v>131</v>
-      </c>
+      <c r="B26" s="14"/>
       <c r="C26" s="14"/>
       <c r="D26" s="14"/>
       <c r="E26" s="14"/>
@@ -3081,10 +3076,12 @@
       <c r="I27" s="14"/>
       <c r="J27" s="14"/>
       <c r="K27" s="14"/>
-      <c r="L27" s="4"/>
+      <c r="L27" s="14"/>
     </row>
     <row r="28" spans="1:12">
-      <c r="A28" s="14"/>
+      <c r="A28" s="15" t="s">
+        <v>67</v>
+      </c>
       <c r="B28" s="14"/>
       <c r="C28" s="14"/>
       <c r="D28" s="14"/>
@@ -3098,10 +3095,12 @@
       <c r="L28" s="14"/>
     </row>
     <row r="29" spans="1:12">
-      <c r="A29" s="15" t="s">
-        <v>67</v>
-      </c>
-      <c r="B29" s="14"/>
+      <c r="A29" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="B29" s="14" t="s">
+        <v>66</v>
+      </c>
       <c r="C29" s="14"/>
       <c r="D29" s="14"/>
       <c r="E29" s="14"/>
@@ -3114,12 +3113,8 @@
       <c r="L29" s="14"/>
     </row>
     <row r="30" spans="1:12">
-      <c r="A30" s="14" t="s">
-        <v>65</v>
-      </c>
-      <c r="B30" s="14" t="s">
-        <v>66</v>
-      </c>
+      <c r="A30" s="14"/>
+      <c r="B30" s="14"/>
       <c r="C30" s="14"/>
       <c r="D30" s="14"/>
       <c r="E30" s="14"/>
@@ -3174,7 +3169,9 @@
       <c r="L33" s="14"/>
     </row>
     <row r="34" spans="1:12">
-      <c r="A34" s="14"/>
+      <c r="A34" s="15" t="s">
+        <v>78</v>
+      </c>
       <c r="B34" s="14"/>
       <c r="C34" s="14"/>
       <c r="D34" s="14"/>
@@ -3187,12 +3184,16 @@
       <c r="K34" s="14"/>
       <c r="L34" s="14"/>
     </row>
-    <row r="35" spans="1:12">
-      <c r="A35" s="15" t="s">
-        <v>78</v>
-      </c>
-      <c r="B35" s="14"/>
-      <c r="C35" s="14"/>
+    <row r="35" spans="1:12" ht="24">
+      <c r="A35" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B35" s="14" t="s">
+        <v>84</v>
+      </c>
+      <c r="C35" s="14" t="s">
+        <v>117</v>
+      </c>
       <c r="D35" s="14"/>
       <c r="E35" s="14"/>
       <c r="F35" s="14"/>
@@ -3203,16 +3204,10 @@
       <c r="K35" s="14"/>
       <c r="L35" s="14"/>
     </row>
-    <row r="36" spans="1:12" ht="24">
-      <c r="A36" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="B36" s="14" t="s">
-        <v>84</v>
-      </c>
-      <c r="C36" s="14" t="s">
-        <v>132</v>
-      </c>
+    <row r="36" spans="1:12">
+      <c r="A36" s="3"/>
+      <c r="B36" s="14"/>
+      <c r="C36" s="14"/>
       <c r="D36" s="14"/>
       <c r="E36" s="14"/>
       <c r="F36" s="14"/>
@@ -3224,7 +3219,7 @@
       <c r="L36" s="14"/>
     </row>
     <row r="37" spans="1:12">
-      <c r="A37" s="3"/>
+      <c r="A37" s="14"/>
       <c r="B37" s="14"/>
       <c r="C37" s="14"/>
       <c r="D37" s="14"/>
@@ -3238,7 +3233,9 @@
       <c r="L37" s="14"/>
     </row>
     <row r="38" spans="1:12">
-      <c r="A38" s="14"/>
+      <c r="A38" s="15" t="s">
+        <v>68</v>
+      </c>
       <c r="B38" s="14"/>
       <c r="C38" s="14"/>
       <c r="D38" s="14"/>
@@ -3252,46 +3249,44 @@
       <c r="L38" s="14"/>
     </row>
     <row r="39" spans="1:12">
-      <c r="A39" s="15" t="s">
-        <v>68</v>
-      </c>
-      <c r="B39" s="14"/>
-      <c r="C39" s="14"/>
-      <c r="D39" s="14"/>
-      <c r="E39" s="14"/>
-      <c r="F39" s="14"/>
-      <c r="G39" s="14"/>
-      <c r="H39" s="14"/>
+      <c r="A39" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="B39" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="C39" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="D39" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="E39" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="F39" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="G39" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="H39" s="14" t="s">
+        <v>89</v>
+      </c>
       <c r="I39" s="14"/>
       <c r="J39" s="14"/>
       <c r="K39" s="14"/>
       <c r="L39" s="14"/>
     </row>
     <row r="40" spans="1:12">
-      <c r="A40" s="14" t="s">
-        <v>86</v>
-      </c>
-      <c r="B40" s="14" t="s">
-        <v>69</v>
-      </c>
-      <c r="C40" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="D40" s="14" t="s">
-        <v>71</v>
-      </c>
-      <c r="E40" s="14" t="s">
-        <v>65</v>
-      </c>
-      <c r="F40" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="G40" s="14" t="s">
-        <v>88</v>
-      </c>
-      <c r="H40" s="14" t="s">
-        <v>89</v>
-      </c>
+      <c r="A40" s="14"/>
+      <c r="B40" s="14"/>
+      <c r="C40" s="14"/>
+      <c r="D40" s="14"/>
+      <c r="E40" s="14"/>
+      <c r="F40" s="14"/>
+      <c r="G40" s="14"/>
+      <c r="H40" s="14"/>
       <c r="I40" s="14"/>
       <c r="J40" s="14"/>
       <c r="K40" s="14"/>
@@ -3325,22 +3320,8 @@
       <c r="K42" s="14"/>
       <c r="L42" s="14"/>
     </row>
-    <row r="43" spans="1:12">
-      <c r="A43" s="14"/>
-      <c r="B43" s="14"/>
-      <c r="C43" s="14"/>
-      <c r="D43" s="14"/>
-      <c r="E43" s="14"/>
-      <c r="F43" s="14"/>
-      <c r="G43" s="14"/>
-      <c r="H43" s="14"/>
-      <c r="I43" s="14"/>
-      <c r="J43" s="14"/>
-      <c r="K43" s="14"/>
-      <c r="L43" s="14"/>
-    </row>
-    <row r="53" spans="3:3">
-      <c r="C53" s="3"/>
+    <row r="52" spans="3:3">
+      <c r="C52" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -3364,7 +3345,7 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="24" t="s">
-        <v>133</v>
+        <v>118</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="9"/>
@@ -3374,13 +3355,13 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="5" t="s">
-        <v>134</v>
+        <v>119</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>159</v>
+        <v>138</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>194</v>
+        <v>160</v>
       </c>
       <c r="D2" s="5" t="s">
         <v>1</v>
@@ -3390,13 +3371,13 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="9" t="s">
-        <v>202</v>
+        <v>165</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>234</v>
+        <v>191</v>
       </c>
       <c r="D3" s="9"/>
       <c r="E3" s="4"/>
@@ -3404,16 +3385,14 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="9" t="s">
-        <v>140</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>196</v>
-      </c>
+        <v>124</v>
+      </c>
+      <c r="B4" s="4"/>
       <c r="C4" s="9" t="s">
-        <v>205</v>
+        <v>193</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>150</v>
+        <v>134</v>
       </c>
       <c r="E4" s="4"/>
       <c r="F4" s="4"/>
@@ -3428,13 +3407,13 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="9" t="s">
-        <v>227</v>
+        <v>183</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>228</v>
+        <v>194</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>231</v>
+        <v>185</v>
       </c>
       <c r="D6" s="9"/>
       <c r="E6" s="4"/>
@@ -3442,13 +3421,11 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="9" t="s">
-        <v>229</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>230</v>
-      </c>
+        <v>184</v>
+      </c>
+      <c r="B7" s="4"/>
       <c r="C7" s="9" t="s">
-        <v>233</v>
+        <v>204</v>
       </c>
       <c r="D7" s="9"/>
       <c r="E7" s="4"/>
@@ -3462,15 +3439,15 @@
       <c r="E8" s="4"/>
       <c r="F8" s="4"/>
     </row>
-    <row r="9" spans="1:6" ht="24">
+    <row r="9" spans="1:6" ht="48">
       <c r="A9" s="9" t="s">
-        <v>141</v>
+        <v>125</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>232</v>
+        <v>198</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>241</v>
+        <v>200</v>
       </c>
       <c r="D9" s="9"/>
       <c r="E9" s="4"/>
@@ -3478,16 +3455,14 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="9" t="s">
-        <v>142</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>154</v>
-      </c>
+        <v>126</v>
+      </c>
+      <c r="B10" s="4"/>
       <c r="C10" s="9" t="s">
-        <v>237</v>
+        <v>199</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>143</v>
+        <v>127</v>
       </c>
       <c r="E10" s="4"/>
       <c r="F10" s="4"/>
@@ -3495,22 +3470,22 @@
     <row r="11" spans="1:6">
       <c r="A11" s="9"/>
       <c r="B11" s="4" t="s">
-        <v>153</v>
+        <v>137</v>
       </c>
       <c r="C11" s="9"/>
       <c r="D11" s="9"/>
       <c r="E11" s="4"/>
       <c r="F11" s="4"/>
     </row>
-    <row r="12" spans="1:6" ht="36">
+    <row r="12" spans="1:6" ht="48">
       <c r="A12" s="9" t="s">
-        <v>144</v>
+        <v>128</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>155</v>
+        <v>201</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>235</v>
+        <v>205</v>
       </c>
       <c r="D12" s="9"/>
       <c r="E12" s="4"/>
@@ -3518,13 +3493,11 @@
     </row>
     <row r="13" spans="1:6" ht="24">
       <c r="A13" s="9" t="s">
-        <v>145</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>156</v>
-      </c>
+        <v>129</v>
+      </c>
+      <c r="B13" s="4"/>
       <c r="C13" s="9" t="s">
-        <v>240</v>
+        <v>202</v>
       </c>
       <c r="D13" s="9"/>
       <c r="E13" s="4"/>
@@ -3533,22 +3506,22 @@
     <row r="14" spans="1:6">
       <c r="A14" s="9"/>
       <c r="B14" s="4" t="s">
-        <v>153</v>
+        <v>137</v>
       </c>
       <c r="C14" s="9"/>
       <c r="D14" s="9"/>
       <c r="E14" s="4"/>
       <c r="F14" s="4"/>
     </row>
-    <row r="15" spans="1:6" ht="36">
+    <row r="15" spans="1:6" ht="60">
       <c r="A15" s="9" t="s">
-        <v>146</v>
+        <v>130</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>242</v>
+        <v>203</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>236</v>
+        <v>206</v>
       </c>
       <c r="D15" s="9"/>
       <c r="E15" s="4"/>
@@ -3556,13 +3529,11 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="9" t="s">
-        <v>147</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>243</v>
-      </c>
+        <v>131</v>
+      </c>
+      <c r="B16" s="4"/>
       <c r="C16" s="9" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
       <c r="D16" s="9"/>
       <c r="E16" s="4"/>
@@ -3571,7 +3542,7 @@
     <row r="17" spans="1:6">
       <c r="A17" s="9"/>
       <c r="B17" s="4" t="s">
-        <v>153</v>
+        <v>137</v>
       </c>
       <c r="C17" s="9"/>
       <c r="D17" s="9"/>
@@ -3580,13 +3551,13 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="9" t="s">
-        <v>148</v>
+        <v>132</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>157</v>
+        <v>211</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>160</v>
+        <v>207</v>
       </c>
       <c r="D18" s="9"/>
       <c r="E18" s="4"/>
@@ -3594,13 +3565,11 @@
     </row>
     <row r="19" spans="1:6" ht="24">
       <c r="A19" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>158</v>
-      </c>
+        <v>133</v>
+      </c>
+      <c r="B19" s="4"/>
       <c r="C19" s="9" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="D19" s="9"/>
       <c r="E19" s="4"/>
@@ -3609,7 +3578,7 @@
     <row r="20" spans="1:6">
       <c r="A20" s="9"/>
       <c r="B20" s="4" t="s">
-        <v>153</v>
+        <v>137</v>
       </c>
       <c r="C20" s="9"/>
       <c r="D20" s="9"/>
@@ -3618,10 +3587,10 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="9" t="s">
-        <v>161</v>
+        <v>139</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>163</v>
+        <v>212</v>
       </c>
       <c r="C21" s="9"/>
       <c r="D21" s="9"/>
@@ -3630,56 +3599,50 @@
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="9" t="s">
-        <v>162</v>
-      </c>
-      <c r="B22" s="4" t="s">
-        <v>164</v>
-      </c>
+        <v>140</v>
+      </c>
+      <c r="B22" s="4"/>
       <c r="C22" s="9" t="s">
-        <v>207</v>
-      </c>
-      <c r="D22" s="9" t="s">
-        <v>135</v>
-      </c>
+        <v>215</v>
+      </c>
+      <c r="D22" s="9"/>
       <c r="E22" s="4"/>
       <c r="F22" s="4"/>
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="9"/>
       <c r="B23" s="4" t="s">
-        <v>153</v>
+        <v>137</v>
       </c>
       <c r="C23" s="9"/>
       <c r="D23" s="9"/>
       <c r="E23" s="4"/>
       <c r="F23" s="4"/>
     </row>
-    <row r="24" spans="1:6" ht="24">
+    <row r="24" spans="1:6">
       <c r="A24" s="9" t="s">
-        <v>165</v>
+        <v>141</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>174</v>
+        <v>216</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>189</v>
+        <v>217</v>
       </c>
       <c r="D24" s="9"/>
       <c r="E24" s="4"/>
       <c r="F24" s="4"/>
     </row>
-    <row r="25" spans="1:6" ht="36">
+    <row r="25" spans="1:6" ht="84">
       <c r="A25" s="9" t="s">
-        <v>166</v>
-      </c>
-      <c r="B25" s="4" t="s">
-        <v>175</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="B25" s="4"/>
       <c r="C25" s="9" t="s">
-        <v>208</v>
+        <v>218</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>183</v>
+        <v>220</v>
       </c>
       <c r="E25" s="4"/>
       <c r="F25" s="4"/>
@@ -3687,22 +3650,22 @@
     <row r="26" spans="1:6">
       <c r="A26" s="9"/>
       <c r="B26" s="4" t="s">
-        <v>153</v>
+        <v>137</v>
       </c>
       <c r="C26" s="9"/>
       <c r="D26" s="9"/>
       <c r="E26" s="4"/>
       <c r="F26" s="4"/>
     </row>
-    <row r="27" spans="1:6" ht="60">
+    <row r="27" spans="1:6" ht="96">
       <c r="A27" s="9" t="s">
-        <v>167</v>
+        <v>143</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>173</v>
+        <v>219</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>190</v>
+        <v>221</v>
       </c>
       <c r="D27" s="9"/>
       <c r="E27" s="4"/>
@@ -3710,13 +3673,11 @@
     </row>
     <row r="28" spans="1:6" ht="60">
       <c r="A28" s="9" t="s">
-        <v>168</v>
-      </c>
-      <c r="B28" s="4" t="s">
-        <v>176</v>
-      </c>
+        <v>144</v>
+      </c>
+      <c r="B28" s="4"/>
       <c r="C28" s="9" t="s">
-        <v>186</v>
+        <v>213</v>
       </c>
       <c r="D28" s="9"/>
       <c r="E28" s="4"/>
@@ -3725,7 +3686,7 @@
     <row r="29" spans="1:6">
       <c r="A29" s="9"/>
       <c r="B29" s="4" t="s">
-        <v>153</v>
+        <v>137</v>
       </c>
       <c r="C29" s="9"/>
       <c r="D29" s="9"/>
@@ -3734,13 +3695,13 @@
     </row>
     <row r="30" spans="1:6" ht="60">
       <c r="A30" s="9" t="s">
-        <v>136</v>
+        <v>120</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>177</v>
+        <v>149</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>191</v>
+        <v>214</v>
       </c>
       <c r="D30" s="9"/>
       <c r="E30" s="4"/>
@@ -3748,16 +3709,16 @@
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="9" t="s">
-        <v>137</v>
+        <v>121</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>178</v>
+        <v>150</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>187</v>
+        <v>156</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="E31" s="4"/>
       <c r="F31" s="4"/>
@@ -3765,7 +3726,7 @@
     <row r="32" spans="1:6">
       <c r="A32" s="9"/>
       <c r="B32" s="4" t="s">
-        <v>153</v>
+        <v>137</v>
       </c>
       <c r="C32" s="9"/>
       <c r="D32" s="9"/>
@@ -3774,13 +3735,13 @@
     </row>
     <row r="33" spans="1:6" ht="60">
       <c r="A33" s="9" t="s">
-        <v>169</v>
+        <v>145</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>179</v>
+        <v>151</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>191</v>
+        <v>214</v>
       </c>
       <c r="D33" s="9"/>
       <c r="E33" s="4"/>
@@ -3788,16 +3749,16 @@
     </row>
     <row r="34" spans="1:6">
       <c r="A34" s="9" t="s">
-        <v>170</v>
+        <v>146</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>180</v>
+        <v>152</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>188</v>
+        <v>157</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="E34" s="4"/>
       <c r="F34" s="4"/>
@@ -3805,7 +3766,7 @@
     <row r="35" spans="1:6">
       <c r="A35" s="9"/>
       <c r="B35" s="4" t="s">
-        <v>153</v>
+        <v>137</v>
       </c>
       <c r="C35" s="9"/>
       <c r="D35" s="9"/>
@@ -3814,13 +3775,13 @@
     </row>
     <row r="36" spans="1:6">
       <c r="A36" s="9" t="s">
-        <v>171</v>
+        <v>147</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>181</v>
+        <v>153</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>184</v>
+        <v>209</v>
       </c>
       <c r="D36" s="9"/>
       <c r="E36" s="4"/>
@@ -3828,13 +3789,13 @@
     </row>
     <row r="37" spans="1:6">
       <c r="A37" s="9" t="s">
-        <v>172</v>
+        <v>148</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>182</v>
+        <v>154</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D37" s="9"/>
       <c r="E37" s="4"/>
@@ -3850,11 +3811,11 @@
     </row>
     <row r="39" spans="1:6">
       <c r="A39" s="9" t="s">
-        <v>212</v>
+        <v>170</v>
       </c>
       <c r="B39" s="4"/>
       <c r="C39" s="9" t="s">
-        <v>210</v>
+        <v>168</v>
       </c>
       <c r="D39" s="9"/>
       <c r="E39" s="4"/>
@@ -3862,27 +3823,27 @@
     </row>
     <row r="40" spans="1:6" ht="24">
       <c r="A40" s="9" t="s">
-        <v>213</v>
+        <v>171</v>
       </c>
       <c r="B40" s="4"/>
       <c r="C40" s="9" t="s">
-        <v>211</v>
+        <v>169</v>
       </c>
       <c r="D40" s="9" t="s">
-        <v>192</v>
+        <v>158</v>
       </c>
       <c r="E40" s="4"/>
       <c r="F40" s="4"/>
     </row>
     <row r="41" spans="1:6" ht="24">
       <c r="A41" s="9" t="s">
-        <v>203</v>
+        <v>166</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>215</v>
+        <v>173</v>
       </c>
       <c r="C41" s="9" t="s">
-        <v>204</v>
+        <v>167</v>
       </c>
       <c r="D41" s="9"/>
       <c r="E41" s="4"/>
@@ -3890,29 +3851,29 @@
     </row>
     <row r="42" spans="1:6" ht="60">
       <c r="A42" s="9" t="s">
-        <v>214</v>
+        <v>172</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>215</v>
+        <v>173</v>
       </c>
       <c r="C42" s="9" t="s">
-        <v>218</v>
+        <v>176</v>
       </c>
       <c r="D42" s="9" t="s">
-        <v>219</v>
+        <v>177</v>
       </c>
       <c r="E42" s="4"/>
       <c r="F42" s="4"/>
     </row>
     <row r="43" spans="1:6" ht="48">
       <c r="A43" s="9" t="s">
-        <v>216</v>
+        <v>174</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>215</v>
+        <v>173</v>
       </c>
       <c r="C43" s="9" t="s">
-        <v>217</v>
+        <v>175</v>
       </c>
       <c r="D43" s="9"/>
       <c r="E43" s="4"/>
@@ -3920,25 +3881,25 @@
     </row>
     <row r="44" spans="1:6" s="23" customFormat="1">
       <c r="A44" s="22" t="s">
-        <v>197</v>
+        <v>161</v>
       </c>
       <c r="B44" s="21"/>
       <c r="C44" s="22"/>
       <c r="D44" s="22" t="s">
-        <v>193</v>
+        <v>159</v>
       </c>
       <c r="E44" s="21"/>
       <c r="F44" s="21"/>
     </row>
     <row r="45" spans="1:6">
       <c r="A45" s="9" t="s">
-        <v>198</v>
+        <v>162</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C45" s="9" t="s">
-        <v>185</v>
+        <v>155</v>
       </c>
       <c r="D45" s="9"/>
       <c r="E45" s="4"/>
@@ -3946,16 +3907,16 @@
     </row>
     <row r="46" spans="1:6" ht="24">
       <c r="A46" s="9" t="s">
-        <v>200</v>
+        <v>163</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>222</v>
+        <v>179</v>
       </c>
       <c r="C46" s="9" t="s">
-        <v>226</v>
+        <v>182</v>
       </c>
       <c r="D46" s="9" t="s">
-        <v>201</v>
+        <v>164</v>
       </c>
       <c r="E46" s="4"/>
       <c r="F46" s="4"/>
@@ -3970,13 +3931,13 @@
     </row>
     <row r="48" spans="1:6">
       <c r="A48" s="9" t="s">
-        <v>220</v>
+        <v>178</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>221</v>
+        <v>195</v>
       </c>
       <c r="C48" s="9" t="s">
-        <v>223</v>
+        <v>196</v>
       </c>
       <c r="D48" s="9"/>
       <c r="E48" s="4"/>
@@ -3984,13 +3945,13 @@
     </row>
     <row r="49" spans="1:6">
       <c r="A49" s="9" t="s">
-        <v>224</v>
+        <v>180</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>225</v>
+        <v>181</v>
       </c>
       <c r="C49" s="9" t="s">
-        <v>211</v>
+        <v>169</v>
       </c>
       <c r="D49" s="9"/>
       <c r="E49" s="4"/>
@@ -4135,18 +4096,18 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
-        <v>152</v>
+        <v>136</v>
       </c>
       <c r="B1" t="s">
-        <v>151</v>
+        <v>135</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="40.5">
       <c r="B8" s="31" t="s">
-        <v>238</v>
+        <v>186</v>
       </c>
       <c r="C8" s="32" t="s">
-        <v>239</v>
+        <v>187</v>
       </c>
     </row>
   </sheetData>

--- a/internal_doc/03.开发设计/OM_web接口.xlsx
+++ b/internal_doc/03.开发设计/OM_web接口.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="6510" activeTab="2"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="6510" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="需求" sheetId="1" r:id="rId1"/>
@@ -279,7 +279,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="233">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="234">
   <si>
     <t>需求</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1095,21 +1095,12 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>{[{IP, HostName, rc, Firework, [Disk],[CPU]…}, ...]}</t>
-  </si>
-  <si>
     <t>AddHostReq</t>
   </si>
   <si>
     <t>{ClusterName:xxx, desc:xxx}</t>
   </si>
   <si>
-    <t>host_info={ClusterName:cls1, host_info:[{IP, HostName, User, Passwd, SshPort:xxx, AgentPort:xxx},...], User:usr1, Passwd:Passwd1, SshPort:xxx, AgentPort:xxx}</t>
-  </si>
-  <si>
-    <t>host_info={ClusterName:cls1, host_info:[{IP, HostName, User, Passwd, SshPort:xxx, AgentPort:xxx, InstallPath:xxx, Firework, [Disk],[CPU]…}, ...], User:xxx, Passwd:xxx, SshPort:xxx, AgentPort:xxx, InstallPath:xxx}</t>
-  </si>
-  <si>
     <t>ClusterName=cls1</t>
   </si>
   <si>
@@ -1126,12 +1117,6 @@
   </si>
   <si>
     <t>QueryBusinessListReq</t>
-  </si>
-  <si>
-    <t>{BusinessType, business_name, cluster_type, ClusterName, [HostName, Disk_name, dbpath, svcname…], [HostName, Disk_name, dbpath, svcname…], [group_name, [HostName, Disk_name, dbpath, svcname…]]}</t>
-  </si>
-  <si>
-    <t>BusinessType=sequoiadb&amp;business_name=db1&amp;cluster_type=cluster&amp;ClusterName=cls1&amp;coord={[HostName, dbpath, svcname…]}&amp;catalog={[HostName, dbpath, svcname…]}&amp;data_group={[group_name, [HostName, dbpath, svcname…]]}</t>
   </si>
   <si>
     <t>{BusinessList:[{BusinessType, BusinessDesc},...]}</t>
@@ -1153,13 +1138,74 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>replname</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>shardname</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>catalogname</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>httpname</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>diaglevel</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>role</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>logfilesz</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>logfilenum</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>transactionon</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>numpagecleaners</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pagecleaninterval</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>host_info={ClusterName:cls1, host_info:[{IP, HostName, User, Passwd, SshPort:xxx, AgentPort:xxx},...], User:usr1, Passwd:Passwd1, SshPort:xxx, AgentPort:xxx}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{[{IP, HostName, rc, Firework, [Disk],[CPU]…}, ...]}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>ClusterType:cluster/standalone
-下拉列表，选中则切换配置</t>
+下拉列表，选中则切换配置
+增加"Desc","配置等级"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>load本地</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>host_info={ClusterName:cls1, host_info:[{IP, Name, User, Passwd, SshPort:xxx, AgentPort:xxx, InstallPath:xxx, Firework, [Disk],[CPU]…}, ...], User:xxx, Passwd:xxx, SshPort:xxx, AgentPort:xxx, InstallPath:xxx}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <r>
-      <t>{"BusinessType":"sequoiadb", "ClusterType": "standalone", "Property": [ { "Name": "replica_num", "Type": "int", "Default": "1", "Valid": "1", "Display": "edit box", "Edit": "false",</t>
+      <t>{"ClusterName":"c1","BusinessType":"sequoiadb", "ClusterType": "standalone", "Property": [ { "Name": "replica_num", "Type": "int", "Default": "1", "Valid": "1", "Display": "edit box", "Edit": "false",</t>
     </r>
     <r>
       <rPr>
@@ -1216,7 +1262,7 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>"HostInfo":[{"IP":"192.168.1.1", "HostName":"host1", Disk["Name":"", "Mount":"", "Size":""]}, ...]</t>
+      <t>"HostInfo":[{"IP":"192.168.1.1", "ClusterName":"c1", "Name":"host1", Disk["Name":"", "Mount":"", "Size":""]}, ...]</t>
     </r>
     <r>
       <rPr>
@@ -1232,47 +1278,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>replname</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>shardname</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>catalogname</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>httpname</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>diaglevel</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>role</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>logfilesz</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>logfilenum</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>transactionon</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>numpagecleaners</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>pagecleaninterval</t>
+    <t>{ClusterName, BusinessType, ClusterType, [{HostName, DiskName, dbpath, svcname…},...]}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{ClusterName, BusinessName, BusinessType, ClusterType, [{HostName, DiskName, dbpath, svcname…},...]}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2775,7 +2785,7 @@
     <row r="14" spans="1:12">
       <c r="A14" s="14"/>
       <c r="B14" s="14" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="C14" s="14">
         <v>11811</v>
@@ -2797,7 +2807,7 @@
     <row r="15" spans="1:12">
       <c r="A15" s="14"/>
       <c r="B15" s="14" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="C15" s="14">
         <v>11812</v>
@@ -2819,7 +2829,7 @@
     <row r="16" spans="1:12">
       <c r="A16" s="14"/>
       <c r="B16" s="14" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="C16" s="14">
         <v>11813</v>
@@ -2841,7 +2851,7 @@
     <row r="17" spans="1:12">
       <c r="A17" s="14"/>
       <c r="B17" s="14" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="C17" s="14">
         <v>11814</v>
@@ -2863,7 +2873,7 @@
     <row r="18" spans="1:12">
       <c r="A18" s="14"/>
       <c r="B18" s="14" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="C18" s="14">
         <v>3</v>
@@ -2887,7 +2897,7 @@
     <row r="19" spans="1:12">
       <c r="A19" s="14"/>
       <c r="B19" s="14" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="C19" s="14" t="s">
         <v>95</v>
@@ -2911,7 +2921,7 @@
     <row r="20" spans="1:12">
       <c r="A20" s="14"/>
       <c r="B20" s="14" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="C20" s="14">
         <v>64</v>
@@ -2935,7 +2945,7 @@
     <row r="21" spans="1:12">
       <c r="A21" s="14"/>
       <c r="B21" s="14" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="C21" s="14">
         <v>20</v>
@@ -2959,7 +2969,7 @@
     <row r="22" spans="1:12">
       <c r="A22" s="14"/>
       <c r="B22" s="14" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="C22" s="17" t="s">
         <v>109</v>
@@ -3007,7 +3017,7 @@
     <row r="24" spans="1:12">
       <c r="A24" s="14"/>
       <c r="B24" s="16" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="C24" s="11">
         <v>1</v>
@@ -3029,7 +3039,7 @@
     <row r="25" spans="1:12" s="19" customFormat="1">
       <c r="A25" s="16"/>
       <c r="B25" s="16" t="s">
-        <v>232</v>
+        <v>225</v>
       </c>
       <c r="C25" s="11">
         <v>10000</v>
@@ -3425,7 +3435,7 @@
       </c>
       <c r="B7" s="4"/>
       <c r="C7" s="9" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D7" s="9"/>
       <c r="E7" s="4"/>
@@ -3485,7 +3495,7 @@
         <v>201</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>205</v>
+        <v>226</v>
       </c>
       <c r="D12" s="9"/>
       <c r="E12" s="4"/>
@@ -3497,7 +3507,7 @@
       </c>
       <c r="B13" s="4"/>
       <c r="C13" s="9" t="s">
-        <v>202</v>
+        <v>227</v>
       </c>
       <c r="D13" s="9"/>
       <c r="E13" s="4"/>
@@ -3518,10 +3528,10 @@
         <v>130</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>206</v>
+        <v>230</v>
       </c>
       <c r="D15" s="9"/>
       <c r="E15" s="4"/>
@@ -3554,10 +3564,10 @@
         <v>132</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="D18" s="9"/>
       <c r="E18" s="4"/>
@@ -3569,7 +3579,7 @@
       </c>
       <c r="B19" s="4"/>
       <c r="C19" s="9" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="D19" s="9"/>
       <c r="E19" s="4"/>
@@ -3590,7 +3600,7 @@
         <v>139</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="C21" s="9"/>
       <c r="D21" s="9"/>
@@ -3603,7 +3613,7 @@
       </c>
       <c r="B22" s="4"/>
       <c r="C22" s="9" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="D22" s="9"/>
       <c r="E22" s="4"/>
@@ -3624,10 +3634,10 @@
         <v>141</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="D24" s="9"/>
       <c r="E24" s="4"/>
@@ -3639,10 +3649,10 @@
       </c>
       <c r="B25" s="4"/>
       <c r="C25" s="9" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="E25" s="4"/>
       <c r="F25" s="4"/>
@@ -3657,27 +3667,29 @@
       <c r="E26" s="4"/>
       <c r="F26" s="4"/>
     </row>
-    <row r="27" spans="1:6" ht="96">
+    <row r="27" spans="1:6" ht="108">
       <c r="A27" s="9" t="s">
         <v>143</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>221</v>
-      </c>
-      <c r="D27" s="9"/>
+        <v>231</v>
+      </c>
+      <c r="D27" s="9" t="s">
+        <v>229</v>
+      </c>
       <c r="E27" s="4"/>
       <c r="F27" s="4"/>
     </row>
-    <row r="28" spans="1:6" ht="60">
+    <row r="28" spans="1:6" ht="24">
       <c r="A28" s="9" t="s">
         <v>144</v>
       </c>
       <c r="B28" s="4"/>
       <c r="C28" s="9" t="s">
-        <v>213</v>
+        <v>232</v>
       </c>
       <c r="D28" s="9"/>
       <c r="E28" s="4"/>
@@ -3693,7 +3705,7 @@
       <c r="E29" s="4"/>
       <c r="F29" s="4"/>
     </row>
-    <row r="30" spans="1:6" ht="60">
+    <row r="30" spans="1:6" ht="24">
       <c r="A30" s="9" t="s">
         <v>120</v>
       </c>
@@ -3701,7 +3713,7 @@
         <v>149</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>214</v>
+        <v>232</v>
       </c>
       <c r="D30" s="9"/>
       <c r="E30" s="4"/>
@@ -3733,7 +3745,7 @@
       <c r="E32" s="4"/>
       <c r="F32" s="4"/>
     </row>
-    <row r="33" spans="1:6" ht="60">
+    <row r="33" spans="1:6" ht="36">
       <c r="A33" s="9" t="s">
         <v>145</v>
       </c>
@@ -3741,7 +3753,7 @@
         <v>151</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>214</v>
+        <v>233</v>
       </c>
       <c r="D33" s="9"/>
       <c r="E33" s="4"/>
@@ -3781,7 +3793,7 @@
         <v>153</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="D36" s="9"/>
       <c r="E36" s="4"/>
@@ -3795,7 +3807,7 @@
         <v>154</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="D37" s="9"/>
       <c r="E37" s="4"/>

--- a/internal_doc/03.开发设计/OM_web接口.xlsx
+++ b/internal_doc/03.开发设计/OM_web接口.xlsx
@@ -1129,11 +1129,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>{"BusinessType":"sequoiadb", "ClusterType": "standalone", "Property": [ { "Name": "replica_num", "Type": "int", "Default": "1", "Valid": "1", "Display": "edit box", "Edit": "false" }, ...] }  
-{"ClusterType": "cluster", "Property":[...]}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>ConfigBusinessReq</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1283,6 +1278,11 @@
   </si>
   <si>
     <t>{ClusterName, BusinessName, BusinessType, ClusterType, [{HostName, DiskName, dbpath, svcname…},...]}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"BusinessType":"sequoiadb", "ClusterType": "standalone", "Property": [ { "Name": "replica_num", "Type": "int", "Default": "1", "Valid": "1", "Display": "edit box", "Edit": "false", "Desc": "", "WebName": "" }, ...] }  
+{"ClusterType": "cluster", "Property":[...]}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1560,6 +1560,10 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1578,10 +1582,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1589,74 +1589,6 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -1668,7 +1600,7 @@
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="C7EDCC"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -1993,7 +1925,7 @@
       </c>
     </row>
     <row r="3" spans="1:8">
-      <c r="A3" s="25" t="s">
+      <c r="A3" s="27" t="s">
         <v>12</v>
       </c>
       <c r="B3" s="4" t="s">
@@ -2011,7 +1943,7 @@
       <c r="H3" s="4"/>
     </row>
     <row r="4" spans="1:8" ht="13.5">
-      <c r="A4" s="26"/>
+      <c r="A4" s="28"/>
       <c r="B4" s="4" t="s">
         <v>5</v>
       </c>
@@ -2027,7 +1959,7 @@
       <c r="H4" s="4"/>
     </row>
     <row r="5" spans="1:8" ht="13.5">
-      <c r="A5" s="26"/>
+      <c r="A5" s="28"/>
       <c r="B5" s="4" t="s">
         <v>8</v>
       </c>
@@ -2043,7 +1975,7 @@
       <c r="H5" s="4"/>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" s="27"/>
+      <c r="A6" s="29"/>
       <c r="B6" s="4" t="s">
         <v>13</v>
       </c>
@@ -2059,7 +1991,7 @@
       <c r="H6" s="4"/>
     </row>
     <row r="7" spans="1:8" ht="24">
-      <c r="A7" s="28" t="s">
+      <c r="A7" s="30" t="s">
         <v>24</v>
       </c>
       <c r="B7" s="4" t="s">
@@ -2077,7 +2009,7 @@
       <c r="H7" s="4"/>
     </row>
     <row r="8" spans="1:8" ht="36">
-      <c r="A8" s="29"/>
+      <c r="A8" s="31"/>
       <c r="B8" s="4" t="s">
         <v>17</v>
       </c>
@@ -2095,7 +2027,7 @@
       <c r="H8" s="4"/>
     </row>
     <row r="9" spans="1:8" ht="72">
-      <c r="A9" s="29"/>
+      <c r="A9" s="31"/>
       <c r="B9" s="4" t="s">
         <v>18</v>
       </c>
@@ -2113,7 +2045,7 @@
       <c r="H9" s="4"/>
     </row>
     <row r="10" spans="1:8" ht="24">
-      <c r="A10" s="30"/>
+      <c r="A10" s="32"/>
       <c r="B10" s="4" t="s">
         <v>21</v>
       </c>
@@ -2151,7 +2083,7 @@
       <c r="H11" s="4"/>
     </row>
     <row r="12" spans="1:8" ht="24">
-      <c r="A12" s="28" t="s">
+      <c r="A12" s="30" t="s">
         <v>26</v>
       </c>
       <c r="B12" s="4" t="s">
@@ -2169,7 +2101,7 @@
       <c r="H12" s="4"/>
     </row>
     <row r="13" spans="1:8">
-      <c r="A13" s="29"/>
+      <c r="A13" s="31"/>
       <c r="B13" s="4" t="s">
         <v>32</v>
       </c>
@@ -2185,7 +2117,7 @@
       <c r="H13" s="4"/>
     </row>
     <row r="14" spans="1:8" ht="24">
-      <c r="A14" s="29"/>
+      <c r="A14" s="31"/>
       <c r="B14" s="4" t="s">
         <v>33</v>
       </c>
@@ -2203,7 +2135,7 @@
       <c r="H14" s="4"/>
     </row>
     <row r="15" spans="1:8">
-      <c r="A15" s="29"/>
+      <c r="A15" s="31"/>
       <c r="B15" s="4" t="s">
         <v>35</v>
       </c>
@@ -2219,7 +2151,7 @@
       <c r="H15" s="4"/>
     </row>
     <row r="16" spans="1:8">
-      <c r="A16" s="29"/>
+      <c r="A16" s="31"/>
       <c r="B16" s="4" t="s">
         <v>57</v>
       </c>
@@ -2231,7 +2163,7 @@
       <c r="H16" s="4"/>
     </row>
     <row r="17" spans="1:8" ht="48">
-      <c r="A17" s="29"/>
+      <c r="A17" s="31"/>
       <c r="B17" s="4" t="s">
         <v>30</v>
       </c>
@@ -2249,7 +2181,7 @@
       <c r="H17" s="4"/>
     </row>
     <row r="18" spans="1:8">
-      <c r="A18" s="29"/>
+      <c r="A18" s="31"/>
       <c r="B18" s="4" t="s">
         <v>38</v>
       </c>
@@ -2265,7 +2197,7 @@
       <c r="H18" s="4"/>
     </row>
     <row r="19" spans="1:8">
-      <c r="A19" s="29"/>
+      <c r="A19" s="31"/>
       <c r="B19" s="4" t="s">
         <v>41</v>
       </c>
@@ -2281,7 +2213,7 @@
       <c r="H19" s="4"/>
     </row>
     <row r="20" spans="1:8">
-      <c r="A20" s="29"/>
+      <c r="A20" s="31"/>
       <c r="B20" s="4" t="s">
         <v>40</v>
       </c>
@@ -2297,7 +2229,7 @@
       <c r="H20" s="4"/>
     </row>
     <row r="21" spans="1:8" ht="24">
-      <c r="A21" s="29"/>
+      <c r="A21" s="31"/>
       <c r="B21" s="4" t="s">
         <v>44</v>
       </c>
@@ -2315,7 +2247,7 @@
       <c r="H21" s="4"/>
     </row>
     <row r="22" spans="1:8" ht="24">
-      <c r="A22" s="29"/>
+      <c r="A22" s="31"/>
       <c r="B22" s="4" t="s">
         <v>47</v>
       </c>
@@ -2331,7 +2263,7 @@
       <c r="H22" s="4"/>
     </row>
     <row r="23" spans="1:8" ht="24">
-      <c r="A23" s="29"/>
+      <c r="A23" s="31"/>
       <c r="B23" s="4" t="s">
         <v>49</v>
       </c>
@@ -2785,7 +2717,7 @@
     <row r="14" spans="1:12">
       <c r="A14" s="14"/>
       <c r="B14" s="14" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C14" s="14">
         <v>11811</v>
@@ -2807,7 +2739,7 @@
     <row r="15" spans="1:12">
       <c r="A15" s="14"/>
       <c r="B15" s="14" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C15" s="14">
         <v>11812</v>
@@ -2829,7 +2761,7 @@
     <row r="16" spans="1:12">
       <c r="A16" s="14"/>
       <c r="B16" s="14" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C16" s="14">
         <v>11813</v>
@@ -2851,7 +2783,7 @@
     <row r="17" spans="1:12">
       <c r="A17" s="14"/>
       <c r="B17" s="14" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C17" s="14">
         <v>11814</v>
@@ -2873,7 +2805,7 @@
     <row r="18" spans="1:12">
       <c r="A18" s="14"/>
       <c r="B18" s="14" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C18" s="14">
         <v>3</v>
@@ -2897,7 +2829,7 @@
     <row r="19" spans="1:12">
       <c r="A19" s="14"/>
       <c r="B19" s="14" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C19" s="14" t="s">
         <v>95</v>
@@ -2921,7 +2853,7 @@
     <row r="20" spans="1:12">
       <c r="A20" s="14"/>
       <c r="B20" s="14" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C20" s="14">
         <v>64</v>
@@ -2945,7 +2877,7 @@
     <row r="21" spans="1:12">
       <c r="A21" s="14"/>
       <c r="B21" s="14" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C21" s="14">
         <v>20</v>
@@ -2969,7 +2901,7 @@
     <row r="22" spans="1:12">
       <c r="A22" s="14"/>
       <c r="B22" s="14" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C22" s="17" t="s">
         <v>109</v>
@@ -3017,7 +2949,7 @@
     <row r="24" spans="1:12">
       <c r="A24" s="14"/>
       <c r="B24" s="16" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C24" s="11">
         <v>1</v>
@@ -3039,7 +2971,7 @@
     <row r="25" spans="1:12" s="19" customFormat="1">
       <c r="A25" s="16"/>
       <c r="B25" s="16" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C25" s="11">
         <v>10000</v>
@@ -3495,7 +3427,7 @@
         <v>201</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D12" s="9"/>
       <c r="E12" s="4"/>
@@ -3507,7 +3439,7 @@
       </c>
       <c r="B13" s="4"/>
       <c r="C13" s="9" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D13" s="9"/>
       <c r="E13" s="4"/>
@@ -3531,7 +3463,7 @@
         <v>202</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D15" s="9"/>
       <c r="E15" s="4"/>
@@ -3649,10 +3581,10 @@
       </c>
       <c r="B25" s="4"/>
       <c r="C25" s="9" t="s">
-        <v>213</v>
+        <v>233</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E25" s="4"/>
       <c r="F25" s="4"/>
@@ -3672,13 +3604,13 @@
         <v>143</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E27" s="4"/>
       <c r="F27" s="4"/>
@@ -3689,7 +3621,7 @@
       </c>
       <c r="B28" s="4"/>
       <c r="C28" s="9" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D28" s="9"/>
       <c r="E28" s="4"/>
@@ -3713,7 +3645,7 @@
         <v>149</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D30" s="9"/>
       <c r="E30" s="4"/>
@@ -3753,7 +3685,7 @@
         <v>151</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D33" s="9"/>
       <c r="E33" s="4"/>
@@ -4115,10 +4047,10 @@
       </c>
     </row>
     <row r="8" spans="1:3" ht="40.5">
-      <c r="B8" s="31" t="s">
+      <c r="B8" s="25" t="s">
         <v>186</v>
       </c>
-      <c r="C8" s="32" t="s">
+      <c r="C8" s="26" t="s">
         <v>187</v>
       </c>
     </row>

--- a/internal_doc/03.开发设计/OM_web接口.xlsx
+++ b/internal_doc/03.开发设计/OM_web接口.xlsx
@@ -279,7 +279,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="234">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="236">
   <si>
     <t>需求</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -797,10 +797,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>rc=ok，ping不通，ssh登陆不上，获取不到hostname</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>检测host</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -881,22 +877,6 @@
   </si>
   <si>
     <t>删除business响应</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>check_business_config_req</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>check_business_config_res</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>add_business_req</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>add_business_res</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1085,9 +1065,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>[{IP, HostName, rc}, ...]</t>
-  </si>
-  <si>
     <t>HostInfo={ClusterName:cls1,HostInfo:[{IP/HostName:xxx, User:xxx, Passwd:xxx, SshPort:xxx, AgentPort:xxx}, ...],User:usr1,Passwd:Passwd1, SshPort:xxx, AgentPort:xxx}</t>
   </si>
   <si>
@@ -1111,9 +1088,6 @@
   </si>
   <si>
     <t>{business_name, ClusterName, rc}</t>
-  </si>
-  <si>
-    <t>QueryHostReq</t>
   </si>
   <si>
     <t>QueryBusinessListReq</t>
@@ -1191,7 +1165,24 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>load本地</t>
+    <t>{"BusinessType":"sequoiadb", "ClusterType": "standalone", "Property": [ { "Name": "replica_num", "Type": "int", "Default": "1", "Valid": "1", "Display": "edit box", "Edit": "false", "Desc": "", "WebName": "" }, ...] }  
+{"ClusterType": "cluster", "Property":[...]}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CheckBusinessConfigReq</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{IP, HostName, Ping:true, Ssh:false, HostName:"rhelt10", rc}, ...]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rc=ok</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>QueryHostReq</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1200,18 +1191,7 @@
   </si>
   <si>
     <r>
-      <t>{"ClusterName":"c1","BusinessType":"sequoiadb", "ClusterType": "standalone", "Property": [ { "Name": "replica_num", "Type": "int", "Default": "1", "Valid": "1", "Display": "edit box", "Edit": "false",</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="3"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
+      <t xml:space="preserve">{"ClusterName":"c1","BusinessType":"sequoiadb","BusinessName":"b1", "ClusterType": "standalone", "Property": [ { "Name": "replica_num", </t>
     </r>
     <r>
       <rPr>
@@ -1257,7 +1237,7 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>"HostInfo":[{"IP":"192.168.1.1", "ClusterName":"c1", "Name":"host1", Disk["Name":"", "Mount":"", "Size":""]}, ...]</t>
+      <t>"HostInfo":[{"HostName":"host1"}, ...]</t>
     </r>
     <r>
       <rPr>
@@ -1273,16 +1253,35 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>{ClusterName, BusinessType, ClusterType, [{HostName, DiskName, dbpath, svcname…},...]}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{ClusterName, BusinessName, BusinessType, ClusterType, [{HostName, DiskName, dbpath, svcname…},...]}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"BusinessType":"sequoiadb", "ClusterType": "standalone", "Property": [ { "Name": "replica_num", "Type": "int", "Default": "1", "Valid": "1", "Display": "edit box", "Edit": "false", "Desc": "", "WebName": "" }, ...] }  
-{"ClusterType": "cluster", "Property":[...]}</t>
+    <t>http://192.168.20.197:11814/?cmd=ConfigBusinessReq&amp;TemplateInfo={"ClusterName":"c1","BusinessType":"sequoiadb","BusinessName":"b1","ClusterType":"standalone","Property":[{"Name":"replica_num","Value":"1"},{"Name":"data_group_num","Value":"1"},{"Name":"catalog_num","Value":"1"},{"Name":"coord_num","Value":"1"},{"Name":"user_name","Value":"sdbadmin"},{"Name":"user_passwd","Value":"sdbadmin"},{"Name":"user_group","Value":"sdbadmin_group"}],"HostInfo":[{"HostName":"host1"}]}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"Config": [ { "HostName": "host1", "username": "sdbadmin", "userpasswd": "sdbadmin", "usergroup": "sdbadmin_group", "datagroupname": "", "dbpath": "/home/db2//standalone/11830", "svcname": "11830", ...} ],"BusinessName": "b1", "BusinessType": "sequoiadb", "ClusterType": "standalone","ClusterName": "c1","Property": [ { "Name": "username", "Type": "string", "Default": "sdbadmin", "Valid": "", "Display": "edit box", "Edit": "true", "Desc": "", "Level": "0", "WebName": "user_name",... }]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{BusinessType, BusinessName,ClusterType, ClusterName, "Config":[{dbpath, svcname…} },...],"Property": [{ "Name": "username", "Type": "string", "Default": "sdbadmin", "Valid": "", "Display": "edit box", "Edit": "true", "Desc": "", "Level": "0", "WebName": "user_name",... }, ...] }</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{BusinessType, BusinessName,ClusterType, ClusterName, "Config":[{"HostName":"host1", "username":"sdbadmin","userpasswd":"sdbadmin", "usergroup":"sdbadmin_group","datagroupname":"", "dbpath":"/home/db2//standalone/11830", "svcname":"11830", ...}, ...] }</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AddBusinessReq</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>192.168.20.197:11814/?cmd=CheckBusinessConfReq&amp;ConfigInfo={"ClusterName":"c1","BusinessType":"sequoiadb","BusinessName":"b1","ClusterType":"cluster", "Config": [ { "HostName": "host1", "username": "sdbadmin", "userpasswd": "sdbadmin", "usergroup": "sdbadmin_group", "datagroupname": "", "dbpath": "/home/db2/standalone/11830", "svcname": "11830", "diaglevel": "3", "role": "standalone", "logfilesz": "64", "logfilenum": "20", "transactionon": "false", "preferedinstance": "A", "numpagecleaners": "1", "pagecleaninterval": "1" } ]}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{BusinessType, BusinessName,ClusterType, ClusterName, "Config":[{"HostName":"host1", "username":"sdbadmin","userpasswd":"sdbadmin", "usergroup":"sdbadmin_group","datagroupname":"", "dbpath":"/home/db2//standalone/11830", "svcname":"11830", ...}, ...] }]}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>192.168.20.197:11814/?cmd=AddBusinessReq&amp;ConfigInfo={"ClusterName":"c1","BusinessType":"sequoiadb","BusinessName":"b1","ClusterType":"cluster", "Config": [ { "HostName": "host1", "username": "sdbadmin", "userpasswd": "sdbadmin", "usergroup": "sdbadmin_group", "datagroupname": "", "dbpath": "/home/db2/standalone/11830", "svcname": "11830", "diaglevel": "3", "role": "standalone", "logfilesz": "64", "logfilenum": "20", "transactionon": "false", "preferedinstance": "A", "numpagecleaners": "1", "pagecleaninterval": "1" } ]}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1290,7 +1289,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="17">
+  <fonts count="16">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1394,14 +1393,6 @@
       <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <family val="2"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -1589,6 +1580,74 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -1600,7 +1659,7 @@
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:sysClr val="window" lastClr="C7EDCC"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -2717,7 +2776,7 @@
     <row r="14" spans="1:12">
       <c r="A14" s="14"/>
       <c r="B14" s="14" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="C14" s="14">
         <v>11811</v>
@@ -2739,7 +2798,7 @@
     <row r="15" spans="1:12">
       <c r="A15" s="14"/>
       <c r="B15" s="14" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="C15" s="14">
         <v>11812</v>
@@ -2761,7 +2820,7 @@
     <row r="16" spans="1:12">
       <c r="A16" s="14"/>
       <c r="B16" s="14" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="C16" s="14">
         <v>11813</v>
@@ -2783,7 +2842,7 @@
     <row r="17" spans="1:12">
       <c r="A17" s="14"/>
       <c r="B17" s="14" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="C17" s="14">
         <v>11814</v>
@@ -2805,7 +2864,7 @@
     <row r="18" spans="1:12">
       <c r="A18" s="14"/>
       <c r="B18" s="14" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="C18" s="14">
         <v>3</v>
@@ -2829,7 +2888,7 @@
     <row r="19" spans="1:12">
       <c r="A19" s="14"/>
       <c r="B19" s="14" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="C19" s="14" t="s">
         <v>95</v>
@@ -2853,7 +2912,7 @@
     <row r="20" spans="1:12">
       <c r="A20" s="14"/>
       <c r="B20" s="14" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="C20" s="14">
         <v>64</v>
@@ -2866,7 +2925,7 @@
         <v>102</v>
       </c>
       <c r="G20" s="14" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="H20" s="14"/>
       <c r="I20" s="14"/>
@@ -2877,7 +2936,7 @@
     <row r="21" spans="1:12">
       <c r="A21" s="14"/>
       <c r="B21" s="14" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="C21" s="14">
         <v>20</v>
@@ -2890,7 +2949,7 @@
         <v>102</v>
       </c>
       <c r="G21" s="14" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="H21" s="14"/>
       <c r="I21" s="14"/>
@@ -2901,7 +2960,7 @@
     <row r="22" spans="1:12">
       <c r="A22" s="14"/>
       <c r="B22" s="14" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="C22" s="17" t="s">
         <v>109</v>
@@ -2949,7 +3008,7 @@
     <row r="24" spans="1:12">
       <c r="A24" s="14"/>
       <c r="B24" s="16" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="C24" s="11">
         <v>1</v>
@@ -2971,7 +3030,7 @@
     <row r="25" spans="1:12" s="19" customFormat="1">
       <c r="A25" s="16"/>
       <c r="B25" s="16" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="C25" s="11">
         <v>10000</v>
@@ -3300,10 +3359,10 @@
         <v>119</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="D2" s="5" t="s">
         <v>1</v>
@@ -3313,13 +3372,13 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="9" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="D3" s="9"/>
       <c r="E3" s="4"/>
@@ -3331,10 +3390,10 @@
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="9" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E4" s="4"/>
       <c r="F4" s="4"/>
@@ -3349,13 +3408,13 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="9" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="D6" s="9"/>
       <c r="E6" s="4"/>
@@ -3363,11 +3422,11 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="9" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="B7" s="4"/>
       <c r="C7" s="9" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="D7" s="9"/>
       <c r="E7" s="4"/>
@@ -3386,25 +3445,25 @@
         <v>125</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="D9" s="9"/>
       <c r="E9" s="4"/>
       <c r="F9" s="4"/>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:6" ht="24">
       <c r="A10" s="9" t="s">
         <v>126</v>
       </c>
       <c r="B10" s="4"/>
       <c r="C10" s="9" t="s">
-        <v>199</v>
+        <v>223</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>127</v>
+        <v>224</v>
       </c>
       <c r="E10" s="4"/>
       <c r="F10" s="4"/>
@@ -3412,7 +3471,7 @@
     <row r="11" spans="1:6">
       <c r="A11" s="9"/>
       <c r="B11" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C11" s="9"/>
       <c r="D11" s="9"/>
@@ -3421,13 +3480,13 @@
     </row>
     <row r="12" spans="1:6" ht="48">
       <c r="A12" s="9" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="D12" s="9"/>
       <c r="E12" s="4"/>
@@ -3435,11 +3494,11 @@
     </row>
     <row r="13" spans="1:6" ht="24">
       <c r="A13" s="9" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B13" s="4"/>
       <c r="C13" s="9" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="D13" s="9"/>
       <c r="E13" s="4"/>
@@ -3448,7 +3507,7 @@
     <row r="14" spans="1:6">
       <c r="A14" s="9"/>
       <c r="B14" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C14" s="9"/>
       <c r="D14" s="9"/>
@@ -3457,13 +3516,13 @@
     </row>
     <row r="15" spans="1:6" ht="60">
       <c r="A15" s="9" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="D15" s="9"/>
       <c r="E15" s="4"/>
@@ -3471,11 +3530,11 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="9" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B16" s="4"/>
       <c r="C16" s="9" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="D16" s="9"/>
       <c r="E16" s="4"/>
@@ -3484,7 +3543,7 @@
     <row r="17" spans="1:6">
       <c r="A17" s="9"/>
       <c r="B17" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C17" s="9"/>
       <c r="D17" s="9"/>
@@ -3493,13 +3552,13 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="9" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>208</v>
+        <v>225</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="D18" s="9"/>
       <c r="E18" s="4"/>
@@ -3507,11 +3566,11 @@
     </row>
     <row r="19" spans="1:6" ht="24">
       <c r="A19" s="9" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B19" s="4"/>
       <c r="C19" s="9" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="D19" s="9"/>
       <c r="E19" s="4"/>
@@ -3520,7 +3579,7 @@
     <row r="20" spans="1:6">
       <c r="A20" s="9"/>
       <c r="B20" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C20" s="9"/>
       <c r="D20" s="9"/>
@@ -3529,10 +3588,10 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="9" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="C21" s="9"/>
       <c r="D21" s="9"/>
@@ -3541,11 +3600,11 @@
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="9" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B22" s="4"/>
       <c r="C22" s="9" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="D22" s="9"/>
       <c r="E22" s="4"/>
@@ -3554,7 +3613,7 @@
     <row r="23" spans="1:6">
       <c r="A23" s="9"/>
       <c r="B23" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C23" s="9"/>
       <c r="D23" s="9"/>
@@ -3563,13 +3622,13 @@
     </row>
     <row r="24" spans="1:6">
       <c r="A24" s="9" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="D24" s="9"/>
       <c r="E24" s="4"/>
@@ -3577,14 +3636,14 @@
     </row>
     <row r="25" spans="1:6" ht="84">
       <c r="A25" s="9" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B25" s="4"/>
       <c r="C25" s="9" t="s">
-        <v>233</v>
+        <v>221</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="E25" s="4"/>
       <c r="F25" s="4"/>
@@ -3592,22 +3651,22 @@
     <row r="26" spans="1:6">
       <c r="A26" s="9"/>
       <c r="B26" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C26" s="9"/>
       <c r="D26" s="9"/>
       <c r="E26" s="4"/>
       <c r="F26" s="4"/>
     </row>
-    <row r="27" spans="1:6" ht="108">
+    <row r="27" spans="1:6" ht="120">
       <c r="A27" s="9" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="D27" s="9" t="s">
         <v>228</v>
@@ -3615,39 +3674,43 @@
       <c r="E27" s="4"/>
       <c r="F27" s="4"/>
     </row>
-    <row r="28" spans="1:6" ht="24">
+    <row r="28" spans="1:6" ht="132">
       <c r="A28" s="9" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B28" s="4"/>
       <c r="C28" s="9" t="s">
-        <v>231</v>
-      </c>
-      <c r="D28" s="9"/>
+        <v>230</v>
+      </c>
+      <c r="D28" s="9" t="s">
+        <v>229</v>
+      </c>
       <c r="E28" s="4"/>
       <c r="F28" s="4"/>
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="9"/>
       <c r="B29" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C29" s="9"/>
       <c r="D29" s="9"/>
       <c r="E29" s="4"/>
       <c r="F29" s="4"/>
     </row>
-    <row r="30" spans="1:6" ht="24">
+    <row r="30" spans="1:6" ht="156">
       <c r="A30" s="9" t="s">
         <v>120</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>149</v>
+        <v>222</v>
       </c>
       <c r="C30" s="9" t="s">
         <v>231</v>
       </c>
-      <c r="D30" s="9"/>
+      <c r="D30" s="9" t="s">
+        <v>233</v>
+      </c>
       <c r="E30" s="4"/>
       <c r="F30" s="4"/>
     </row>
@@ -3655,11 +3718,9 @@
       <c r="A31" s="9" t="s">
         <v>121</v>
       </c>
-      <c r="B31" s="4" t="s">
-        <v>150</v>
-      </c>
+      <c r="B31" s="4"/>
       <c r="C31" s="11" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="D31" s="9" t="s">
         <v>122</v>
@@ -3670,36 +3731,36 @@
     <row r="32" spans="1:6">
       <c r="A32" s="9"/>
       <c r="B32" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C32" s="9"/>
       <c r="D32" s="9"/>
       <c r="E32" s="4"/>
       <c r="F32" s="4"/>
     </row>
-    <row r="33" spans="1:6" ht="36">
+    <row r="33" spans="1:6" ht="144">
       <c r="A33" s="9" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>151</v>
+        <v>232</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>232</v>
-      </c>
-      <c r="D33" s="9"/>
+        <v>234</v>
+      </c>
+      <c r="D33" s="9" t="s">
+        <v>235</v>
+      </c>
       <c r="E33" s="4"/>
       <c r="F33" s="4"/>
     </row>
     <row r="34" spans="1:6">
       <c r="A34" s="9" t="s">
-        <v>146</v>
-      </c>
-      <c r="B34" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="B34" s="4"/>
+      <c r="C34" s="9" t="s">
         <v>152</v>
-      </c>
-      <c r="C34" s="9" t="s">
-        <v>157</v>
       </c>
       <c r="D34" s="9" t="s">
         <v>123</v>
@@ -3710,7 +3771,7 @@
     <row r="35" spans="1:6">
       <c r="A35" s="9"/>
       <c r="B35" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C35" s="9"/>
       <c r="D35" s="9"/>
@@ -3719,13 +3780,13 @@
     </row>
     <row r="36" spans="1:6">
       <c r="A36" s="9" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="D36" s="9"/>
       <c r="E36" s="4"/>
@@ -3733,13 +3794,13 @@
     </row>
     <row r="37" spans="1:6">
       <c r="A37" s="9" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="D37" s="9"/>
       <c r="E37" s="4"/>
@@ -3755,11 +3816,11 @@
     </row>
     <row r="39" spans="1:6">
       <c r="A39" s="9" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="B39" s="4"/>
       <c r="C39" s="9" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="D39" s="9"/>
       <c r="E39" s="4"/>
@@ -3767,27 +3828,27 @@
     </row>
     <row r="40" spans="1:6" ht="24">
       <c r="A40" s="9" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="B40" s="4"/>
       <c r="C40" s="9" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="D40" s="9" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="E40" s="4"/>
       <c r="F40" s="4"/>
     </row>
     <row r="41" spans="1:6" ht="24">
       <c r="A41" s="9" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="C41" s="9" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="D41" s="9"/>
       <c r="E41" s="4"/>
@@ -3795,29 +3856,29 @@
     </row>
     <row r="42" spans="1:6" ht="60">
       <c r="A42" s="9" t="s">
+        <v>167</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="C42" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="D42" s="9" t="s">
         <v>172</v>
-      </c>
-      <c r="B42" s="4" t="s">
-        <v>173</v>
-      </c>
-      <c r="C42" s="9" t="s">
-        <v>176</v>
-      </c>
-      <c r="D42" s="9" t="s">
-        <v>177</v>
       </c>
       <c r="E42" s="4"/>
       <c r="F42" s="4"/>
     </row>
     <row r="43" spans="1:6" ht="48">
       <c r="A43" s="9" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="C43" s="9" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="D43" s="9"/>
       <c r="E43" s="4"/>
@@ -3825,25 +3886,25 @@
     </row>
     <row r="44" spans="1:6" s="23" customFormat="1">
       <c r="A44" s="22" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="B44" s="21"/>
       <c r="C44" s="22"/>
       <c r="D44" s="22" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="E44" s="21"/>
       <c r="F44" s="21"/>
     </row>
     <row r="45" spans="1:6">
       <c r="A45" s="9" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="C45" s="9" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="D45" s="9"/>
       <c r="E45" s="4"/>
@@ -3851,16 +3912,16 @@
     </row>
     <row r="46" spans="1:6" ht="24">
       <c r="A46" s="9" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="C46" s="9" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="D46" s="9" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="E46" s="4"/>
       <c r="F46" s="4"/>
@@ -3875,13 +3936,13 @@
     </row>
     <row r="48" spans="1:6">
       <c r="A48" s="9" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="C48" s="9" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="D48" s="9"/>
       <c r="E48" s="4"/>
@@ -3889,13 +3950,13 @@
     </row>
     <row r="49" spans="1:6">
       <c r="A49" s="9" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="C49" s="9" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="D49" s="9"/>
       <c r="E49" s="4"/>
@@ -4040,18 +4101,18 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="40.5">
       <c r="B8" s="25" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="C8" s="26" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
     </row>
   </sheetData>

--- a/internal_doc/03.开发设计/OM_web接口.xlsx
+++ b/internal_doc/03.开发设计/OM_web接口.xlsx
@@ -279,7 +279,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="236">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="242">
   <si>
     <t>需求</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1035,10 +1035,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>ClusterInfo={ClusterName=cls1, Desc=xxx}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>{ClusterName, rc}</t>
   </si>
   <si>
@@ -1046,10 +1042,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>QueryClusterReq</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>LoginReq</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1078,9 +1070,6 @@
     <t>{ClusterName:xxx, desc:xxx}</t>
   </si>
   <si>
-    <t>ClusterName=cls1</t>
-  </si>
-  <si>
     <t>{ClusterName, rc, [IP, HostName, Firework, [Disk],[CPU]...]}</t>
   </si>
   <si>
@@ -1090,9 +1079,6 @@
     <t>{business_name, ClusterName, rc}</t>
   </si>
   <si>
-    <t>QueryBusinessListReq</t>
-  </si>
-  <si>
     <t>{BusinessList:[{BusinessType, BusinessDesc},...]}</t>
   </si>
   <si>
@@ -1148,10 +1134,6 @@
   </si>
   <si>
     <t>pagecleaninterval</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>host_info={ClusterName:cls1, host_info:[{IP, HostName, User, Passwd, SshPort:xxx, AgentPort:xxx},...], User:usr1, Passwd:Passwd1, SshPort:xxx, AgentPort:xxx}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1282,6 +1264,50 @@
   </si>
   <si>
     <t>192.168.20.197:11814/?cmd=AddBusinessReq&amp;ConfigInfo={"ClusterName":"c1","BusinessType":"sequoiadb","BusinessName":"b1","ClusterType":"cluster", "Config": [ { "HostName": "host1", "username": "sdbadmin", "userpasswd": "sdbadmin", "usergroup": "sdbadmin_group", "datagroupname": "", "dbpath": "/home/db2/standalone/11830", "svcname": "11830", "diaglevel": "3", "role": "standalone", "logfilesz": "64", "logfilenum": "20", "transactionon": "false", "preferedinstance": "A", "numpagecleaners": "1", "pagecleaninterval": "1" } ]}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>host_info={ClusterName:cls1, host_info:[{IP, HostName, User, Passwd, SshPort:xxx, AgentPort:xxx},...], User:usr1, Passwd:Passwd1, SshPort:xxx}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ClusterInfo={ClusterName=cls1, Desc=xxx, SdbUser=sdbadmin, SdbPasswd=sdbadmin, SdbUserGroup=sdbadmin_group}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ClusterName=cls1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://192.168.20.197:11814/?cmd=QueryHostReq&amp;ClusterName=c1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>一个host一个bson</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>QueryBusinessListReq</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>QueryClusterReq</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://192.168.20.197:11814/?cmd=QueryBusinessListReq</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{ "rc": 0 }{ "BusinessList": [ { "BusinessType": "sequoiadb", "BusinessDesc": "haha" }, { "BusinessType": "sequoiasql", "BusinessDesc": "haha" } ] }</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://192.168.20.197:11814/?cmd=QueryClusterReq</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{ "rc": 0 }{ "ClusterName": "c1", "Desc": "" }</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2776,7 +2802,7 @@
     <row r="14" spans="1:12">
       <c r="A14" s="14"/>
       <c r="B14" s="14" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="C14" s="14">
         <v>11811</v>
@@ -2798,7 +2824,7 @@
     <row r="15" spans="1:12">
       <c r="A15" s="14"/>
       <c r="B15" s="14" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="C15" s="14">
         <v>11812</v>
@@ -2820,7 +2846,7 @@
     <row r="16" spans="1:12">
       <c r="A16" s="14"/>
       <c r="B16" s="14" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="C16" s="14">
         <v>11813</v>
@@ -2842,7 +2868,7 @@
     <row r="17" spans="1:12">
       <c r="A17" s="14"/>
       <c r="B17" s="14" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="C17" s="14">
         <v>11814</v>
@@ -2864,7 +2890,7 @@
     <row r="18" spans="1:12">
       <c r="A18" s="14"/>
       <c r="B18" s="14" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="C18" s="14">
         <v>3</v>
@@ -2888,7 +2914,7 @@
     <row r="19" spans="1:12">
       <c r="A19" s="14"/>
       <c r="B19" s="14" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="C19" s="14" t="s">
         <v>95</v>
@@ -2912,7 +2938,7 @@
     <row r="20" spans="1:12">
       <c r="A20" s="14"/>
       <c r="B20" s="14" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="C20" s="14">
         <v>64</v>
@@ -2936,7 +2962,7 @@
     <row r="21" spans="1:12">
       <c r="A21" s="14"/>
       <c r="B21" s="14" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="C21" s="14">
         <v>20</v>
@@ -2960,7 +2986,7 @@
     <row r="22" spans="1:12">
       <c r="A22" s="14"/>
       <c r="B22" s="14" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="C22" s="17" t="s">
         <v>109</v>
@@ -3008,7 +3034,7 @@
     <row r="24" spans="1:12">
       <c r="A24" s="14"/>
       <c r="B24" s="16" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="C24" s="11">
         <v>1</v>
@@ -3030,7 +3056,7 @@
     <row r="25" spans="1:12" s="19" customFormat="1">
       <c r="A25" s="16"/>
       <c r="B25" s="16" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="C25" s="11">
         <v>10000</v>
@@ -3370,7 +3396,7 @@
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:6" ht="36">
       <c r="A3" s="9" t="s">
         <v>160</v>
       </c>
@@ -3378,7 +3404,7 @@
         <v>185</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>186</v>
+        <v>232</v>
       </c>
       <c r="D3" s="9"/>
       <c r="E3" s="4"/>
@@ -3390,7 +3416,7 @@
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="9" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D4" s="9" t="s">
         <v>133</v>
@@ -3411,12 +3437,14 @@
         <v>178</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>189</v>
+        <v>237</v>
       </c>
       <c r="C6" s="9" t="s">
         <v>180</v>
       </c>
-      <c r="D6" s="9"/>
+      <c r="D6" s="9" t="s">
+        <v>240</v>
+      </c>
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
     </row>
@@ -3426,9 +3454,11 @@
       </c>
       <c r="B7" s="4"/>
       <c r="C7" s="9" t="s">
-        <v>197</v>
-      </c>
-      <c r="D7" s="9"/>
+        <v>195</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>241</v>
+      </c>
       <c r="E7" s="4"/>
       <c r="F7" s="4"/>
     </row>
@@ -3445,10 +3475,10 @@
         <v>125</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D9" s="9"/>
       <c r="E9" s="4"/>
@@ -3460,10 +3490,10 @@
       </c>
       <c r="B10" s="4"/>
       <c r="C10" s="9" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="E10" s="4"/>
       <c r="F10" s="4"/>
@@ -3483,10 +3513,10 @@
         <v>127</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="D12" s="9"/>
       <c r="E12" s="4"/>
@@ -3498,7 +3528,7 @@
       </c>
       <c r="B13" s="4"/>
       <c r="C13" s="9" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="D13" s="9"/>
       <c r="E13" s="4"/>
@@ -3519,10 +3549,10 @@
         <v>129</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="D15" s="9"/>
       <c r="E15" s="4"/>
@@ -3534,7 +3564,7 @@
       </c>
       <c r="B16" s="4"/>
       <c r="C16" s="9" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D16" s="9"/>
       <c r="E16" s="4"/>
@@ -3550,17 +3580,19 @@
       <c r="E17" s="4"/>
       <c r="F17" s="4"/>
     </row>
-    <row r="18" spans="1:6">
+    <row r="18" spans="1:6" ht="27">
       <c r="A18" s="9" t="s">
         <v>131</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>198</v>
-      </c>
-      <c r="D18" s="9"/>
+        <v>233</v>
+      </c>
+      <c r="D18" s="25" t="s">
+        <v>234</v>
+      </c>
       <c r="E18" s="4"/>
       <c r="F18" s="4"/>
     </row>
@@ -3570,9 +3602,11 @@
       </c>
       <c r="B19" s="4"/>
       <c r="C19" s="9" t="s">
-        <v>199</v>
-      </c>
-      <c r="D19" s="9"/>
+        <v>196</v>
+      </c>
+      <c r="D19" s="9" t="s">
+        <v>235</v>
+      </c>
       <c r="E19" s="4"/>
       <c r="F19" s="4"/>
     </row>
@@ -3586,27 +3620,31 @@
       <c r="E20" s="4"/>
       <c r="F20" s="4"/>
     </row>
-    <row r="21" spans="1:6">
+    <row r="21" spans="1:6" ht="24">
       <c r="A21" s="9" t="s">
         <v>138</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>202</v>
+        <v>236</v>
       </c>
       <c r="C21" s="9"/>
-      <c r="D21" s="9"/>
+      <c r="D21" s="9" t="s">
+        <v>238</v>
+      </c>
       <c r="E21" s="4"/>
       <c r="F21" s="4"/>
     </row>
-    <row r="22" spans="1:6">
+    <row r="22" spans="1:6" ht="48">
       <c r="A22" s="9" t="s">
         <v>139</v>
       </c>
       <c r="B22" s="4"/>
       <c r="C22" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="D22" s="9"/>
+        <v>199</v>
+      </c>
+      <c r="D22" s="9" t="s">
+        <v>239</v>
+      </c>
       <c r="E22" s="4"/>
       <c r="F22" s="4"/>
     </row>
@@ -3625,10 +3663,10 @@
         <v>140</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="D24" s="9"/>
       <c r="E24" s="4"/>
@@ -3640,10 +3678,10 @@
       </c>
       <c r="B25" s="4"/>
       <c r="C25" s="9" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="E25" s="4"/>
       <c r="F25" s="4"/>
@@ -3663,13 +3701,13 @@
         <v>142</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="E27" s="4"/>
       <c r="F27" s="4"/>
@@ -3680,10 +3718,10 @@
       </c>
       <c r="B28" s="4"/>
       <c r="C28" s="9" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="E28" s="4"/>
       <c r="F28" s="4"/>
@@ -3703,13 +3741,13 @@
         <v>120</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="E30" s="4"/>
       <c r="F30" s="4"/>
@@ -3743,13 +3781,13 @@
         <v>144</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="E33" s="4"/>
       <c r="F33" s="4"/>
@@ -3786,7 +3824,7 @@
         <v>148</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="D36" s="9"/>
       <c r="E36" s="4"/>
@@ -3800,7 +3838,7 @@
         <v>149</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="D37" s="9"/>
       <c r="E37" s="4"/>
@@ -3901,7 +3939,7 @@
         <v>157</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C45" s="9" t="s">
         <v>150</v>
@@ -3939,10 +3977,10 @@
         <v>173</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C48" s="9" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D48" s="9"/>
       <c r="E48" s="4"/>

--- a/internal_doc/03.开发设计/OM_web接口.xlsx
+++ b/internal_doc/03.开发设计/OM_web接口.xlsx
@@ -279,7 +279,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="242">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="240">
   <si>
     <t>需求</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -769,18 +769,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>校验配置</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>校验配置响应</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>仅返回错误描述</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>返回错误描述</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -889,10 +877,6 @@
   </si>
   <si>
     <t>NA</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{rc, [???]}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1149,10 +1133,6 @@
   <si>
     <t>{"BusinessType":"sequoiadb", "ClusterType": "standalone", "Property": [ { "Name": "replica_num", "Type": "int", "Default": "1", "Valid": "1", "Display": "edit box", "Edit": "false", "Desc": "", "WebName": "" }, ...] }  
 {"ClusterType": "cluster", "Property":[...]}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CheckBusinessConfigReq</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1247,7 +1227,55 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>{BusinessType, BusinessName,ClusterType, ClusterName, "Config":[{"HostName":"host1", "username":"sdbadmin","userpasswd":"sdbadmin", "usergroup":"sdbadmin_group","datagroupname":"", "dbpath":"/home/db2//standalone/11830", "svcname":"11830", ...}, ...] }</t>
+    <t>192.168.20.197:11814/?cmd=AddBusinessReq&amp;ConfigInfo={"ClusterName":"c1","BusinessType":"sequoiadb","BusinessName":"b1","ClusterType":"cluster", "Config": [ { "HostName": "host1", "username": "sdbadmin", "userpasswd": "sdbadmin", "usergroup": "sdbadmin_group", "datagroupname": "", "dbpath": "/home/db2/standalone/11830", "svcname": "11830", "diaglevel": "3", "role": "standalone", "logfilesz": "64", "logfilenum": "20", "transactionon": "false", "preferedinstance": "A", "numpagecleaners": "1", "pagecleaninterval": "1" } ]}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>host_info={ClusterName:cls1, host_info:[{IP, HostName, User, Passwd, SshPort:xxx, AgentPort:xxx},...], User:usr1, Passwd:Passwd1, SshPort:xxx}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ClusterInfo={ClusterName=cls1, Desc=xxx, SdbUser=sdbadmin, SdbPasswd=sdbadmin, SdbUserGroup=sdbadmin_group}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ClusterName=cls1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://192.168.20.197:11814/?cmd=QueryHostReq&amp;ClusterName=c1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>一个host一个bson</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>QueryBusinessListReq</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>QueryClusterReq</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://192.168.20.197:11814/?cmd=QueryBusinessListReq</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{ "rc": 0 }{ "BusinessList": [ { "BusinessType": "sequoiadb", "BusinessDesc": "haha" }, { "BusinessType": "sequoiasql", "BusinessDesc": "haha" } ] }</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://192.168.20.197:11814/?cmd=QueryClusterReq</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{ "rc": 0 }{ "ClusterName": "c1", "Desc": "" }</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{BusinessType, BusinessName,ClusterType, ClusterName, "Config":[{"HostName":"host1","datagroupname":"", "dbpath":"/home/db2//standalone/11830", "svcname":"11830", ...}, ...] }]}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1255,59 +1283,24 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>192.168.20.197:11814/?cmd=CheckBusinessConfReq&amp;ConfigInfo={"ClusterName":"c1","BusinessType":"sequoiadb","BusinessName":"b1","ClusterType":"cluster", "Config": [ { "HostName": "host1", "username": "sdbadmin", "userpasswd": "sdbadmin", "usergroup": "sdbadmin_group", "datagroupname": "", "dbpath": "/home/db2/standalone/11830", "svcname": "11830", "diaglevel": "3", "role": "standalone", "logfilesz": "64", "logfilenum": "20", "transactionon": "false", "preferedinstance": "A", "numpagecleaners": "1", "pagecleaninterval": "1" } ]}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{BusinessType, BusinessName,ClusterType, ClusterName, "Config":[{"HostName":"host1", "username":"sdbadmin","userpasswd":"sdbadmin", "usergroup":"sdbadmin_group","datagroupname":"", "dbpath":"/home/db2//standalone/11830", "svcname":"11830", ...}, ...] }]}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>192.168.20.197:11814/?cmd=AddBusinessReq&amp;ConfigInfo={"ClusterName":"c1","BusinessType":"sequoiadb","BusinessName":"b1","ClusterType":"cluster", "Config": [ { "HostName": "host1", "username": "sdbadmin", "userpasswd": "sdbadmin", "usergroup": "sdbadmin_group", "datagroupname": "", "dbpath": "/home/db2/standalone/11830", "svcname": "11830", "diaglevel": "3", "role": "standalone", "logfilesz": "64", "logfilenum": "20", "transactionon": "false", "preferedinstance": "A", "numpagecleaners": "1", "pagecleaninterval": "1" } ]}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>host_info={ClusterName:cls1, host_info:[{IP, HostName, User, Passwd, SshPort:xxx, AgentPort:xxx},...], User:usr1, Passwd:Passwd1, SshPort:xxx}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ClusterInfo={ClusterName=cls1, Desc=xxx, SdbUser=sdbadmin, SdbPasswd=sdbadmin, SdbUserGroup=sdbadmin_group}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ClusterName=cls1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>http://192.168.20.197:11814/?cmd=QueryHostReq&amp;ClusterName=c1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>一个host一个bson</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>QueryBusinessListReq</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>QueryClusterReq</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>http://192.168.20.197:11814/?cmd=QueryBusinessListReq</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{ "rc": 0 }{ "BusinessList": [ { "BusinessType": "sequoiadb", "BusinessDesc": "haha" }, { "BusinessType": "sequoiasql", "BusinessDesc": "haha" } ] }</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>http://192.168.20.197:11814/?cmd=QueryClusterReq</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{ "rc": 0 }{ "ClusterName": "c1", "Desc": "" }</t>
+    <t>查询安装进度</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"TaskID":"asd"}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>QueryInstallProgress</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>查询安装进度响应</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"rc":0, "Detail":"","TaskID":"asd", "isAllFinish":true,"Progress":[{"Name":"Coord","TotalCount":7 "InstalledCount":100, "Desc":""}, {"Name":"Group1","TotalCount":3,"InstalledCount":50,"Desc":""},
+{"Name":"Group2","TotalCount":4,"InstalledCount":50,"Desc":""} ...]}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2802,7 +2795,7 @@
     <row r="14" spans="1:12">
       <c r="A14" s="14"/>
       <c r="B14" s="14" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="C14" s="14">
         <v>11811</v>
@@ -2824,7 +2817,7 @@
     <row r="15" spans="1:12">
       <c r="A15" s="14"/>
       <c r="B15" s="14" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="C15" s="14">
         <v>11812</v>
@@ -2846,7 +2839,7 @@
     <row r="16" spans="1:12">
       <c r="A16" s="14"/>
       <c r="B16" s="14" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="C16" s="14">
         <v>11813</v>
@@ -2868,7 +2861,7 @@
     <row r="17" spans="1:12">
       <c r="A17" s="14"/>
       <c r="B17" s="14" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="C17" s="14">
         <v>11814</v>
@@ -2890,7 +2883,7 @@
     <row r="18" spans="1:12">
       <c r="A18" s="14"/>
       <c r="B18" s="14" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="C18" s="14">
         <v>3</v>
@@ -2914,7 +2907,7 @@
     <row r="19" spans="1:12">
       <c r="A19" s="14"/>
       <c r="B19" s="14" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="C19" s="14" t="s">
         <v>95</v>
@@ -2938,7 +2931,7 @@
     <row r="20" spans="1:12">
       <c r="A20" s="14"/>
       <c r="B20" s="14" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="C20" s="14">
         <v>64</v>
@@ -2951,7 +2944,7 @@
         <v>102</v>
       </c>
       <c r="G20" s="14" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="H20" s="14"/>
       <c r="I20" s="14"/>
@@ -2962,7 +2955,7 @@
     <row r="21" spans="1:12">
       <c r="A21" s="14"/>
       <c r="B21" s="14" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="C21" s="14">
         <v>20</v>
@@ -2975,7 +2968,7 @@
         <v>102</v>
       </c>
       <c r="G21" s="14" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="H21" s="14"/>
       <c r="I21" s="14"/>
@@ -2986,7 +2979,7 @@
     <row r="22" spans="1:12">
       <c r="A22" s="14"/>
       <c r="B22" s="14" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="C22" s="17" t="s">
         <v>109</v>
@@ -3034,7 +3027,7 @@
     <row r="24" spans="1:12">
       <c r="A24" s="14"/>
       <c r="B24" s="16" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="C24" s="11">
         <v>1</v>
@@ -3056,7 +3049,7 @@
     <row r="25" spans="1:12" s="19" customFormat="1">
       <c r="A25" s="16"/>
       <c r="B25" s="16" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="C25" s="11">
         <v>10000</v>
@@ -3360,7 +3353,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F64"/>
+  <dimension ref="A1:F67"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="26" style="10" bestFit="1" customWidth="1"/>
@@ -3385,10 +3378,10 @@
         <v>119</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="D2" s="5" t="s">
         <v>1</v>
@@ -3398,13 +3391,13 @@
     </row>
     <row r="3" spans="1:6" ht="36">
       <c r="A3" s="9" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>232</v>
+        <v>223</v>
       </c>
       <c r="D3" s="9"/>
       <c r="E3" s="4"/>
@@ -3412,14 +3405,14 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="9" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="9" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="E4" s="4"/>
       <c r="F4" s="4"/>
@@ -3434,30 +3427,30 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="9" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>237</v>
+        <v>228</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>240</v>
+        <v>231</v>
       </c>
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="9" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="B7" s="4"/>
       <c r="C7" s="9" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>241</v>
+        <v>232</v>
       </c>
       <c r="E7" s="4"/>
       <c r="F7" s="4"/>
@@ -3472,13 +3465,13 @@
     </row>
     <row r="9" spans="1:6" ht="48">
       <c r="A9" s="9" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="D9" s="9"/>
       <c r="E9" s="4"/>
@@ -3486,14 +3479,14 @@
     </row>
     <row r="10" spans="1:6" ht="24">
       <c r="A10" s="9" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="B10" s="4"/>
       <c r="C10" s="9" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="E10" s="4"/>
       <c r="F10" s="4"/>
@@ -3501,7 +3494,7 @@
     <row r="11" spans="1:6">
       <c r="A11" s="9"/>
       <c r="B11" s="4" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="C11" s="9"/>
       <c r="D11" s="9"/>
@@ -3510,13 +3503,13 @@
     </row>
     <row r="12" spans="1:6" ht="48">
       <c r="A12" s="9" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>231</v>
+        <v>222</v>
       </c>
       <c r="D12" s="9"/>
       <c r="E12" s="4"/>
@@ -3524,11 +3517,11 @@
     </row>
     <row r="13" spans="1:6" ht="24">
       <c r="A13" s="9" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B13" s="4"/>
       <c r="C13" s="9" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="D13" s="9"/>
       <c r="E13" s="4"/>
@@ -3537,7 +3530,7 @@
     <row r="14" spans="1:6">
       <c r="A14" s="9"/>
       <c r="B14" s="4" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="C14" s="9"/>
       <c r="D14" s="9"/>
@@ -3546,13 +3539,13 @@
     </row>
     <row r="15" spans="1:6" ht="60">
       <c r="A15" s="9" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="D15" s="9"/>
       <c r="E15" s="4"/>
@@ -3560,11 +3553,11 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="9" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="B16" s="4"/>
       <c r="C16" s="9" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="D16" s="9"/>
       <c r="E16" s="4"/>
@@ -3573,7 +3566,7 @@
     <row r="17" spans="1:6">
       <c r="A17" s="9"/>
       <c r="B17" s="4" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="C17" s="9"/>
       <c r="D17" s="9"/>
@@ -3582,30 +3575,30 @@
     </row>
     <row r="18" spans="1:6" ht="27">
       <c r="A18" s="9" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>233</v>
+        <v>224</v>
       </c>
       <c r="D18" s="25" t="s">
-        <v>234</v>
+        <v>225</v>
       </c>
       <c r="E18" s="4"/>
       <c r="F18" s="4"/>
     </row>
     <row r="19" spans="1:6" ht="24">
       <c r="A19" s="9" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="B19" s="4"/>
       <c r="C19" s="9" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>235</v>
+        <v>226</v>
       </c>
       <c r="E19" s="4"/>
       <c r="F19" s="4"/>
@@ -3613,7 +3606,7 @@
     <row r="20" spans="1:6">
       <c r="A20" s="9"/>
       <c r="B20" s="4" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="C20" s="9"/>
       <c r="D20" s="9"/>
@@ -3622,28 +3615,28 @@
     </row>
     <row r="21" spans="1:6" ht="24">
       <c r="A21" s="9" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>236</v>
+        <v>227</v>
       </c>
       <c r="C21" s="9"/>
       <c r="D21" s="9" t="s">
-        <v>238</v>
+        <v>229</v>
       </c>
       <c r="E21" s="4"/>
       <c r="F21" s="4"/>
     </row>
     <row r="22" spans="1:6" ht="48">
       <c r="A22" s="9" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="B22" s="4"/>
       <c r="C22" s="9" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>239</v>
+        <v>230</v>
       </c>
       <c r="E22" s="4"/>
       <c r="F22" s="4"/>
@@ -3651,7 +3644,7 @@
     <row r="23" spans="1:6">
       <c r="A23" s="9"/>
       <c r="B23" s="4" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="C23" s="9"/>
       <c r="D23" s="9"/>
@@ -3660,13 +3653,13 @@
     </row>
     <row r="24" spans="1:6">
       <c r="A24" s="9" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="D24" s="9"/>
       <c r="E24" s="4"/>
@@ -3674,14 +3667,14 @@
     </row>
     <row r="25" spans="1:6" ht="84">
       <c r="A25" s="9" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B25" s="4"/>
       <c r="C25" s="9" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="E25" s="4"/>
       <c r="F25" s="4"/>
@@ -3689,7 +3682,7 @@
     <row r="26" spans="1:6">
       <c r="A26" s="9"/>
       <c r="B26" s="4" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="C26" s="9"/>
       <c r="D26" s="9"/>
@@ -3698,30 +3691,30 @@
     </row>
     <row r="27" spans="1:6" ht="120">
       <c r="A27" s="9" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="E27" s="4"/>
       <c r="F27" s="4"/>
     </row>
     <row r="28" spans="1:6" ht="132">
       <c r="A28" s="9" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="B28" s="4"/>
       <c r="C28" s="9" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="E28" s="4"/>
       <c r="F28" s="4"/>
@@ -3729,47 +3722,33 @@
     <row r="29" spans="1:6">
       <c r="A29" s="9"/>
       <c r="B29" s="4" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="C29" s="9"/>
       <c r="D29" s="9"/>
       <c r="E29" s="4"/>
       <c r="F29" s="4"/>
     </row>
-    <row r="30" spans="1:6" ht="156">
-      <c r="A30" s="9" t="s">
-        <v>120</v>
-      </c>
-      <c r="B30" s="4" t="s">
-        <v>217</v>
-      </c>
-      <c r="C30" s="9" t="s">
-        <v>226</v>
-      </c>
-      <c r="D30" s="9" t="s">
-        <v>228</v>
-      </c>
+    <row r="30" spans="1:6">
+      <c r="A30" s="9"/>
+      <c r="B30" s="4"/>
+      <c r="C30" s="9"/>
+      <c r="D30" s="9"/>
       <c r="E30" s="4"/>
       <c r="F30" s="4"/>
     </row>
     <row r="31" spans="1:6">
-      <c r="A31" s="9" t="s">
-        <v>121</v>
-      </c>
+      <c r="A31" s="9"/>
       <c r="B31" s="4"/>
-      <c r="C31" s="11" t="s">
-        <v>151</v>
-      </c>
-      <c r="D31" s="9" t="s">
-        <v>122</v>
-      </c>
+      <c r="C31" s="11"/>
+      <c r="D31" s="9"/>
       <c r="E31" s="4"/>
       <c r="F31" s="4"/>
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="9"/>
       <c r="B32" s="4" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="C32" s="9"/>
       <c r="D32" s="9"/>
@@ -3778,39 +3757,37 @@
     </row>
     <row r="33" spans="1:6" ht="144">
       <c r="A33" s="9" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="E33" s="4"/>
       <c r="F33" s="4"/>
     </row>
     <row r="34" spans="1:6">
       <c r="A34" s="9" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="B34" s="4"/>
       <c r="C34" s="9" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="E34" s="4"/>
       <c r="F34" s="4"/>
     </row>
     <row r="35" spans="1:6">
       <c r="A35" s="9"/>
-      <c r="B35" s="4" t="s">
-        <v>136</v>
-      </c>
+      <c r="B35" s="4"/>
       <c r="C35" s="9"/>
       <c r="D35" s="9"/>
       <c r="E35" s="4"/>
@@ -3818,27 +3795,25 @@
     </row>
     <row r="36" spans="1:6">
       <c r="A36" s="9" t="s">
-        <v>146</v>
+        <v>235</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>148</v>
+        <v>237</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>197</v>
+        <v>236</v>
       </c>
       <c r="D36" s="9"/>
       <c r="E36" s="4"/>
       <c r="F36" s="4"/>
     </row>
-    <row r="37" spans="1:6">
+    <row r="37" spans="1:6" ht="84">
       <c r="A37" s="9" t="s">
-        <v>147</v>
-      </c>
-      <c r="B37" s="4" t="s">
-        <v>149</v>
-      </c>
+        <v>238</v>
+      </c>
+      <c r="B37" s="4"/>
       <c r="C37" s="9" t="s">
-        <v>198</v>
+        <v>239</v>
       </c>
       <c r="D37" s="9"/>
       <c r="E37" s="4"/>
@@ -3846,7 +3821,9 @@
     </row>
     <row r="38" spans="1:6">
       <c r="A38" s="9"/>
-      <c r="B38" s="4"/>
+      <c r="B38" s="4" t="s">
+        <v>133</v>
+      </c>
       <c r="C38" s="9"/>
       <c r="D38" s="9"/>
       <c r="E38" s="4"/>
@@ -3854,149 +3831,149 @@
     </row>
     <row r="39" spans="1:6">
       <c r="A39" s="9" t="s">
-        <v>165</v>
-      </c>
-      <c r="B39" s="4"/>
+        <v>143</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>145</v>
+      </c>
       <c r="C39" s="9" t="s">
-        <v>163</v>
+        <v>193</v>
       </c>
       <c r="D39" s="9"/>
       <c r="E39" s="4"/>
       <c r="F39" s="4"/>
     </row>
-    <row r="40" spans="1:6" ht="24">
+    <row r="40" spans="1:6">
       <c r="A40" s="9" t="s">
-        <v>166</v>
-      </c>
-      <c r="B40" s="4"/>
+        <v>144</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>146</v>
+      </c>
       <c r="C40" s="9" t="s">
-        <v>164</v>
-      </c>
-      <c r="D40" s="9" t="s">
-        <v>153</v>
-      </c>
+        <v>194</v>
+      </c>
+      <c r="D40" s="9"/>
       <c r="E40" s="4"/>
       <c r="F40" s="4"/>
     </row>
-    <row r="41" spans="1:6" ht="24">
-      <c r="A41" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="B41" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="C41" s="9" t="s">
-        <v>162</v>
-      </c>
+    <row r="41" spans="1:6">
+      <c r="A41" s="9"/>
+      <c r="B41" s="4"/>
+      <c r="C41" s="9"/>
       <c r="D41" s="9"/>
       <c r="E41" s="4"/>
       <c r="F41" s="4"/>
     </row>
-    <row r="42" spans="1:6" ht="60">
+    <row r="42" spans="1:6">
       <c r="A42" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="B42" s="4" t="s">
-        <v>168</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="B42" s="4"/>
       <c r="C42" s="9" t="s">
-        <v>171</v>
-      </c>
-      <c r="D42" s="9" t="s">
-        <v>172</v>
-      </c>
+        <v>159</v>
+      </c>
+      <c r="D42" s="9"/>
       <c r="E42" s="4"/>
       <c r="F42" s="4"/>
     </row>
-    <row r="43" spans="1:6" ht="48">
+    <row r="43" spans="1:6" ht="24">
       <c r="A43" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="B43" s="4" t="s">
-        <v>168</v>
-      </c>
+        <v>162</v>
+      </c>
+      <c r="B43" s="4"/>
       <c r="C43" s="9" t="s">
-        <v>170</v>
-      </c>
-      <c r="D43" s="9"/>
+        <v>160</v>
+      </c>
+      <c r="D43" s="9" t="s">
+        <v>149</v>
+      </c>
       <c r="E43" s="4"/>
       <c r="F43" s="4"/>
     </row>
-    <row r="44" spans="1:6" s="23" customFormat="1">
-      <c r="A44" s="22" t="s">
-        <v>156</v>
-      </c>
-      <c r="B44" s="21"/>
-      <c r="C44" s="22"/>
-      <c r="D44" s="22" t="s">
-        <v>154</v>
-      </c>
-      <c r="E44" s="21"/>
-      <c r="F44" s="21"/>
-    </row>
-    <row r="45" spans="1:6">
+    <row r="44" spans="1:6" ht="24">
+      <c r="A44" s="9" t="s">
+        <v>157</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="C44" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="D44" s="9"/>
+      <c r="E44" s="4"/>
+      <c r="F44" s="4"/>
+    </row>
+    <row r="45" spans="1:6" ht="60">
       <c r="A45" s="9" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>190</v>
+        <v>164</v>
       </c>
       <c r="C45" s="9" t="s">
-        <v>150</v>
-      </c>
-      <c r="D45" s="9"/>
+        <v>167</v>
+      </c>
+      <c r="D45" s="9" t="s">
+        <v>168</v>
+      </c>
       <c r="E45" s="4"/>
       <c r="F45" s="4"/>
     </row>
-    <row r="46" spans="1:6" ht="24">
+    <row r="46" spans="1:6" ht="48">
       <c r="A46" s="9" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
       <c r="C46" s="9" t="s">
-        <v>177</v>
-      </c>
-      <c r="D46" s="9" t="s">
-        <v>159</v>
-      </c>
+        <v>166</v>
+      </c>
+      <c r="D46" s="9"/>
       <c r="E46" s="4"/>
       <c r="F46" s="4"/>
     </row>
-    <row r="47" spans="1:6">
-      <c r="A47" s="9"/>
-      <c r="B47" s="4"/>
-      <c r="C47" s="9"/>
-      <c r="D47" s="9"/>
-      <c r="E47" s="4"/>
-      <c r="F47" s="4"/>
+    <row r="47" spans="1:6" s="23" customFormat="1">
+      <c r="A47" s="22" t="s">
+        <v>152</v>
+      </c>
+      <c r="B47" s="21"/>
+      <c r="C47" s="22"/>
+      <c r="D47" s="22" t="s">
+        <v>150</v>
+      </c>
+      <c r="E47" s="21"/>
+      <c r="F47" s="21"/>
     </row>
     <row r="48" spans="1:6">
       <c r="A48" s="9" t="s">
-        <v>173</v>
+        <v>153</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C48" s="9" t="s">
-        <v>189</v>
+        <v>147</v>
       </c>
       <c r="D48" s="9"/>
       <c r="E48" s="4"/>
       <c r="F48" s="4"/>
     </row>
-    <row r="49" spans="1:6">
+    <row r="49" spans="1:6" ht="24">
       <c r="A49" s="9" t="s">
-        <v>175</v>
+        <v>154</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="C49" s="9" t="s">
-        <v>164</v>
-      </c>
-      <c r="D49" s="9"/>
+        <v>173</v>
+      </c>
+      <c r="D49" s="9" t="s">
+        <v>155</v>
+      </c>
       <c r="E49" s="4"/>
       <c r="F49" s="4"/>
     </row>
@@ -4009,17 +3986,29 @@
       <c r="F50" s="4"/>
     </row>
     <row r="51" spans="1:6">
-      <c r="A51" s="9"/>
-      <c r="B51" s="4"/>
-      <c r="C51" s="9"/>
+      <c r="A51" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="C51" s="9" t="s">
+        <v>185</v>
+      </c>
       <c r="D51" s="9"/>
       <c r="E51" s="4"/>
       <c r="F51" s="4"/>
     </row>
     <row r="52" spans="1:6">
-      <c r="A52" s="9"/>
-      <c r="B52" s="4"/>
-      <c r="C52" s="9"/>
+      <c r="A52" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="C52" s="9" t="s">
+        <v>160</v>
+      </c>
       <c r="D52" s="9"/>
       <c r="E52" s="4"/>
       <c r="F52" s="4"/>
@@ -4119,6 +4108,30 @@
       <c r="D64" s="9"/>
       <c r="E64" s="4"/>
       <c r="F64" s="4"/>
+    </row>
+    <row r="65" spans="1:6">
+      <c r="A65" s="9"/>
+      <c r="B65" s="4"/>
+      <c r="C65" s="9"/>
+      <c r="D65" s="9"/>
+      <c r="E65" s="4"/>
+      <c r="F65" s="4"/>
+    </row>
+    <row r="66" spans="1:6">
+      <c r="A66" s="9"/>
+      <c r="B66" s="4"/>
+      <c r="C66" s="9"/>
+      <c r="D66" s="9"/>
+      <c r="E66" s="4"/>
+      <c r="F66" s="4"/>
+    </row>
+    <row r="67" spans="1:6">
+      <c r="A67" s="9"/>
+      <c r="B67" s="4"/>
+      <c r="C67" s="9"/>
+      <c r="D67" s="9"/>
+      <c r="E67" s="4"/>
+      <c r="F67" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -4139,18 +4152,18 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="B1" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="40.5">
       <c r="B8" s="25" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="C8" s="26" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
     </row>
   </sheetData>

--- a/internal_doc/03.开发设计/OM_web接口.xlsx
+++ b/internal_doc/03.开发设计/OM_web接口.xlsx
@@ -279,7 +279,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="240">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="241">
   <si>
     <t>需求</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1215,10 +1215,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>http://192.168.20.197:11814/?cmd=ConfigBusinessReq&amp;TemplateInfo={"ClusterName":"c1","BusinessType":"sequoiadb","BusinessName":"b1","ClusterType":"standalone","Property":[{"Name":"replica_num","Value":"1"},{"Name":"data_group_num","Value":"1"},{"Name":"catalog_num","Value":"1"},{"Name":"coord_num","Value":"1"},{"Name":"user_name","Value":"sdbadmin"},{"Name":"user_passwd","Value":"sdbadmin"},{"Name":"user_group","Value":"sdbadmin_group"}],"HostInfo":[{"HostName":"host1"}]}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>"Config": [ { "HostName": "host1", "username": "sdbadmin", "userpasswd": "sdbadmin", "usergroup": "sdbadmin_group", "datagroupname": "", "dbpath": "/home/db2//standalone/11830", "svcname": "11830", ...} ],"BusinessName": "b1", "BusinessType": "sequoiadb", "ClusterType": "standalone","ClusterName": "c1","Property": [ { "Name": "username", "Type": "string", "Default": "sdbadmin", "Valid": "", "Display": "edit box", "Edit": "true", "Desc": "", "Level": "0", "WebName": "user_name",... }]</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1284,10 +1280,6 @@
   </si>
   <si>
     <t>查询安装进度</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"TaskID":"asd"}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1301,6 +1293,18 @@
   <si>
     <t>{"rc":0, "Detail":"","TaskID":"asd", "isAllFinish":true,"Progress":[{"Name":"Coord","TotalCount":7 "InstalledCount":100, "Desc":""}, {"Name":"Group1","TotalCount":3,"InstalledCount":50,"Desc":""},
 {"Name":"Group2","TotalCount":4,"InstalledCount":50,"Desc":""} ...]}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"TaskID":"asd"}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://192.168.20.197:11814/?cmd=ConfigBusinessReq&amp;TemplateInfo={"ClusterName":"c1","BusinessType":"sequoiadb","BusinessName":"b1","ClusterType":"standalone","Property":[{"Name":"replica_num","Value":"1"},{"Name":"data_group_num","Value":"1"},{"Name":"catalog_num","Value":"1"},{"Name":"coord_num","Value":"1"}],"HostInfo":[{"HostName":"host1"}]}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://192.168.20.197:11814/?cmd=QueryInstallProgress&amp;Task={"TaskID":"ad"}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3397,7 +3401,7 @@
         <v>181</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D3" s="9"/>
       <c r="E3" s="4"/>
@@ -3430,13 +3434,13 @@
         <v>174</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C6" s="9" t="s">
         <v>176</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
@@ -3450,7 +3454,7 @@
         <v>191</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E7" s="4"/>
       <c r="F7" s="4"/>
@@ -3509,7 +3513,7 @@
         <v>189</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D12" s="9"/>
       <c r="E12" s="4"/>
@@ -3581,10 +3585,10 @@
         <v>215</v>
       </c>
       <c r="C18" s="9" t="s">
+        <v>223</v>
+      </c>
+      <c r="D18" s="25" t="s">
         <v>224</v>
-      </c>
-      <c r="D18" s="25" t="s">
-        <v>225</v>
       </c>
       <c r="E18" s="4"/>
       <c r="F18" s="4"/>
@@ -3598,7 +3602,7 @@
         <v>192</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E19" s="4"/>
       <c r="F19" s="4"/>
@@ -3618,11 +3622,11 @@
         <v>135</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C21" s="9"/>
       <c r="D21" s="9" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E21" s="4"/>
       <c r="F21" s="4"/>
@@ -3636,7 +3640,7 @@
         <v>195</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E22" s="4"/>
       <c r="F22" s="4"/>
@@ -3689,7 +3693,7 @@
       <c r="E26" s="4"/>
       <c r="F26" s="4"/>
     </row>
-    <row r="27" spans="1:6" ht="120">
+    <row r="27" spans="1:6" ht="96">
       <c r="A27" s="9" t="s">
         <v>139</v>
       </c>
@@ -3700,7 +3704,7 @@
         <v>217</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>218</v>
+        <v>239</v>
       </c>
       <c r="E27" s="4"/>
       <c r="F27" s="4"/>
@@ -3711,10 +3715,10 @@
       </c>
       <c r="B28" s="4"/>
       <c r="C28" s="9" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E28" s="4"/>
       <c r="F28" s="4"/>
@@ -3760,13 +3764,13 @@
         <v>141</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E33" s="4"/>
       <c r="F33" s="4"/>
@@ -3793,27 +3797,29 @@
       <c r="E35" s="4"/>
       <c r="F35" s="4"/>
     </row>
-    <row r="36" spans="1:6">
+    <row r="36" spans="1:6" ht="24">
       <c r="A36" s="9" t="s">
+        <v>234</v>
+      </c>
+      <c r="B36" s="4" t="s">
         <v>235</v>
       </c>
-      <c r="B36" s="4" t="s">
-        <v>237</v>
-      </c>
       <c r="C36" s="9" t="s">
-        <v>236</v>
-      </c>
-      <c r="D36" s="9"/>
+        <v>238</v>
+      </c>
+      <c r="D36" s="9" t="s">
+        <v>240</v>
+      </c>
       <c r="E36" s="4"/>
       <c r="F36" s="4"/>
     </row>
     <row r="37" spans="1:6" ht="84">
       <c r="A37" s="9" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="B37" s="4"/>
       <c r="C37" s="9" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D37" s="9"/>
       <c r="E37" s="4"/>

--- a/internal_doc/03.开发设计/OM_web接口.xlsx
+++ b/internal_doc/03.开发设计/OM_web接口.xlsx
@@ -279,7 +279,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="241">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="239">
   <si>
     <t>需求</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -970,15 +970,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>check_session_res</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>登陆命令响应</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>login_res</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1015,10 +1007,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>CreateClusterReq</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>{ClusterName, rc}</t>
   </si>
   <si>
@@ -1026,31 +1014,12 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>LoginReq</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>User=xx&amp;Passwd=xx&amp;Timestamp=xx</t>
   </si>
   <si>
-    <t>CheckSessionReq</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ScanHostReq</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>HostInfo={ClusterName:cls1,HostInfo:[{IP/HostName:xxx, User:xxx, Passwd:xxx, SshPort:xxx, AgentPort:xxx}, ...],User:usr1,Passwd:Passwd1, SshPort:xxx, AgentPort:xxx}</t>
   </si>
   <si>
-    <t>CheckHostReq</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>AddHostReq</t>
-  </si>
-  <si>
     <t>{ClusterName:xxx, desc:xxx}</t>
   </si>
   <si>
@@ -1066,14 +1035,7 @@
     <t>{BusinessList:[{BusinessType, BusinessDesc},...]}</t>
   </si>
   <si>
-    <t>QueryBusinessTemplateReq</t>
-  </si>
-  <si>
     <t>BusinessType=xxx</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ConfigBusinessReq</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1141,10 +1103,6 @@
   </si>
   <si>
     <t>rc=ok</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>QueryHostReq</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1247,14 +1205,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>QueryBusinessListReq</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>QueryClusterReq</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>http://192.168.20.197:11814/?cmd=QueryBusinessListReq</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1275,15 +1225,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>AddBusinessReq</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>查询安装进度</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>QueryInstallProgress</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1305,6 +1247,58 @@
   </si>
   <si>
     <t>http://192.168.20.197:11814/?cmd=QueryInstallProgress&amp;Task={"TaskID":"ad"}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>create cluster</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>query cluster</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>login</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>check session</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>scan host</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>check host</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>add host</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>query host</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>query business list</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>query business template</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>config business</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>add business</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>query install progress</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2799,7 +2793,7 @@
     <row r="14" spans="1:12">
       <c r="A14" s="14"/>
       <c r="B14" s="14" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="C14" s="14">
         <v>11811</v>
@@ -2821,7 +2815,7 @@
     <row r="15" spans="1:12">
       <c r="A15" s="14"/>
       <c r="B15" s="14" t="s">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="C15" s="14">
         <v>11812</v>
@@ -2843,7 +2837,7 @@
     <row r="16" spans="1:12">
       <c r="A16" s="14"/>
       <c r="B16" s="14" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="C16" s="14">
         <v>11813</v>
@@ -2865,7 +2859,7 @@
     <row r="17" spans="1:12">
       <c r="A17" s="14"/>
       <c r="B17" s="14" t="s">
-        <v>202</v>
+        <v>192</v>
       </c>
       <c r="C17" s="14">
         <v>11814</v>
@@ -2887,7 +2881,7 @@
     <row r="18" spans="1:12">
       <c r="A18" s="14"/>
       <c r="B18" s="14" t="s">
-        <v>203</v>
+        <v>193</v>
       </c>
       <c r="C18" s="14">
         <v>3</v>
@@ -2911,7 +2905,7 @@
     <row r="19" spans="1:12">
       <c r="A19" s="14"/>
       <c r="B19" s="14" t="s">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="C19" s="14" t="s">
         <v>95</v>
@@ -2935,7 +2929,7 @@
     <row r="20" spans="1:12">
       <c r="A20" s="14"/>
       <c r="B20" s="14" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
       <c r="C20" s="14">
         <v>64</v>
@@ -2948,7 +2942,7 @@
         <v>102</v>
       </c>
       <c r="G20" s="14" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="H20" s="14"/>
       <c r="I20" s="14"/>
@@ -2959,7 +2953,7 @@
     <row r="21" spans="1:12">
       <c r="A21" s="14"/>
       <c r="B21" s="14" t="s">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="C21" s="14">
         <v>20</v>
@@ -2972,7 +2966,7 @@
         <v>102</v>
       </c>
       <c r="G21" s="14" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H21" s="14"/>
       <c r="I21" s="14"/>
@@ -2983,7 +2977,7 @@
     <row r="22" spans="1:12">
       <c r="A22" s="14"/>
       <c r="B22" s="14" t="s">
-        <v>207</v>
+        <v>197</v>
       </c>
       <c r="C22" s="17" t="s">
         <v>109</v>
@@ -3031,7 +3025,7 @@
     <row r="24" spans="1:12">
       <c r="A24" s="14"/>
       <c r="B24" s="16" t="s">
-        <v>208</v>
+        <v>198</v>
       </c>
       <c r="C24" s="11">
         <v>1</v>
@@ -3053,7 +3047,7 @@
     <row r="25" spans="1:12" s="19" customFormat="1">
       <c r="A25" s="16"/>
       <c r="B25" s="16" t="s">
-        <v>209</v>
+        <v>199</v>
       </c>
       <c r="C25" s="11">
         <v>10000</v>
@@ -3398,10 +3392,10 @@
         <v>156</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>181</v>
+        <v>226</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>222</v>
+        <v>211</v>
       </c>
       <c r="D3" s="9"/>
       <c r="E3" s="4"/>
@@ -3413,7 +3407,7 @@
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="9" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="D4" s="9" t="s">
         <v>130</v>
@@ -3431,30 +3425,30 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="9" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>227</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>230</v>
+        <v>217</v>
       </c>
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="9" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B7" s="4"/>
       <c r="C7" s="9" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>231</v>
+        <v>218</v>
       </c>
       <c r="E7" s="4"/>
       <c r="F7" s="4"/>
@@ -3472,10 +3466,10 @@
         <v>122</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>187</v>
+        <v>230</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="D9" s="9"/>
       <c r="E9" s="4"/>
@@ -3487,10 +3481,10 @@
       </c>
       <c r="B10" s="4"/>
       <c r="C10" s="9" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>214</v>
+        <v>204</v>
       </c>
       <c r="E10" s="4"/>
       <c r="F10" s="4"/>
@@ -3510,10 +3504,10 @@
         <v>124</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>189</v>
+        <v>231</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>221</v>
+        <v>210</v>
       </c>
       <c r="D12" s="9"/>
       <c r="E12" s="4"/>
@@ -3525,7 +3519,7 @@
       </c>
       <c r="B13" s="4"/>
       <c r="C13" s="9" t="s">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="D13" s="9"/>
       <c r="E13" s="4"/>
@@ -3546,10 +3540,10 @@
         <v>126</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>190</v>
+        <v>232</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>216</v>
+        <v>205</v>
       </c>
       <c r="D15" s="9"/>
       <c r="E15" s="4"/>
@@ -3561,7 +3555,7 @@
       </c>
       <c r="B16" s="4"/>
       <c r="C16" s="9" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="D16" s="9"/>
       <c r="E16" s="4"/>
@@ -3582,13 +3576,13 @@
         <v>128</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>215</v>
+        <v>233</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>223</v>
+        <v>212</v>
       </c>
       <c r="D18" s="25" t="s">
-        <v>224</v>
+        <v>213</v>
       </c>
       <c r="E18" s="4"/>
       <c r="F18" s="4"/>
@@ -3599,10 +3593,10 @@
       </c>
       <c r="B19" s="4"/>
       <c r="C19" s="9" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>225</v>
+        <v>214</v>
       </c>
       <c r="E19" s="4"/>
       <c r="F19" s="4"/>
@@ -3622,11 +3616,11 @@
         <v>135</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="C21" s="9"/>
       <c r="D21" s="9" t="s">
-        <v>228</v>
+        <v>215</v>
       </c>
       <c r="E21" s="4"/>
       <c r="F21" s="4"/>
@@ -3637,10 +3631,10 @@
       </c>
       <c r="B22" s="4"/>
       <c r="C22" s="9" t="s">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>229</v>
+        <v>216</v>
       </c>
       <c r="E22" s="4"/>
       <c r="F22" s="4"/>
@@ -3660,10 +3654,10 @@
         <v>137</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>196</v>
+        <v>235</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>197</v>
+        <v>188</v>
       </c>
       <c r="D24" s="9"/>
       <c r="E24" s="4"/>
@@ -3675,10 +3669,10 @@
       </c>
       <c r="B25" s="4"/>
       <c r="C25" s="9" t="s">
-        <v>212</v>
+        <v>202</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>211</v>
+        <v>201</v>
       </c>
       <c r="E25" s="4"/>
       <c r="F25" s="4"/>
@@ -3698,13 +3692,13 @@
         <v>139</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>198</v>
+        <v>236</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>217</v>
+        <v>206</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>239</v>
+        <v>224</v>
       </c>
       <c r="E27" s="4"/>
       <c r="F27" s="4"/>
@@ -3715,10 +3709,10 @@
       </c>
       <c r="B28" s="4"/>
       <c r="C28" s="9" t="s">
-        <v>219</v>
+        <v>208</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="E28" s="4"/>
       <c r="F28" s="4"/>
@@ -3764,13 +3758,13 @@
         <v>141</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>232</v>
+        <v>219</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>220</v>
+        <v>209</v>
       </c>
       <c r="E33" s="4"/>
       <c r="F33" s="4"/>
@@ -3799,27 +3793,27 @@
     </row>
     <row r="36" spans="1:6" ht="24">
       <c r="A36" s="9" t="s">
-        <v>234</v>
+        <v>220</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>238</v>
+        <v>223</v>
       </c>
       <c r="D36" s="9" t="s">
-        <v>240</v>
+        <v>225</v>
       </c>
       <c r="E36" s="4"/>
       <c r="F36" s="4"/>
     </row>
     <row r="37" spans="1:6" ht="84">
       <c r="A37" s="9" t="s">
-        <v>236</v>
+        <v>221</v>
       </c>
       <c r="B37" s="4"/>
       <c r="C37" s="9" t="s">
-        <v>237</v>
+        <v>222</v>
       </c>
       <c r="D37" s="9"/>
       <c r="E37" s="4"/>
@@ -3843,7 +3837,7 @@
         <v>145</v>
       </c>
       <c r="C39" s="9" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="D39" s="9"/>
       <c r="E39" s="4"/>
@@ -3857,7 +3851,7 @@
         <v>146</v>
       </c>
       <c r="C40" s="9" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="D40" s="9"/>
       <c r="E40" s="4"/>
@@ -3958,7 +3952,7 @@
         <v>153</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>186</v>
+        <v>229</v>
       </c>
       <c r="C48" s="9" t="s">
         <v>147</v>
@@ -3971,11 +3965,9 @@
       <c r="A49" s="9" t="s">
         <v>154</v>
       </c>
-      <c r="B49" s="4" t="s">
-        <v>170</v>
-      </c>
+      <c r="B49" s="4"/>
       <c r="C49" s="9" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D49" s="9" t="s">
         <v>155</v>
@@ -3996,10 +3988,10 @@
         <v>169</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>184</v>
+        <v>228</v>
       </c>
       <c r="C51" s="9" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="D51" s="9"/>
       <c r="E51" s="4"/>
@@ -4007,11 +3999,9 @@
     </row>
     <row r="52" spans="1:6">
       <c r="A52" s="9" t="s">
-        <v>171</v>
-      </c>
-      <c r="B52" s="4" t="s">
-        <v>172</v>
-      </c>
+        <v>170</v>
+      </c>
+      <c r="B52" s="4"/>
       <c r="C52" s="9" t="s">
         <v>160</v>
       </c>
@@ -4166,10 +4156,10 @@
     </row>
     <row r="8" spans="1:3" ht="40.5">
       <c r="B8" s="25" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C8" s="26" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
   </sheetData>

--- a/internal_doc/03.开发设计/OM_web接口.xlsx
+++ b/internal_doc/03.开发设计/OM_web接口.xlsx
@@ -279,7 +279,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="239">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="243">
   <si>
     <t>需求</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1012,9 +1012,6 @@
   <si>
     <t>{ClusterName, rc}</t>
     <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>User=xx&amp;Passwd=xx&amp;Timestamp=xx</t>
   </si>
   <si>
     <t>HostInfo={ClusterName:cls1,HostInfo:[{IP/HostName:xxx, User:xxx, Passwd:xxx, SshPort:xxx, AgentPort:xxx}, ...],User:usr1,Passwd:Passwd1, SshPort:xxx, AgentPort:xxx}</t>
@@ -1233,72 +1230,92 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>{"rc":0, "Detail":"","TaskID":"asd", "isAllFinish":true,"Progress":[{"Name":"Coord","TotalCount":7 "InstalledCount":100, "Desc":""}, {"Name":"Group1","TotalCount":3,"InstalledCount":50,"Desc":""},
+    <t>{"TaskID":"asd"}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://192.168.20.197:11814/?cmd=ConfigBusinessReq&amp;TemplateInfo={"ClusterName":"c1","BusinessType":"sequoiadb","BusinessName":"b1","ClusterType":"standalone","Property":[{"Name":"replica_num","Value":"1"},{"Name":"data_group_num","Value":"1"},{"Name":"catalog_num","Value":"1"},{"Name":"coord_num","Value":"1"}],"HostInfo":[{"HostName":"host1"}]}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://192.168.20.197:11814/?cmd=QueryInstallProgress&amp;Task={"TaskID":"ad"}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>create cluster</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>query cluster</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>login</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>check session</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>scan host</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>check host</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>add host</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>query host</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>query business list</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>query business template</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>config business</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>add business</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>query install progress</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"rc":0, "Detail":"","TaskID":"asd", "isFinish":true,"Status":"install/rollback","Progress":[{"Name":"Coord","TotalCount":7 "InstalledCount":100, "Desc":""}, {"Name":"Group1","TotalCount":3,"InstalledCount":50,"Desc":""},
 {"Name":"Group2","TotalCount":4,"InstalledCount":50,"Desc":""} ...]}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>{"TaskID":"asd"}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>http://192.168.20.197:11814/?cmd=ConfigBusinessReq&amp;TemplateInfo={"ClusterName":"c1","BusinessType":"sequoiadb","BusinessName":"b1","ClusterType":"standalone","Property":[{"Name":"replica_num","Value":"1"},{"Name":"data_group_num","Value":"1"},{"Name":"catalog_num","Value":"1"},{"Name":"coord_num","Value":"1"}],"HostInfo":[{"HostName":"host1"}]}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>http://192.168.20.197:11814/?cmd=QueryInstallProgress&amp;Task={"TaskID":"ad"}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>create cluster</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>query cluster</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>login</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>check session</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>scan host</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>check host</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>add host</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>query host</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>query business list</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>query business template</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>config business</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>add business</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>query install progress</t>
+    <t>修改密码</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>change passwd</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>User=xx&amp;Passwd=xx&amp;Timestamp=xx</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>User=admin&amp;Passwd=admin&amp;Newpasswd=admin&amp;Timestamp=123</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://192.168.20.197:11814/?cmd=change passwd&amp;user=admin&amp;passwd=admin&amp;Newpasswd=admin&amp;Timestamp=123</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2793,7 +2810,7 @@
     <row r="14" spans="1:12">
       <c r="A14" s="14"/>
       <c r="B14" s="14" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C14" s="14">
         <v>11811</v>
@@ -2815,7 +2832,7 @@
     <row r="15" spans="1:12">
       <c r="A15" s="14"/>
       <c r="B15" s="14" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C15" s="14">
         <v>11812</v>
@@ -2837,7 +2854,7 @@
     <row r="16" spans="1:12">
       <c r="A16" s="14"/>
       <c r="B16" s="14" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C16" s="14">
         <v>11813</v>
@@ -2859,7 +2876,7 @@
     <row r="17" spans="1:12">
       <c r="A17" s="14"/>
       <c r="B17" s="14" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C17" s="14">
         <v>11814</v>
@@ -2881,7 +2898,7 @@
     <row r="18" spans="1:12">
       <c r="A18" s="14"/>
       <c r="B18" s="14" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C18" s="14">
         <v>3</v>
@@ -2905,7 +2922,7 @@
     <row r="19" spans="1:12">
       <c r="A19" s="14"/>
       <c r="B19" s="14" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C19" s="14" t="s">
         <v>95</v>
@@ -2929,7 +2946,7 @@
     <row r="20" spans="1:12">
       <c r="A20" s="14"/>
       <c r="B20" s="14" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C20" s="14">
         <v>64</v>
@@ -2953,7 +2970,7 @@
     <row r="21" spans="1:12">
       <c r="A21" s="14"/>
       <c r="B21" s="14" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C21" s="14">
         <v>20</v>
@@ -2977,7 +2994,7 @@
     <row r="22" spans="1:12">
       <c r="A22" s="14"/>
       <c r="B22" s="14" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C22" s="17" t="s">
         <v>109</v>
@@ -3025,7 +3042,7 @@
     <row r="24" spans="1:12">
       <c r="A24" s="14"/>
       <c r="B24" s="16" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C24" s="11">
         <v>1</v>
@@ -3047,7 +3064,7 @@
     <row r="25" spans="1:12" s="19" customFormat="1">
       <c r="A25" s="16"/>
       <c r="B25" s="16" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C25" s="11">
         <v>10000</v>
@@ -3392,10 +3409,10 @@
         <v>156</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D3" s="9"/>
       <c r="E3" s="4"/>
@@ -3428,13 +3445,13 @@
         <v>172</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C6" s="9" t="s">
         <v>174</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
@@ -3445,10 +3462,10 @@
       </c>
       <c r="B7" s="4"/>
       <c r="C7" s="9" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E7" s="4"/>
       <c r="F7" s="4"/>
@@ -3466,10 +3483,10 @@
         <v>122</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D9" s="9"/>
       <c r="E9" s="4"/>
@@ -3481,10 +3498,10 @@
       </c>
       <c r="B10" s="4"/>
       <c r="C10" s="9" t="s">
+        <v>202</v>
+      </c>
+      <c r="D10" s="9" t="s">
         <v>203</v>
-      </c>
-      <c r="D10" s="9" t="s">
-        <v>204</v>
       </c>
       <c r="E10" s="4"/>
       <c r="F10" s="4"/>
@@ -3504,10 +3521,10 @@
         <v>124</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D12" s="9"/>
       <c r="E12" s="4"/>
@@ -3519,7 +3536,7 @@
       </c>
       <c r="B13" s="4"/>
       <c r="C13" s="9" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D13" s="9"/>
       <c r="E13" s="4"/>
@@ -3540,10 +3557,10 @@
         <v>126</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D15" s="9"/>
       <c r="E15" s="4"/>
@@ -3576,13 +3593,13 @@
         <v>128</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C18" s="9" t="s">
+        <v>211</v>
+      </c>
+      <c r="D18" s="25" t="s">
         <v>212</v>
-      </c>
-      <c r="D18" s="25" t="s">
-        <v>213</v>
       </c>
       <c r="E18" s="4"/>
       <c r="F18" s="4"/>
@@ -3593,10 +3610,10 @@
       </c>
       <c r="B19" s="4"/>
       <c r="C19" s="9" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E19" s="4"/>
       <c r="F19" s="4"/>
@@ -3616,11 +3633,11 @@
         <v>135</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C21" s="9"/>
       <c r="D21" s="9" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E21" s="4"/>
       <c r="F21" s="4"/>
@@ -3631,10 +3648,10 @@
       </c>
       <c r="B22" s="4"/>
       <c r="C22" s="9" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E22" s="4"/>
       <c r="F22" s="4"/>
@@ -3654,10 +3671,10 @@
         <v>137</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D24" s="9"/>
       <c r="E24" s="4"/>
@@ -3669,10 +3686,10 @@
       </c>
       <c r="B25" s="4"/>
       <c r="C25" s="9" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E25" s="4"/>
       <c r="F25" s="4"/>
@@ -3692,13 +3709,13 @@
         <v>139</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="E27" s="4"/>
       <c r="F27" s="4"/>
@@ -3709,10 +3726,10 @@
       </c>
       <c r="B28" s="4"/>
       <c r="C28" s="9" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E28" s="4"/>
       <c r="F28" s="4"/>
@@ -3758,13 +3775,13 @@
         <v>141</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E33" s="4"/>
       <c r="F33" s="4"/>
@@ -3793,27 +3810,27 @@
     </row>
     <row r="36" spans="1:6" ht="24">
       <c r="A36" s="9" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C36" s="9" t="s">
+        <v>221</v>
+      </c>
+      <c r="D36" s="9" t="s">
         <v>223</v>
-      </c>
-      <c r="D36" s="9" t="s">
-        <v>225</v>
       </c>
       <c r="E36" s="4"/>
       <c r="F36" s="4"/>
     </row>
-    <row r="37" spans="1:6" ht="84">
+    <row r="37" spans="1:6" ht="96">
       <c r="A37" s="9" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B37" s="4"/>
       <c r="C37" s="9" t="s">
-        <v>222</v>
+        <v>237</v>
       </c>
       <c r="D37" s="9"/>
       <c r="E37" s="4"/>
@@ -3837,7 +3854,7 @@
         <v>145</v>
       </c>
       <c r="C39" s="9" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D39" s="9"/>
       <c r="E39" s="4"/>
@@ -3851,7 +3868,7 @@
         <v>146</v>
       </c>
       <c r="C40" s="9" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D40" s="9"/>
       <c r="E40" s="4"/>
@@ -3952,7 +3969,7 @@
         <v>153</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C48" s="9" t="s">
         <v>147</v>
@@ -3988,10 +4005,10 @@
         <v>169</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C51" s="9" t="s">
-        <v>181</v>
+        <v>240</v>
       </c>
       <c r="D51" s="9"/>
       <c r="E51" s="4"/>
@@ -4009,11 +4026,19 @@
       <c r="E52" s="4"/>
       <c r="F52" s="4"/>
     </row>
-    <row r="53" spans="1:6">
-      <c r="A53" s="9"/>
-      <c r="B53" s="4"/>
-      <c r="C53" s="9"/>
-      <c r="D53" s="9"/>
+    <row r="53" spans="1:6" ht="36">
+      <c r="A53" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="C53" s="9" t="s">
+        <v>241</v>
+      </c>
+      <c r="D53" s="9" t="s">
+        <v>242</v>
+      </c>
       <c r="E53" s="4"/>
       <c r="F53" s="4"/>
     </row>

--- a/internal_doc/03.开发设计/OM_web接口.xlsx
+++ b/internal_doc/03.开发设计/OM_web接口.xlsx
@@ -279,7 +279,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="243">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="245">
   <si>
     <t>需求</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1316,6 +1316,14 @@
   </si>
   <si>
     <t>http://192.168.20.197:11814/?cmd=change passwd&amp;user=admin&amp;passwd=admin&amp;Newpasswd=admin&amp;Timestamp=123</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>登出</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>logout</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1577,10 +1585,6 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1607,6 +1611,10 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2018,7 +2026,7 @@
       </c>
     </row>
     <row r="3" spans="1:8">
-      <c r="A3" s="27" t="s">
+      <c r="A3" s="25" t="s">
         <v>12</v>
       </c>
       <c r="B3" s="4" t="s">
@@ -2036,7 +2044,7 @@
       <c r="H3" s="4"/>
     </row>
     <row r="4" spans="1:8" ht="13.5">
-      <c r="A4" s="28"/>
+      <c r="A4" s="26"/>
       <c r="B4" s="4" t="s">
         <v>5</v>
       </c>
@@ -2052,7 +2060,7 @@
       <c r="H4" s="4"/>
     </row>
     <row r="5" spans="1:8" ht="13.5">
-      <c r="A5" s="28"/>
+      <c r="A5" s="26"/>
       <c r="B5" s="4" t="s">
         <v>8</v>
       </c>
@@ -2068,7 +2076,7 @@
       <c r="H5" s="4"/>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" s="29"/>
+      <c r="A6" s="27"/>
       <c r="B6" s="4" t="s">
         <v>13</v>
       </c>
@@ -2084,7 +2092,7 @@
       <c r="H6" s="4"/>
     </row>
     <row r="7" spans="1:8" ht="24">
-      <c r="A7" s="30" t="s">
+      <c r="A7" s="28" t="s">
         <v>24</v>
       </c>
       <c r="B7" s="4" t="s">
@@ -2102,7 +2110,7 @@
       <c r="H7" s="4"/>
     </row>
     <row r="8" spans="1:8" ht="36">
-      <c r="A8" s="31"/>
+      <c r="A8" s="29"/>
       <c r="B8" s="4" t="s">
         <v>17</v>
       </c>
@@ -2120,7 +2128,7 @@
       <c r="H8" s="4"/>
     </row>
     <row r="9" spans="1:8" ht="72">
-      <c r="A9" s="31"/>
+      <c r="A9" s="29"/>
       <c r="B9" s="4" t="s">
         <v>18</v>
       </c>
@@ -2138,7 +2146,7 @@
       <c r="H9" s="4"/>
     </row>
     <row r="10" spans="1:8" ht="24">
-      <c r="A10" s="32"/>
+      <c r="A10" s="30"/>
       <c r="B10" s="4" t="s">
         <v>21</v>
       </c>
@@ -2176,7 +2184,7 @@
       <c r="H11" s="4"/>
     </row>
     <row r="12" spans="1:8" ht="24">
-      <c r="A12" s="30" t="s">
+      <c r="A12" s="28" t="s">
         <v>26</v>
       </c>
       <c r="B12" s="4" t="s">
@@ -2194,7 +2202,7 @@
       <c r="H12" s="4"/>
     </row>
     <row r="13" spans="1:8">
-      <c r="A13" s="31"/>
+      <c r="A13" s="29"/>
       <c r="B13" s="4" t="s">
         <v>32</v>
       </c>
@@ -2210,7 +2218,7 @@
       <c r="H13" s="4"/>
     </row>
     <row r="14" spans="1:8" ht="24">
-      <c r="A14" s="31"/>
+      <c r="A14" s="29"/>
       <c r="B14" s="4" t="s">
         <v>33</v>
       </c>
@@ -2228,7 +2236,7 @@
       <c r="H14" s="4"/>
     </row>
     <row r="15" spans="1:8">
-      <c r="A15" s="31"/>
+      <c r="A15" s="29"/>
       <c r="B15" s="4" t="s">
         <v>35</v>
       </c>
@@ -2244,7 +2252,7 @@
       <c r="H15" s="4"/>
     </row>
     <row r="16" spans="1:8">
-      <c r="A16" s="31"/>
+      <c r="A16" s="29"/>
       <c r="B16" s="4" t="s">
         <v>57</v>
       </c>
@@ -2256,7 +2264,7 @@
       <c r="H16" s="4"/>
     </row>
     <row r="17" spans="1:8" ht="48">
-      <c r="A17" s="31"/>
+      <c r="A17" s="29"/>
       <c r="B17" s="4" t="s">
         <v>30</v>
       </c>
@@ -2274,7 +2282,7 @@
       <c r="H17" s="4"/>
     </row>
     <row r="18" spans="1:8">
-      <c r="A18" s="31"/>
+      <c r="A18" s="29"/>
       <c r="B18" s="4" t="s">
         <v>38</v>
       </c>
@@ -2290,7 +2298,7 @@
       <c r="H18" s="4"/>
     </row>
     <row r="19" spans="1:8">
-      <c r="A19" s="31"/>
+      <c r="A19" s="29"/>
       <c r="B19" s="4" t="s">
         <v>41</v>
       </c>
@@ -2306,7 +2314,7 @@
       <c r="H19" s="4"/>
     </row>
     <row r="20" spans="1:8">
-      <c r="A20" s="31"/>
+      <c r="A20" s="29"/>
       <c r="B20" s="4" t="s">
         <v>40</v>
       </c>
@@ -2322,7 +2330,7 @@
       <c r="H20" s="4"/>
     </row>
     <row r="21" spans="1:8" ht="24">
-      <c r="A21" s="31"/>
+      <c r="A21" s="29"/>
       <c r="B21" s="4" t="s">
         <v>44</v>
       </c>
@@ -2340,7 +2348,7 @@
       <c r="H21" s="4"/>
     </row>
     <row r="22" spans="1:8" ht="24">
-      <c r="A22" s="31"/>
+      <c r="A22" s="29"/>
       <c r="B22" s="4" t="s">
         <v>47</v>
       </c>
@@ -2356,7 +2364,7 @@
       <c r="H22" s="4"/>
     </row>
     <row r="23" spans="1:8" ht="24">
-      <c r="A23" s="31"/>
+      <c r="A23" s="29"/>
       <c r="B23" s="4" t="s">
         <v>49</v>
       </c>
@@ -3368,7 +3376,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F67"/>
+  <dimension ref="A1:F64"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="26" style="10" bestFit="1" customWidth="1"/>
@@ -3379,7 +3387,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="22" t="s">
         <v>118</v>
       </c>
       <c r="B1" s="4"/>
@@ -3598,7 +3606,7 @@
       <c r="C18" s="9" t="s">
         <v>211</v>
       </c>
-      <c r="D18" s="25" t="s">
+      <c r="D18" s="23" t="s">
         <v>212</v>
       </c>
       <c r="E18" s="4"/>
@@ -3744,93 +3752,105 @@
       <c r="E29" s="4"/>
       <c r="F29" s="4"/>
     </row>
-    <row r="30" spans="1:6">
-      <c r="A30" s="9"/>
-      <c r="B30" s="4"/>
-      <c r="C30" s="9"/>
-      <c r="D30" s="9"/>
+    <row r="30" spans="1:6" ht="144">
+      <c r="A30" s="9" t="s">
+        <v>141</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="C30" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="D30" s="9" t="s">
+        <v>208</v>
+      </c>
       <c r="E30" s="4"/>
       <c r="F30" s="4"/>
     </row>
     <row r="31" spans="1:6">
-      <c r="A31" s="9"/>
+      <c r="A31" s="9" t="s">
+        <v>142</v>
+      </c>
       <c r="B31" s="4"/>
-      <c r="C31" s="11"/>
-      <c r="D31" s="9"/>
+      <c r="C31" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="D31" s="9" t="s">
+        <v>120</v>
+      </c>
       <c r="E31" s="4"/>
       <c r="F31" s="4"/>
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="9"/>
-      <c r="B32" s="4" t="s">
-        <v>133</v>
-      </c>
+      <c r="B32" s="4"/>
       <c r="C32" s="9"/>
       <c r="D32" s="9"/>
       <c r="E32" s="4"/>
       <c r="F32" s="4"/>
     </row>
-    <row r="33" spans="1:6" ht="144">
+    <row r="33" spans="1:6" ht="24">
       <c r="A33" s="9" t="s">
-        <v>141</v>
+        <v>219</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>208</v>
+        <v>223</v>
       </c>
       <c r="E33" s="4"/>
       <c r="F33" s="4"/>
     </row>
-    <row r="34" spans="1:6">
+    <row r="34" spans="1:6" ht="96">
       <c r="A34" s="9" t="s">
-        <v>142</v>
+        <v>220</v>
       </c>
       <c r="B34" s="4"/>
       <c r="C34" s="9" t="s">
-        <v>148</v>
-      </c>
-      <c r="D34" s="9" t="s">
-        <v>120</v>
-      </c>
+        <v>237</v>
+      </c>
+      <c r="D34" s="9"/>
       <c r="E34" s="4"/>
       <c r="F34" s="4"/>
     </row>
     <row r="35" spans="1:6">
       <c r="A35" s="9"/>
-      <c r="B35" s="4"/>
+      <c r="B35" s="4" t="s">
+        <v>133</v>
+      </c>
       <c r="C35" s="9"/>
       <c r="D35" s="9"/>
       <c r="E35" s="4"/>
       <c r="F35" s="4"/>
     </row>
-    <row r="36" spans="1:6" ht="24">
+    <row r="36" spans="1:6">
       <c r="A36" s="9" t="s">
-        <v>219</v>
+        <v>143</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>236</v>
+        <v>145</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>221</v>
-      </c>
-      <c r="D36" s="9" t="s">
-        <v>223</v>
-      </c>
+        <v>184</v>
+      </c>
+      <c r="D36" s="9"/>
       <c r="E36" s="4"/>
       <c r="F36" s="4"/>
     </row>
-    <row r="37" spans="1:6" ht="96">
+    <row r="37" spans="1:6">
       <c r="A37" s="9" t="s">
-        <v>220</v>
-      </c>
-      <c r="B37" s="4"/>
+        <v>144</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>146</v>
+      </c>
       <c r="C37" s="9" t="s">
-        <v>237</v>
+        <v>185</v>
       </c>
       <c r="D37" s="9"/>
       <c r="E37" s="4"/>
@@ -3838,257 +3858,199 @@
     </row>
     <row r="38" spans="1:6">
       <c r="A38" s="9"/>
-      <c r="B38" s="4" t="s">
-        <v>133</v>
-      </c>
+      <c r="B38" s="4"/>
       <c r="C38" s="9"/>
       <c r="D38" s="9"/>
       <c r="E38" s="4"/>
       <c r="F38" s="4"/>
     </row>
-    <row r="39" spans="1:6">
-      <c r="A39" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="B39" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="C39" s="9" t="s">
-        <v>184</v>
-      </c>
-      <c r="D39" s="9"/>
-      <c r="E39" s="4"/>
-      <c r="F39" s="4"/>
-    </row>
-    <row r="40" spans="1:6">
-      <c r="A40" s="9" t="s">
-        <v>144</v>
-      </c>
-      <c r="B40" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="C40" s="9" t="s">
-        <v>185</v>
-      </c>
-      <c r="D40" s="9"/>
-      <c r="E40" s="4"/>
-      <c r="F40" s="4"/>
-    </row>
-    <row r="41" spans="1:6">
-      <c r="A41" s="9"/>
-      <c r="B41" s="4"/>
-      <c r="C41" s="9"/>
-      <c r="D41" s="9"/>
-      <c r="E41" s="4"/>
-      <c r="F41" s="4"/>
-    </row>
-    <row r="42" spans="1:6">
-      <c r="A42" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="B42" s="4"/>
-      <c r="C42" s="9" t="s">
-        <v>159</v>
-      </c>
-      <c r="D42" s="9"/>
-      <c r="E42" s="4"/>
-      <c r="F42" s="4"/>
-    </row>
-    <row r="43" spans="1:6" ht="24">
-      <c r="A43" s="9" t="s">
-        <v>162</v>
-      </c>
-      <c r="B43" s="4"/>
-      <c r="C43" s="9" t="s">
-        <v>160</v>
-      </c>
-      <c r="D43" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="E43" s="4"/>
-      <c r="F43" s="4"/>
-    </row>
-    <row r="44" spans="1:6" ht="24">
-      <c r="A44" s="9" t="s">
-        <v>157</v>
-      </c>
-      <c r="B44" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="C44" s="9" t="s">
-        <v>158</v>
-      </c>
-      <c r="D44" s="9"/>
-      <c r="E44" s="4"/>
-      <c r="F44" s="4"/>
-    </row>
-    <row r="45" spans="1:6" ht="60">
+    <row r="45" spans="1:6">
       <c r="A45" s="9" t="s">
-        <v>163</v>
+        <v>153</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>164</v>
+        <v>227</v>
       </c>
       <c r="C45" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="D45" s="9" t="s">
-        <v>168</v>
-      </c>
+        <v>147</v>
+      </c>
+      <c r="D45" s="9"/>
       <c r="E45" s="4"/>
       <c r="F45" s="4"/>
     </row>
-    <row r="46" spans="1:6" ht="48">
+    <row r="46" spans="1:6" ht="24">
       <c r="A46" s="9" t="s">
-        <v>165</v>
-      </c>
-      <c r="B46" s="4" t="s">
-        <v>164</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="B46" s="4"/>
       <c r="C46" s="9" t="s">
-        <v>166</v>
-      </c>
-      <c r="D46" s="9"/>
+        <v>171</v>
+      </c>
+      <c r="D46" s="9" t="s">
+        <v>155</v>
+      </c>
       <c r="E46" s="4"/>
       <c r="F46" s="4"/>
     </row>
-    <row r="47" spans="1:6" s="23" customFormat="1">
-      <c r="A47" s="22" t="s">
-        <v>152</v>
-      </c>
-      <c r="B47" s="21"/>
-      <c r="C47" s="22"/>
-      <c r="D47" s="22" t="s">
-        <v>150</v>
-      </c>
-      <c r="E47" s="21"/>
-      <c r="F47" s="21"/>
+    <row r="47" spans="1:6">
+      <c r="A47" s="9"/>
+      <c r="B47" s="4"/>
+      <c r="C47" s="9"/>
+      <c r="D47" s="9"/>
+      <c r="E47" s="4"/>
+      <c r="F47" s="4"/>
     </row>
     <row r="48" spans="1:6">
       <c r="A48" s="9" t="s">
-        <v>153</v>
+        <v>169</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C48" s="9" t="s">
-        <v>147</v>
+        <v>240</v>
       </c>
       <c r="D48" s="9"/>
       <c r="E48" s="4"/>
       <c r="F48" s="4"/>
     </row>
-    <row r="49" spans="1:6" ht="24">
+    <row r="49" spans="1:6">
       <c r="A49" s="9" t="s">
-        <v>154</v>
+        <v>170</v>
       </c>
       <c r="B49" s="4"/>
       <c r="C49" s="9" t="s">
-        <v>171</v>
-      </c>
-      <c r="D49" s="9" t="s">
-        <v>155</v>
-      </c>
+        <v>160</v>
+      </c>
+      <c r="D49" s="9"/>
       <c r="E49" s="4"/>
       <c r="F49" s="4"/>
     </row>
-    <row r="50" spans="1:6">
-      <c r="A50" s="9"/>
-      <c r="B50" s="4"/>
-      <c r="C50" s="9"/>
-      <c r="D50" s="9"/>
+    <row r="50" spans="1:6" ht="36">
+      <c r="A50" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="C50" s="9" t="s">
+        <v>241</v>
+      </c>
+      <c r="D50" s="9" t="s">
+        <v>242</v>
+      </c>
       <c r="E50" s="4"/>
       <c r="F50" s="4"/>
     </row>
     <row r="51" spans="1:6">
       <c r="A51" s="9" t="s">
-        <v>169</v>
+        <v>243</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>226</v>
-      </c>
-      <c r="C51" s="9" t="s">
-        <v>240</v>
-      </c>
+        <v>244</v>
+      </c>
+      <c r="C51" s="9"/>
       <c r="D51" s="9"/>
       <c r="E51" s="4"/>
       <c r="F51" s="4"/>
     </row>
     <row r="52" spans="1:6">
-      <c r="A52" s="9" t="s">
-        <v>170</v>
-      </c>
+      <c r="A52" s="9"/>
       <c r="B52" s="4"/>
-      <c r="C52" s="9" t="s">
-        <v>160</v>
-      </c>
+      <c r="C52" s="9"/>
       <c r="D52" s="9"/>
       <c r="E52" s="4"/>
       <c r="F52" s="4"/>
     </row>
-    <row r="53" spans="1:6" ht="36">
-      <c r="A53" s="9" t="s">
-        <v>238</v>
-      </c>
-      <c r="B53" s="4" t="s">
-        <v>239</v>
-      </c>
-      <c r="C53" s="9" t="s">
-        <v>241</v>
-      </c>
-      <c r="D53" s="9" t="s">
-        <v>242</v>
-      </c>
-      <c r="E53" s="4"/>
-      <c r="F53" s="4"/>
-    </row>
-    <row r="54" spans="1:6">
-      <c r="A54" s="9"/>
-      <c r="B54" s="4"/>
-      <c r="C54" s="9"/>
-      <c r="D54" s="9"/>
-      <c r="E54" s="4"/>
-      <c r="F54" s="4"/>
-    </row>
-    <row r="55" spans="1:6">
-      <c r="A55" s="9"/>
-      <c r="B55" s="4"/>
-      <c r="C55" s="9"/>
-      <c r="D55" s="9"/>
-      <c r="E55" s="4"/>
-      <c r="F55" s="4"/>
-    </row>
-    <row r="56" spans="1:6">
-      <c r="A56" s="9"/>
-      <c r="B56" s="4"/>
-      <c r="C56" s="9"/>
-      <c r="D56" s="9"/>
-      <c r="E56" s="4"/>
-      <c r="F56" s="4"/>
-    </row>
-    <row r="57" spans="1:6">
-      <c r="A57" s="9"/>
-      <c r="B57" s="4"/>
-      <c r="C57" s="9"/>
-      <c r="D57" s="9"/>
-      <c r="E57" s="4"/>
-      <c r="F57" s="4"/>
-    </row>
-    <row r="58" spans="1:6">
-      <c r="A58" s="9"/>
-      <c r="B58" s="4"/>
-      <c r="C58" s="9"/>
-      <c r="D58" s="9"/>
-      <c r="E58" s="4"/>
-      <c r="F58" s="4"/>
+    <row r="53" spans="1:6">
+      <c r="A53" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="B53" s="2"/>
+      <c r="C53" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="D53" s="5"/>
+      <c r="E53" s="2"/>
+      <c r="F53" s="2"/>
+    </row>
+    <row r="54" spans="1:6" ht="24">
+      <c r="A54" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="B54" s="2"/>
+      <c r="C54" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="D54" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="E54" s="2"/>
+      <c r="F54" s="2"/>
+    </row>
+    <row r="55" spans="1:6" ht="24">
+      <c r="A55" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="C55" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="D55" s="5"/>
+      <c r="E55" s="2"/>
+      <c r="F55" s="2"/>
+    </row>
+    <row r="56" spans="1:6" ht="60">
+      <c r="A56" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="C56" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="D56" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="E56" s="2"/>
+      <c r="F56" s="2"/>
+    </row>
+    <row r="57" spans="1:6" ht="48">
+      <c r="A57" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="C57" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="D57" s="5"/>
+      <c r="E57" s="2"/>
+      <c r="F57" s="2"/>
+    </row>
+    <row r="58" spans="1:6" s="21" customFormat="1">
+      <c r="A58" s="31" t="s">
+        <v>152</v>
+      </c>
+      <c r="B58" s="32"/>
+      <c r="C58" s="31"/>
+      <c r="D58" s="31" t="s">
+        <v>150</v>
+      </c>
+      <c r="E58" s="32"/>
+      <c r="F58" s="32"/>
     </row>
     <row r="59" spans="1:6">
-      <c r="A59" s="9"/>
-      <c r="B59" s="4"/>
-      <c r="C59" s="9"/>
-      <c r="D59" s="9"/>
-      <c r="E59" s="4"/>
-      <c r="F59" s="4"/>
+      <c r="A59" s="5"/>
+      <c r="B59" s="2"/>
+      <c r="C59" s="5"/>
+      <c r="D59" s="5"/>
+      <c r="E59" s="2"/>
+      <c r="F59" s="2"/>
     </row>
     <row r="60" spans="1:6">
       <c r="A60" s="9"/>
@@ -4129,30 +4091,6 @@
       <c r="D64" s="9"/>
       <c r="E64" s="4"/>
       <c r="F64" s="4"/>
-    </row>
-    <row r="65" spans="1:6">
-      <c r="A65" s="9"/>
-      <c r="B65" s="4"/>
-      <c r="C65" s="9"/>
-      <c r="D65" s="9"/>
-      <c r="E65" s="4"/>
-      <c r="F65" s="4"/>
-    </row>
-    <row r="66" spans="1:6">
-      <c r="A66" s="9"/>
-      <c r="B66" s="4"/>
-      <c r="C66" s="9"/>
-      <c r="D66" s="9"/>
-      <c r="E66" s="4"/>
-      <c r="F66" s="4"/>
-    </row>
-    <row r="67" spans="1:6">
-      <c r="A67" s="9"/>
-      <c r="B67" s="4"/>
-      <c r="C67" s="9"/>
-      <c r="D67" s="9"/>
-      <c r="E67" s="4"/>
-      <c r="F67" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -4180,10 +4118,10 @@
       </c>
     </row>
     <row r="8" spans="1:3" ht="40.5">
-      <c r="B8" s="25" t="s">
+      <c r="B8" s="23" t="s">
         <v>175</v>
       </c>
-      <c r="C8" s="26" t="s">
+      <c r="C8" s="24" t="s">
         <v>176</v>
       </c>
     </row>

--- a/internal_doc/03.开发设计/OM_web接口.xlsx
+++ b/internal_doc/03.开发设计/OM_web接口.xlsx
@@ -279,7 +279,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="245">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="246">
   <si>
     <t>需求</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1029,9 +1029,6 @@
     <t>{business_name, ClusterName, rc}</t>
   </si>
   <si>
-    <t>{BusinessList:[{BusinessType, BusinessDesc},...]}</t>
-  </si>
-  <si>
     <t>BusinessType=xxx</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1081,12 +1078,6 @@
   </si>
   <si>
     <t>{[{IP, HostName, rc, Firework, [Disk],[CPU]…}, ...]}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ClusterType:cluster/standalone
-下拉列表，选中则切换配置
-增加"Desc","配置等级"</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1194,18 +1185,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>http://192.168.20.197:11814/?cmd=QueryHostReq&amp;ClusterName=c1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>一个host一个bson</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>http://192.168.20.197:11814/?cmd=QueryBusinessListReq</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>{ "rc": 0 }{ "BusinessList": [ { "BusinessType": "sequoiadb", "BusinessDesc": "haha" }, { "BusinessType": "sequoiasql", "BusinessDesc": "haha" } ] }</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1234,10 +1217,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>http://192.168.20.197:11814/?cmd=ConfigBusinessReq&amp;TemplateInfo={"ClusterName":"c1","BusinessType":"sequoiadb","BusinessName":"b1","ClusterType":"standalone","Property":[{"Name":"replica_num","Value":"1"},{"Name":"data_group_num","Value":"1"},{"Name":"catalog_num","Value":"1"},{"Name":"coord_num","Value":"1"}],"HostInfo":[{"HostName":"host1"}]}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>http://192.168.20.197:11814/?cmd=QueryInstallProgress&amp;Task={"TaskID":"ad"}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1271,10 +1250,6 @@
   </si>
   <si>
     <t>query host</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>query business list</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1324,6 +1299,34 @@
   </si>
   <si>
     <t>logout</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://192.168.20.197:11814/?cmd=query host&amp;ClusterName=c1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>query business list</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://192.168.20.197:11814/?cmd=query business list</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{BusinessList:[{BusinessType, BusinessDesc},...]}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{ "rc": 0 }{ "ClusterType": "standalone", "ClusterTypeWebName": "aa", "BusinessType": "sequoiadb", "Property": [ { "Name": "replicanum", "Type": "int", "Default": "1", "Valid": "1", "Display": "edit box", "Edit": "false", "Desc": "", "Level": "0", "WebName": "replica_num" }, { "Name": "datagroupnum", "Type": "int", "Default": "1", "Valid": "1", "Display": "edit box", "Edit": "false", "Desc": "", "Level": "0", "WebName": "data_group_num" }, { "Name": "catalognum", "Type": "int", "Default": "1", "Valid": "1", "Display": "edit box", "Edit": "false", "Desc": "", "Level": "0", "WebName": "catalog_num" }, { "Name": "coordnum", "Type": "int", "Default": "1", "Valid": "1", "Display": "edit box", "Edit": "false", "Desc": "", "Level": "0", "WebName": "coord_num" } ] }{ "ClusterType": "cluster", "ClusterTypeWebName": "aa", "BusinessType": "sequoiadb", "Property": [ { "Name": "replicanum", "Type": "int", "Default": "3", "Valid": "2-3", "Display": "edit box", "Edit": "true", "Desc": "", "Level": "0", "WebName": "replica_num" }, { "Name": "datagroupnum", "Type": "int", "Default": "1", "Valid": "", "Display": "edit box", "Edit": "true", "Desc": "", "Level": "0", "WebName": "data_group_num" }, { "Name": "catalognum", "Type": "int", "Default": "1", "Valid": "", "Display": "edit box", "Edit": "true", "Desc": "", "Level": "0", "WebName": "catalog_num" }, { "Name": "coordnum", "Type": "int", "Default": "0", "Valid": "0-7", "Display": "edit box", "Edit": "true", "Desc": "", "Level": "0", "WebName": "coord_num" } ] }</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://192.168.20.197:11814/?cmd=query%20business%20template&amp;BusinessType=sequoiadb</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://192.168.20.197:11814/?cmd=config business&amp;TemplateInfo={"ClusterName":"c1","BusinessType":"sequoiadb","BusinessName":"b1","ClusterType":"standalone","Property":[{"Name":"replicanum","Value":"1"},{"Name":"datagroupnum","Value":"1"},{"Name":"catalognum","Value":"1"},{"Name":"coordnum","Value":"1"}],"HostInfo":[{"HostName":"host1"}]}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2818,7 +2821,7 @@
     <row r="14" spans="1:12">
       <c r="A14" s="14"/>
       <c r="B14" s="14" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C14" s="14">
         <v>11811</v>
@@ -2840,7 +2843,7 @@
     <row r="15" spans="1:12">
       <c r="A15" s="14"/>
       <c r="B15" s="14" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C15" s="14">
         <v>11812</v>
@@ -2862,7 +2865,7 @@
     <row r="16" spans="1:12">
       <c r="A16" s="14"/>
       <c r="B16" s="14" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C16" s="14">
         <v>11813</v>
@@ -2884,7 +2887,7 @@
     <row r="17" spans="1:12">
       <c r="A17" s="14"/>
       <c r="B17" s="14" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C17" s="14">
         <v>11814</v>
@@ -2906,7 +2909,7 @@
     <row r="18" spans="1:12">
       <c r="A18" s="14"/>
       <c r="B18" s="14" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C18" s="14">
         <v>3</v>
@@ -2930,7 +2933,7 @@
     <row r="19" spans="1:12">
       <c r="A19" s="14"/>
       <c r="B19" s="14" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C19" s="14" t="s">
         <v>95</v>
@@ -2954,7 +2957,7 @@
     <row r="20" spans="1:12">
       <c r="A20" s="14"/>
       <c r="B20" s="14" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C20" s="14">
         <v>64</v>
@@ -2978,7 +2981,7 @@
     <row r="21" spans="1:12">
       <c r="A21" s="14"/>
       <c r="B21" s="14" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C21" s="14">
         <v>20</v>
@@ -3002,7 +3005,7 @@
     <row r="22" spans="1:12">
       <c r="A22" s="14"/>
       <c r="B22" s="14" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C22" s="17" t="s">
         <v>109</v>
@@ -3050,7 +3053,7 @@
     <row r="24" spans="1:12">
       <c r="A24" s="14"/>
       <c r="B24" s="16" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C24" s="11">
         <v>1</v>
@@ -3072,7 +3075,7 @@
     <row r="25" spans="1:12" s="19" customFormat="1">
       <c r="A25" s="16"/>
       <c r="B25" s="16" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C25" s="11">
         <v>10000</v>
@@ -3382,7 +3385,7 @@
     <col min="1" max="1" width="26" style="10" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="28.75" style="3" customWidth="1"/>
     <col min="3" max="3" width="45.125" style="10" customWidth="1"/>
-    <col min="4" max="4" width="43.375" style="10" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="52.25" style="10" customWidth="1"/>
     <col min="5" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
@@ -3417,10 +3420,10 @@
         <v>156</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="D3" s="9"/>
       <c r="E3" s="4"/>
@@ -3453,13 +3456,13 @@
         <v>172</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="C6" s="9" t="s">
         <v>174</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
@@ -3473,7 +3476,7 @@
         <v>182</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="E7" s="4"/>
       <c r="F7" s="4"/>
@@ -3491,7 +3494,7 @@
         <v>122</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="C9" s="9" t="s">
         <v>181</v>
@@ -3506,10 +3509,10 @@
       </c>
       <c r="B10" s="4"/>
       <c r="C10" s="9" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E10" s="4"/>
       <c r="F10" s="4"/>
@@ -3529,10 +3532,10 @@
         <v>124</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="D12" s="9"/>
       <c r="E12" s="4"/>
@@ -3544,7 +3547,7 @@
       </c>
       <c r="B13" s="4"/>
       <c r="C13" s="9" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D13" s="9"/>
       <c r="E13" s="4"/>
@@ -3565,10 +3568,10 @@
         <v>126</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D15" s="9"/>
       <c r="E15" s="4"/>
@@ -3601,13 +3604,13 @@
         <v>128</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="D18" s="23" t="s">
-        <v>212</v>
+        <v>239</v>
       </c>
       <c r="E18" s="4"/>
       <c r="F18" s="4"/>
@@ -3621,7 +3624,7 @@
         <v>183</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="E19" s="4"/>
       <c r="F19" s="4"/>
@@ -3641,11 +3644,11 @@
         <v>135</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="C21" s="9"/>
       <c r="D21" s="9" t="s">
-        <v>214</v>
+        <v>241</v>
       </c>
       <c r="E21" s="4"/>
       <c r="F21" s="4"/>
@@ -3656,10 +3659,10 @@
       </c>
       <c r="B22" s="4"/>
       <c r="C22" s="9" t="s">
-        <v>186</v>
+        <v>242</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="E22" s="4"/>
       <c r="F22" s="4"/>
@@ -3674,30 +3677,32 @@
       <c r="E23" s="4"/>
       <c r="F23" s="4"/>
     </row>
-    <row r="24" spans="1:6">
+    <row r="24" spans="1:6" ht="24">
       <c r="A24" s="9" t="s">
         <v>137</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>187</v>
-      </c>
-      <c r="D24" s="9"/>
+        <v>186</v>
+      </c>
+      <c r="D24" s="9" t="s">
+        <v>244</v>
+      </c>
       <c r="E24" s="4"/>
       <c r="F24" s="4"/>
     </row>
-    <row r="25" spans="1:6" ht="84">
+    <row r="25" spans="1:6" ht="252">
       <c r="A25" s="9" t="s">
         <v>138</v>
       </c>
       <c r="B25" s="4"/>
       <c r="C25" s="9" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>200</v>
+        <v>243</v>
       </c>
       <c r="E25" s="4"/>
       <c r="F25" s="4"/>
@@ -3712,32 +3717,32 @@
       <c r="E26" s="4"/>
       <c r="F26" s="4"/>
     </row>
-    <row r="27" spans="1:6" ht="96">
+    <row r="27" spans="1:6" ht="84">
       <c r="A27" s="9" t="s">
         <v>139</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>222</v>
+        <v>245</v>
       </c>
       <c r="E27" s="4"/>
       <c r="F27" s="4"/>
     </row>
-    <row r="28" spans="1:6" ht="132">
+    <row r="28" spans="1:6" ht="120">
       <c r="A28" s="9" t="s">
         <v>140</v>
       </c>
       <c r="B28" s="4"/>
       <c r="C28" s="9" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="E28" s="4"/>
       <c r="F28" s="4"/>
@@ -3757,13 +3762,13 @@
         <v>141</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E30" s="4"/>
       <c r="F30" s="4"/>
@@ -3792,27 +3797,27 @@
     </row>
     <row r="33" spans="1:6" ht="24">
       <c r="A33" s="9" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="E33" s="4"/>
       <c r="F33" s="4"/>
     </row>
     <row r="34" spans="1:6" ht="96">
       <c r="A34" s="9" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="B34" s="4"/>
       <c r="C34" s="9" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="D34" s="9"/>
       <c r="E34" s="4"/>
@@ -3869,7 +3874,7 @@
         <v>153</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="C45" s="9" t="s">
         <v>147</v>
@@ -3905,10 +3910,10 @@
         <v>169</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="C48" s="9" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="D48" s="9"/>
       <c r="E48" s="4"/>
@@ -3928,26 +3933,26 @@
     </row>
     <row r="50" spans="1:6" ht="36">
       <c r="A50" s="9" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="C50" s="9" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="D50" s="9" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="E50" s="4"/>
       <c r="F50" s="4"/>
     </row>
     <row r="51" spans="1:6">
       <c r="A51" s="9" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="C51" s="9"/>
       <c r="D51" s="9"/>

--- a/internal_doc/03.开发设计/OM_web接口.xlsx
+++ b/internal_doc/03.开发设计/OM_web接口.xlsx
@@ -279,7 +279,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="246">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="247">
   <si>
     <t>需求</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1327,6 +1327,10 @@
   </si>
   <si>
     <t>http://192.168.20.197:11814/?cmd=config business&amp;TemplateInfo={"ClusterName":"c1","BusinessType":"sequoiadb","BusinessName":"b1","ClusterType":"standalone","Property":[{"Name":"replicanum","Value":"1"},{"Name":"datagroupnum","Value":"1"},{"Name":"catalognum","Value":"1"},{"Name":"coordnum","Value":"1"}],"HostInfo":[{"HostName":"host1"}]}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://192.168.20.197:11814/?cmd=create cluster&amp;ClusterInfo={"ClusterName":"cls1", "Desc":"xxx", "SdbUser":"sdbadmin", "SdbPasswd":"sdbadmin", "SdbUserGroup":"sdbadmin_group"}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3415,7 +3419,7 @@
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
     </row>
-    <row r="3" spans="1:6" ht="36">
+    <row r="3" spans="1:6" ht="48">
       <c r="A3" s="9" t="s">
         <v>156</v>
       </c>
@@ -3425,7 +3429,9 @@
       <c r="C3" s="9" t="s">
         <v>208</v>
       </c>
-      <c r="D3" s="9"/>
+      <c r="D3" s="9" t="s">
+        <v>246</v>
+      </c>
       <c r="E3" s="4"/>
       <c r="F3" s="4"/>
     </row>

--- a/internal_doc/03.开发设计/OM_web接口.xlsx
+++ b/internal_doc/03.开发设计/OM_web接口.xlsx
@@ -279,7 +279,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="247">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="246">
   <si>
     <t>需求</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -928,10 +928,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>{rc,local}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>命令错误响应1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1017,20 +1013,10 @@
     <t>HostInfo={ClusterName:cls1,HostInfo:[{IP/HostName:xxx, User:xxx, Passwd:xxx, SshPort:xxx, AgentPort:xxx}, ...],User:usr1,Passwd:Passwd1, SshPort:xxx, AgentPort:xxx}</t>
   </si>
   <si>
-    <t>{ClusterName:xxx, desc:xxx}</t>
-  </si>
-  <si>
-    <t>{ClusterName, rc, [IP, HostName, Firework, [Disk],[CPU]...]}</t>
-  </si>
-  <si>
     <t>business_name=xxx&amp;ClusterName=xxx</t>
   </si>
   <si>
     <t>{business_name, ClusterName, rc}</t>
-  </si>
-  <si>
-    <t>BusinessType=xxx</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>replname</t>
@@ -1098,31 +1084,203 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>"Config": [ { "HostName": "host1", "username": "sdbadmin", "userpasswd": "sdbadmin", "usergroup": "sdbadmin_group", "datagroupname": "", "dbpath": "/home/db2//standalone/11830", "svcname": "11830", ...} ],"BusinessName": "b1", "BusinessType": "sequoiadb", "ClusterType": "standalone","ClusterName": "c1","Property": [ { "Name": "username", "Type": "string", "Default": "sdbadmin", "Valid": "", "Display": "edit box", "Edit": "true", "Desc": "", "Level": "0", "WebName": "user_name",... }]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{BusinessType, BusinessName,ClusterType, ClusterName, "Config":[{dbpath, svcname…} },...],"Property": [{ "Name": "username", "Type": "string", "Default": "sdbadmin", "Valid": "", "Display": "edit box", "Edit": "true", "Desc": "", "Level": "0", "WebName": "user_name",... }, ...] }</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>192.168.20.197:11814/?cmd=AddBusinessReq&amp;ConfigInfo={"ClusterName":"c1","BusinessType":"sequoiadb","BusinessName":"b1","ClusterType":"cluster", "Config": [ { "HostName": "host1", "username": "sdbadmin", "userpasswd": "sdbadmin", "usergroup": "sdbadmin_group", "datagroupname": "", "dbpath": "/home/db2/standalone/11830", "svcname": "11830", "diaglevel": "3", "role": "standalone", "logfilesz": "64", "logfilenum": "20", "transactionon": "false", "preferedinstance": "A", "numpagecleaners": "1", "pagecleaninterval": "1" } ]}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>host_info={ClusterName:cls1, host_info:[{IP, HostName, User, Passwd, SshPort:xxx, AgentPort:xxx},...], User:usr1, Passwd:Passwd1, SshPort:xxx}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ClusterName=cls1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{ "rc": 0 }{ "BusinessList": [ { "BusinessType": "sequoiadb", "BusinessDesc": "haha" }, { "BusinessType": "sequoiasql", "BusinessDesc": "haha" } ] }</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{BusinessType, BusinessName,ClusterType, ClusterName, "Config":[{"HostName":"host1","datagroupname":"", "dbpath":"/home/db2//standalone/11830", "svcname":"11830", ...}, ...] }]}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"TaskID":"asd"}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://192.168.20.197:11814/?cmd=QueryInstallProgress&amp;Task={"TaskID":"ad"}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>create cluster</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>query cluster</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>check session</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>scan host</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>check host</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>add host</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>query host</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>config business</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>add business</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"rc":0, "Detail":"","TaskID":"asd", "isFinish":true,"Status":"install/rollback","Progress":[{"Name":"Coord","TotalCount":7 "InstalledCount":100, "Desc":""}, {"Name":"Group1","TotalCount":3,"InstalledCount":50,"Desc":""},
+{"Name":"Group2","TotalCount":4,"InstalledCount":50,"Desc":""} ...]}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>User=xx&amp;Passwd=xx&amp;Timestamp=xx</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>修改密码</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>change passwd</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>User=admin&amp;Passwd=admin&amp;Newpasswd=admin&amp;Timestamp=123</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://192.168.20.197:11814/?cmd=change passwd&amp;user=admin&amp;passwd=admin&amp;Newpasswd=admin&amp;Timestamp=123</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>登出</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>logout</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://192.168.20.197:11814/?cmd=query host&amp;ClusterName=c1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>query business list</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{BusinessList:[{BusinessType, BusinessDesc},...]}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://192.168.20.197:11814/?cmd=query%20business%20template&amp;BusinessType=sequoiadb</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://192.168.20.197:11814/?cmd=create cluster&amp;ClusterInfo={"ClusterName":"cls1", "Desc":"xxx", "SdbUser":"sdbadmin", "SdbPasswd":"sdbadmin", "SdbUserGroup":"sdbadmin_group"}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>login</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{rc,local}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>query progress</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ClusterInfo={ClusterName=cls1, Desc=xxx, SdbUser=sdbadmin, SdbPasswd=sdbadmin, SdbUserGroup=sdbadmin_group}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://192.168.20.197:11814/?cmd=query cluster</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{ClusterName:xxx, desc:xxx}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{ "rc": 0 }{ "ClusterName": "c1", "Desc": "" }</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>查询进度</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>查询进度响应</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{ClusterName, rc, [IP, HostName, Firework, [Disk],[CPU]...]}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://192.168.20.197:11814/?cmd=query business list</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>query business template</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BusinessType=xxx</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://192.168.20.197:11814/?cmd=config business&amp;TemplateInfo={"ClusterName":"c1","BusinessType":"sequoiadb","BusinessName":"b1","DeployMod":"standalone","Property":[{"Name":"replicanum","Value":"1"},{"Name":"datagroupnum","Value":"1"},{"Name":"catalognum","Value":"1"},{"Name":"coordnum","Value":"1"}],"HostInfo":[{"HostName":"host1"}]}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{ "rc": 0 }{ "DeployMod": "standalone", "WebName": "standalone", "BusinessType": "sequoiadb", "Property": [ { "Name": "replicanum", "Type": "int", "Default": "1", "Valid": "1", "Display": "edit box", "Edit": "false", "Desc": "", "Level": "0", "WebName": "replica_num" }, { "Name": "datagroupnum", "Type": "int", "Default": "1", "Valid": "1", "Display": "edit box", "Edit": "false", "Desc": "", "Level": "0", "WebName": "data_group_num" }, { "Name": "catalognum", "Type": "int", "Default": "1", "Valid": "1", "Display": "edit box", "Edit": "false", "Desc": "1", "Level": "0", "WebName": "catalog_num" }, { "Name": "coordnum", "Type": "int", "Default": "1", "Valid": "1", "Display": "edit box", "Edit": "false", "Desc": "", "Level": "0", "WebName": "coord_num" } ] }{ "DeployMod": "distribution", "WebName": "distribution", "BusinessType": "sequoiadb", "Property": [ { "Name": "replicanum", "Type": "int", "Default": "3", "Valid": "2-3", "Display": "edit box", "Edit": "false", "Desc": "", "Level": "0", "WebName": "replica_num" }, { "Name": "datagroupnum", "Type": "int", "Default": "1", "Valid": "", "Display": "edit box", "Edit": "false", "Desc": "", "Level": "0", "WebName": "data_group_num" }, { "Name": "catalognum", "Type": "int", "Default": "1", "Valid": "", "Display": "edit box", "Edit": "false", "Desc": "1", "Level": "0", "WebName": "catalog_num" }, { "Name": "coordnum", "Type": "int", "Default": "0", "Valid": "0-7", "Display": "edit box", "Edit": "false", "Desc": "0 means one coord each host", "Level": "0", "WebName": "coord_num" } ] }</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <r>
-      <t xml:space="preserve">{"ClusterName":"c1","BusinessType":"sequoiadb","BusinessName":"b1", "ClusterType": "standalone", "Property": [ { "Name": "replica_num", </t>
+      <t>{"ClusterName":"c1","BusinessType":"sequoiadb","BusinessName":"b1", "ClusterType": "standalone", "Property": [ { "Name": "replica_num",</t>
     </r>
     <r>
       <rPr>
-        <b/>
         <sz val="10"/>
-        <color rgb="FF00B0F0"/>
         <rFont val="宋体"/>
         <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>"Value":""</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
+      <t xml:space="preserve"> "Value":"" </t>
     </r>
     <r>
       <rPr>
@@ -1158,179 +1316,6 @@
       </rPr>
       <t>}</t>
     </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>"Config": [ { "HostName": "host1", "username": "sdbadmin", "userpasswd": "sdbadmin", "usergroup": "sdbadmin_group", "datagroupname": "", "dbpath": "/home/db2//standalone/11830", "svcname": "11830", ...} ],"BusinessName": "b1", "BusinessType": "sequoiadb", "ClusterType": "standalone","ClusterName": "c1","Property": [ { "Name": "username", "Type": "string", "Default": "sdbadmin", "Valid": "", "Display": "edit box", "Edit": "true", "Desc": "", "Level": "0", "WebName": "user_name",... }]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{BusinessType, BusinessName,ClusterType, ClusterName, "Config":[{dbpath, svcname…} },...],"Property": [{ "Name": "username", "Type": "string", "Default": "sdbadmin", "Valid": "", "Display": "edit box", "Edit": "true", "Desc": "", "Level": "0", "WebName": "user_name",... }, ...] }</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>192.168.20.197:11814/?cmd=AddBusinessReq&amp;ConfigInfo={"ClusterName":"c1","BusinessType":"sequoiadb","BusinessName":"b1","ClusterType":"cluster", "Config": [ { "HostName": "host1", "username": "sdbadmin", "userpasswd": "sdbadmin", "usergroup": "sdbadmin_group", "datagroupname": "", "dbpath": "/home/db2/standalone/11830", "svcname": "11830", "diaglevel": "3", "role": "standalone", "logfilesz": "64", "logfilenum": "20", "transactionon": "false", "preferedinstance": "A", "numpagecleaners": "1", "pagecleaninterval": "1" } ]}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>host_info={ClusterName:cls1, host_info:[{IP, HostName, User, Passwd, SshPort:xxx, AgentPort:xxx},...], User:usr1, Passwd:Passwd1, SshPort:xxx}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ClusterInfo={ClusterName=cls1, Desc=xxx, SdbUser=sdbadmin, SdbPasswd=sdbadmin, SdbUserGroup=sdbadmin_group}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ClusterName=cls1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>一个host一个bson</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{ "rc": 0 }{ "BusinessList": [ { "BusinessType": "sequoiadb", "BusinessDesc": "haha" }, { "BusinessType": "sequoiasql", "BusinessDesc": "haha" } ] }</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>http://192.168.20.197:11814/?cmd=QueryClusterReq</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{ "rc": 0 }{ "ClusterName": "c1", "Desc": "" }</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{BusinessType, BusinessName,ClusterType, ClusterName, "Config":[{"HostName":"host1","datagroupname":"", "dbpath":"/home/db2//standalone/11830", "svcname":"11830", ...}, ...] }]}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>查询安装进度</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>查询安装进度响应</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"TaskID":"asd"}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>http://192.168.20.197:11814/?cmd=QueryInstallProgress&amp;Task={"TaskID":"ad"}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>create cluster</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>query cluster</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>login</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>check session</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>scan host</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>check host</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>add host</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>query host</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>query business template</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>config business</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>add business</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>query install progress</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"rc":0, "Detail":"","TaskID":"asd", "isFinish":true,"Status":"install/rollback","Progress":[{"Name":"Coord","TotalCount":7 "InstalledCount":100, "Desc":""}, {"Name":"Group1","TotalCount":3,"InstalledCount":50,"Desc":""},
-{"Name":"Group2","TotalCount":4,"InstalledCount":50,"Desc":""} ...]}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>修改密码</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>change passwd</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>User=xx&amp;Passwd=xx&amp;Timestamp=xx</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>User=admin&amp;Passwd=admin&amp;Newpasswd=admin&amp;Timestamp=123</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>http://192.168.20.197:11814/?cmd=change passwd&amp;user=admin&amp;passwd=admin&amp;Newpasswd=admin&amp;Timestamp=123</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>登出</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>logout</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>http://192.168.20.197:11814/?cmd=query host&amp;ClusterName=c1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>query business list</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>http://192.168.20.197:11814/?cmd=query business list</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{BusinessList:[{BusinessType, BusinessDesc},...]}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{ "rc": 0 }{ "ClusterType": "standalone", "ClusterTypeWebName": "aa", "BusinessType": "sequoiadb", "Property": [ { "Name": "replicanum", "Type": "int", "Default": "1", "Valid": "1", "Display": "edit box", "Edit": "false", "Desc": "", "Level": "0", "WebName": "replica_num" }, { "Name": "datagroupnum", "Type": "int", "Default": "1", "Valid": "1", "Display": "edit box", "Edit": "false", "Desc": "", "Level": "0", "WebName": "data_group_num" }, { "Name": "catalognum", "Type": "int", "Default": "1", "Valid": "1", "Display": "edit box", "Edit": "false", "Desc": "", "Level": "0", "WebName": "catalog_num" }, { "Name": "coordnum", "Type": "int", "Default": "1", "Valid": "1", "Display": "edit box", "Edit": "false", "Desc": "", "Level": "0", "WebName": "coord_num" } ] }{ "ClusterType": "cluster", "ClusterTypeWebName": "aa", "BusinessType": "sequoiadb", "Property": [ { "Name": "replicanum", "Type": "int", "Default": "3", "Valid": "2-3", "Display": "edit box", "Edit": "true", "Desc": "", "Level": "0", "WebName": "replica_num" }, { "Name": "datagroupnum", "Type": "int", "Default": "1", "Valid": "", "Display": "edit box", "Edit": "true", "Desc": "", "Level": "0", "WebName": "data_group_num" }, { "Name": "catalognum", "Type": "int", "Default": "1", "Valid": "", "Display": "edit box", "Edit": "true", "Desc": "", "Level": "0", "WebName": "catalog_num" }, { "Name": "coordnum", "Type": "int", "Default": "0", "Valid": "0-7", "Display": "edit box", "Edit": "true", "Desc": "", "Level": "0", "WebName": "coord_num" } ] }</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>http://192.168.20.197:11814/?cmd=query%20business%20template&amp;BusinessType=sequoiadb</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>http://192.168.20.197:11814/?cmd=config business&amp;TemplateInfo={"ClusterName":"c1","BusinessType":"sequoiadb","BusinessName":"b1","ClusterType":"standalone","Property":[{"Name":"replicanum","Value":"1"},{"Name":"datagroupnum","Value":"1"},{"Name":"catalognum","Value":"1"},{"Name":"coordnum","Value":"1"}],"HostInfo":[{"HostName":"host1"}]}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>http://192.168.20.197:11814/?cmd=create cluster&amp;ClusterInfo={"ClusterName":"cls1", "Desc":"xxx", "SdbUser":"sdbadmin", "SdbPasswd":"sdbadmin", "SdbUserGroup":"sdbadmin_group"}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1456,7 +1441,6 @@
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FF00B0F0"/>
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
@@ -2825,7 +2809,7 @@
     <row r="14" spans="1:12">
       <c r="A14" s="14"/>
       <c r="B14" s="14" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="C14" s="14">
         <v>11811</v>
@@ -2847,7 +2831,7 @@
     <row r="15" spans="1:12">
       <c r="A15" s="14"/>
       <c r="B15" s="14" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="C15" s="14">
         <v>11812</v>
@@ -2869,7 +2853,7 @@
     <row r="16" spans="1:12">
       <c r="A16" s="14"/>
       <c r="B16" s="14" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="C16" s="14">
         <v>11813</v>
@@ -2891,7 +2875,7 @@
     <row r="17" spans="1:12">
       <c r="A17" s="14"/>
       <c r="B17" s="14" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="C17" s="14">
         <v>11814</v>
@@ -2913,7 +2897,7 @@
     <row r="18" spans="1:12">
       <c r="A18" s="14"/>
       <c r="B18" s="14" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="C18" s="14">
         <v>3</v>
@@ -2937,7 +2921,7 @@
     <row r="19" spans="1:12">
       <c r="A19" s="14"/>
       <c r="B19" s="14" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="C19" s="14" t="s">
         <v>95</v>
@@ -2961,7 +2945,7 @@
     <row r="20" spans="1:12">
       <c r="A20" s="14"/>
       <c r="B20" s="14" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="C20" s="14">
         <v>64</v>
@@ -2974,7 +2958,7 @@
         <v>102</v>
       </c>
       <c r="G20" s="14" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H20" s="14"/>
       <c r="I20" s="14"/>
@@ -2985,7 +2969,7 @@
     <row r="21" spans="1:12">
       <c r="A21" s="14"/>
       <c r="B21" s="14" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="C21" s="14">
         <v>20</v>
@@ -2998,7 +2982,7 @@
         <v>102</v>
       </c>
       <c r="G21" s="14" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H21" s="14"/>
       <c r="I21" s="14"/>
@@ -3009,7 +2993,7 @@
     <row r="22" spans="1:12">
       <c r="A22" s="14"/>
       <c r="B22" s="14" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="C22" s="17" t="s">
         <v>109</v>
@@ -3057,7 +3041,7 @@
     <row r="24" spans="1:12">
       <c r="A24" s="14"/>
       <c r="B24" s="16" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="C24" s="11">
         <v>1</v>
@@ -3079,7 +3063,7 @@
     <row r="25" spans="1:12" s="19" customFormat="1">
       <c r="A25" s="16"/>
       <c r="B25" s="16" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="C25" s="11">
         <v>10000</v>
@@ -3424,13 +3408,13 @@
         <v>156</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>219</v>
+        <v>208</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>208</v>
+        <v>233</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>246</v>
+        <v>229</v>
       </c>
       <c r="E3" s="4"/>
       <c r="F3" s="4"/>
@@ -3441,7 +3425,7 @@
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="9" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D4" s="9" t="s">
         <v>130</v>
@@ -3459,30 +3443,30 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>220</v>
+        <v>209</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>212</v>
+        <v>234</v>
       </c>
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="9" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B7" s="4"/>
       <c r="C7" s="9" t="s">
-        <v>182</v>
+        <v>235</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>213</v>
+        <v>236</v>
       </c>
       <c r="E7" s="4"/>
       <c r="F7" s="4"/>
@@ -3500,10 +3484,10 @@
         <v>122</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>223</v>
+        <v>211</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D9" s="9"/>
       <c r="E9" s="4"/>
@@ -3515,10 +3499,10 @@
       </c>
       <c r="B10" s="4"/>
       <c r="C10" s="9" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="E10" s="4"/>
       <c r="F10" s="4"/>
@@ -3538,10 +3522,10 @@
         <v>124</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>224</v>
+        <v>212</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="D12" s="9"/>
       <c r="E12" s="4"/>
@@ -3553,7 +3537,7 @@
       </c>
       <c r="B13" s="4"/>
       <c r="C13" s="9" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="D13" s="9"/>
       <c r="E13" s="4"/>
@@ -3574,10 +3558,10 @@
         <v>126</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="D15" s="9"/>
       <c r="E15" s="4"/>
@@ -3589,7 +3573,7 @@
       </c>
       <c r="B16" s="4"/>
       <c r="C16" s="9" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D16" s="9"/>
       <c r="E16" s="4"/>
@@ -3610,13 +3594,13 @@
         <v>128</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="D18" s="23" t="s">
-        <v>239</v>
+        <v>225</v>
       </c>
       <c r="E18" s="4"/>
       <c r="F18" s="4"/>
@@ -3627,11 +3611,9 @@
       </c>
       <c r="B19" s="4"/>
       <c r="C19" s="9" t="s">
-        <v>183</v>
-      </c>
-      <c r="D19" s="9" t="s">
-        <v>210</v>
-      </c>
+        <v>239</v>
+      </c>
+      <c r="D19" s="9"/>
       <c r="E19" s="4"/>
       <c r="F19" s="4"/>
     </row>
@@ -3645,30 +3627,30 @@
       <c r="E20" s="4"/>
       <c r="F20" s="4"/>
     </row>
-    <row r="21" spans="1:6" ht="24">
+    <row r="21" spans="1:6">
       <c r="A21" s="9" t="s">
         <v>135</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>240</v>
+        <v>226</v>
       </c>
       <c r="C21" s="9"/>
       <c r="D21" s="9" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E21" s="4"/>
       <c r="F21" s="4"/>
     </row>
-    <row r="22" spans="1:6" ht="48">
+    <row r="22" spans="1:6" ht="36">
       <c r="A22" s="9" t="s">
         <v>136</v>
       </c>
       <c r="B22" s="4"/>
       <c r="C22" s="9" t="s">
-        <v>242</v>
+        <v>227</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="E22" s="4"/>
       <c r="F22" s="4"/>
@@ -3688,27 +3670,27 @@
         <v>137</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>227</v>
+        <v>241</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>186</v>
+        <v>242</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>244</v>
+        <v>228</v>
       </c>
       <c r="E24" s="4"/>
       <c r="F24" s="4"/>
     </row>
-    <row r="25" spans="1:6" ht="252">
+    <row r="25" spans="1:6" ht="240">
       <c r="A25" s="9" t="s">
         <v>138</v>
       </c>
       <c r="B25" s="4"/>
       <c r="C25" s="9" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E25" s="4"/>
       <c r="F25" s="4"/>
@@ -3728,13 +3710,13 @@
         <v>139</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>228</v>
+        <v>215</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>203</v>
+        <v>245</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="E27" s="4"/>
       <c r="F27" s="4"/>
@@ -3745,10 +3727,10 @@
       </c>
       <c r="B28" s="4"/>
       <c r="C28" s="9" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="E28" s="4"/>
       <c r="F28" s="4"/>
@@ -3768,13 +3750,13 @@
         <v>141</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>229</v>
+        <v>216</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>214</v>
+        <v>205</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="E30" s="4"/>
       <c r="F30" s="4"/>
@@ -3803,27 +3785,27 @@
     </row>
     <row r="33" spans="1:6" ht="24">
       <c r="A33" s="9" t="s">
-        <v>215</v>
+        <v>237</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>217</v>
+        <v>206</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="E33" s="4"/>
       <c r="F33" s="4"/>
     </row>
     <row r="34" spans="1:6" ht="96">
       <c r="A34" s="9" t="s">
-        <v>216</v>
+        <v>238</v>
       </c>
       <c r="B34" s="4"/>
       <c r="C34" s="9" t="s">
-        <v>231</v>
+        <v>217</v>
       </c>
       <c r="D34" s="9"/>
       <c r="E34" s="4"/>
@@ -3847,7 +3829,7 @@
         <v>145</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="D36" s="9"/>
       <c r="E36" s="4"/>
@@ -3861,7 +3843,7 @@
         <v>146</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="D37" s="9"/>
       <c r="E37" s="4"/>
@@ -3880,7 +3862,7 @@
         <v>153</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>222</v>
+        <v>210</v>
       </c>
       <c r="C45" s="9" t="s">
         <v>147</v>
@@ -3895,7 +3877,7 @@
       </c>
       <c r="B46" s="4"/>
       <c r="C46" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D46" s="9" t="s">
         <v>155</v>
@@ -3913,13 +3895,13 @@
     </row>
     <row r="48" spans="1:6">
       <c r="A48" s="9" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="C48" s="9" t="s">
-        <v>234</v>
+        <v>218</v>
       </c>
       <c r="D48" s="9"/>
       <c r="E48" s="4"/>
@@ -3927,11 +3909,11 @@
     </row>
     <row r="49" spans="1:6">
       <c r="A49" s="9" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B49" s="4"/>
       <c r="C49" s="9" t="s">
-        <v>160</v>
+        <v>231</v>
       </c>
       <c r="D49" s="9"/>
       <c r="E49" s="4"/>
@@ -3939,26 +3921,26 @@
     </row>
     <row r="50" spans="1:6" ht="36">
       <c r="A50" s="9" t="s">
-        <v>232</v>
+        <v>219</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>233</v>
+        <v>220</v>
       </c>
       <c r="C50" s="9" t="s">
-        <v>235</v>
+        <v>221</v>
       </c>
       <c r="D50" s="9" t="s">
-        <v>236</v>
+        <v>222</v>
       </c>
       <c r="E50" s="4"/>
       <c r="F50" s="4"/>
     </row>
     <row r="51" spans="1:6">
       <c r="A51" s="9" t="s">
-        <v>237</v>
+        <v>223</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>238</v>
+        <v>224</v>
       </c>
       <c r="C51" s="9"/>
       <c r="D51" s="9"/>
@@ -3975,7 +3957,7 @@
     </row>
     <row r="53" spans="1:6">
       <c r="A53" s="5" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B53" s="2"/>
       <c r="C53" s="5" t="s">
@@ -3987,11 +3969,11 @@
     </row>
     <row r="54" spans="1:6" ht="24">
       <c r="A54" s="5" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B54" s="2"/>
       <c r="C54" s="5" t="s">
-        <v>160</v>
+        <v>231</v>
       </c>
       <c r="D54" s="5" t="s">
         <v>149</v>
@@ -4004,7 +3986,7 @@
         <v>157</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C55" s="5" t="s">
         <v>158</v>
@@ -4015,29 +3997,29 @@
     </row>
     <row r="56" spans="1:6" ht="60">
       <c r="A56" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="B56" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="B56" s="2" t="s">
-        <v>164</v>
-      </c>
       <c r="C56" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="D56" s="5" t="s">
         <v>167</v>
-      </c>
-      <c r="D56" s="5" t="s">
-        <v>168</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" s="2"/>
     </row>
     <row r="57" spans="1:6" ht="48">
       <c r="A57" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="C57" s="5" t="s">
         <v>165</v>
-      </c>
-      <c r="B57" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="C57" s="5" t="s">
-        <v>166</v>
       </c>
       <c r="D57" s="5"/>
       <c r="E57" s="2"/>
@@ -4130,10 +4112,10 @@
     </row>
     <row r="8" spans="1:3" ht="40.5">
       <c r="B8" s="23" t="s">
+        <v>174</v>
+      </c>
+      <c r="C8" s="24" t="s">
         <v>175</v>
-      </c>
-      <c r="C8" s="24" t="s">
-        <v>176</v>
       </c>
     </row>
   </sheetData>

--- a/internal_doc/03.开发设计/OM_web接口.xlsx
+++ b/internal_doc/03.开发设计/OM_web接口.xlsx
@@ -279,7 +279,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="246">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="247">
   <si>
     <t>需求</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1116,10 +1116,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>http://192.168.20.197:11814/?cmd=QueryInstallProgress&amp;Task={"TaskID":"ad"}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>create cluster</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1197,6 +1193,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>http://192.168.20.197:11814/?cmd=query business list</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>{BusinessList:[{BusinessType, BusinessDesc},...]}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1246,10 +1246,6 @@
   </si>
   <si>
     <t>{ClusterName, rc, [IP, HostName, Firework, [Disk],[CPU]...]}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>http://192.168.20.197:11814/?cmd=query business list</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1316,6 +1312,14 @@
       </rPr>
       <t>}</t>
     </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://192.168.20.197:11814/?cmd=login&amp;user=admin&amp;passwd=admin&amp;Timestamp=123</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://192.168.20.197:11814/?cmd=query progress&amp;Task={"TaskID":"ad"}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3408,7 +3412,7 @@
         <v>156</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C3" s="9" t="s">
         <v>233</v>
@@ -3446,7 +3450,7 @@
         <v>171</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C6" s="9" t="s">
         <v>173</v>
@@ -3484,7 +3488,7 @@
         <v>122</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C9" s="9" t="s">
         <v>180</v>
@@ -3522,7 +3526,7 @@
         <v>124</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C12" s="9" t="s">
         <v>202</v>
@@ -3558,7 +3562,7 @@
         <v>126</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C15" s="9" t="s">
         <v>198</v>
@@ -3594,13 +3598,13 @@
         <v>128</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C18" s="9" t="s">
         <v>203</v>
       </c>
       <c r="D18" s="23" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E18" s="4"/>
       <c r="F18" s="4"/>
@@ -3632,11 +3636,11 @@
         <v>135</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C21" s="9"/>
       <c r="D21" s="9" t="s">
-        <v>240</v>
+        <v>226</v>
       </c>
       <c r="E21" s="4"/>
       <c r="F21" s="4"/>
@@ -3670,10 +3674,10 @@
         <v>137</v>
       </c>
       <c r="B24" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="C24" s="9" t="s">
         <v>241</v>
-      </c>
-      <c r="C24" s="9" t="s">
-        <v>242</v>
       </c>
       <c r="D24" s="9" t="s">
         <v>228</v>
@@ -3690,7 +3694,7 @@
         <v>195</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="E25" s="4"/>
       <c r="F25" s="4"/>
@@ -3710,13 +3714,13 @@
         <v>139</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E27" s="4"/>
       <c r="F27" s="4"/>
@@ -3750,7 +3754,7 @@
         <v>141</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C30" s="9" t="s">
         <v>205</v>
@@ -3794,7 +3798,7 @@
         <v>206</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>207</v>
+        <v>246</v>
       </c>
       <c r="E33" s="4"/>
       <c r="F33" s="4"/>
@@ -3805,7 +3809,7 @@
       </c>
       <c r="B34" s="4"/>
       <c r="C34" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D34" s="9"/>
       <c r="E34" s="4"/>
@@ -3862,7 +3866,7 @@
         <v>153</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C45" s="9" t="s">
         <v>147</v>
@@ -3893,7 +3897,7 @@
       <c r="E47" s="4"/>
       <c r="F47" s="4"/>
     </row>
-    <row r="48" spans="1:6">
+    <row r="48" spans="1:6" ht="24">
       <c r="A48" s="9" t="s">
         <v>168</v>
       </c>
@@ -3901,9 +3905,11 @@
         <v>230</v>
       </c>
       <c r="C48" s="9" t="s">
-        <v>218</v>
-      </c>
-      <c r="D48" s="9"/>
+        <v>217</v>
+      </c>
+      <c r="D48" s="9" t="s">
+        <v>245</v>
+      </c>
       <c r="E48" s="4"/>
       <c r="F48" s="4"/>
     </row>
@@ -3921,26 +3927,26 @@
     </row>
     <row r="50" spans="1:6" ht="36">
       <c r="A50" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="B50" s="4" t="s">
         <v>219</v>
       </c>
-      <c r="B50" s="4" t="s">
+      <c r="C50" s="9" t="s">
         <v>220</v>
       </c>
-      <c r="C50" s="9" t="s">
+      <c r="D50" s="9" t="s">
         <v>221</v>
-      </c>
-      <c r="D50" s="9" t="s">
-        <v>222</v>
       </c>
       <c r="E50" s="4"/>
       <c r="F50" s="4"/>
     </row>
     <row r="51" spans="1:6">
       <c r="A51" s="9" t="s">
+        <v>222</v>
+      </c>
+      <c r="B51" s="4" t="s">
         <v>223</v>
-      </c>
-      <c r="B51" s="4" t="s">
-        <v>224</v>
       </c>
       <c r="C51" s="9"/>
       <c r="D51" s="9"/>

--- a/internal_doc/03.开发设计/OM_web接口.xlsx
+++ b/internal_doc/03.开发设计/OM_web接口.xlsx
@@ -1092,10 +1092,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>192.168.20.197:11814/?cmd=AddBusinessReq&amp;ConfigInfo={"ClusterName":"c1","BusinessType":"sequoiadb","BusinessName":"b1","ClusterType":"cluster", "Config": [ { "HostName": "host1", "username": "sdbadmin", "userpasswd": "sdbadmin", "usergroup": "sdbadmin_group", "datagroupname": "", "dbpath": "/home/db2/standalone/11830", "svcname": "11830", "diaglevel": "3", "role": "standalone", "logfilesz": "64", "logfilenum": "20", "transactionon": "false", "preferedinstance": "A", "numpagecleaners": "1", "pagecleaninterval": "1" } ]}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>host_info={ClusterName:cls1, host_info:[{IP, HostName, User, Passwd, SshPort:xxx, AgentPort:xxx},...], User:usr1, Passwd:Passwd1, SshPort:xxx}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1320,6 +1316,10 @@
   </si>
   <si>
     <t>http://192.168.20.197:11814/?cmd=query progress&amp;Task={"TaskID":"ad"}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>192.168.20.197:11814/?cmd=add business&amp;ConfigInfo={"ClusterName":"c1","BusinessType":"sequoiadb","BusinessName":"b1","DeployMod":"distribution", "Config": [{ "HostName": "host1", "datagroupname": "", "dbpath": "/home/db2/standalone/11830", "svcname": "11830", "diaglevel": "3", "role": "standalone", "logfilesz": "64", "logfilenum": "20", "transactionon": "false", "preferedinstance": "A", "numpagecleaners": "1", "pagecleaninterval": "1", "datagroupname": "group1", "hjbuf": "128", "logbuffsize": "1024", "maxprefpool": "200", "maxreplsync": "10", "numpreload": "0", "sortbuf": "512", "syncstrategy": "none"} ]}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3412,13 +3412,13 @@
         <v>156</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E3" s="4"/>
       <c r="F3" s="4"/>
@@ -3450,13 +3450,13 @@
         <v>171</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C6" s="9" t="s">
         <v>173</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
@@ -3467,10 +3467,10 @@
       </c>
       <c r="B7" s="4"/>
       <c r="C7" s="9" t="s">
+        <v>234</v>
+      </c>
+      <c r="D7" s="9" t="s">
         <v>235</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>236</v>
       </c>
       <c r="E7" s="4"/>
       <c r="F7" s="4"/>
@@ -3488,7 +3488,7 @@
         <v>122</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C9" s="9" t="s">
         <v>180</v>
@@ -3526,10 +3526,10 @@
         <v>124</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D12" s="9"/>
       <c r="E12" s="4"/>
@@ -3562,7 +3562,7 @@
         <v>126</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C15" s="9" t="s">
         <v>198</v>
@@ -3598,13 +3598,13 @@
         <v>128</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D18" s="23" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E18" s="4"/>
       <c r="F18" s="4"/>
@@ -3615,7 +3615,7 @@
       </c>
       <c r="B19" s="4"/>
       <c r="C19" s="9" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D19" s="9"/>
       <c r="E19" s="4"/>
@@ -3636,11 +3636,11 @@
         <v>135</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C21" s="9"/>
       <c r="D21" s="9" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E21" s="4"/>
       <c r="F21" s="4"/>
@@ -3651,10 +3651,10 @@
       </c>
       <c r="B22" s="4"/>
       <c r="C22" s="9" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E22" s="4"/>
       <c r="F22" s="4"/>
@@ -3674,13 +3674,13 @@
         <v>137</v>
       </c>
       <c r="B24" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="C24" s="9" t="s">
         <v>240</v>
       </c>
-      <c r="C24" s="9" t="s">
-        <v>241</v>
-      </c>
       <c r="D24" s="9" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E24" s="4"/>
       <c r="F24" s="4"/>
@@ -3694,7 +3694,7 @@
         <v>195</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E25" s="4"/>
       <c r="F25" s="4"/>
@@ -3714,13 +3714,13 @@
         <v>139</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E27" s="4"/>
       <c r="F27" s="4"/>
@@ -3754,13 +3754,13 @@
         <v>141</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>201</v>
+        <v>246</v>
       </c>
       <c r="E30" s="4"/>
       <c r="F30" s="4"/>
@@ -3789,27 +3789,27 @@
     </row>
     <row r="33" spans="1:6" ht="24">
       <c r="A33" s="9" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="E33" s="4"/>
       <c r="F33" s="4"/>
     </row>
     <row r="34" spans="1:6" ht="96">
       <c r="A34" s="9" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B34" s="4"/>
       <c r="C34" s="9" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D34" s="9"/>
       <c r="E34" s="4"/>
@@ -3866,7 +3866,7 @@
         <v>153</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C45" s="9" t="s">
         <v>147</v>
@@ -3902,13 +3902,13 @@
         <v>168</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C48" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D48" s="9" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="E48" s="4"/>
       <c r="F48" s="4"/>
@@ -3919,7 +3919,7 @@
       </c>
       <c r="B49" s="4"/>
       <c r="C49" s="9" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D49" s="9"/>
       <c r="E49" s="4"/>
@@ -3927,26 +3927,26 @@
     </row>
     <row r="50" spans="1:6" ht="36">
       <c r="A50" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="B50" s="4" t="s">
         <v>218</v>
       </c>
-      <c r="B50" s="4" t="s">
+      <c r="C50" s="9" t="s">
         <v>219</v>
       </c>
-      <c r="C50" s="9" t="s">
+      <c r="D50" s="9" t="s">
         <v>220</v>
-      </c>
-      <c r="D50" s="9" t="s">
-        <v>221</v>
       </c>
       <c r="E50" s="4"/>
       <c r="F50" s="4"/>
     </row>
     <row r="51" spans="1:6">
       <c r="A51" s="9" t="s">
+        <v>221</v>
+      </c>
+      <c r="B51" s="4" t="s">
         <v>222</v>
-      </c>
-      <c r="B51" s="4" t="s">
-        <v>223</v>
       </c>
       <c r="C51" s="9"/>
       <c r="D51" s="9"/>
@@ -3979,7 +3979,7 @@
       </c>
       <c r="B54" s="2"/>
       <c r="C54" s="5" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D54" s="5" t="s">
         <v>149</v>

--- a/internal_doc/03.开发设计/OM_web接口.xlsx
+++ b/internal_doc/03.开发设计/OM_web接口.xlsx
@@ -1319,7 +1319,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>192.168.20.197:11814/?cmd=add business&amp;ConfigInfo={"ClusterName":"c1","BusinessType":"sequoiadb","BusinessName":"b1","DeployMod":"distribution", "Config": [{ "HostName": "host1", "datagroupname": "", "dbpath": "/home/db2/standalone/11830", "svcname": "11830", "diaglevel": "3", "role": "standalone", "logfilesz": "64", "logfilenum": "20", "transactionon": "false", "preferedinstance": "A", "numpagecleaners": "1", "pagecleaninterval": "1", "datagroupname": "group1", "hjbuf": "128", "logbuffsize": "1024", "maxprefpool": "200", "maxreplsync": "10", "numpreload": "0", "sortbuf": "512", "syncstrategy": "none"} ]}</t>
+    <t>192.168.20.197:11814/?cmd=add business&amp;ConfigInfo={"ClusterName":"c1","BusinessType":"sequoiadb","BusinessName":"b1","DeployMod":"standalone", "Config": [{ "HostName": "host1", "datagroupname": "", "dbpath": "/home/db2/standalone/11830", "svcname": "11830", "diaglevel": "3", "role": "standalone", "logfilesz": "64", "logfilenum": "20", "transactionon": "false", "preferedinstance": "A", "numpagecleaners": "1", "pagecleaninterval": "1", "datagroupname": "group1", "hjbuf": "128", "logbuffsize": "1024", "maxprefpool": "200", "maxreplsync": "10", "numpreload": "0", "sortbuf": "512", "syncstrategy": "none"} ]}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>

--- a/internal_doc/03.开发设计/OM_web接口.xlsx
+++ b/internal_doc/03.开发设计/OM_web接口.xlsx
@@ -1315,11 +1315,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>http://192.168.20.197:11814/?cmd=query progress&amp;Task={"TaskID":"ad"}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>192.168.20.197:11814/?cmd=add business&amp;ConfigInfo={"ClusterName":"c1","BusinessType":"sequoiadb","BusinessName":"b1","DeployMod":"standalone", "Config": [{ "HostName": "host1", "datagroupname": "", "dbpath": "/home/db2/standalone/11830", "svcname": "11830", "diaglevel": "3", "role": "standalone", "logfilesz": "64", "logfilenum": "20", "transactionon": "false", "preferedinstance": "A", "numpagecleaners": "1", "pagecleaninterval": "1", "datagroupname": "group1", "hjbuf": "128", "logbuffsize": "1024", "maxprefpool": "200", "maxreplsync": "10", "numpreload": "0", "sortbuf": "512", "syncstrategy": "none"} ]}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://192.168.20.197:11814/?cmd=query progress&amp;Task={"TaskID":"12345"}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3760,7 +3760,7 @@
         <v>204</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="E30" s="4"/>
       <c r="F30" s="4"/>
@@ -3798,7 +3798,7 @@
         <v>205</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E33" s="4"/>
       <c r="F33" s="4"/>

--- a/internal_doc/03.开发设计/OM_web接口.xlsx
+++ b/internal_doc/03.开发设计/OM_web接口.xlsx
@@ -279,7 +279,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="247">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="248">
   <si>
     <t>需求</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1008,9 +1008,6 @@
   <si>
     <t>{ClusterName, rc}</t>
     <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>HostInfo={ClusterName:cls1,HostInfo:[{IP/HostName:xxx, User:xxx, Passwd:xxx, SshPort:xxx, AgentPort:xxx}, ...],User:usr1,Passwd:Passwd1, SshPort:xxx, AgentPort:xxx}</t>
   </si>
   <si>
     <t>business_name=xxx&amp;ClusterName=xxx</t>
@@ -1320,6 +1317,14 @@
   </si>
   <si>
     <t>http://192.168.20.197:11814/?cmd=query progress&amp;Task={"TaskID":"12345"}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>HostInfo={ClusterName:cls1,HostInfo:[{IP/HostName:xxx, User:xxx, Passwd:xxx, SshPort:xxx, AgentPort:xxx}, ...],User:usr1,Passwd:Passwd1, SshPort:xxx, AgentPort:xxx}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://192.168.20.197:11814/?cmd=scan host&amp;HostInfo={"ClusterName":"c1","HostInfo":[{"IP":"192.168.20.197","User":"root","Passwd":"sequoiad",SshPort:"22",AgentPort:"11810"}],"User":"root","Passwd":"sequoiadb",SshPort:"22",AgentPort:"11810"}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2813,7 +2818,7 @@
     <row r="14" spans="1:12">
       <c r="A14" s="14"/>
       <c r="B14" s="14" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C14" s="14">
         <v>11811</v>
@@ -2835,7 +2840,7 @@
     <row r="15" spans="1:12">
       <c r="A15" s="14"/>
       <c r="B15" s="14" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C15" s="14">
         <v>11812</v>
@@ -2857,7 +2862,7 @@
     <row r="16" spans="1:12">
       <c r="A16" s="14"/>
       <c r="B16" s="14" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C16" s="14">
         <v>11813</v>
@@ -2879,7 +2884,7 @@
     <row r="17" spans="1:12">
       <c r="A17" s="14"/>
       <c r="B17" s="14" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C17" s="14">
         <v>11814</v>
@@ -2901,7 +2906,7 @@
     <row r="18" spans="1:12">
       <c r="A18" s="14"/>
       <c r="B18" s="14" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C18" s="14">
         <v>3</v>
@@ -2925,7 +2930,7 @@
     <row r="19" spans="1:12">
       <c r="A19" s="14"/>
       <c r="B19" s="14" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C19" s="14" t="s">
         <v>95</v>
@@ -2949,7 +2954,7 @@
     <row r="20" spans="1:12">
       <c r="A20" s="14"/>
       <c r="B20" s="14" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C20" s="14">
         <v>64</v>
@@ -2973,7 +2978,7 @@
     <row r="21" spans="1:12">
       <c r="A21" s="14"/>
       <c r="B21" s="14" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C21" s="14">
         <v>20</v>
@@ -2997,7 +3002,7 @@
     <row r="22" spans="1:12">
       <c r="A22" s="14"/>
       <c r="B22" s="14" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C22" s="17" t="s">
         <v>109</v>
@@ -3045,7 +3050,7 @@
     <row r="24" spans="1:12">
       <c r="A24" s="14"/>
       <c r="B24" s="16" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C24" s="11">
         <v>1</v>
@@ -3067,7 +3072,7 @@
     <row r="25" spans="1:12" s="19" customFormat="1">
       <c r="A25" s="16"/>
       <c r="B25" s="16" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C25" s="11">
         <v>10000</v>
@@ -3412,13 +3417,13 @@
         <v>156</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E3" s="4"/>
       <c r="F3" s="4"/>
@@ -3450,13 +3455,13 @@
         <v>171</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C6" s="9" t="s">
         <v>173</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
@@ -3467,10 +3472,10 @@
       </c>
       <c r="B7" s="4"/>
       <c r="C7" s="9" t="s">
+        <v>233</v>
+      </c>
+      <c r="D7" s="9" t="s">
         <v>234</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>235</v>
       </c>
       <c r="E7" s="4"/>
       <c r="F7" s="4"/>
@@ -3483,17 +3488,19 @@
       <c r="E8" s="4"/>
       <c r="F8" s="4"/>
     </row>
-    <row r="9" spans="1:6" ht="48">
+    <row r="9" spans="1:6" ht="60">
       <c r="A9" s="9" t="s">
         <v>122</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>180</v>
-      </c>
-      <c r="D9" s="9"/>
+        <v>246</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>247</v>
+      </c>
       <c r="E9" s="4"/>
       <c r="F9" s="4"/>
     </row>
@@ -3503,10 +3510,10 @@
       </c>
       <c r="B10" s="4"/>
       <c r="C10" s="9" t="s">
+        <v>195</v>
+      </c>
+      <c r="D10" s="9" t="s">
         <v>196</v>
-      </c>
-      <c r="D10" s="9" t="s">
-        <v>197</v>
       </c>
       <c r="E10" s="4"/>
       <c r="F10" s="4"/>
@@ -3526,10 +3533,10 @@
         <v>124</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D12" s="9"/>
       <c r="E12" s="4"/>
@@ -3541,7 +3548,7 @@
       </c>
       <c r="B13" s="4"/>
       <c r="C13" s="9" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D13" s="9"/>
       <c r="E13" s="4"/>
@@ -3562,10 +3569,10 @@
         <v>126</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D15" s="9"/>
       <c r="E15" s="4"/>
@@ -3598,13 +3605,13 @@
         <v>128</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D18" s="23" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E18" s="4"/>
       <c r="F18" s="4"/>
@@ -3615,7 +3622,7 @@
       </c>
       <c r="B19" s="4"/>
       <c r="C19" s="9" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D19" s="9"/>
       <c r="E19" s="4"/>
@@ -3636,11 +3643,11 @@
         <v>135</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C21" s="9"/>
       <c r="D21" s="9" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E21" s="4"/>
       <c r="F21" s="4"/>
@@ -3651,10 +3658,10 @@
       </c>
       <c r="B22" s="4"/>
       <c r="C22" s="9" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E22" s="4"/>
       <c r="F22" s="4"/>
@@ -3674,13 +3681,13 @@
         <v>137</v>
       </c>
       <c r="B24" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="C24" s="9" t="s">
         <v>239</v>
       </c>
-      <c r="C24" s="9" t="s">
-        <v>240</v>
-      </c>
       <c r="D24" s="9" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E24" s="4"/>
       <c r="F24" s="4"/>
@@ -3691,10 +3698,10 @@
       </c>
       <c r="B25" s="4"/>
       <c r="C25" s="9" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E25" s="4"/>
       <c r="F25" s="4"/>
@@ -3714,13 +3721,13 @@
         <v>139</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E27" s="4"/>
       <c r="F27" s="4"/>
@@ -3731,10 +3738,10 @@
       </c>
       <c r="B28" s="4"/>
       <c r="C28" s="9" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E28" s="4"/>
       <c r="F28" s="4"/>
@@ -3754,13 +3761,13 @@
         <v>141</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="E30" s="4"/>
       <c r="F30" s="4"/>
@@ -3789,27 +3796,27 @@
     </row>
     <row r="33" spans="1:6" ht="24">
       <c r="A33" s="9" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="E33" s="4"/>
       <c r="F33" s="4"/>
     </row>
     <row r="34" spans="1:6" ht="96">
       <c r="A34" s="9" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B34" s="4"/>
       <c r="C34" s="9" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D34" s="9"/>
       <c r="E34" s="4"/>
@@ -3833,7 +3840,7 @@
         <v>145</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D36" s="9"/>
       <c r="E36" s="4"/>
@@ -3847,7 +3854,7 @@
         <v>146</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D37" s="9"/>
       <c r="E37" s="4"/>
@@ -3866,7 +3873,7 @@
         <v>153</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C45" s="9" t="s">
         <v>147</v>
@@ -3902,13 +3909,13 @@
         <v>168</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C48" s="9" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D48" s="9" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="E48" s="4"/>
       <c r="F48" s="4"/>
@@ -3919,7 +3926,7 @@
       </c>
       <c r="B49" s="4"/>
       <c r="C49" s="9" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D49" s="9"/>
       <c r="E49" s="4"/>
@@ -3927,26 +3934,26 @@
     </row>
     <row r="50" spans="1:6" ht="36">
       <c r="A50" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="B50" s="4" t="s">
         <v>217</v>
       </c>
-      <c r="B50" s="4" t="s">
+      <c r="C50" s="9" t="s">
         <v>218</v>
       </c>
-      <c r="C50" s="9" t="s">
+      <c r="D50" s="9" t="s">
         <v>219</v>
-      </c>
-      <c r="D50" s="9" t="s">
-        <v>220</v>
       </c>
       <c r="E50" s="4"/>
       <c r="F50" s="4"/>
     </row>
     <row r="51" spans="1:6">
       <c r="A51" s="9" t="s">
+        <v>220</v>
+      </c>
+      <c r="B51" s="4" t="s">
         <v>221</v>
-      </c>
-      <c r="B51" s="4" t="s">
-        <v>222</v>
       </c>
       <c r="C51" s="9"/>
       <c r="D51" s="9"/>
@@ -3979,7 +3986,7 @@
       </c>
       <c r="B54" s="2"/>
       <c r="C54" s="5" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D54" s="5" t="s">
         <v>149</v>

--- a/internal_doc/03.开发设计/OM_web接口.xlsx
+++ b/internal_doc/03.开发设计/OM_web接口.xlsx
@@ -1145,11 +1145,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>{"rc":0, "Detail":"","TaskID":"asd", "isFinish":true,"Status":"install/rollback","Progress":[{"Name":"Coord","TotalCount":7 "InstalledCount":100, "Desc":""}, {"Name":"Group1","TotalCount":3,"InstalledCount":50,"Desc":""},
-{"Name":"Group2","TotalCount":4,"InstalledCount":50,"Desc":""} ...]}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>User=xx&amp;Passwd=xx&amp;Timestamp=xx</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1324,7 +1319,12 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>http://192.168.20.197:11814/?cmd=scan host&amp;HostInfo={"ClusterName":"c1","HostInfo":[{"IP":"192.168.20.197","User":"root","Passwd":"sequoiad",SshPort:"22",AgentPort:"11810"}],"User":"root","Passwd":"sequoiadb",SshPort:"22",AgentPort:"11810"}</t>
+    <t>{"rc":0, "Detail":"","TaskID":"asd", "isFinish":true,"Status":"install/rollback","Progress":[{"Name":"Coord","TotalCount":7 "InstalledCount":100, "Desc":""}, {"Name":"Group1","TotalCount":3,"InstalledCount":50,"Desc":""},
+{"Name":"Group2","TotalCount":4,"InstalledCount":50,"Desc":""} ...]}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://192.168.20.197:11814/?cmd=scan host&amp;HostInfo={"ClusterName":"c1","HostInfo":[{"IP":"192.168.20.196","User":"root","Passwd":"sequoiad",SshPort:"22",AgentPort:"11790"}],"User":"root","Passwd":"sequoiadb",SshPort:"22",AgentPort:"11810"}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3420,10 +3420,10 @@
         <v>205</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E3" s="4"/>
       <c r="F3" s="4"/>
@@ -3461,7 +3461,7 @@
         <v>173</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
@@ -3472,10 +3472,10 @@
       </c>
       <c r="B7" s="4"/>
       <c r="C7" s="9" t="s">
+        <v>232</v>
+      </c>
+      <c r="D7" s="9" t="s">
         <v>233</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>234</v>
       </c>
       <c r="E7" s="4"/>
       <c r="F7" s="4"/>
@@ -3496,7 +3496,7 @@
         <v>208</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D9" s="9" t="s">
         <v>247</v>
@@ -3611,7 +3611,7 @@
         <v>201</v>
       </c>
       <c r="D18" s="23" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E18" s="4"/>
       <c r="F18" s="4"/>
@@ -3622,7 +3622,7 @@
       </c>
       <c r="B19" s="4"/>
       <c r="C19" s="9" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D19" s="9"/>
       <c r="E19" s="4"/>
@@ -3643,11 +3643,11 @@
         <v>135</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C21" s="9"/>
       <c r="D21" s="9" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E21" s="4"/>
       <c r="F21" s="4"/>
@@ -3658,7 +3658,7 @@
       </c>
       <c r="B22" s="4"/>
       <c r="C22" s="9" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D22" s="9" t="s">
         <v>202</v>
@@ -3681,13 +3681,13 @@
         <v>137</v>
       </c>
       <c r="B24" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="C24" s="9" t="s">
         <v>238</v>
       </c>
-      <c r="C24" s="9" t="s">
-        <v>239</v>
-      </c>
       <c r="D24" s="9" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E24" s="4"/>
       <c r="F24" s="4"/>
@@ -3701,7 +3701,7 @@
         <v>194</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E25" s="4"/>
       <c r="F25" s="4"/>
@@ -3724,10 +3724,10 @@
         <v>212</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E27" s="4"/>
       <c r="F27" s="4"/>
@@ -3767,7 +3767,7 @@
         <v>203</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="E30" s="4"/>
       <c r="F30" s="4"/>
@@ -3796,27 +3796,27 @@
     </row>
     <row r="33" spans="1:6" ht="24">
       <c r="A33" s="9" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C33" s="9" t="s">
         <v>204</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="E33" s="4"/>
       <c r="F33" s="4"/>
     </row>
     <row r="34" spans="1:6" ht="96">
       <c r="A34" s="9" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B34" s="4"/>
       <c r="C34" s="9" t="s">
-        <v>214</v>
+        <v>246</v>
       </c>
       <c r="D34" s="9"/>
       <c r="E34" s="4"/>
@@ -3909,13 +3909,13 @@
         <v>168</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C48" s="9" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D48" s="9" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E48" s="4"/>
       <c r="F48" s="4"/>
@@ -3926,7 +3926,7 @@
       </c>
       <c r="B49" s="4"/>
       <c r="C49" s="9" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D49" s="9"/>
       <c r="E49" s="4"/>
@@ -3934,26 +3934,26 @@
     </row>
     <row r="50" spans="1:6" ht="36">
       <c r="A50" s="9" t="s">
+        <v>215</v>
+      </c>
+      <c r="B50" s="4" t="s">
         <v>216</v>
       </c>
-      <c r="B50" s="4" t="s">
+      <c r="C50" s="9" t="s">
         <v>217</v>
       </c>
-      <c r="C50" s="9" t="s">
+      <c r="D50" s="9" t="s">
         <v>218</v>
-      </c>
-      <c r="D50" s="9" t="s">
-        <v>219</v>
       </c>
       <c r="E50" s="4"/>
       <c r="F50" s="4"/>
     </row>
     <row r="51" spans="1:6">
       <c r="A51" s="9" t="s">
+        <v>219</v>
+      </c>
+      <c r="B51" s="4" t="s">
         <v>220</v>
-      </c>
-      <c r="B51" s="4" t="s">
-        <v>221</v>
       </c>
       <c r="C51" s="9"/>
       <c r="D51" s="9"/>
@@ -3986,7 +3986,7 @@
       </c>
       <c r="B54" s="2"/>
       <c r="C54" s="5" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D54" s="5" t="s">
         <v>149</v>

--- a/internal_doc/03.开发设计/OM_web接口.xlsx
+++ b/internal_doc/03.开发设计/OM_web接口.xlsx
@@ -1060,6 +1060,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>host_info={ClusterName:cls1, host_info:[{IP, HostName, User, Passwd, SshPort:xxx, AgentPort:xxx},...], User:usr1, Passwd:Passwd1, SshPort:xxx, AgentPort:xxx}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>{[{IP, HostName, rc, Firework, [Disk],[CPU]…}, ...]}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1086,10 +1090,6 @@
   </si>
   <si>
     <t>{BusinessType, BusinessName,ClusterType, ClusterName, "Config":[{dbpath, svcname…} },...],"Property": [{ "Name": "username", "Type": "string", "Default": "sdbadmin", "Valid": "", "Display": "edit box", "Edit": "true", "Desc": "", "Level": "0", "WebName": "user_name",... }, ...] }</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>host_info={ClusterName:cls1, host_info:[{IP, HostName, User, Passwd, SshPort:xxx, AgentPort:xxx},...], User:usr1, Passwd:Passwd1, SshPort:xxx}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -3510,10 +3510,10 @@
       </c>
       <c r="B10" s="4"/>
       <c r="C10" s="9" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E10" s="4"/>
       <c r="F10" s="4"/>
@@ -3536,7 +3536,7 @@
         <v>209</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="D12" s="9"/>
       <c r="E12" s="4"/>
@@ -3548,7 +3548,7 @@
       </c>
       <c r="B13" s="4"/>
       <c r="C13" s="9" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D13" s="9"/>
       <c r="E13" s="4"/>
@@ -3572,7 +3572,7 @@
         <v>210</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D15" s="9"/>
       <c r="E15" s="4"/>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="B25" s="4"/>
       <c r="C25" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D25" s="9" t="s">
         <v>240</v>
@@ -3738,10 +3738,10 @@
       </c>
       <c r="B28" s="4"/>
       <c r="C28" s="9" t="s">
+        <v>200</v>
+      </c>
+      <c r="D28" s="9" t="s">
         <v>199</v>
-      </c>
-      <c r="D28" s="9" t="s">
-        <v>198</v>
       </c>
       <c r="E28" s="4"/>
       <c r="F28" s="4"/>

--- a/internal_doc/03.开发设计/OM_web接口.xlsx
+++ b/internal_doc/03.开发设计/OM_web接口.xlsx
@@ -279,7 +279,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="248">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="249">
   <si>
     <t>需求</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1189,10 +1189,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>http://192.168.20.197:11814/?cmd=query%20business%20template&amp;BusinessType=sequoiadb</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>http://192.168.20.197:11814/?cmd=create cluster&amp;ClusterInfo={"ClusterName":"cls1", "Desc":"xxx", "SdbUser":"sdbadmin", "SdbPasswd":"sdbadmin", "SdbUserGroup":"sdbadmin_group"}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1242,14 +1238,6 @@
   </si>
   <si>
     <t>BusinessType=xxx</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>http://192.168.20.197:11814/?cmd=config business&amp;TemplateInfo={"ClusterName":"c1","BusinessType":"sequoiadb","BusinessName":"b1","DeployMod":"standalone","Property":[{"Name":"replicanum","Value":"1"},{"Name":"datagroupnum","Value":"1"},{"Name":"catalognum","Value":"1"},{"Name":"coordnum","Value":"1"}],"HostInfo":[{"HostName":"host1"}]}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{ "rc": 0 }{ "DeployMod": "standalone", "WebName": "standalone", "BusinessType": "sequoiadb", "Property": [ { "Name": "replicanum", "Type": "int", "Default": "1", "Valid": "1", "Display": "edit box", "Edit": "false", "Desc": "", "Level": "0", "WebName": "replica_num" }, { "Name": "datagroupnum", "Type": "int", "Default": "1", "Valid": "1", "Display": "edit box", "Edit": "false", "Desc": "", "Level": "0", "WebName": "data_group_num" }, { "Name": "catalognum", "Type": "int", "Default": "1", "Valid": "1", "Display": "edit box", "Edit": "false", "Desc": "1", "Level": "0", "WebName": "catalog_num" }, { "Name": "coordnum", "Type": "int", "Default": "1", "Valid": "1", "Display": "edit box", "Edit": "false", "Desc": "", "Level": "0", "WebName": "coord_num" } ] }{ "DeployMod": "distribution", "WebName": "distribution", "BusinessType": "sequoiadb", "Property": [ { "Name": "replicanum", "Type": "int", "Default": "3", "Valid": "2-3", "Display": "edit box", "Edit": "false", "Desc": "", "Level": "0", "WebName": "replica_num" }, { "Name": "datagroupnum", "Type": "int", "Default": "1", "Valid": "", "Display": "edit box", "Edit": "false", "Desc": "", "Level": "0", "WebName": "data_group_num" }, { "Name": "catalognum", "Type": "int", "Default": "1", "Valid": "", "Display": "edit box", "Edit": "false", "Desc": "1", "Level": "0", "WebName": "catalog_num" }, { "Name": "coordnum", "Type": "int", "Default": "0", "Valid": "0-7", "Display": "edit box", "Edit": "false", "Desc": "0 means one coord each host", "Level": "0", "WebName": "coord_num" } ] }</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1325,6 +1313,22 @@
   </si>
   <si>
     <t>http://192.168.20.197:11814/?cmd=scan host&amp;HostInfo={"ClusterName":"c1","HostInfo":[{"IP":"192.168.20.196","User":"root","Passwd":"sequoiad",SshPort:"22",AgentPort:"11790"}],"User":"root","Passwd":"sequoiadb",SshPort:"22",AgentPort:"11810"}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://192.168.20.197:11814/?cmd=query business template&amp;BusinessType=sequoiadb</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{ "rc": 0 }{ "DeployMod": "standalone", "WebName": "standalone", "BusinessType": "sequoiadb", "Property": [ { "Name": "replicanum", "Type": "int", "Default": "1", "Valid": "1", "Display": "edit box", "Edit": "false", "Desc": "", "Level": "0", "WebName": "replica_num" }, { "Name": "datagroupnum", "Type": "int", "Default": "1", "Valid": "1", "Display": "edit box", "Edit": "false", "Desc": "", "Level": "0", "WebName": "data_group_num" }, { "Name": "catalognum", "Type": "int", "Default": "1", "Valid": "1", "Display": "edit box", "Edit": "false", "Desc": "1", "Level": "0", "WebName": "catalog_num" }, { "Name": "coordnum", "Type": "int", "Default": "1", "Valid": "1", "Display": "edit box", "Edit": "false", "Desc": "", "Level": "0", "WebName": "coord_num" }, { "Name": "transactionon", "Type": "string", "Default": "false", "Valid": "true,false", "Display": "edit box", "Edit": "false", "Desc": "", "Level": "0", "WebName": "transactionon" } ] }{ "DeployMod": "distribution", "WebName": "distribution", "BusinessType": "sequoiadb", "Property": [ { "Name": "replicanum", "Type": "int", "Default": "3", "Valid": "1-7", "Display": "edit box", "Edit": "true", "Desc": "", "Level": "0", "WebName": "replica_num" }, { "Name": "datagroupnum", "Type": "int", "Default": "1", "Valid": "", "Display": "edit box", "Edit": "false", "Desc": "", "Level": "0", "WebName": "data_group_num" }, { "Name": "catalognum", "Type": "int", "Default": "1", "Valid": "", "Display": "edit box", "Edit": "false", "Desc": "1", "Level": "0", "WebName": "catalog_num" }, { "Name": "coordnum", "Type": "int", "Default": "0", "Valid": "0-7", "Display": "edit box", "Edit": "false", "Desc": "0 means one coord each host", "Level": "0", "WebName": "coord_num" }, { "Name": "transactionon", "Type": "string", "Default": "false", "Valid": "true,false", "Display": "edit box", "Edit": "false", "Desc": "", "Level": "0", "WebName": "transactionon" } ] }</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://192.168.20.197:11814/?cmd=config business&amp;TemplateInfo={"ClusterName":"c1","BusinessType":"sequoiadb","BusinessName":"b1","DeployMod":"distribution","Property":[{"Name":"replicanum","Value":"1"},{"Name":"datagroupnum","Value":"2"},{"Name":"catalognum","Value":"1"},{"Name":"coordnum","Value":"1"},{"Name":"transactionon","Value":"false"}],"HostInfo":[{"HostName":"host1"}]}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://192.168.20.197:11814/?cmd=check host&amp;HostInfo={"ClusterName":"c1","HostInfo":[{"IP":"192.168.20.196","User":"root","Passwd":"sequoiad",SshPort:"22",AgentPort:"11790"}],"User":"root","Passwd":"sequoiadb",SshPort:"22",AgentPort:"11810"}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1593,6 +1597,10 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1611,10 +1619,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2026,7 +2030,7 @@
       </c>
     </row>
     <row r="3" spans="1:8">
-      <c r="A3" s="25" t="s">
+      <c r="A3" s="27" t="s">
         <v>12</v>
       </c>
       <c r="B3" s="4" t="s">
@@ -2044,7 +2048,7 @@
       <c r="H3" s="4"/>
     </row>
     <row r="4" spans="1:8" ht="13.5">
-      <c r="A4" s="26"/>
+      <c r="A4" s="28"/>
       <c r="B4" s="4" t="s">
         <v>5</v>
       </c>
@@ -2060,7 +2064,7 @@
       <c r="H4" s="4"/>
     </row>
     <row r="5" spans="1:8" ht="13.5">
-      <c r="A5" s="26"/>
+      <c r="A5" s="28"/>
       <c r="B5" s="4" t="s">
         <v>8</v>
       </c>
@@ -2076,7 +2080,7 @@
       <c r="H5" s="4"/>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" s="27"/>
+      <c r="A6" s="29"/>
       <c r="B6" s="4" t="s">
         <v>13</v>
       </c>
@@ -2092,7 +2096,7 @@
       <c r="H6" s="4"/>
     </row>
     <row r="7" spans="1:8" ht="24">
-      <c r="A7" s="28" t="s">
+      <c r="A7" s="30" t="s">
         <v>24</v>
       </c>
       <c r="B7" s="4" t="s">
@@ -2110,7 +2114,7 @@
       <c r="H7" s="4"/>
     </row>
     <row r="8" spans="1:8" ht="36">
-      <c r="A8" s="29"/>
+      <c r="A8" s="31"/>
       <c r="B8" s="4" t="s">
         <v>17</v>
       </c>
@@ -2128,7 +2132,7 @@
       <c r="H8" s="4"/>
     </row>
     <row r="9" spans="1:8" ht="72">
-      <c r="A9" s="29"/>
+      <c r="A9" s="31"/>
       <c r="B9" s="4" t="s">
         <v>18</v>
       </c>
@@ -2146,7 +2150,7 @@
       <c r="H9" s="4"/>
     </row>
     <row r="10" spans="1:8" ht="24">
-      <c r="A10" s="30"/>
+      <c r="A10" s="32"/>
       <c r="B10" s="4" t="s">
         <v>21</v>
       </c>
@@ -2184,7 +2188,7 @@
       <c r="H11" s="4"/>
     </row>
     <row r="12" spans="1:8" ht="24">
-      <c r="A12" s="28" t="s">
+      <c r="A12" s="30" t="s">
         <v>26</v>
       </c>
       <c r="B12" s="4" t="s">
@@ -2202,7 +2206,7 @@
       <c r="H12" s="4"/>
     </row>
     <row r="13" spans="1:8">
-      <c r="A13" s="29"/>
+      <c r="A13" s="31"/>
       <c r="B13" s="4" t="s">
         <v>32</v>
       </c>
@@ -2218,7 +2222,7 @@
       <c r="H13" s="4"/>
     </row>
     <row r="14" spans="1:8" ht="24">
-      <c r="A14" s="29"/>
+      <c r="A14" s="31"/>
       <c r="B14" s="4" t="s">
         <v>33</v>
       </c>
@@ -2236,7 +2240,7 @@
       <c r="H14" s="4"/>
     </row>
     <row r="15" spans="1:8">
-      <c r="A15" s="29"/>
+      <c r="A15" s="31"/>
       <c r="B15" s="4" t="s">
         <v>35</v>
       </c>
@@ -2252,7 +2256,7 @@
       <c r="H15" s="4"/>
     </row>
     <row r="16" spans="1:8">
-      <c r="A16" s="29"/>
+      <c r="A16" s="31"/>
       <c r="B16" s="4" t="s">
         <v>57</v>
       </c>
@@ -2264,7 +2268,7 @@
       <c r="H16" s="4"/>
     </row>
     <row r="17" spans="1:8" ht="48">
-      <c r="A17" s="29"/>
+      <c r="A17" s="31"/>
       <c r="B17" s="4" t="s">
         <v>30</v>
       </c>
@@ -2282,7 +2286,7 @@
       <c r="H17" s="4"/>
     </row>
     <row r="18" spans="1:8">
-      <c r="A18" s="29"/>
+      <c r="A18" s="31"/>
       <c r="B18" s="4" t="s">
         <v>38</v>
       </c>
@@ -2298,7 +2302,7 @@
       <c r="H18" s="4"/>
     </row>
     <row r="19" spans="1:8">
-      <c r="A19" s="29"/>
+      <c r="A19" s="31"/>
       <c r="B19" s="4" t="s">
         <v>41</v>
       </c>
@@ -2314,7 +2318,7 @@
       <c r="H19" s="4"/>
     </row>
     <row r="20" spans="1:8">
-      <c r="A20" s="29"/>
+      <c r="A20" s="31"/>
       <c r="B20" s="4" t="s">
         <v>40</v>
       </c>
@@ -2330,7 +2334,7 @@
       <c r="H20" s="4"/>
     </row>
     <row r="21" spans="1:8" ht="24">
-      <c r="A21" s="29"/>
+      <c r="A21" s="31"/>
       <c r="B21" s="4" t="s">
         <v>44</v>
       </c>
@@ -2348,7 +2352,7 @@
       <c r="H21" s="4"/>
     </row>
     <row r="22" spans="1:8" ht="24">
-      <c r="A22" s="29"/>
+      <c r="A22" s="31"/>
       <c r="B22" s="4" t="s">
         <v>47</v>
       </c>
@@ -2364,7 +2368,7 @@
       <c r="H22" s="4"/>
     </row>
     <row r="23" spans="1:8" ht="24">
-      <c r="A23" s="29"/>
+      <c r="A23" s="31"/>
       <c r="B23" s="4" t="s">
         <v>49</v>
       </c>
@@ -3420,10 +3424,10 @@
         <v>205</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E3" s="4"/>
       <c r="F3" s="4"/>
@@ -3461,7 +3465,7 @@
         <v>173</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
@@ -3472,10 +3476,10 @@
       </c>
       <c r="B7" s="4"/>
       <c r="C7" s="9" t="s">
+        <v>231</v>
+      </c>
+      <c r="D7" s="9" t="s">
         <v>232</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>233</v>
       </c>
       <c r="E7" s="4"/>
       <c r="F7" s="4"/>
@@ -3496,10 +3500,10 @@
         <v>208</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="E9" s="4"/>
       <c r="F9" s="4"/>
@@ -3528,7 +3532,7 @@
       <c r="E11" s="4"/>
       <c r="F11" s="4"/>
     </row>
-    <row r="12" spans="1:6" ht="48">
+    <row r="12" spans="1:6" ht="60">
       <c r="A12" s="9" t="s">
         <v>124</v>
       </c>
@@ -3538,7 +3542,9 @@
       <c r="C12" s="9" t="s">
         <v>193</v>
       </c>
-      <c r="D12" s="9"/>
+      <c r="D12" s="9" t="s">
+        <v>248</v>
+      </c>
       <c r="E12" s="4"/>
       <c r="F12" s="4"/>
     </row>
@@ -3622,7 +3628,7 @@
       </c>
       <c r="B19" s="4"/>
       <c r="C19" s="9" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D19" s="9"/>
       <c r="E19" s="4"/>
@@ -3681,13 +3687,13 @@
         <v>137</v>
       </c>
       <c r="B24" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="C24" s="9" t="s">
         <v>237</v>
       </c>
-      <c r="C24" s="9" t="s">
-        <v>238</v>
-      </c>
       <c r="D24" s="9" t="s">
-        <v>225</v>
+        <v>245</v>
       </c>
       <c r="E24" s="4"/>
       <c r="F24" s="4"/>
@@ -3701,7 +3707,7 @@
         <v>195</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="E25" s="4"/>
       <c r="F25" s="4"/>
@@ -3724,10 +3730,10 @@
         <v>212</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="E27" s="4"/>
       <c r="F27" s="4"/>
@@ -3767,7 +3773,7 @@
         <v>203</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="E30" s="4"/>
       <c r="F30" s="4"/>
@@ -3796,27 +3802,27 @@
     </row>
     <row r="33" spans="1:6" ht="24">
       <c r="A33" s="9" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C33" s="9" t="s">
         <v>204</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="E33" s="4"/>
       <c r="F33" s="4"/>
     </row>
     <row r="34" spans="1:6" ht="96">
       <c r="A34" s="9" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B34" s="4"/>
       <c r="C34" s="9" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="D34" s="9"/>
       <c r="E34" s="4"/>
@@ -3909,13 +3915,13 @@
         <v>168</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C48" s="9" t="s">
         <v>214</v>
       </c>
       <c r="D48" s="9" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="E48" s="4"/>
       <c r="F48" s="4"/>
@@ -3926,7 +3932,7 @@
       </c>
       <c r="B49" s="4"/>
       <c r="C49" s="9" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D49" s="9"/>
       <c r="E49" s="4"/>
@@ -3986,7 +3992,7 @@
       </c>
       <c r="B54" s="2"/>
       <c r="C54" s="5" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D54" s="5" t="s">
         <v>149</v>
@@ -4039,16 +4045,16 @@
       <c r="F57" s="2"/>
     </row>
     <row r="58" spans="1:6" s="21" customFormat="1">
-      <c r="A58" s="31" t="s">
+      <c r="A58" s="25" t="s">
         <v>152</v>
       </c>
-      <c r="B58" s="32"/>
-      <c r="C58" s="31"/>
-      <c r="D58" s="31" t="s">
+      <c r="B58" s="26"/>
+      <c r="C58" s="25"/>
+      <c r="D58" s="25" t="s">
         <v>150</v>
       </c>
-      <c r="E58" s="32"/>
-      <c r="F58" s="32"/>
+      <c r="E58" s="26"/>
+      <c r="F58" s="26"/>
     </row>
     <row r="59" spans="1:6">
       <c r="A59" s="5"/>

--- a/internal_doc/03.开发设计/OM_web接口.xlsx
+++ b/internal_doc/03.开发设计/OM_web接口.xlsx
@@ -279,7 +279,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="249">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="250">
   <si>
     <t>需求</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1328,7 +1328,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>http://192.168.20.197:11814/?cmd=check host&amp;HostInfo={"ClusterName":"c1","HostInfo":[{"IP":"192.168.20.196","User":"root","Passwd":"sequoiad",SshPort:"22",AgentPort:"11790"}],"User":"root","Passwd":"sequoiadb",SshPort:"22",AgentPort:"11810"}</t>
+    <t>http://192.168.20.197:11814/?cmd=check host&amp;HostInfo={"ClusterName":"c1","HostInfo":[{"IP":"192.168.20.196","HostName":"aa","User":"root","Passwd":"sequoiad",SshPort:"22",AgentPort:"11790"}],"User":"root","Passwd":"sequoiadb",SshPort:"22",AgentPort:"11810"}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://192.168.20.197:11814/?cmd=add host&amp;HostInfo={"ClusterName":"c1","HostInfo":[{"IP":"192.168.20.196","HostName":"aa","User":"root","Passwd":"sequoiad",SshPort:"22",AgentPort:"11790"}],"User":"root","Passwd":"sequoiadb",SshPort:"22",AgentPort:"11810",InstallPath:"/opt/sequoiadb/"}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3570,7 +3574,7 @@
       <c r="E14" s="4"/>
       <c r="F14" s="4"/>
     </row>
-    <row r="15" spans="1:6" ht="60">
+    <row r="15" spans="1:6" ht="72">
       <c r="A15" s="9" t="s">
         <v>126</v>
       </c>
@@ -3580,7 +3584,9 @@
       <c r="C15" s="9" t="s">
         <v>198</v>
       </c>
-      <c r="D15" s="9"/>
+      <c r="D15" s="9" t="s">
+        <v>249</v>
+      </c>
       <c r="E15" s="4"/>
       <c r="F15" s="4"/>
     </row>

--- a/internal_doc/03.开发设计/OM_web接口.xlsx
+++ b/internal_doc/03.开发设计/OM_web接口.xlsx
@@ -1177,10 +1177,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>query business list</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>http://192.168.20.197:11814/?cmd=query business list</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1333,6 +1329,10 @@
   </si>
   <si>
     <t>http://192.168.20.197:11814/?cmd=add host&amp;HostInfo={"ClusterName":"c1","HostInfo":[{"IP":"192.168.20.196","HostName":"aa","User":"root","Passwd":"sequoiad",SshPort:"22",AgentPort:"11790"}],"User":"root","Passwd":"sequoiadb",SshPort:"22",AgentPort:"11810",InstallPath:"/opt/sequoiadb/"}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>query business type</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3428,10 +3428,10 @@
         <v>205</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E3" s="4"/>
       <c r="F3" s="4"/>
@@ -3469,7 +3469,7 @@
         <v>173</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
@@ -3480,10 +3480,10 @@
       </c>
       <c r="B7" s="4"/>
       <c r="C7" s="9" t="s">
+        <v>230</v>
+      </c>
+      <c r="D7" s="9" t="s">
         <v>231</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>232</v>
       </c>
       <c r="E7" s="4"/>
       <c r="F7" s="4"/>
@@ -3504,10 +3504,10 @@
         <v>208</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="E9" s="4"/>
       <c r="F9" s="4"/>
@@ -3547,7 +3547,7 @@
         <v>193</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E12" s="4"/>
       <c r="F12" s="4"/>
@@ -3585,7 +3585,7 @@
         <v>198</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E15" s="4"/>
       <c r="F15" s="4"/>
@@ -3634,7 +3634,7 @@
       </c>
       <c r="B19" s="4"/>
       <c r="C19" s="9" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D19" s="9"/>
       <c r="E19" s="4"/>
@@ -3655,11 +3655,11 @@
         <v>135</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>222</v>
+        <v>249</v>
       </c>
       <c r="C21" s="9"/>
       <c r="D21" s="9" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E21" s="4"/>
       <c r="F21" s="4"/>
@@ -3670,7 +3670,7 @@
       </c>
       <c r="B22" s="4"/>
       <c r="C22" s="9" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D22" s="9" t="s">
         <v>202</v>
@@ -3693,13 +3693,13 @@
         <v>137</v>
       </c>
       <c r="B24" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="C24" s="9" t="s">
         <v>236</v>
       </c>
-      <c r="C24" s="9" t="s">
-        <v>237</v>
-      </c>
       <c r="D24" s="9" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="E24" s="4"/>
       <c r="F24" s="4"/>
@@ -3713,7 +3713,7 @@
         <v>195</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="E25" s="4"/>
       <c r="F25" s="4"/>
@@ -3736,10 +3736,10 @@
         <v>212</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="E27" s="4"/>
       <c r="F27" s="4"/>
@@ -3779,7 +3779,7 @@
         <v>203</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E30" s="4"/>
       <c r="F30" s="4"/>
@@ -3808,27 +3808,27 @@
     </row>
     <row r="33" spans="1:6" ht="24">
       <c r="A33" s="9" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C33" s="9" t="s">
         <v>204</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E33" s="4"/>
       <c r="F33" s="4"/>
     </row>
     <row r="34" spans="1:6" ht="96">
       <c r="A34" s="9" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B34" s="4"/>
       <c r="C34" s="9" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D34" s="9"/>
       <c r="E34" s="4"/>
@@ -3921,13 +3921,13 @@
         <v>168</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C48" s="9" t="s">
         <v>214</v>
       </c>
       <c r="D48" s="9" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E48" s="4"/>
       <c r="F48" s="4"/>
@@ -3938,7 +3938,7 @@
       </c>
       <c r="B49" s="4"/>
       <c r="C49" s="9" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D49" s="9"/>
       <c r="E49" s="4"/>
@@ -3998,7 +3998,7 @@
       </c>
       <c r="B54" s="2"/>
       <c r="C54" s="5" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D54" s="5" t="s">
         <v>149</v>

--- a/internal_doc/03.开发设计/OM_web接口.xlsx
+++ b/internal_doc/03.开发设计/OM_web接口.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="6510" activeTab="3"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="6510" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="需求" sheetId="1" r:id="rId1"/>
@@ -12,6 +12,7 @@
     <sheet name="表结构设计" sheetId="3" r:id="rId3"/>
     <sheet name="消息定义" sheetId="4" r:id="rId4"/>
     <sheet name="Sheet1" sheetId="5" r:id="rId5"/>
+    <sheet name="agent接口" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="124519"/>
 </workbook>
@@ -279,7 +280,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="250">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="258">
   <si>
     <t>需求</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1335,12 +1336,46 @@
     <t>query business type</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>update host</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>命令字</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>请求内容</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>OM-&gt;Agent</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{Rc}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{HostInfo:[{"HostName":"h1", "IP":"192.168.20.30", AgentPort:""}, ...], HostName:"", IP:"", User:"", Passwd:""}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AgentPort为可选参数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>更新host文件请求
+Agent收到请求后，更新本地host文件，将缺少的Hostname添加到本地;
+同时如果请求中带有AgentPort字段，则需要将该信息添加到sdbcm.conf文件</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="16">
+  <fonts count="17">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1463,6 +1498,13 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -1545,7 +1587,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1623,6 +1665,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4147,4 +4190,53 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
+  <cols>
+    <col min="1" max="1" width="29.5" customWidth="1"/>
+    <col min="2" max="2" width="12.75" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="61.5" style="23" customWidth="1"/>
+    <col min="5" max="5" width="21" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" t="s">
+        <v>253</v>
+      </c>
+      <c r="B1" t="s">
+        <v>251</v>
+      </c>
+      <c r="C1" s="23" t="s">
+        <v>252</v>
+      </c>
+      <c r="E1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="94.5">
+      <c r="A2" s="23" t="s">
+        <v>257</v>
+      </c>
+      <c r="B2" t="s">
+        <v>250</v>
+      </c>
+      <c r="C2" s="23" t="s">
+        <v>255</v>
+      </c>
+      <c r="D2" t="s">
+        <v>254</v>
+      </c>
+      <c r="E2" s="33" t="s">
+        <v>256</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>
--- a/internal_doc/03.开发设计/OM_web接口.xlsx
+++ b/internal_doc/03.开发设计/OM_web接口.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="6510" activeTab="5"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="6510" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="需求" sheetId="1" r:id="rId1"/>
@@ -280,7 +280,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="258">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="262">
   <si>
     <t>需求</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1079,10 +1079,6 @@
   </si>
   <si>
     <t>rc=ok</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>host_info={ClusterName:cls1, host_info:[{IP, Name, User, Passwd, SshPort:xxx, AgentPort:xxx, InstallPath:xxx, Firework, [Disk],[CPU]…}, ...], User:xxx, Passwd:xxx, SshPort:xxx, AgentPort:xxx, InstallPath:xxx}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1368,6 +1364,26 @@
     <t>更新host文件请求
 Agent收到请求后，更新本地host文件，将缺少的Hostname添加到本地;
 同时如果请求中带有AgentPort字段，则需要将该信息添加到sdbcm.conf文件</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>host_info={ClusterName:cls1, HostInfo:[{IP, HostName, User, Passwd, SshPort:xxx, AgentPort:xxx, InstallPath:xxx, Firework, [Disk],[CPU]…}, ...], User:xxx, Passwd:xxx, SshPort:xxx, AgentPort:xxx, InstallPath:xxx}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>根据clusterName查询业务</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>query business</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ClusterName=cl</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://192.168.20.197:11814/?cmd=query business&amp;ClusterName=cl</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3427,7 +3443,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F64"/>
+  <dimension ref="A1:F69"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="26" style="10" bestFit="1" customWidth="1"/>
@@ -3468,13 +3484,13 @@
         <v>156</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E3" s="4"/>
       <c r="F3" s="4"/>
@@ -3506,13 +3522,13 @@
         <v>171</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C6" s="9" t="s">
         <v>173</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
@@ -3523,10 +3539,10 @@
       </c>
       <c r="B7" s="4"/>
       <c r="C7" s="9" t="s">
+        <v>229</v>
+      </c>
+      <c r="D7" s="9" t="s">
         <v>230</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>231</v>
       </c>
       <c r="E7" s="4"/>
       <c r="F7" s="4"/>
@@ -3544,13 +3560,13 @@
         <v>122</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E9" s="4"/>
       <c r="F9" s="4"/>
@@ -3584,13 +3600,13 @@
         <v>124</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C12" s="9" t="s">
         <v>193</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="E12" s="4"/>
       <c r="F12" s="4"/>
@@ -3622,13 +3638,13 @@
         <v>126</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>198</v>
+        <v>257</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E15" s="4"/>
       <c r="F15" s="4"/>
@@ -3660,13 +3676,13 @@
         <v>128</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D18" s="23" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E18" s="4"/>
       <c r="F18" s="4"/>
@@ -3677,7 +3693,7 @@
       </c>
       <c r="B19" s="4"/>
       <c r="C19" s="9" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D19" s="9"/>
       <c r="E19" s="4"/>
@@ -3698,11 +3714,11 @@
         <v>135</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C21" s="9"/>
       <c r="D21" s="9" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E21" s="4"/>
       <c r="F21" s="4"/>
@@ -3713,10 +3729,10 @@
       </c>
       <c r="B22" s="4"/>
       <c r="C22" s="9" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E22" s="4"/>
       <c r="F22" s="4"/>
@@ -3736,13 +3752,13 @@
         <v>137</v>
       </c>
       <c r="B24" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="C24" s="9" t="s">
         <v>235</v>
       </c>
-      <c r="C24" s="9" t="s">
-        <v>236</v>
-      </c>
       <c r="D24" s="9" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="E24" s="4"/>
       <c r="F24" s="4"/>
@@ -3756,7 +3772,7 @@
         <v>195</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="E25" s="4"/>
       <c r="F25" s="4"/>
@@ -3776,13 +3792,13 @@
         <v>139</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="E27" s="4"/>
       <c r="F27" s="4"/>
@@ -3793,10 +3809,10 @@
       </c>
       <c r="B28" s="4"/>
       <c r="C28" s="9" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E28" s="4"/>
       <c r="F28" s="4"/>
@@ -3816,13 +3832,13 @@
         <v>141</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E30" s="4"/>
       <c r="F30" s="4"/>
@@ -3851,27 +3867,27 @@
     </row>
     <row r="33" spans="1:6" ht="24">
       <c r="A33" s="9" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E33" s="4"/>
       <c r="F33" s="4"/>
     </row>
     <row r="34" spans="1:6" ht="96">
       <c r="A34" s="9" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B34" s="4"/>
       <c r="C34" s="9" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D34" s="9"/>
       <c r="E34" s="4"/>
@@ -3879,38 +3895,32 @@
     </row>
     <row r="35" spans="1:6">
       <c r="A35" s="9"/>
-      <c r="B35" s="4" t="s">
-        <v>133</v>
-      </c>
+      <c r="B35" s="4"/>
       <c r="C35" s="9"/>
       <c r="D35" s="9"/>
       <c r="E35" s="4"/>
       <c r="F35" s="4"/>
     </row>
-    <row r="36" spans="1:6">
+    <row r="36" spans="1:6" ht="24">
       <c r="A36" s="9" t="s">
-        <v>143</v>
+        <v>258</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>145</v>
+        <v>259</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>180</v>
-      </c>
-      <c r="D36" s="9"/>
+        <v>260</v>
+      </c>
+      <c r="D36" s="9" t="s">
+        <v>261</v>
+      </c>
       <c r="E36" s="4"/>
       <c r="F36" s="4"/>
     </row>
     <row r="37" spans="1:6">
-      <c r="A37" s="9" t="s">
-        <v>144</v>
-      </c>
-      <c r="B37" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="C37" s="9" t="s">
-        <v>181</v>
-      </c>
+      <c r="A37" s="9"/>
+      <c r="B37" s="4"/>
+      <c r="C37" s="9"/>
       <c r="D37" s="9"/>
       <c r="E37" s="4"/>
       <c r="F37" s="4"/>
@@ -3923,95 +3933,85 @@
       <c r="E38" s="4"/>
       <c r="F38" s="4"/>
     </row>
-    <row r="45" spans="1:6">
-      <c r="A45" s="9" t="s">
+    <row r="39" spans="1:6">
+      <c r="A39" s="9"/>
+      <c r="B39" s="4"/>
+      <c r="C39" s="9"/>
+      <c r="D39" s="9"/>
+      <c r="E39" s="4"/>
+      <c r="F39" s="4"/>
+    </row>
+    <row r="40" spans="1:6">
+      <c r="A40" s="9"/>
+      <c r="B40" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="C40" s="9"/>
+      <c r="D40" s="9"/>
+      <c r="E40" s="4"/>
+      <c r="F40" s="4"/>
+    </row>
+    <row r="41" spans="1:6">
+      <c r="A41" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="C41" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="D41" s="9"/>
+      <c r="E41" s="4"/>
+      <c r="F41" s="4"/>
+    </row>
+    <row r="42" spans="1:6">
+      <c r="A42" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="C42" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="D42" s="9"/>
+      <c r="E42" s="4"/>
+      <c r="F42" s="4"/>
+    </row>
+    <row r="43" spans="1:6">
+      <c r="A43" s="9"/>
+      <c r="B43" s="4"/>
+      <c r="C43" s="9"/>
+      <c r="D43" s="9"/>
+      <c r="E43" s="4"/>
+      <c r="F43" s="4"/>
+    </row>
+    <row r="50" spans="1:6">
+      <c r="A50" s="9" t="s">
         <v>153</v>
       </c>
-      <c r="B45" s="4" t="s">
-        <v>207</v>
-      </c>
-      <c r="C45" s="9" t="s">
+      <c r="B50" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="C50" s="9" t="s">
         <v>147</v>
       </c>
-      <c r="D45" s="9"/>
-      <c r="E45" s="4"/>
-      <c r="F45" s="4"/>
-    </row>
-    <row r="46" spans="1:6" ht="24">
-      <c r="A46" s="9" t="s">
-        <v>154</v>
-      </c>
-      <c r="B46" s="4"/>
-      <c r="C46" s="9" t="s">
-        <v>170</v>
-      </c>
-      <c r="D46" s="9" t="s">
-        <v>155</v>
-      </c>
-      <c r="E46" s="4"/>
-      <c r="F46" s="4"/>
-    </row>
-    <row r="47" spans="1:6">
-      <c r="A47" s="9"/>
-      <c r="B47" s="4"/>
-      <c r="C47" s="9"/>
-      <c r="D47" s="9"/>
-      <c r="E47" s="4"/>
-      <c r="F47" s="4"/>
-    </row>
-    <row r="48" spans="1:6" ht="24">
-      <c r="A48" s="9" t="s">
-        <v>168</v>
-      </c>
-      <c r="B48" s="4" t="s">
-        <v>225</v>
-      </c>
-      <c r="C48" s="9" t="s">
-        <v>214</v>
-      </c>
-      <c r="D48" s="9" t="s">
-        <v>238</v>
-      </c>
-      <c r="E48" s="4"/>
-      <c r="F48" s="4"/>
-    </row>
-    <row r="49" spans="1:6">
-      <c r="A49" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="B49" s="4"/>
-      <c r="C49" s="9" t="s">
-        <v>226</v>
-      </c>
-      <c r="D49" s="9"/>
-      <c r="E49" s="4"/>
-      <c r="F49" s="4"/>
-    </row>
-    <row r="50" spans="1:6" ht="36">
-      <c r="A50" s="9" t="s">
-        <v>215</v>
-      </c>
-      <c r="B50" s="4" t="s">
-        <v>216</v>
-      </c>
-      <c r="C50" s="9" t="s">
-        <v>217</v>
-      </c>
-      <c r="D50" s="9" t="s">
-        <v>218</v>
-      </c>
+      <c r="D50" s="9"/>
       <c r="E50" s="4"/>
       <c r="F50" s="4"/>
     </row>
-    <row r="51" spans="1:6">
+    <row r="51" spans="1:6" ht="24">
       <c r="A51" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="B51" s="4" t="s">
-        <v>220</v>
-      </c>
-      <c r="C51" s="9"/>
-      <c r="D51" s="9"/>
+        <v>154</v>
+      </c>
+      <c r="B51" s="4"/>
+      <c r="C51" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="D51" s="9" t="s">
+        <v>155</v>
+      </c>
       <c r="E51" s="4"/>
       <c r="F51" s="4"/>
     </row>
@@ -4023,135 +4023,199 @@
       <c r="E52" s="4"/>
       <c r="F52" s="4"/>
     </row>
-    <row r="53" spans="1:6">
-      <c r="A53" s="5" t="s">
+    <row r="53" spans="1:6" ht="24">
+      <c r="A53" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="C53" s="9" t="s">
+        <v>213</v>
+      </c>
+      <c r="D53" s="9" t="s">
+        <v>237</v>
+      </c>
+      <c r="E53" s="4"/>
+      <c r="F53" s="4"/>
+    </row>
+    <row r="54" spans="1:6">
+      <c r="A54" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="B54" s="4"/>
+      <c r="C54" s="9" t="s">
+        <v>225</v>
+      </c>
+      <c r="D54" s="9"/>
+      <c r="E54" s="4"/>
+      <c r="F54" s="4"/>
+    </row>
+    <row r="55" spans="1:6" ht="36">
+      <c r="A55" s="9" t="s">
+        <v>214</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="C55" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="D55" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="E55" s="4"/>
+      <c r="F55" s="4"/>
+    </row>
+    <row r="56" spans="1:6">
+      <c r="A56" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="B56" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="C56" s="9"/>
+      <c r="D56" s="9"/>
+      <c r="E56" s="4"/>
+      <c r="F56" s="4"/>
+    </row>
+    <row r="57" spans="1:6">
+      <c r="A57" s="9"/>
+      <c r="B57" s="4"/>
+      <c r="C57" s="9"/>
+      <c r="D57" s="9"/>
+      <c r="E57" s="4"/>
+      <c r="F57" s="4"/>
+    </row>
+    <row r="58" spans="1:6">
+      <c r="A58" s="5" t="s">
         <v>160</v>
       </c>
-      <c r="B53" s="2"/>
-      <c r="C53" s="5" t="s">
+      <c r="B58" s="2"/>
+      <c r="C58" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="D53" s="5"/>
-      <c r="E53" s="2"/>
-      <c r="F53" s="2"/>
-    </row>
-    <row r="54" spans="1:6" ht="24">
-      <c r="A54" s="5" t="s">
+      <c r="D58" s="5"/>
+      <c r="E58" s="2"/>
+      <c r="F58" s="2"/>
+    </row>
+    <row r="59" spans="1:6" ht="24">
+      <c r="A59" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="B54" s="2"/>
-      <c r="C54" s="5" t="s">
-        <v>226</v>
-      </c>
-      <c r="D54" s="5" t="s">
+      <c r="B59" s="2"/>
+      <c r="C59" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="D59" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="E54" s="2"/>
-      <c r="F54" s="2"/>
-    </row>
-    <row r="55" spans="1:6" ht="24">
-      <c r="A55" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="B55" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="C55" s="5" t="s">
-        <v>158</v>
-      </c>
-      <c r="D55" s="5"/>
-      <c r="E55" s="2"/>
-      <c r="F55" s="2"/>
-    </row>
-    <row r="56" spans="1:6" ht="60">
-      <c r="A56" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="B56" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="C56" s="5" t="s">
-        <v>166</v>
-      </c>
-      <c r="D56" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="E56" s="2"/>
-      <c r="F56" s="2"/>
-    </row>
-    <row r="57" spans="1:6" ht="48">
-      <c r="A57" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="B57" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="C57" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="D57" s="5"/>
-      <c r="E57" s="2"/>
-      <c r="F57" s="2"/>
-    </row>
-    <row r="58" spans="1:6" s="21" customFormat="1">
-      <c r="A58" s="25" t="s">
-        <v>152</v>
-      </c>
-      <c r="B58" s="26"/>
-      <c r="C58" s="25"/>
-      <c r="D58" s="25" t="s">
-        <v>150</v>
-      </c>
-      <c r="E58" s="26"/>
-      <c r="F58" s="26"/>
-    </row>
-    <row r="59" spans="1:6">
-      <c r="A59" s="5"/>
-      <c r="B59" s="2"/>
-      <c r="C59" s="5"/>
-      <c r="D59" s="5"/>
       <c r="E59" s="2"/>
       <c r="F59" s="2"/>
     </row>
-    <row r="60" spans="1:6">
-      <c r="A60" s="9"/>
-      <c r="B60" s="4"/>
-      <c r="C60" s="9"/>
-      <c r="D60" s="9"/>
-      <c r="E60" s="4"/>
-      <c r="F60" s="4"/>
-    </row>
-    <row r="61" spans="1:6">
-      <c r="A61" s="9"/>
-      <c r="B61" s="4"/>
-      <c r="C61" s="9"/>
-      <c r="D61" s="9"/>
-      <c r="E61" s="4"/>
-      <c r="F61" s="4"/>
-    </row>
-    <row r="62" spans="1:6">
-      <c r="A62" s="9"/>
-      <c r="B62" s="4"/>
-      <c r="C62" s="9"/>
-      <c r="D62" s="9"/>
-      <c r="E62" s="4"/>
-      <c r="F62" s="4"/>
-    </row>
-    <row r="63" spans="1:6">
-      <c r="A63" s="9"/>
-      <c r="B63" s="4"/>
-      <c r="C63" s="9"/>
-      <c r="D63" s="9"/>
-      <c r="E63" s="4"/>
-      <c r="F63" s="4"/>
+    <row r="60" spans="1:6" ht="24">
+      <c r="A60" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="C60" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="D60" s="5"/>
+      <c r="E60" s="2"/>
+      <c r="F60" s="2"/>
+    </row>
+    <row r="61" spans="1:6" ht="60">
+      <c r="A61" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="C61" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="D61" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="E61" s="2"/>
+      <c r="F61" s="2"/>
+    </row>
+    <row r="62" spans="1:6" ht="48">
+      <c r="A62" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="C62" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="D62" s="5"/>
+      <c r="E62" s="2"/>
+      <c r="F62" s="2"/>
+    </row>
+    <row r="63" spans="1:6" s="21" customFormat="1">
+      <c r="A63" s="25" t="s">
+        <v>152</v>
+      </c>
+      <c r="B63" s="26"/>
+      <c r="C63" s="25"/>
+      <c r="D63" s="25" t="s">
+        <v>150</v>
+      </c>
+      <c r="E63" s="26"/>
+      <c r="F63" s="26"/>
     </row>
     <row r="64" spans="1:6">
-      <c r="A64" s="9"/>
-      <c r="B64" s="4"/>
-      <c r="C64" s="9"/>
-      <c r="D64" s="9"/>
-      <c r="E64" s="4"/>
-      <c r="F64" s="4"/>
+      <c r="A64" s="5"/>
+      <c r="B64" s="2"/>
+      <c r="C64" s="5"/>
+      <c r="D64" s="5"/>
+      <c r="E64" s="2"/>
+      <c r="F64" s="2"/>
+    </row>
+    <row r="65" spans="1:6">
+      <c r="A65" s="9"/>
+      <c r="B65" s="4"/>
+      <c r="C65" s="9"/>
+      <c r="D65" s="9"/>
+      <c r="E65" s="4"/>
+      <c r="F65" s="4"/>
+    </row>
+    <row r="66" spans="1:6">
+      <c r="A66" s="9"/>
+      <c r="B66" s="4"/>
+      <c r="C66" s="9"/>
+      <c r="D66" s="9"/>
+      <c r="E66" s="4"/>
+      <c r="F66" s="4"/>
+    </row>
+    <row r="67" spans="1:6">
+      <c r="A67" s="9"/>
+      <c r="B67" s="4"/>
+      <c r="C67" s="9"/>
+      <c r="D67" s="9"/>
+      <c r="E67" s="4"/>
+      <c r="F67" s="4"/>
+    </row>
+    <row r="68" spans="1:6">
+      <c r="A68" s="9"/>
+      <c r="B68" s="4"/>
+      <c r="C68" s="9"/>
+      <c r="D68" s="9"/>
+      <c r="E68" s="4"/>
+      <c r="F68" s="4"/>
+    </row>
+    <row r="69" spans="1:6">
+      <c r="A69" s="9"/>
+      <c r="B69" s="4"/>
+      <c r="C69" s="9"/>
+      <c r="D69" s="9"/>
+      <c r="E69" s="4"/>
+      <c r="F69" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -4205,13 +4269,13 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B1" t="s">
+        <v>250</v>
+      </c>
+      <c r="C1" s="23" t="s">
         <v>251</v>
-      </c>
-      <c r="C1" s="23" t="s">
-        <v>252</v>
       </c>
       <c r="E1" t="s">
         <v>51</v>
@@ -4219,19 +4283,19 @@
     </row>
     <row r="2" spans="1:5" ht="94.5">
       <c r="A2" s="23" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C2" s="23" t="s">
+        <v>254</v>
+      </c>
+      <c r="D2" t="s">
+        <v>253</v>
+      </c>
+      <c r="E2" s="33" t="s">
         <v>255</v>
-      </c>
-      <c r="D2" t="s">
-        <v>254</v>
-      </c>
-      <c r="E2" s="33" t="s">
-        <v>256</v>
       </c>
     </row>
   </sheetData>

--- a/internal_doc/03.开发设计/OM_web接口.xlsx
+++ b/internal_doc/03.开发设计/OM_web接口.xlsx
@@ -280,7 +280,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="262">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="266">
   <si>
     <t>需求</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1371,19 +1371,35 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>query business</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ClusterName=cl</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://192.168.20.197:11814/?cmd=query business&amp;ClusterName=cl</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>删除集群</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>根据clusterName查询业务</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>query business</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ClusterName=cl</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>http://192.168.20.197:11814/?cmd=query business&amp;ClusterName=cl</t>
+    <t>根据clusterName查询业务响应</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>remove cluster</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://192.168.20.197:11814/?cmd=remove business&amp;ClusterName=cl</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3443,7 +3459,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F69"/>
+  <dimension ref="A1:F71"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="26" style="10" bestFit="1" customWidth="1"/>
@@ -3903,22 +3919,24 @@
     </row>
     <row r="36" spans="1:6" ht="24">
       <c r="A36" s="9" t="s">
+        <v>262</v>
+      </c>
+      <c r="B36" s="4" t="s">
         <v>258</v>
       </c>
-      <c r="B36" s="4" t="s">
+      <c r="C36" s="9" t="s">
         <v>259</v>
       </c>
-      <c r="C36" s="9" t="s">
+      <c r="D36" s="9" t="s">
         <v>260</v>
-      </c>
-      <c r="D36" s="9" t="s">
-        <v>261</v>
       </c>
       <c r="E36" s="4"/>
       <c r="F36" s="4"/>
     </row>
     <row r="37" spans="1:6">
-      <c r="A37" s="9"/>
+      <c r="A37" s="9" t="s">
+        <v>263</v>
+      </c>
       <c r="B37" s="4"/>
       <c r="C37" s="9"/>
       <c r="D37" s="9"/>
@@ -3933,265 +3951,273 @@
       <c r="E38" s="4"/>
       <c r="F38" s="4"/>
     </row>
-    <row r="39" spans="1:6">
-      <c r="A39" s="9"/>
-      <c r="B39" s="4"/>
-      <c r="C39" s="9"/>
-      <c r="D39" s="9"/>
+    <row r="39" spans="1:6" ht="24">
+      <c r="A39" s="9" t="s">
+        <v>261</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>264</v>
+      </c>
+      <c r="C39" s="9" t="s">
+        <v>259</v>
+      </c>
+      <c r="D39" s="9" t="s">
+        <v>265</v>
+      </c>
       <c r="E39" s="4"/>
       <c r="F39" s="4"/>
     </row>
     <row r="40" spans="1:6">
       <c r="A40" s="9"/>
-      <c r="B40" s="4" t="s">
-        <v>133</v>
-      </c>
+      <c r="B40" s="4"/>
       <c r="C40" s="9"/>
       <c r="D40" s="9"/>
       <c r="E40" s="4"/>
       <c r="F40" s="4"/>
     </row>
     <row r="41" spans="1:6">
-      <c r="A41" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="B41" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="C41" s="9" t="s">
-        <v>180</v>
-      </c>
+      <c r="A41" s="9"/>
+      <c r="B41" s="4"/>
+      <c r="C41" s="9"/>
       <c r="D41" s="9"/>
       <c r="E41" s="4"/>
       <c r="F41" s="4"/>
     </row>
     <row r="42" spans="1:6">
-      <c r="A42" s="9" t="s">
-        <v>144</v>
-      </c>
+      <c r="A42" s="9"/>
       <c r="B42" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="C42" s="9" t="s">
-        <v>181</v>
-      </c>
+        <v>133</v>
+      </c>
+      <c r="C42" s="9"/>
       <c r="D42" s="9"/>
       <c r="E42" s="4"/>
       <c r="F42" s="4"/>
     </row>
     <row r="43" spans="1:6">
-      <c r="A43" s="9"/>
-      <c r="B43" s="4"/>
-      <c r="C43" s="9"/>
+      <c r="A43" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="C43" s="9" t="s">
+        <v>180</v>
+      </c>
       <c r="D43" s="9"/>
       <c r="E43" s="4"/>
       <c r="F43" s="4"/>
     </row>
-    <row r="50" spans="1:6">
-      <c r="A50" s="9" t="s">
+    <row r="44" spans="1:6">
+      <c r="A44" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="C44" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="D44" s="9"/>
+      <c r="E44" s="4"/>
+      <c r="F44" s="4"/>
+    </row>
+    <row r="45" spans="1:6">
+      <c r="A45" s="9"/>
+      <c r="B45" s="4"/>
+      <c r="C45" s="9"/>
+      <c r="D45" s="9"/>
+      <c r="E45" s="4"/>
+      <c r="F45" s="4"/>
+    </row>
+    <row r="52" spans="1:6">
+      <c r="A52" s="9" t="s">
         <v>153</v>
       </c>
-      <c r="B50" s="4" t="s">
+      <c r="B52" s="4" t="s">
         <v>206</v>
       </c>
-      <c r="C50" s="9" t="s">
+      <c r="C52" s="9" t="s">
         <v>147</v>
       </c>
-      <c r="D50" s="9"/>
-      <c r="E50" s="4"/>
-      <c r="F50" s="4"/>
-    </row>
-    <row r="51" spans="1:6" ht="24">
-      <c r="A51" s="9" t="s">
-        <v>154</v>
-      </c>
-      <c r="B51" s="4"/>
-      <c r="C51" s="9" t="s">
-        <v>170</v>
-      </c>
-      <c r="D51" s="9" t="s">
-        <v>155</v>
-      </c>
-      <c r="E51" s="4"/>
-      <c r="F51" s="4"/>
-    </row>
-    <row r="52" spans="1:6">
-      <c r="A52" s="9"/>
-      <c r="B52" s="4"/>
-      <c r="C52" s="9"/>
       <c r="D52" s="9"/>
       <c r="E52" s="4"/>
       <c r="F52" s="4"/>
     </row>
     <row r="53" spans="1:6" ht="24">
       <c r="A53" s="9" t="s">
-        <v>168</v>
-      </c>
-      <c r="B53" s="4" t="s">
-        <v>224</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="B53" s="4"/>
       <c r="C53" s="9" t="s">
-        <v>213</v>
+        <v>170</v>
       </c>
       <c r="D53" s="9" t="s">
-        <v>237</v>
+        <v>155</v>
       </c>
       <c r="E53" s="4"/>
       <c r="F53" s="4"/>
     </row>
     <row r="54" spans="1:6">
-      <c r="A54" s="9" t="s">
-        <v>169</v>
-      </c>
+      <c r="A54" s="9"/>
       <c r="B54" s="4"/>
-      <c r="C54" s="9" t="s">
-        <v>225</v>
-      </c>
+      <c r="C54" s="9"/>
       <c r="D54" s="9"/>
       <c r="E54" s="4"/>
       <c r="F54" s="4"/>
     </row>
-    <row r="55" spans="1:6" ht="36">
+    <row r="55" spans="1:6" ht="24">
       <c r="A55" s="9" t="s">
-        <v>214</v>
+        <v>168</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>215</v>
+        <v>224</v>
       </c>
       <c r="C55" s="9" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="D55" s="9" t="s">
-        <v>217</v>
+        <v>237</v>
       </c>
       <c r="E55" s="4"/>
       <c r="F55" s="4"/>
     </row>
     <row r="56" spans="1:6">
       <c r="A56" s="9" t="s">
-        <v>218</v>
-      </c>
-      <c r="B56" s="4" t="s">
-        <v>219</v>
-      </c>
-      <c r="C56" s="9"/>
+        <v>169</v>
+      </c>
+      <c r="B56" s="4"/>
+      <c r="C56" s="9" t="s">
+        <v>225</v>
+      </c>
       <c r="D56" s="9"/>
       <c r="E56" s="4"/>
       <c r="F56" s="4"/>
     </row>
-    <row r="57" spans="1:6">
-      <c r="A57" s="9"/>
-      <c r="B57" s="4"/>
-      <c r="C57" s="9"/>
-      <c r="D57" s="9"/>
+    <row r="57" spans="1:6" ht="36">
+      <c r="A57" s="9" t="s">
+        <v>214</v>
+      </c>
+      <c r="B57" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="C57" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="D57" s="9" t="s">
+        <v>217</v>
+      </c>
       <c r="E57" s="4"/>
       <c r="F57" s="4"/>
     </row>
     <row r="58" spans="1:6">
-      <c r="A58" s="5" t="s">
+      <c r="A58" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="B58" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="C58" s="9"/>
+      <c r="D58" s="9"/>
+      <c r="E58" s="4"/>
+      <c r="F58" s="4"/>
+    </row>
+    <row r="59" spans="1:6">
+      <c r="A59" s="9"/>
+      <c r="B59" s="4"/>
+      <c r="C59" s="9"/>
+      <c r="D59" s="9"/>
+      <c r="E59" s="4"/>
+      <c r="F59" s="4"/>
+    </row>
+    <row r="60" spans="1:6">
+      <c r="A60" s="5" t="s">
         <v>160</v>
       </c>
-      <c r="B58" s="2"/>
-      <c r="C58" s="5" t="s">
+      <c r="B60" s="2"/>
+      <c r="C60" s="5" t="s">
         <v>159</v>
-      </c>
-      <c r="D58" s="5"/>
-      <c r="E58" s="2"/>
-      <c r="F58" s="2"/>
-    </row>
-    <row r="59" spans="1:6" ht="24">
-      <c r="A59" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="B59" s="2"/>
-      <c r="C59" s="5" t="s">
-        <v>225</v>
-      </c>
-      <c r="D59" s="5" t="s">
-        <v>149</v>
-      </c>
-      <c r="E59" s="2"/>
-      <c r="F59" s="2"/>
-    </row>
-    <row r="60" spans="1:6" ht="24">
-      <c r="A60" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="B60" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="C60" s="5" t="s">
-        <v>158</v>
       </c>
       <c r="D60" s="5"/>
       <c r="E60" s="2"/>
       <c r="F60" s="2"/>
     </row>
-    <row r="61" spans="1:6" ht="60">
+    <row r="61" spans="1:6" ht="24">
       <c r="A61" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="B61" s="2" t="s">
-        <v>163</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="B61" s="2"/>
       <c r="C61" s="5" t="s">
-        <v>166</v>
+        <v>225</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>167</v>
+        <v>149</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" s="2"/>
     </row>
-    <row r="62" spans="1:6" ht="48">
+    <row r="62" spans="1:6" ht="24">
       <c r="A62" s="5" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>163</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="D62" s="5"/>
       <c r="E62" s="2"/>
       <c r="F62" s="2"/>
     </row>
-    <row r="63" spans="1:6" s="21" customFormat="1">
-      <c r="A63" s="25" t="s">
-        <v>152</v>
-      </c>
-      <c r="B63" s="26"/>
-      <c r="C63" s="25"/>
-      <c r="D63" s="25" t="s">
-        <v>150</v>
-      </c>
-      <c r="E63" s="26"/>
-      <c r="F63" s="26"/>
-    </row>
-    <row r="64" spans="1:6">
-      <c r="A64" s="5"/>
-      <c r="B64" s="2"/>
-      <c r="C64" s="5"/>
+    <row r="63" spans="1:6" ht="60">
+      <c r="A63" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="C63" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="D63" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="E63" s="2"/>
+      <c r="F63" s="2"/>
+    </row>
+    <row r="64" spans="1:6" ht="48">
+      <c r="A64" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="C64" s="5" t="s">
+        <v>165</v>
+      </c>
       <c r="D64" s="5"/>
       <c r="E64" s="2"/>
       <c r="F64" s="2"/>
     </row>
-    <row r="65" spans="1:6">
-      <c r="A65" s="9"/>
-      <c r="B65" s="4"/>
-      <c r="C65" s="9"/>
-      <c r="D65" s="9"/>
-      <c r="E65" s="4"/>
-      <c r="F65" s="4"/>
+    <row r="65" spans="1:6" s="21" customFormat="1">
+      <c r="A65" s="25" t="s">
+        <v>152</v>
+      </c>
+      <c r="B65" s="26"/>
+      <c r="C65" s="25"/>
+      <c r="D65" s="25" t="s">
+        <v>150</v>
+      </c>
+      <c r="E65" s="26"/>
+      <c r="F65" s="26"/>
     </row>
     <row r="66" spans="1:6">
-      <c r="A66" s="9"/>
-      <c r="B66" s="4"/>
-      <c r="C66" s="9"/>
-      <c r="D66" s="9"/>
-      <c r="E66" s="4"/>
-      <c r="F66" s="4"/>
+      <c r="A66" s="5"/>
+      <c r="B66" s="2"/>
+      <c r="C66" s="5"/>
+      <c r="D66" s="5"/>
+      <c r="E66" s="2"/>
+      <c r="F66" s="2"/>
     </row>
     <row r="67" spans="1:6">
       <c r="A67" s="9"/>
@@ -4216,6 +4242,22 @@
       <c r="D69" s="9"/>
       <c r="E69" s="4"/>
       <c r="F69" s="4"/>
+    </row>
+    <row r="70" spans="1:6">
+      <c r="A70" s="9"/>
+      <c r="B70" s="4"/>
+      <c r="C70" s="9"/>
+      <c r="D70" s="9"/>
+      <c r="E70" s="4"/>
+      <c r="F70" s="4"/>
+    </row>
+    <row r="71" spans="1:6">
+      <c r="A71" s="9"/>
+      <c r="B71" s="4"/>
+      <c r="C71" s="9"/>
+      <c r="D71" s="9"/>
+      <c r="E71" s="4"/>
+      <c r="F71" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/internal_doc/03.开发设计/OM_web接口.xlsx
+++ b/internal_doc/03.开发设计/OM_web接口.xlsx
@@ -280,7 +280,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="266">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="267">
   <si>
     <t>需求</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1321,10 +1321,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>http://192.168.20.197:11814/?cmd=check host&amp;HostInfo={"ClusterName":"c1","HostInfo":[{"IP":"192.168.20.196","HostName":"aa","User":"root","Passwd":"sequoiad",SshPort:"22",AgentPort:"11790"}],"User":"root","Passwd":"sequoiadb",SshPort:"22",AgentPort:"11810"}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>http://192.168.20.197:11814/?cmd=add host&amp;HostInfo={"ClusterName":"c1","HostInfo":[{"IP":"192.168.20.196","HostName":"aa","User":"root","Passwd":"sequoiad",SshPort:"22",AgentPort:"11790"}],"User":"root","Passwd":"sequoiadb",SshPort:"22",AgentPort:"11810",InstallPath:"/opt/sequoiadb/"}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1400,6 +1396,14 @@
   </si>
   <si>
     <t>http://192.168.20.197:11814/?cmd=remove business&amp;ClusterName=cl</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{ "Rc": 0 }{ "Rc": 0, "IP": [ "192.168.20.196" ], "CPU": [ { "ID": "", "Model": "", "Core": 1, "Freq": "2.00GHz" } ], "Net": [ { "Name": "lo", "Model": "", "Bandwidth": "", "IP": "127.0.0.1" }, { "Name": "eth0", "Model": "", "Bandwidth": "", "IP": "192.168.20.196" } ], "Memory": { "Model": "", "Size": 2003, "Free": 905, "Unit": "M" }, "Host": [ { "Port": 0, "Status": 0 } ], "Service": [ { "Name": "", "Status": 0, "Version": "" } ], "OM": { "Status": 0, "Version": "" }, "Safety": { "Name": "", "Context": "", "Status": 0 }, "HostName": "data0", "User": "root", "Password": "sequoiadb", "OS": { "Distributor": "Ubuntu", "Release": "12.04", "Bit": 64 }, "Disk": [ { "Name": "/dev/sda1", "Mount": "/", "Size": 32530, "Free": 8470, "Unit": "M", "Used": 1, "CanUse": true }, { "Name": "udev", "Mount": "/dev", "Size": 995, "Free": 994, "Unit": "M", "Used": 1, "CanUse": true }, { "Name": "tmpfs", "Mount": "/run", "Size": 402, "Free": 401, "Unit": "M", "Used": 1, "CanUse": false }, { "Name": "none", "Mount": "/run/lock", "Size": 5, "Free": 5, "Unit": "M", "Used": 1, "CanUse": false }, { "Name": "none", "Mount": "/run/shm", "Size": 1002, "Free": 1002, "Unit": "M", "Used": 1, "CanUse": true }, { "Name": "//192.168.20.10/files", "Mount": "/mnt", "Size": 47837, "Free": 4663, "Unit": "M", "Used": 1, "CanUse": true } ] }</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://192.168.20.197:11814/?cmd=check host&amp;HostInfo={"ClusterName":"c1","HostInfo":[{"IP":"192.168.20.196", "HostName":"data0", AgentPort:"11790"}],"User":"root","Passwd":"sequoiadb",SshPort:"22",AgentPort:"11790"}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3622,12 +3626,12 @@
         <v>193</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>246</v>
+        <v>266</v>
       </c>
       <c r="E12" s="4"/>
       <c r="F12" s="4"/>
     </row>
-    <row r="13" spans="1:6" ht="24">
+    <row r="13" spans="1:6" ht="102.75" customHeight="1">
       <c r="A13" s="9" t="s">
         <v>125</v>
       </c>
@@ -3635,7 +3639,9 @@
       <c r="C13" s="9" t="s">
         <v>194</v>
       </c>
-      <c r="D13" s="9"/>
+      <c r="D13" s="9" t="s">
+        <v>265</v>
+      </c>
       <c r="E13" s="4"/>
       <c r="F13" s="4"/>
     </row>
@@ -3657,10 +3663,10 @@
         <v>209</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="E15" s="4"/>
       <c r="F15" s="4"/>
@@ -3730,7 +3736,7 @@
         <v>135</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C21" s="9"/>
       <c r="D21" s="9" t="s">
@@ -3919,23 +3925,23 @@
     </row>
     <row r="36" spans="1:6" ht="24">
       <c r="A36" s="9" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B36" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="C36" s="9" t="s">
         <v>258</v>
       </c>
-      <c r="C36" s="9" t="s">
+      <c r="D36" s="9" t="s">
         <v>259</v>
-      </c>
-      <c r="D36" s="9" t="s">
-        <v>260</v>
       </c>
       <c r="E36" s="4"/>
       <c r="F36" s="4"/>
     </row>
     <row r="37" spans="1:6">
       <c r="A37" s="9" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B37" s="4"/>
       <c r="C37" s="9"/>
@@ -3953,16 +3959,16 @@
     </row>
     <row r="39" spans="1:6" ht="24">
       <c r="A39" s="9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B39" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="C39" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="D39" s="9" t="s">
         <v>264</v>
-      </c>
-      <c r="C39" s="9" t="s">
-        <v>259</v>
-      </c>
-      <c r="D39" s="9" t="s">
-        <v>265</v>
       </c>
       <c r="E39" s="4"/>
       <c r="F39" s="4"/>
@@ -4311,13 +4317,13 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B1" t="s">
+        <v>249</v>
+      </c>
+      <c r="C1" s="23" t="s">
         <v>250</v>
-      </c>
-      <c r="C1" s="23" t="s">
-        <v>251</v>
       </c>
       <c r="E1" t="s">
         <v>51</v>
@@ -4325,19 +4331,19 @@
     </row>
     <row r="2" spans="1:5" ht="94.5">
       <c r="A2" s="23" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B2" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C2" s="23" t="s">
+        <v>253</v>
+      </c>
+      <c r="D2" t="s">
+        <v>252</v>
+      </c>
+      <c r="E2" s="33" t="s">
         <v>254</v>
-      </c>
-      <c r="D2" t="s">
-        <v>253</v>
-      </c>
-      <c r="E2" s="33" t="s">
-        <v>255</v>
       </c>
     </row>
   </sheetData>

--- a/internal_doc/03.开发设计/OM_web接口.xlsx
+++ b/internal_doc/03.开发设计/OM_web接口.xlsx
@@ -1321,10 +1321,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>http://192.168.20.197:11814/?cmd=add host&amp;HostInfo={"ClusterName":"c1","HostInfo":[{"IP":"192.168.20.196","HostName":"aa","User":"root","Passwd":"sequoiad",SshPort:"22",AgentPort:"11790"}],"User":"root","Passwd":"sequoiadb",SshPort:"22",AgentPort:"11810",InstallPath:"/opt/sequoiadb/"}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>query business type</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1404,6 +1400,14 @@
   </si>
   <si>
     <t>http://192.168.20.197:11814/?cmd=check host&amp;HostInfo={"ClusterName":"c1","HostInfo":[{"IP":"192.168.20.196", "HostName":"data0", AgentPort:"11790"}],"User":"root","Passwd":"sequoiadb",SshPort:"22",AgentPort:"11790"}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://192.168.20.197:11814/?cmd=add host&amp;HostInfo={"ClusterName":"c1","HostInfo":[{"IP":"192.168.20.196", "HostName":"data0", "User":"root", "Passwd":"sequoiadb", SshPort:"22", AgentPort:"11790", "CPU": [ { "I
+D": "", "Model": "", "Core": 1, "Freq": "2.00GHz" } ], "Net": [ { "Name": "lo", "Model": "", "Bandwidth": "", "IP": "127.0.0.1" }, { "Name": "eth0", "Model": "", "Bandwidth": "", "IP": "192.168.20.196" } ], "Disk": [ { "Name"
+: "/dev/sda1", "Mount": "/", "Size": 32529, "Free": 6525, "Unit": "M", "Used": 1 }], "Memory": { "Model": "", "Size": 2003, "Free": 916, "Unit": "M" }, "Host": [ { "Port": 0, "Status": 0 } ], "Service": [ { "Nam
+e": "", "Status": 0, "Version": "" } ], "OM": { "Status": 0, "Version": "" }, "Safety": { "Name": "", "Context": "", "Status": 0 }, "OS": { "Distributor": "Ubuntu", "Release": "12.04", "Bit": 64 }}],"User":"root","Passwd":"se
+quoiadb",SshPort:"22",AgentPort:"11790"}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3626,7 +3630,7 @@
         <v>193</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="E12" s="4"/>
       <c r="F12" s="4"/>
@@ -3640,7 +3644,7 @@
         <v>194</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E13" s="4"/>
       <c r="F13" s="4"/>
@@ -3655,7 +3659,7 @@
       <c r="E14" s="4"/>
       <c r="F14" s="4"/>
     </row>
-    <row r="15" spans="1:6" ht="72">
+    <row r="15" spans="1:6" ht="120" customHeight="1">
       <c r="A15" s="9" t="s">
         <v>126</v>
       </c>
@@ -3663,10 +3667,10 @@
         <v>209</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>246</v>
+        <v>266</v>
       </c>
       <c r="E15" s="4"/>
       <c r="F15" s="4"/>
@@ -3736,7 +3740,7 @@
         <v>135</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C21" s="9"/>
       <c r="D21" s="9" t="s">
@@ -3925,23 +3929,23 @@
     </row>
     <row r="36" spans="1:6" ht="24">
       <c r="A36" s="9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B36" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="C36" s="9" t="s">
         <v>257</v>
       </c>
-      <c r="C36" s="9" t="s">
+      <c r="D36" s="9" t="s">
         <v>258</v>
-      </c>
-      <c r="D36" s="9" t="s">
-        <v>259</v>
       </c>
       <c r="E36" s="4"/>
       <c r="F36" s="4"/>
     </row>
     <row r="37" spans="1:6">
       <c r="A37" s="9" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B37" s="4"/>
       <c r="C37" s="9"/>
@@ -3959,16 +3963,16 @@
     </row>
     <row r="39" spans="1:6" ht="24">
       <c r="A39" s="9" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B39" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="C39" s="9" t="s">
+        <v>257</v>
+      </c>
+      <c r="D39" s="9" t="s">
         <v>263</v>
-      </c>
-      <c r="C39" s="9" t="s">
-        <v>258</v>
-      </c>
-      <c r="D39" s="9" t="s">
-        <v>264</v>
       </c>
       <c r="E39" s="4"/>
       <c r="F39" s="4"/>
@@ -4317,13 +4321,13 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B1" t="s">
+        <v>248</v>
+      </c>
+      <c r="C1" s="23" t="s">
         <v>249</v>
-      </c>
-      <c r="C1" s="23" t="s">
-        <v>250</v>
       </c>
       <c r="E1" t="s">
         <v>51</v>
@@ -4331,19 +4335,19 @@
     </row>
     <row r="2" spans="1:5" ht="94.5">
       <c r="A2" s="23" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C2" s="23" t="s">
+        <v>252</v>
+      </c>
+      <c r="D2" t="s">
+        <v>251</v>
+      </c>
+      <c r="E2" s="33" t="s">
         <v>253</v>
-      </c>
-      <c r="D2" t="s">
-        <v>252</v>
-      </c>
-      <c r="E2" s="33" t="s">
-        <v>254</v>
       </c>
     </row>
   </sheetData>

--- a/internal_doc/03.开发设计/OM_web接口.xlsx
+++ b/internal_doc/03.开发设计/OM_web接口.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="6510" activeTab="3"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="6510" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="需求" sheetId="1" r:id="rId1"/>
@@ -280,7 +280,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="267">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="270">
   <si>
     <t>需求</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1325,10 +1325,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>update host</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>命令字</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1408,6 +1404,22 @@
 : "/dev/sda1", "Mount": "/", "Size": 32529, "Free": 6525, "Unit": "M", "Used": 1 }], "Memory": { "Model": "", "Size": 2003, "Free": 916, "Unit": "M" }, "Host": [ { "Port": 0, "Status": 0 } ], "Service": [ { "Nam
 e": "", "Status": 0, "Version": "" } ], "OM": { "Status": 0, "Version": "" }, "Safety": { "Name": "", "Context": "", "Status": 0 }, "OS": { "Distributor": "Ubuntu", "Release": "12.04", "Bit": 64 }}],"User":"root","Passwd":"se
 quoiadb",SshPort:"22",AgentPort:"11790"}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>删除host命令</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>update hostname</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"HostName":"", "IP":"", "User":"", "Passwd":""}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{Rc, 0}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3630,7 +3642,7 @@
         <v>193</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E12" s="4"/>
       <c r="F12" s="4"/>
@@ -3644,7 +3656,7 @@
         <v>194</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E13" s="4"/>
       <c r="F13" s="4"/>
@@ -3667,10 +3679,10 @@
         <v>209</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="E15" s="4"/>
       <c r="F15" s="4"/>
@@ -3929,23 +3941,23 @@
     </row>
     <row r="36" spans="1:6" ht="24">
       <c r="A36" s="9" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B36" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="C36" s="9" t="s">
         <v>256</v>
       </c>
-      <c r="C36" s="9" t="s">
+      <c r="D36" s="9" t="s">
         <v>257</v>
-      </c>
-      <c r="D36" s="9" t="s">
-        <v>258</v>
       </c>
       <c r="E36" s="4"/>
       <c r="F36" s="4"/>
     </row>
     <row r="37" spans="1:6">
       <c r="A37" s="9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B37" s="4"/>
       <c r="C37" s="9"/>
@@ -3963,16 +3975,16 @@
     </row>
     <row r="39" spans="1:6" ht="24">
       <c r="A39" s="9" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B39" s="4" t="s">
+        <v>261</v>
+      </c>
+      <c r="C39" s="9" t="s">
+        <v>256</v>
+      </c>
+      <c r="D39" s="9" t="s">
         <v>262</v>
-      </c>
-      <c r="C39" s="9" t="s">
-        <v>257</v>
-      </c>
-      <c r="D39" s="9" t="s">
-        <v>263</v>
       </c>
       <c r="E39" s="4"/>
       <c r="F39" s="4"/>
@@ -4310,24 +4322,25 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="29.5" customWidth="1"/>
-    <col min="2" max="2" width="12.75" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.25" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="61.5" style="23" customWidth="1"/>
+    <col min="4" max="4" width="30.5" style="23" customWidth="1"/>
     <col min="5" max="5" width="21" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B1" t="s">
+        <v>247</v>
+      </c>
+      <c r="C1" s="23" t="s">
         <v>248</v>
-      </c>
-      <c r="C1" s="23" t="s">
-        <v>249</v>
       </c>
       <c r="E1" t="s">
         <v>51</v>
@@ -4335,19 +4348,33 @@
     </row>
     <row r="2" spans="1:5" ht="94.5">
       <c r="A2" s="23" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B2" t="s">
-        <v>247</v>
+        <v>267</v>
       </c>
       <c r="C2" s="23" t="s">
+        <v>251</v>
+      </c>
+      <c r="D2" s="23" t="s">
+        <v>250</v>
+      </c>
+      <c r="E2" s="33" t="s">
         <v>252</v>
       </c>
-      <c r="D2" t="s">
-        <v>251</v>
-      </c>
-      <c r="E2" s="33" t="s">
-        <v>253</v>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" t="s">
+        <v>266</v>
+      </c>
+      <c r="B4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C4" s="23" t="s">
+        <v>268</v>
+      </c>
+      <c r="D4" s="23" t="s">
+        <v>269</v>
       </c>
     </row>
   </sheetData>

--- a/internal_doc/03.开发设计/OM_web接口.xlsx
+++ b/internal_doc/03.开发设计/OM_web接口.xlsx
@@ -280,7 +280,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="270">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="272">
   <si>
     <t>需求</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1420,6 +1420,14 @@
   </si>
   <si>
     <t>{Rc, 0}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>响应</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rest隐藏参数IsForce， 在agent卸载主机失败时仍然强行删除host信息</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1558,7 +1566,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1568,6 +1576,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1639,7 +1653,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1717,7 +1731,17 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4322,60 +4346,206 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="29.5" customWidth="1"/>
+    <col min="1" max="1" width="34.25" customWidth="1"/>
     <col min="2" max="2" width="17.25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="61.5" style="23" customWidth="1"/>
+    <col min="3" max="3" width="44.25" style="23" customWidth="1"/>
     <col min="4" max="4" width="30.5" style="23" customWidth="1"/>
-    <col min="5" max="5" width="21" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="37.375" style="23" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" t="s">
+      <c r="A1" s="33" t="s">
         <v>249</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="33" t="s">
         <v>247</v>
       </c>
-      <c r="C1" s="23" t="s">
+      <c r="C1" s="34" t="s">
         <v>248</v>
       </c>
-      <c r="E1" t="s">
+      <c r="D1" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="E1" s="34" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="94.5">
-      <c r="A2" s="23" t="s">
+    <row r="2" spans="1:5" ht="67.5">
+      <c r="A2" s="35" t="s">
         <v>253</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="36" t="s">
         <v>267</v>
       </c>
-      <c r="C2" s="23" t="s">
+      <c r="C2" s="35" t="s">
         <v>251</v>
       </c>
-      <c r="D2" s="23" t="s">
+      <c r="D2" s="35" t="s">
         <v>250</v>
       </c>
-      <c r="E2" s="33" t="s">
+      <c r="E2" s="37" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
-      <c r="A4" t="s">
+    <row r="3" spans="1:5">
+      <c r="A3" s="36"/>
+      <c r="B3" s="36"/>
+      <c r="C3" s="35"/>
+      <c r="D3" s="35"/>
+      <c r="E3" s="35"/>
+    </row>
+    <row r="4" spans="1:5" ht="27">
+      <c r="A4" s="36" t="s">
         <v>266</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="36" t="s">
         <v>44</v>
       </c>
-      <c r="C4" s="23" t="s">
+      <c r="C4" s="35" t="s">
         <v>268</v>
       </c>
-      <c r="D4" s="23" t="s">
+      <c r="D4" s="35" t="s">
         <v>269</v>
       </c>
+      <c r="E4" s="37" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="36"/>
+      <c r="B5" s="36"/>
+      <c r="C5" s="35"/>
+      <c r="D5" s="35"/>
+      <c r="E5" s="35"/>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="36"/>
+      <c r="B6" s="36"/>
+      <c r="C6" s="35"/>
+      <c r="D6" s="35"/>
+      <c r="E6" s="35"/>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="36"/>
+      <c r="B7" s="36"/>
+      <c r="C7" s="35"/>
+      <c r="D7" s="35"/>
+      <c r="E7" s="35"/>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="36"/>
+      <c r="B8" s="36"/>
+      <c r="C8" s="35"/>
+      <c r="D8" s="35"/>
+      <c r="E8" s="35"/>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="36"/>
+      <c r="B9" s="36"/>
+      <c r="C9" s="35"/>
+      <c r="D9" s="35"/>
+      <c r="E9" s="35"/>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="36"/>
+      <c r="B10" s="36"/>
+      <c r="C10" s="35"/>
+      <c r="D10" s="35"/>
+      <c r="E10" s="35"/>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="36"/>
+      <c r="B11" s="36"/>
+      <c r="C11" s="35"/>
+      <c r="D11" s="35"/>
+      <c r="E11" s="35"/>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="36"/>
+      <c r="B12" s="36"/>
+      <c r="C12" s="35"/>
+      <c r="D12" s="35"/>
+      <c r="E12" s="35"/>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="36"/>
+      <c r="B13" s="36"/>
+      <c r="C13" s="35"/>
+      <c r="D13" s="35"/>
+      <c r="E13" s="35"/>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="36"/>
+      <c r="B14" s="36"/>
+      <c r="C14" s="35"/>
+      <c r="D14" s="35"/>
+      <c r="E14" s="35"/>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="36"/>
+      <c r="B15" s="36"/>
+      <c r="C15" s="35"/>
+      <c r="D15" s="35"/>
+      <c r="E15" s="35"/>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="36"/>
+      <c r="B16" s="36"/>
+      <c r="C16" s="35"/>
+      <c r="D16" s="35"/>
+      <c r="E16" s="35"/>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="36"/>
+      <c r="B17" s="36"/>
+      <c r="C17" s="35"/>
+      <c r="D17" s="35"/>
+      <c r="E17" s="35"/>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="36"/>
+      <c r="B18" s="36"/>
+      <c r="C18" s="35"/>
+      <c r="D18" s="35"/>
+      <c r="E18" s="35"/>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="36"/>
+      <c r="B19" s="36"/>
+      <c r="C19" s="35"/>
+      <c r="D19" s="35"/>
+      <c r="E19" s="35"/>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="36"/>
+      <c r="B20" s="36"/>
+      <c r="C20" s="35"/>
+      <c r="D20" s="35"/>
+      <c r="E20" s="35"/>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="36"/>
+      <c r="B21" s="36"/>
+      <c r="C21" s="35"/>
+      <c r="D21" s="35"/>
+      <c r="E21" s="35"/>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="36"/>
+      <c r="B22" s="36"/>
+      <c r="C22" s="35"/>
+      <c r="D22" s="35"/>
+      <c r="E22" s="35"/>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="36"/>
+      <c r="B23" s="36"/>
+      <c r="C23" s="35"/>
+      <c r="D23" s="35"/>
+      <c r="E23" s="35"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/internal_doc/03.开发设计/OM_web接口.xlsx
+++ b/internal_doc/03.开发设计/OM_web接口.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="6510" activeTab="5"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="6510" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="需求" sheetId="1" r:id="rId1"/>
@@ -13,6 +13,7 @@
     <sheet name="消息定义" sheetId="4" r:id="rId4"/>
     <sheet name="Sheet1" sheetId="5" r:id="rId5"/>
     <sheet name="agent接口" sheetId="6" r:id="rId6"/>
+    <sheet name="Sheet3" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="124519"/>
 </workbook>
@@ -280,7 +281,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="272">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="299">
   <si>
     <t>需求</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1288,10 +1289,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>192.168.20.197:11814/?cmd=add business&amp;ConfigInfo={"ClusterName":"c1","BusinessType":"sequoiadb","BusinessName":"b1","DeployMod":"standalone", "Config": [{ "HostName": "host1", "datagroupname": "", "dbpath": "/home/db2/standalone/11830", "svcname": "11830", "diaglevel": "3", "role": "standalone", "logfilesz": "64", "logfilenum": "20", "transactionon": "false", "preferedinstance": "A", "numpagecleaners": "1", "pagecleaninterval": "1", "datagroupname": "group1", "hjbuf": "128", "logbuffsize": "1024", "maxprefpool": "200", "maxreplsync": "10", "numpreload": "0", "sortbuf": "512", "syncstrategy": "none"} ]}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>http://192.168.20.197:11814/?cmd=query progress&amp;Task={"TaskID":"12345"}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1430,12 +1427,130 @@
     <t>rest隐藏参数IsForce， 在agent卸载主机失败时仍然强行删除host信息</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>192.168.20.197:11814/?cmd=add business&amp;ConfigInfo={"ClusterName":"c1","BusinessType":"sequoiadb","BusinessName":"b1","DeployMod":"standalone", "Config": [{ "HostName": "host1", "datagroupname": "", "dbpath": "/home/db2/standalone/11830", "svcname": "11830", "diaglevel": "3", "role": "standalone", "logfilesz": "64", "logfilenum": "20", "transactionon": "false", "preferedinstance": "A", "numpagecleaners": "1", "pagecleaninterval": "1", "datagroupname": "group1", "hjbuf": "128", "logbuffsize": "1024", "maxprefpool": "200", "maxreplsync": "10", "numpreload": "0", "sortbuf": "512", "syncstrategy": "none"} ]}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>预计</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>9月18日</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>需要完成相关功能的编码</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>待调试</t>
+  </si>
+  <si>
+    <t>预计安装部署、卸载10月15日发布</t>
+  </si>
+  <si>
+    <t>接口调整</t>
+  </si>
+  <si>
+    <t>安装业务</t>
+  </si>
+  <si>
+    <t>scanhost</t>
+  </si>
+  <si>
+    <t>addhost</t>
+  </si>
+  <si>
+    <t>agent重启</t>
+  </si>
+  <si>
+    <t>卸载机器</t>
+  </si>
+  <si>
+    <t>卸载集群</t>
+  </si>
+  <si>
+    <t>卸载业务</t>
+  </si>
+  <si>
+    <t>业务状态</t>
+  </si>
+  <si>
+    <t>******</t>
+  </si>
+  <si>
+    <t>启动业务</t>
+  </si>
+  <si>
+    <t>停止业务</t>
+  </si>
+  <si>
+    <t>页面优先显示</t>
+  </si>
+  <si>
+    <t>异常处理(业务已经存在，版本冲突）</t>
+  </si>
+  <si>
+    <t>业务扩容</t>
+  </si>
+  <si>
+    <t>messageReply返回值的模式</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>待完成功能</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>详细说明</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>调整为1个机器最耗时1s</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>修改为后台并发</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>开始编码</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>开始编码，后台并发</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>返回值定义</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>优化</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="17">
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1565,6 +1680,29 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1" tint="0.499984740745262"/>
+      <name val="宋体"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1" tint="0.499984740745262"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -1653,7 +1791,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1735,12 +1873,27 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3623,10 +3776,10 @@
         <v>207</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E9" s="4"/>
       <c r="F9" s="4"/>
@@ -3666,7 +3819,7 @@
         <v>193</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E12" s="4"/>
       <c r="F12" s="4"/>
@@ -3680,7 +3833,7 @@
         <v>194</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E13" s="4"/>
       <c r="F13" s="4"/>
@@ -3703,10 +3856,10 @@
         <v>209</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E15" s="4"/>
       <c r="F15" s="4"/>
@@ -3776,7 +3929,7 @@
         <v>135</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C21" s="9"/>
       <c r="D21" s="9" t="s">
@@ -3820,7 +3973,7 @@
         <v>235</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E24" s="4"/>
       <c r="F24" s="4"/>
@@ -3834,7 +3987,7 @@
         <v>195</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="E25" s="4"/>
       <c r="F25" s="4"/>
@@ -3860,7 +4013,7 @@
         <v>236</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="E27" s="4"/>
       <c r="F27" s="4"/>
@@ -3900,7 +4053,7 @@
         <v>202</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>238</v>
+        <v>271</v>
       </c>
       <c r="E30" s="4"/>
       <c r="F30" s="4"/>
@@ -3938,7 +4091,7 @@
         <v>203</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E33" s="4"/>
       <c r="F33" s="4"/>
@@ -3949,7 +4102,7 @@
       </c>
       <c r="B34" s="4"/>
       <c r="C34" s="9" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D34" s="9"/>
       <c r="E34" s="4"/>
@@ -3965,23 +4118,23 @@
     </row>
     <row r="36" spans="1:6" ht="24">
       <c r="A36" s="9" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B36" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="C36" s="9" t="s">
         <v>255</v>
       </c>
-      <c r="C36" s="9" t="s">
+      <c r="D36" s="9" t="s">
         <v>256</v>
-      </c>
-      <c r="D36" s="9" t="s">
-        <v>257</v>
       </c>
       <c r="E36" s="4"/>
       <c r="F36" s="4"/>
     </row>
     <row r="37" spans="1:6">
       <c r="A37" s="9" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B37" s="4"/>
       <c r="C37" s="9"/>
@@ -3999,16 +4152,16 @@
     </row>
     <row r="39" spans="1:6" ht="24">
       <c r="A39" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B39" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="C39" s="9" t="s">
+        <v>255</v>
+      </c>
+      <c r="D39" s="9" t="s">
         <v>261</v>
-      </c>
-      <c r="C39" s="9" t="s">
-        <v>256</v>
-      </c>
-      <c r="D39" s="9" t="s">
-        <v>262</v>
       </c>
       <c r="E39" s="4"/>
       <c r="F39" s="4"/>
@@ -4358,194 +4511,371 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="33" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B1" s="33" t="s">
+        <v>246</v>
+      </c>
+      <c r="C1" s="34" t="s">
         <v>247</v>
       </c>
-      <c r="C1" s="34" t="s">
-        <v>248</v>
-      </c>
       <c r="D1" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="E1" s="34" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="67.5">
-      <c r="A2" s="35" t="s">
-        <v>253</v>
-      </c>
-      <c r="B2" s="36" t="s">
+      <c r="A2" s="36" t="s">
+        <v>252</v>
+      </c>
+      <c r="B2" s="37" t="s">
+        <v>266</v>
+      </c>
+      <c r="C2" s="36" t="s">
+        <v>250</v>
+      </c>
+      <c r="D2" s="36" t="s">
+        <v>249</v>
+      </c>
+      <c r="E2" s="38" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="37"/>
+      <c r="B3" s="37"/>
+      <c r="C3" s="36"/>
+      <c r="D3" s="36"/>
+      <c r="E3" s="36"/>
+    </row>
+    <row r="4" spans="1:5" ht="27">
+      <c r="A4" s="37" t="s">
+        <v>265</v>
+      </c>
+      <c r="B4" s="37" t="s">
+        <v>44</v>
+      </c>
+      <c r="C4" s="36" t="s">
         <v>267</v>
       </c>
-      <c r="C2" s="35" t="s">
-        <v>251</v>
-      </c>
-      <c r="D2" s="35" t="s">
-        <v>250</v>
-      </c>
-      <c r="E2" s="37" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="36"/>
-      <c r="B3" s="36"/>
-      <c r="C3" s="35"/>
-      <c r="D3" s="35"/>
-      <c r="E3" s="35"/>
-    </row>
-    <row r="4" spans="1:5" ht="27">
-      <c r="A4" s="36" t="s">
-        <v>266</v>
-      </c>
-      <c r="B4" s="36" t="s">
-        <v>44</v>
-      </c>
-      <c r="C4" s="35" t="s">
+      <c r="D4" s="36" t="s">
         <v>268</v>
       </c>
-      <c r="D4" s="35" t="s">
-        <v>269</v>
-      </c>
-      <c r="E4" s="37" t="s">
-        <v>271</v>
+      <c r="E4" s="38" t="s">
+        <v>270</v>
       </c>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="36"/>
-      <c r="B5" s="36"/>
+      <c r="A5" s="37"/>
+      <c r="B5" s="37"/>
+      <c r="C5" s="36"/>
+      <c r="D5" s="36"/>
+      <c r="E5" s="36"/>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="37"/>
+      <c r="B6" s="37"/>
+      <c r="C6" s="36"/>
+      <c r="D6" s="36"/>
+      <c r="E6" s="36"/>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="37"/>
+      <c r="B7" s="37"/>
+      <c r="C7" s="36"/>
+      <c r="D7" s="36"/>
+      <c r="E7" s="36"/>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="37"/>
+      <c r="B8" s="37"/>
+      <c r="C8" s="36"/>
+      <c r="D8" s="36"/>
+      <c r="E8" s="36"/>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="37"/>
+      <c r="B9" s="37"/>
+      <c r="C9" s="36"/>
+      <c r="D9" s="36"/>
+      <c r="E9" s="36"/>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="37"/>
+      <c r="B10" s="37"/>
+      <c r="C10" s="36"/>
+      <c r="D10" s="36"/>
+      <c r="E10" s="36"/>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="37"/>
+      <c r="B11" s="37"/>
+      <c r="C11" s="36"/>
+      <c r="D11" s="36"/>
+      <c r="E11" s="36"/>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="37"/>
+      <c r="B12" s="37"/>
+      <c r="C12" s="36"/>
+      <c r="D12" s="36"/>
+      <c r="E12" s="36"/>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="37"/>
+      <c r="B13" s="37"/>
+      <c r="C13" s="36"/>
+      <c r="D13" s="36"/>
+      <c r="E13" s="36"/>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="37"/>
+      <c r="B14" s="37"/>
+      <c r="C14" s="36"/>
+      <c r="D14" s="36"/>
+      <c r="E14" s="36"/>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="37"/>
+      <c r="B15" s="37"/>
+      <c r="C15" s="36"/>
+      <c r="D15" s="36"/>
+      <c r="E15" s="36"/>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="37"/>
+      <c r="B16" s="37"/>
+      <c r="C16" s="36"/>
+      <c r="D16" s="36"/>
+      <c r="E16" s="36"/>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="37"/>
+      <c r="B17" s="37"/>
+      <c r="C17" s="36"/>
+      <c r="D17" s="36"/>
+      <c r="E17" s="36"/>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="37"/>
+      <c r="B18" s="37"/>
+      <c r="C18" s="36"/>
+      <c r="D18" s="36"/>
+      <c r="E18" s="36"/>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="37"/>
+      <c r="B19" s="37"/>
+      <c r="C19" s="36"/>
+      <c r="D19" s="36"/>
+      <c r="E19" s="36"/>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="37"/>
+      <c r="B20" s="37"/>
+      <c r="C20" s="36"/>
+      <c r="D20" s="36"/>
+      <c r="E20" s="36"/>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="37"/>
+      <c r="B21" s="37"/>
+      <c r="C21" s="36"/>
+      <c r="D21" s="36"/>
+      <c r="E21" s="36"/>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="37"/>
+      <c r="B22" s="37"/>
+      <c r="C22" s="36"/>
+      <c r="D22" s="36"/>
+      <c r="E22" s="36"/>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="37"/>
+      <c r="B23" s="37"/>
+      <c r="C23" s="36"/>
+      <c r="D23" s="36"/>
+      <c r="E23" s="36"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H18"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
+  <cols>
+    <col min="1" max="1" width="23.125" style="23" customWidth="1"/>
+    <col min="2" max="2" width="27.75" style="23" customWidth="1"/>
+    <col min="3" max="8" width="9" style="23"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="27">
+      <c r="A1" s="23" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="27">
+      <c r="A2" s="23" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="34" t="s">
+        <v>291</v>
+      </c>
+      <c r="B4" s="34" t="s">
+        <v>292</v>
+      </c>
+      <c r="C4" s="34"/>
+      <c r="D4" s="34"/>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="39" t="s">
+        <v>275</v>
+      </c>
+      <c r="B5" s="35" t="s">
+        <v>290</v>
+      </c>
       <c r="C5" s="35"/>
       <c r="D5" s="35"/>
-      <c r="E5" s="35"/>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" s="36"/>
-      <c r="B6" s="36"/>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="39" t="s">
+        <v>276</v>
+      </c>
+      <c r="B6" s="35" t="s">
+        <v>273</v>
+      </c>
       <c r="C6" s="35"/>
       <c r="D6" s="35"/>
-      <c r="E6" s="35"/>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7" s="36"/>
-      <c r="B7" s="36"/>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="39" t="s">
+        <v>277</v>
+      </c>
+      <c r="B7" s="35" t="s">
+        <v>293</v>
+      </c>
       <c r="C7" s="35"/>
       <c r="D7" s="35"/>
-      <c r="E7" s="35"/>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" s="36"/>
-      <c r="B8" s="36"/>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="39" t="s">
+        <v>278</v>
+      </c>
+      <c r="B8" s="35" t="s">
+        <v>294</v>
+      </c>
       <c r="C8" s="35"/>
       <c r="D8" s="35"/>
-      <c r="E8" s="35"/>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9" s="36"/>
-      <c r="B9" s="36"/>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="39" t="s">
+        <v>279</v>
+      </c>
+      <c r="B9" s="35" t="s">
+        <v>295</v>
+      </c>
       <c r="C9" s="35"/>
       <c r="D9" s="35"/>
-      <c r="E9" s="35"/>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10" s="36"/>
-      <c r="B10" s="36"/>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="39" t="s">
+        <v>280</v>
+      </c>
+      <c r="B10" s="35" t="s">
+        <v>295</v>
+      </c>
       <c r="C10" s="35"/>
       <c r="D10" s="35"/>
-      <c r="E10" s="35"/>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11" s="36"/>
-      <c r="B11" s="36"/>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="39" t="s">
+        <v>281</v>
+      </c>
+      <c r="B11" s="35" t="s">
+        <v>295</v>
+      </c>
       <c r="C11" s="35"/>
       <c r="D11" s="35"/>
-      <c r="E11" s="35"/>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12" s="36"/>
-      <c r="B12" s="36"/>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="39" t="s">
+        <v>282</v>
+      </c>
+      <c r="B12" s="35" t="s">
+        <v>296</v>
+      </c>
       <c r="C12" s="35"/>
       <c r="D12" s="35"/>
-      <c r="E12" s="35"/>
-    </row>
-    <row r="13" spans="1:5">
-      <c r="A13" s="36"/>
-      <c r="B13" s="36"/>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="39" t="s">
+        <v>287</v>
+      </c>
+      <c r="B13" s="35" t="s">
+        <v>297</v>
+      </c>
       <c r="C13" s="35"/>
       <c r="D13" s="35"/>
-      <c r="E13" s="35"/>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14" s="36"/>
-      <c r="B14" s="36"/>
+    </row>
+    <row r="14" spans="1:4" ht="27">
+      <c r="A14" s="39" t="s">
+        <v>288</v>
+      </c>
+      <c r="B14" s="35" t="s">
+        <v>298</v>
+      </c>
       <c r="C14" s="35"/>
       <c r="D14" s="35"/>
-      <c r="E14" s="35"/>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15" s="36"/>
-      <c r="B15" s="36"/>
-      <c r="C15" s="35"/>
-      <c r="D15" s="35"/>
-      <c r="E15" s="35"/>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="A16" s="36"/>
-      <c r="B16" s="36"/>
-      <c r="C16" s="35"/>
-      <c r="D16" s="35"/>
-      <c r="E16" s="35"/>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="36"/>
-      <c r="B17" s="36"/>
-      <c r="C17" s="35"/>
-      <c r="D17" s="35"/>
-      <c r="E17" s="35"/>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="36"/>
-      <c r="B18" s="36"/>
-      <c r="C18" s="35"/>
-      <c r="D18" s="35"/>
-      <c r="E18" s="35"/>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="36"/>
-      <c r="B19" s="36"/>
-      <c r="C19" s="35"/>
-      <c r="D19" s="35"/>
-      <c r="E19" s="35"/>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="36"/>
-      <c r="B20" s="36"/>
-      <c r="C20" s="35"/>
-      <c r="D20" s="35"/>
-      <c r="E20" s="35"/>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="36"/>
-      <c r="B21" s="36"/>
-      <c r="C21" s="35"/>
-      <c r="D21" s="35"/>
-      <c r="E21" s="35"/>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="36"/>
-      <c r="B22" s="36"/>
-      <c r="C22" s="35"/>
-      <c r="D22" s="35"/>
-      <c r="E22" s="35"/>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="36"/>
-      <c r="B23" s="36"/>
-      <c r="C23" s="35"/>
-      <c r="D23" s="35"/>
-      <c r="E23" s="35"/>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="40" t="s">
+        <v>289</v>
+      </c>
+      <c r="B15" s="41" t="s">
+        <v>284</v>
+      </c>
+      <c r="C15" s="41"/>
+      <c r="D15" s="41"/>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="42" t="s">
+        <v>283</v>
+      </c>
+      <c r="B16" s="41" t="s">
+        <v>284</v>
+      </c>
+      <c r="C16" s="41"/>
+      <c r="D16" s="41"/>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" s="42" t="s">
+        <v>285</v>
+      </c>
+      <c r="B17" s="41" t="s">
+        <v>284</v>
+      </c>
+      <c r="C17" s="41"/>
+      <c r="D17" s="41"/>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" s="42" t="s">
+        <v>286</v>
+      </c>
+      <c r="B18" s="41" t="s">
+        <v>284</v>
+      </c>
+      <c r="C18" s="41"/>
+      <c r="D18" s="41"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/internal_doc/03.开发设计/OM_web接口.xlsx
+++ b/internal_doc/03.开发设计/OM_web接口.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="6510" activeTab="6"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="6510" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="需求" sheetId="1" r:id="rId1"/>
@@ -1412,10 +1412,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>{"HostName":"", "IP":"", "User":"", "Passwd":""}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>{Rc, 0}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1543,6 +1539,10 @@
   </si>
   <si>
     <t>优化</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"HostName":"", "IP":"", "User":"", "Passwd":"", "InstallPath":""}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1791,7 +1791,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1851,24 +1851,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1895,6 +1877,32 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2306,7 +2314,7 @@
       </c>
     </row>
     <row r="3" spans="1:8">
-      <c r="A3" s="27" t="s">
+      <c r="A3" s="37" t="s">
         <v>12</v>
       </c>
       <c r="B3" s="4" t="s">
@@ -2324,7 +2332,7 @@
       <c r="H3" s="4"/>
     </row>
     <row r="4" spans="1:8" ht="13.5">
-      <c r="A4" s="28"/>
+      <c r="A4" s="38"/>
       <c r="B4" s="4" t="s">
         <v>5</v>
       </c>
@@ -2340,7 +2348,7 @@
       <c r="H4" s="4"/>
     </row>
     <row r="5" spans="1:8" ht="13.5">
-      <c r="A5" s="28"/>
+      <c r="A5" s="38"/>
       <c r="B5" s="4" t="s">
         <v>8</v>
       </c>
@@ -2356,7 +2364,7 @@
       <c r="H5" s="4"/>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" s="29"/>
+      <c r="A6" s="39"/>
       <c r="B6" s="4" t="s">
         <v>13</v>
       </c>
@@ -2372,7 +2380,7 @@
       <c r="H6" s="4"/>
     </row>
     <row r="7" spans="1:8" ht="24">
-      <c r="A7" s="30" t="s">
+      <c r="A7" s="40" t="s">
         <v>24</v>
       </c>
       <c r="B7" s="4" t="s">
@@ -2390,7 +2398,7 @@
       <c r="H7" s="4"/>
     </row>
     <row r="8" spans="1:8" ht="36">
-      <c r="A8" s="31"/>
+      <c r="A8" s="41"/>
       <c r="B8" s="4" t="s">
         <v>17</v>
       </c>
@@ -2408,7 +2416,7 @@
       <c r="H8" s="4"/>
     </row>
     <row r="9" spans="1:8" ht="72">
-      <c r="A9" s="31"/>
+      <c r="A9" s="41"/>
       <c r="B9" s="4" t="s">
         <v>18</v>
       </c>
@@ -2426,7 +2434,7 @@
       <c r="H9" s="4"/>
     </row>
     <row r="10" spans="1:8" ht="24">
-      <c r="A10" s="32"/>
+      <c r="A10" s="42"/>
       <c r="B10" s="4" t="s">
         <v>21</v>
       </c>
@@ -2464,7 +2472,7 @@
       <c r="H11" s="4"/>
     </row>
     <row r="12" spans="1:8" ht="24">
-      <c r="A12" s="30" t="s">
+      <c r="A12" s="40" t="s">
         <v>26</v>
       </c>
       <c r="B12" s="4" t="s">
@@ -2482,7 +2490,7 @@
       <c r="H12" s="4"/>
     </row>
     <row r="13" spans="1:8">
-      <c r="A13" s="31"/>
+      <c r="A13" s="41"/>
       <c r="B13" s="4" t="s">
         <v>32</v>
       </c>
@@ -2498,7 +2506,7 @@
       <c r="H13" s="4"/>
     </row>
     <row r="14" spans="1:8" ht="24">
-      <c r="A14" s="31"/>
+      <c r="A14" s="41"/>
       <c r="B14" s="4" t="s">
         <v>33</v>
       </c>
@@ -2516,7 +2524,7 @@
       <c r="H14" s="4"/>
     </row>
     <row r="15" spans="1:8">
-      <c r="A15" s="31"/>
+      <c r="A15" s="41"/>
       <c r="B15" s="4" t="s">
         <v>35</v>
       </c>
@@ -2532,7 +2540,7 @@
       <c r="H15" s="4"/>
     </row>
     <row r="16" spans="1:8">
-      <c r="A16" s="31"/>
+      <c r="A16" s="41"/>
       <c r="B16" s="4" t="s">
         <v>57</v>
       </c>
@@ -2544,7 +2552,7 @@
       <c r="H16" s="4"/>
     </row>
     <row r="17" spans="1:8" ht="48">
-      <c r="A17" s="31"/>
+      <c r="A17" s="41"/>
       <c r="B17" s="4" t="s">
         <v>30</v>
       </c>
@@ -2562,7 +2570,7 @@
       <c r="H17" s="4"/>
     </row>
     <row r="18" spans="1:8">
-      <c r="A18" s="31"/>
+      <c r="A18" s="41"/>
       <c r="B18" s="4" t="s">
         <v>38</v>
       </c>
@@ -2578,7 +2586,7 @@
       <c r="H18" s="4"/>
     </row>
     <row r="19" spans="1:8">
-      <c r="A19" s="31"/>
+      <c r="A19" s="41"/>
       <c r="B19" s="4" t="s">
         <v>41</v>
       </c>
@@ -2594,7 +2602,7 @@
       <c r="H19" s="4"/>
     </row>
     <row r="20" spans="1:8">
-      <c r="A20" s="31"/>
+      <c r="A20" s="41"/>
       <c r="B20" s="4" t="s">
         <v>40</v>
       </c>
@@ -2610,7 +2618,7 @@
       <c r="H20" s="4"/>
     </row>
     <row r="21" spans="1:8" ht="24">
-      <c r="A21" s="31"/>
+      <c r="A21" s="41"/>
       <c r="B21" s="4" t="s">
         <v>44</v>
       </c>
@@ -2628,7 +2636,7 @@
       <c r="H21" s="4"/>
     </row>
     <row r="22" spans="1:8" ht="24">
-      <c r="A22" s="31"/>
+      <c r="A22" s="41"/>
       <c r="B22" s="4" t="s">
         <v>47</v>
       </c>
@@ -2644,7 +2652,7 @@
       <c r="H22" s="4"/>
     </row>
     <row r="23" spans="1:8" ht="24">
-      <c r="A23" s="31"/>
+      <c r="A23" s="41"/>
       <c r="B23" s="4" t="s">
         <v>49</v>
       </c>
@@ -3656,7 +3664,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F71"/>
+  <dimension ref="A1:F74"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="26" style="10" bestFit="1" customWidth="1"/>
@@ -4053,7 +4061,7 @@
         <v>202</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E30" s="4"/>
       <c r="F30" s="4"/>
@@ -4221,226 +4229,247 @@
       <c r="F44" s="4"/>
     </row>
     <row r="45" spans="1:6">
-      <c r="A45" s="9"/>
-      <c r="B45" s="4"/>
-      <c r="C45" s="9"/>
-      <c r="D45" s="9"/>
-      <c r="E45" s="4"/>
-      <c r="F45" s="4"/>
-    </row>
-    <row r="52" spans="1:6">
-      <c r="A52" s="9" t="s">
-        <v>153</v>
-      </c>
-      <c r="B52" s="4" t="s">
-        <v>206</v>
-      </c>
-      <c r="C52" s="9" t="s">
-        <v>147</v>
-      </c>
+      <c r="A45" s="43"/>
+      <c r="B45" s="44"/>
+      <c r="C45" s="43"/>
+      <c r="D45" s="43"/>
+      <c r="E45" s="44"/>
+      <c r="F45" s="44"/>
+    </row>
+    <row r="46" spans="1:6" s="4" customFormat="1">
+      <c r="A46" s="9"/>
+      <c r="C46" s="9"/>
+      <c r="D46" s="9"/>
+    </row>
+    <row r="47" spans="1:6" s="4" customFormat="1">
+      <c r="A47" s="9"/>
+      <c r="C47" s="9"/>
+      <c r="D47" s="9"/>
+    </row>
+    <row r="48" spans="1:6" s="4" customFormat="1">
+      <c r="A48" s="9"/>
+      <c r="C48" s="9"/>
+      <c r="D48" s="9"/>
+    </row>
+    <row r="49" spans="1:6" s="4" customFormat="1">
+      <c r="A49" s="9"/>
+      <c r="C49" s="9"/>
+      <c r="D49" s="9"/>
+    </row>
+    <row r="50" spans="1:6" s="4" customFormat="1">
+      <c r="A50" s="9"/>
+      <c r="C50" s="9"/>
+      <c r="D50" s="9"/>
+    </row>
+    <row r="51" spans="1:6" s="4" customFormat="1">
+      <c r="A51" s="9"/>
+      <c r="C51" s="9"/>
+      <c r="D51" s="9"/>
+    </row>
+    <row r="52" spans="1:6" s="4" customFormat="1">
+      <c r="A52" s="9"/>
+      <c r="C52" s="9"/>
       <c r="D52" s="9"/>
-      <c r="E52" s="4"/>
-      <c r="F52" s="4"/>
-    </row>
-    <row r="53" spans="1:6" ht="24">
-      <c r="A53" s="9" t="s">
-        <v>154</v>
-      </c>
-      <c r="B53" s="4"/>
-      <c r="C53" s="9" t="s">
-        <v>170</v>
-      </c>
-      <c r="D53" s="9" t="s">
-        <v>155</v>
-      </c>
-      <c r="E53" s="4"/>
-      <c r="F53" s="4"/>
-    </row>
-    <row r="54" spans="1:6">
+    </row>
+    <row r="53" spans="1:6" s="4" customFormat="1">
+      <c r="A53" s="9"/>
+      <c r="C53" s="9"/>
+      <c r="D53" s="9"/>
+    </row>
+    <row r="54" spans="1:6" s="4" customFormat="1">
       <c r="A54" s="9"/>
-      <c r="B54" s="4"/>
       <c r="C54" s="9"/>
       <c r="D54" s="9"/>
-      <c r="E54" s="4"/>
-      <c r="F54" s="4"/>
-    </row>
-    <row r="55" spans="1:6" ht="24">
-      <c r="A55" s="9" t="s">
-        <v>168</v>
-      </c>
-      <c r="B55" s="4" t="s">
-        <v>224</v>
-      </c>
-      <c r="C55" s="9" t="s">
-        <v>213</v>
-      </c>
-      <c r="D55" s="9" t="s">
-        <v>237</v>
-      </c>
-      <c r="E55" s="4"/>
-      <c r="F55" s="4"/>
-    </row>
-    <row r="56" spans="1:6">
+    </row>
+    <row r="55" spans="1:6">
+      <c r="A55" s="45" t="s">
+        <v>153</v>
+      </c>
+      <c r="B55" s="46" t="s">
+        <v>206</v>
+      </c>
+      <c r="C55" s="45" t="s">
+        <v>147</v>
+      </c>
+      <c r="D55" s="45"/>
+      <c r="E55" s="46"/>
+      <c r="F55" s="46"/>
+    </row>
+    <row r="56" spans="1:6" ht="24">
       <c r="A56" s="9" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="B56" s="4"/>
       <c r="C56" s="9" t="s">
-        <v>225</v>
-      </c>
-      <c r="D56" s="9"/>
+        <v>170</v>
+      </c>
+      <c r="D56" s="9" t="s">
+        <v>155</v>
+      </c>
       <c r="E56" s="4"/>
       <c r="F56" s="4"/>
     </row>
-    <row r="57" spans="1:6" ht="36">
-      <c r="A57" s="9" t="s">
-        <v>214</v>
-      </c>
-      <c r="B57" s="4" t="s">
-        <v>215</v>
-      </c>
-      <c r="C57" s="9" t="s">
-        <v>216</v>
-      </c>
-      <c r="D57" s="9" t="s">
-        <v>217</v>
-      </c>
+    <row r="57" spans="1:6">
+      <c r="A57" s="9"/>
+      <c r="B57" s="4"/>
+      <c r="C57" s="9"/>
+      <c r="D57" s="9"/>
       <c r="E57" s="4"/>
       <c r="F57" s="4"/>
     </row>
-    <row r="58" spans="1:6">
+    <row r="58" spans="1:6" ht="24">
       <c r="A58" s="9" t="s">
-        <v>218</v>
+        <v>168</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>219</v>
-      </c>
-      <c r="C58" s="9"/>
-      <c r="D58" s="9"/>
+        <v>224</v>
+      </c>
+      <c r="C58" s="9" t="s">
+        <v>213</v>
+      </c>
+      <c r="D58" s="9" t="s">
+        <v>237</v>
+      </c>
       <c r="E58" s="4"/>
       <c r="F58" s="4"/>
     </row>
     <row r="59" spans="1:6">
-      <c r="A59" s="9"/>
+      <c r="A59" s="9" t="s">
+        <v>169</v>
+      </c>
       <c r="B59" s="4"/>
-      <c r="C59" s="9"/>
+      <c r="C59" s="9" t="s">
+        <v>225</v>
+      </c>
       <c r="D59" s="9"/>
       <c r="E59" s="4"/>
       <c r="F59" s="4"/>
     </row>
-    <row r="60" spans="1:6">
-      <c r="A60" s="5" t="s">
+    <row r="60" spans="1:6" ht="36">
+      <c r="A60" s="9" t="s">
+        <v>214</v>
+      </c>
+      <c r="B60" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="C60" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="D60" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="E60" s="4"/>
+      <c r="F60" s="4"/>
+    </row>
+    <row r="61" spans="1:6">
+      <c r="A61" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="B61" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="C61" s="9"/>
+      <c r="D61" s="9"/>
+      <c r="E61" s="4"/>
+      <c r="F61" s="4"/>
+    </row>
+    <row r="62" spans="1:6">
+      <c r="A62" s="9"/>
+      <c r="B62" s="4"/>
+      <c r="C62" s="9"/>
+      <c r="D62" s="9"/>
+      <c r="E62" s="4"/>
+      <c r="F62" s="4"/>
+    </row>
+    <row r="63" spans="1:6">
+      <c r="A63" s="5" t="s">
         <v>160</v>
       </c>
-      <c r="B60" s="2"/>
-      <c r="C60" s="5" t="s">
+      <c r="B63" s="2"/>
+      <c r="C63" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="D60" s="5"/>
-      <c r="E60" s="2"/>
-      <c r="F60" s="2"/>
-    </row>
-    <row r="61" spans="1:6" ht="24">
-      <c r="A61" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="B61" s="2"/>
-      <c r="C61" s="5" t="s">
-        <v>225</v>
-      </c>
-      <c r="D61" s="5" t="s">
-        <v>149</v>
-      </c>
-      <c r="E61" s="2"/>
-      <c r="F61" s="2"/>
-    </row>
-    <row r="62" spans="1:6" ht="24">
-      <c r="A62" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="B62" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="C62" s="5" t="s">
-        <v>158</v>
-      </c>
-      <c r="D62" s="5"/>
-      <c r="E62" s="2"/>
-      <c r="F62" s="2"/>
-    </row>
-    <row r="63" spans="1:6" ht="60">
-      <c r="A63" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="B63" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="C63" s="5" t="s">
-        <v>166</v>
-      </c>
-      <c r="D63" s="5" t="s">
-        <v>167</v>
-      </c>
+      <c r="D63" s="5"/>
       <c r="E63" s="2"/>
       <c r="F63" s="2"/>
     </row>
-    <row r="64" spans="1:6" ht="48">
+    <row r="64" spans="1:6" ht="24">
       <c r="A64" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="B64" s="2" t="s">
-        <v>163</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="B64" s="2"/>
       <c r="C64" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="D64" s="5"/>
+        <v>225</v>
+      </c>
+      <c r="D64" s="5" t="s">
+        <v>149</v>
+      </c>
       <c r="E64" s="2"/>
       <c r="F64" s="2"/>
     </row>
-    <row r="65" spans="1:6" s="21" customFormat="1">
-      <c r="A65" s="25" t="s">
-        <v>152</v>
-      </c>
-      <c r="B65" s="26"/>
-      <c r="C65" s="25"/>
-      <c r="D65" s="25" t="s">
-        <v>150</v>
-      </c>
-      <c r="E65" s="26"/>
-      <c r="F65" s="26"/>
-    </row>
-    <row r="66" spans="1:6">
-      <c r="A66" s="5"/>
-      <c r="B66" s="2"/>
-      <c r="C66" s="5"/>
-      <c r="D66" s="5"/>
+    <row r="65" spans="1:6" ht="24">
+      <c r="A65" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="C65" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="D65" s="5"/>
+      <c r="E65" s="2"/>
+      <c r="F65" s="2"/>
+    </row>
+    <row r="66" spans="1:6" ht="60">
+      <c r="A66" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="C66" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="D66" s="5" t="s">
+        <v>167</v>
+      </c>
       <c r="E66" s="2"/>
       <c r="F66" s="2"/>
     </row>
-    <row r="67" spans="1:6">
-      <c r="A67" s="9"/>
-      <c r="B67" s="4"/>
-      <c r="C67" s="9"/>
-      <c r="D67" s="9"/>
-      <c r="E67" s="4"/>
-      <c r="F67" s="4"/>
-    </row>
-    <row r="68" spans="1:6">
-      <c r="A68" s="9"/>
-      <c r="B68" s="4"/>
-      <c r="C68" s="9"/>
-      <c r="D68" s="9"/>
-      <c r="E68" s="4"/>
-      <c r="F68" s="4"/>
+    <row r="67" spans="1:6" ht="48">
+      <c r="A67" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="C67" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="D67" s="5"/>
+      <c r="E67" s="2"/>
+      <c r="F67" s="2"/>
+    </row>
+    <row r="68" spans="1:6" s="21" customFormat="1">
+      <c r="A68" s="25" t="s">
+        <v>152</v>
+      </c>
+      <c r="B68" s="26"/>
+      <c r="C68" s="25"/>
+      <c r="D68" s="25" t="s">
+        <v>150</v>
+      </c>
+      <c r="E68" s="26"/>
+      <c r="F68" s="26"/>
     </row>
     <row r="69" spans="1:6">
-      <c r="A69" s="9"/>
-      <c r="B69" s="4"/>
-      <c r="C69" s="9"/>
-      <c r="D69" s="9"/>
-      <c r="E69" s="4"/>
-      <c r="F69" s="4"/>
+      <c r="A69" s="5"/>
+      <c r="B69" s="2"/>
+      <c r="C69" s="5"/>
+      <c r="D69" s="5"/>
+      <c r="E69" s="2"/>
+      <c r="F69" s="2"/>
     </row>
     <row r="70" spans="1:6">
       <c r="A70" s="9"/>
@@ -4457,6 +4486,30 @@
       <c r="D71" s="9"/>
       <c r="E71" s="4"/>
       <c r="F71" s="4"/>
+    </row>
+    <row r="72" spans="1:6">
+      <c r="A72" s="9"/>
+      <c r="B72" s="4"/>
+      <c r="C72" s="9"/>
+      <c r="D72" s="9"/>
+      <c r="E72" s="4"/>
+      <c r="F72" s="4"/>
+    </row>
+    <row r="73" spans="1:6">
+      <c r="A73" s="9"/>
+      <c r="B73" s="4"/>
+      <c r="C73" s="9"/>
+      <c r="D73" s="9"/>
+      <c r="E73" s="4"/>
+      <c r="F73" s="4"/>
+    </row>
+    <row r="74" spans="1:6">
+      <c r="A74" s="9"/>
+      <c r="B74" s="4"/>
+      <c r="C74" s="9"/>
+      <c r="D74" s="9"/>
+      <c r="E74" s="4"/>
+      <c r="F74" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -4510,195 +4563,195 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="27" t="s">
         <v>248</v>
       </c>
-      <c r="B1" s="33" t="s">
+      <c r="B1" s="27" t="s">
         <v>246</v>
       </c>
-      <c r="C1" s="34" t="s">
+      <c r="C1" s="28" t="s">
         <v>247</v>
       </c>
-      <c r="D1" s="34" t="s">
+      <c r="D1" s="28" t="s">
+        <v>268</v>
+      </c>
+      <c r="E1" s="28" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="67.5">
+      <c r="A2" s="30" t="s">
+        <v>252</v>
+      </c>
+      <c r="B2" s="31" t="s">
+        <v>266</v>
+      </c>
+      <c r="C2" s="30" t="s">
+        <v>250</v>
+      </c>
+      <c r="D2" s="30" t="s">
+        <v>249</v>
+      </c>
+      <c r="E2" s="32" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="31"/>
+      <c r="B3" s="31"/>
+      <c r="C3" s="30"/>
+      <c r="D3" s="30"/>
+      <c r="E3" s="30"/>
+    </row>
+    <row r="4" spans="1:5" ht="27">
+      <c r="A4" s="31" t="s">
+        <v>265</v>
+      </c>
+      <c r="B4" s="31" t="s">
+        <v>44</v>
+      </c>
+      <c r="C4" s="30" t="s">
+        <v>298</v>
+      </c>
+      <c r="D4" s="30" t="s">
+        <v>267</v>
+      </c>
+      <c r="E4" s="32" t="s">
         <v>269</v>
       </c>
-      <c r="E1" s="34" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="67.5">
-      <c r="A2" s="36" t="s">
-        <v>252</v>
-      </c>
-      <c r="B2" s="37" t="s">
-        <v>266</v>
-      </c>
-      <c r="C2" s="36" t="s">
-        <v>250</v>
-      </c>
-      <c r="D2" s="36" t="s">
-        <v>249</v>
-      </c>
-      <c r="E2" s="38" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="37"/>
-      <c r="B3" s="37"/>
-      <c r="C3" s="36"/>
-      <c r="D3" s="36"/>
-      <c r="E3" s="36"/>
-    </row>
-    <row r="4" spans="1:5" ht="27">
-      <c r="A4" s="37" t="s">
-        <v>265</v>
-      </c>
-      <c r="B4" s="37" t="s">
-        <v>44</v>
-      </c>
-      <c r="C4" s="36" t="s">
-        <v>267</v>
-      </c>
-      <c r="D4" s="36" t="s">
-        <v>268</v>
-      </c>
-      <c r="E4" s="38" t="s">
-        <v>270</v>
-      </c>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="37"/>
-      <c r="B5" s="37"/>
-      <c r="C5" s="36"/>
-      <c r="D5" s="36"/>
-      <c r="E5" s="36"/>
+      <c r="A5" s="31"/>
+      <c r="B5" s="31"/>
+      <c r="C5" s="30"/>
+      <c r="D5" s="30"/>
+      <c r="E5" s="30"/>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="37"/>
-      <c r="B6" s="37"/>
-      <c r="C6" s="36"/>
-      <c r="D6" s="36"/>
-      <c r="E6" s="36"/>
+      <c r="A6" s="31"/>
+      <c r="B6" s="31"/>
+      <c r="C6" s="30"/>
+      <c r="D6" s="30"/>
+      <c r="E6" s="30"/>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7" s="37"/>
-      <c r="B7" s="37"/>
-      <c r="C7" s="36"/>
-      <c r="D7" s="36"/>
-      <c r="E7" s="36"/>
+      <c r="A7" s="31"/>
+      <c r="B7" s="31"/>
+      <c r="C7" s="30"/>
+      <c r="D7" s="30"/>
+      <c r="E7" s="30"/>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" s="37"/>
-      <c r="B8" s="37"/>
-      <c r="C8" s="36"/>
-      <c r="D8" s="36"/>
-      <c r="E8" s="36"/>
+      <c r="A8" s="31"/>
+      <c r="B8" s="31"/>
+      <c r="C8" s="30"/>
+      <c r="D8" s="30"/>
+      <c r="E8" s="30"/>
     </row>
     <row r="9" spans="1:5">
-      <c r="A9" s="37"/>
-      <c r="B9" s="37"/>
-      <c r="C9" s="36"/>
-      <c r="D9" s="36"/>
-      <c r="E9" s="36"/>
+      <c r="A9" s="31"/>
+      <c r="B9" s="31"/>
+      <c r="C9" s="30"/>
+      <c r="D9" s="30"/>
+      <c r="E9" s="30"/>
     </row>
     <row r="10" spans="1:5">
-      <c r="A10" s="37"/>
-      <c r="B10" s="37"/>
-      <c r="C10" s="36"/>
-      <c r="D10" s="36"/>
-      <c r="E10" s="36"/>
+      <c r="A10" s="31"/>
+      <c r="B10" s="31"/>
+      <c r="C10" s="30"/>
+      <c r="D10" s="30"/>
+      <c r="E10" s="30"/>
     </row>
     <row r="11" spans="1:5">
-      <c r="A11" s="37"/>
-      <c r="B11" s="37"/>
-      <c r="C11" s="36"/>
-      <c r="D11" s="36"/>
-      <c r="E11" s="36"/>
+      <c r="A11" s="31"/>
+      <c r="B11" s="31"/>
+      <c r="C11" s="30"/>
+      <c r="D11" s="30"/>
+      <c r="E11" s="30"/>
     </row>
     <row r="12" spans="1:5">
-      <c r="A12" s="37"/>
-      <c r="B12" s="37"/>
-      <c r="C12" s="36"/>
-      <c r="D12" s="36"/>
-      <c r="E12" s="36"/>
+      <c r="A12" s="31"/>
+      <c r="B12" s="31"/>
+      <c r="C12" s="30"/>
+      <c r="D12" s="30"/>
+      <c r="E12" s="30"/>
     </row>
     <row r="13" spans="1:5">
-      <c r="A13" s="37"/>
-      <c r="B13" s="37"/>
-      <c r="C13" s="36"/>
-      <c r="D13" s="36"/>
-      <c r="E13" s="36"/>
+      <c r="A13" s="31"/>
+      <c r="B13" s="31"/>
+      <c r="C13" s="30"/>
+      <c r="D13" s="30"/>
+      <c r="E13" s="30"/>
     </row>
     <row r="14" spans="1:5">
-      <c r="A14" s="37"/>
-      <c r="B14" s="37"/>
-      <c r="C14" s="36"/>
-      <c r="D14" s="36"/>
-      <c r="E14" s="36"/>
+      <c r="A14" s="31"/>
+      <c r="B14" s="31"/>
+      <c r="C14" s="30"/>
+      <c r="D14" s="30"/>
+      <c r="E14" s="30"/>
     </row>
     <row r="15" spans="1:5">
-      <c r="A15" s="37"/>
-      <c r="B15" s="37"/>
-      <c r="C15" s="36"/>
-      <c r="D15" s="36"/>
-      <c r="E15" s="36"/>
+      <c r="A15" s="31"/>
+      <c r="B15" s="31"/>
+      <c r="C15" s="30"/>
+      <c r="D15" s="30"/>
+      <c r="E15" s="30"/>
     </row>
     <row r="16" spans="1:5">
-      <c r="A16" s="37"/>
-      <c r="B16" s="37"/>
-      <c r="C16" s="36"/>
-      <c r="D16" s="36"/>
-      <c r="E16" s="36"/>
+      <c r="A16" s="31"/>
+      <c r="B16" s="31"/>
+      <c r="C16" s="30"/>
+      <c r="D16" s="30"/>
+      <c r="E16" s="30"/>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="37"/>
-      <c r="B17" s="37"/>
-      <c r="C17" s="36"/>
-      <c r="D17" s="36"/>
-      <c r="E17" s="36"/>
+      <c r="A17" s="31"/>
+      <c r="B17" s="31"/>
+      <c r="C17" s="30"/>
+      <c r="D17" s="30"/>
+      <c r="E17" s="30"/>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="37"/>
-      <c r="B18" s="37"/>
-      <c r="C18" s="36"/>
-      <c r="D18" s="36"/>
-      <c r="E18" s="36"/>
+      <c r="A18" s="31"/>
+      <c r="B18" s="31"/>
+      <c r="C18" s="30"/>
+      <c r="D18" s="30"/>
+      <c r="E18" s="30"/>
     </row>
     <row r="19" spans="1:5">
-      <c r="A19" s="37"/>
-      <c r="B19" s="37"/>
-      <c r="C19" s="36"/>
-      <c r="D19" s="36"/>
-      <c r="E19" s="36"/>
+      <c r="A19" s="31"/>
+      <c r="B19" s="31"/>
+      <c r="C19" s="30"/>
+      <c r="D19" s="30"/>
+      <c r="E19" s="30"/>
     </row>
     <row r="20" spans="1:5">
-      <c r="A20" s="37"/>
-      <c r="B20" s="37"/>
-      <c r="C20" s="36"/>
-      <c r="D20" s="36"/>
-      <c r="E20" s="36"/>
+      <c r="A20" s="31"/>
+      <c r="B20" s="31"/>
+      <c r="C20" s="30"/>
+      <c r="D20" s="30"/>
+      <c r="E20" s="30"/>
     </row>
     <row r="21" spans="1:5">
-      <c r="A21" s="37"/>
-      <c r="B21" s="37"/>
-      <c r="C21" s="36"/>
-      <c r="D21" s="36"/>
-      <c r="E21" s="36"/>
+      <c r="A21" s="31"/>
+      <c r="B21" s="31"/>
+      <c r="C21" s="30"/>
+      <c r="D21" s="30"/>
+      <c r="E21" s="30"/>
     </row>
     <row r="22" spans="1:5">
-      <c r="A22" s="37"/>
-      <c r="B22" s="37"/>
-      <c r="C22" s="36"/>
-      <c r="D22" s="36"/>
-      <c r="E22" s="36"/>
+      <c r="A22" s="31"/>
+      <c r="B22" s="31"/>
+      <c r="C22" s="30"/>
+      <c r="D22" s="30"/>
+      <c r="E22" s="30"/>
     </row>
     <row r="23" spans="1:5">
-      <c r="A23" s="37"/>
-      <c r="B23" s="37"/>
-      <c r="C23" s="36"/>
-      <c r="D23" s="36"/>
-      <c r="E23" s="36"/>
+      <c r="A23" s="31"/>
+      <c r="B23" s="31"/>
+      <c r="C23" s="30"/>
+      <c r="D23" s="30"/>
+      <c r="E23" s="30"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -4719,163 +4772,163 @@
   <sheetData>
     <row r="1" spans="1:4" ht="27">
       <c r="A1" s="23" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="27">
       <c r="A2" s="23" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="28" t="s">
+        <v>290</v>
+      </c>
+      <c r="B4" s="28" t="s">
+        <v>291</v>
+      </c>
+      <c r="C4" s="28"/>
+      <c r="D4" s="28"/>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="33" t="s">
+        <v>274</v>
+      </c>
+      <c r="B5" s="29" t="s">
+        <v>289</v>
+      </c>
+      <c r="C5" s="29"/>
+      <c r="D5" s="29"/>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="33" t="s">
+        <v>275</v>
+      </c>
+      <c r="B6" s="29" t="s">
         <v>272</v>
       </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="34" t="s">
-        <v>291</v>
-      </c>
-      <c r="B4" s="34" t="s">
+      <c r="C6" s="29"/>
+      <c r="D6" s="29"/>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="33" t="s">
+        <v>276</v>
+      </c>
+      <c r="B7" s="29" t="s">
         <v>292</v>
       </c>
-      <c r="C4" s="34"/>
-      <c r="D4" s="34"/>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="39" t="s">
-        <v>275</v>
-      </c>
-      <c r="B5" s="35" t="s">
-        <v>290</v>
-      </c>
-      <c r="C5" s="35"/>
-      <c r="D5" s="35"/>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" s="39" t="s">
-        <v>276</v>
-      </c>
-      <c r="B6" s="35" t="s">
-        <v>273</v>
-      </c>
-      <c r="C6" s="35"/>
-      <c r="D6" s="35"/>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" s="39" t="s">
+      <c r="C7" s="29"/>
+      <c r="D7" s="29"/>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="33" t="s">
         <v>277</v>
       </c>
-      <c r="B7" s="35" t="s">
+      <c r="B8" s="29" t="s">
         <v>293</v>
       </c>
-      <c r="C7" s="35"/>
-      <c r="D7" s="35"/>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" s="39" t="s">
+      <c r="C8" s="29"/>
+      <c r="D8" s="29"/>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="33" t="s">
         <v>278</v>
       </c>
-      <c r="B8" s="35" t="s">
+      <c r="B9" s="29" t="s">
         <v>294</v>
       </c>
-      <c r="C8" s="35"/>
-      <c r="D8" s="35"/>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" s="39" t="s">
+      <c r="C9" s="29"/>
+      <c r="D9" s="29"/>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="33" t="s">
         <v>279</v>
       </c>
-      <c r="B9" s="35" t="s">
+      <c r="B10" s="29" t="s">
+        <v>294</v>
+      </c>
+      <c r="C10" s="29"/>
+      <c r="D10" s="29"/>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="33" t="s">
+        <v>280</v>
+      </c>
+      <c r="B11" s="29" t="s">
+        <v>294</v>
+      </c>
+      <c r="C11" s="29"/>
+      <c r="D11" s="29"/>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="33" t="s">
+        <v>281</v>
+      </c>
+      <c r="B12" s="29" t="s">
         <v>295</v>
       </c>
-      <c r="C9" s="35"/>
-      <c r="D9" s="35"/>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" s="39" t="s">
-        <v>280</v>
-      </c>
-      <c r="B10" s="35" t="s">
-        <v>295</v>
-      </c>
-      <c r="C10" s="35"/>
-      <c r="D10" s="35"/>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11" s="39" t="s">
-        <v>281</v>
-      </c>
-      <c r="B11" s="35" t="s">
-        <v>295</v>
-      </c>
-      <c r="C11" s="35"/>
-      <c r="D11" s="35"/>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12" s="39" t="s">
+      <c r="C12" s="29"/>
+      <c r="D12" s="29"/>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="33" t="s">
+        <v>286</v>
+      </c>
+      <c r="B13" s="29" t="s">
+        <v>296</v>
+      </c>
+      <c r="C13" s="29"/>
+      <c r="D13" s="29"/>
+    </row>
+    <row r="14" spans="1:4" ht="27">
+      <c r="A14" s="33" t="s">
+        <v>287</v>
+      </c>
+      <c r="B14" s="29" t="s">
+        <v>297</v>
+      </c>
+      <c r="C14" s="29"/>
+      <c r="D14" s="29"/>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="34" t="s">
+        <v>288</v>
+      </c>
+      <c r="B15" s="35" t="s">
+        <v>283</v>
+      </c>
+      <c r="C15" s="35"/>
+      <c r="D15" s="35"/>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="36" t="s">
         <v>282</v>
       </c>
-      <c r="B12" s="35" t="s">
-        <v>296</v>
-      </c>
-      <c r="C12" s="35"/>
-      <c r="D12" s="35"/>
-    </row>
-    <row r="13" spans="1:4">
-      <c r="A13" s="39" t="s">
-        <v>287</v>
-      </c>
-      <c r="B13" s="35" t="s">
-        <v>297</v>
-      </c>
-      <c r="C13" s="35"/>
-      <c r="D13" s="35"/>
-    </row>
-    <row r="14" spans="1:4" ht="27">
-      <c r="A14" s="39" t="s">
-        <v>288</v>
-      </c>
-      <c r="B14" s="35" t="s">
-        <v>298</v>
-      </c>
-      <c r="C14" s="35"/>
-      <c r="D14" s="35"/>
-    </row>
-    <row r="15" spans="1:4">
-      <c r="A15" s="40" t="s">
-        <v>289</v>
-      </c>
-      <c r="B15" s="41" t="s">
+      <c r="B16" s="35" t="s">
+        <v>283</v>
+      </c>
+      <c r="C16" s="35"/>
+      <c r="D16" s="35"/>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" s="36" t="s">
         <v>284</v>
       </c>
-      <c r="C15" s="41"/>
-      <c r="D15" s="41"/>
-    </row>
-    <row r="16" spans="1:4">
-      <c r="A16" s="42" t="s">
+      <c r="B17" s="35" t="s">
         <v>283</v>
       </c>
-      <c r="B16" s="41" t="s">
-        <v>284</v>
-      </c>
-      <c r="C16" s="41"/>
-      <c r="D16" s="41"/>
-    </row>
-    <row r="17" spans="1:4">
-      <c r="A17" s="42" t="s">
+      <c r="C17" s="35"/>
+      <c r="D17" s="35"/>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" s="36" t="s">
         <v>285</v>
       </c>
-      <c r="B17" s="41" t="s">
-        <v>284</v>
-      </c>
-      <c r="C17" s="41"/>
-      <c r="D17" s="41"/>
-    </row>
-    <row r="18" spans="1:4">
-      <c r="A18" s="42" t="s">
-        <v>286</v>
-      </c>
-      <c r="B18" s="41" t="s">
-        <v>284</v>
-      </c>
-      <c r="C18" s="41"/>
-      <c r="D18" s="41"/>
+      <c r="B18" s="35" t="s">
+        <v>283</v>
+      </c>
+      <c r="C18" s="35"/>
+      <c r="D18" s="35"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/internal_doc/03.开发设计/OM_web接口.xlsx
+++ b/internal_doc/03.开发设计/OM_web接口.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="6510" activeTab="5"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="6510" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="需求" sheetId="1" r:id="rId1"/>
@@ -281,7 +281,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="299">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="313">
   <si>
     <t>需求</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -811,10 +811,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>rc=ok, 已经存在</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>INT32 catMainController::_ensureMetadata()</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -874,18 +870,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>remove_business_res</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>NA</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>{rc, ???}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>返回跳转页面命令</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -894,10 +882,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>rest参数(响应最外层统一加上rc)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>网页跳转响应(GETFILE)(废除)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -923,10 +907,6 @@
   </si>
   <si>
     <t>通过接口获取（pAdptor-&gt;recvRequestBody( this, httpCommon, &amp;pFilePath, bodySize )）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{rc,detail}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -972,11 +952,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>成功时：{rc}
-校验失败时：{rc,local} local为跳转文件login.html</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>获取cluster信息</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1005,19 +980,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>{ClusterName, rc}</t>
-  </si>
-  <si>
-    <t>{ClusterName, rc}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>business_name=xxx&amp;ClusterName=xxx</t>
-  </si>
-  <si>
-    <t>{business_name, ClusterName, rc}</t>
-  </si>
-  <si>
     <t>replname</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1063,10 +1025,6 @@
   </si>
   <si>
     <t>host_info={ClusterName:cls1, host_info:[{IP, HostName, User, Passwd, SshPort:xxx, AgentPort:xxx},...], User:usr1, Passwd:Passwd1, SshPort:xxx, AgentPort:xxx}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{[{IP, HostName, rc, Firework, [Disk],[CPU]…}, ...]}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1075,14 +1033,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>[{IP, HostName, Ping:true, Ssh:false, HostName:"rhelt10", rc}, ...]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>rc=ok</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>"Config": [ { "HostName": "host1", "username": "sdbadmin", "userpasswd": "sdbadmin", "usergroup": "sdbadmin_group", "datagroupname": "", "dbpath": "/home/db2//standalone/11830", "svcname": "11830", ...} ],"BusinessName": "b1", "BusinessType": "sequoiadb", "ClusterType": "standalone","ClusterName": "c1","Property": [ { "Name": "username", "Type": "string", "Default": "sdbadmin", "Valid": "", "Display": "edit box", "Edit": "true", "Desc": "", "Level": "0", "WebName": "user_name",... }]</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1091,14 +1041,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>ClusterName=cls1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{ "rc": 0 }{ "BusinessList": [ { "BusinessType": "sequoiadb", "BusinessDesc": "haha" }, { "BusinessType": "sequoiasql", "BusinessDesc": "haha" } ] }</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>{BusinessType, BusinessName,ClusterType, ClusterName, "Config":[{"HostName":"host1","datagroupname":"", "dbpath":"/home/db2//standalone/11830", "svcname":"11830", ...}, ...] }]}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1171,10 +1113,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>http://192.168.20.197:11814/?cmd=query host&amp;ClusterName=c1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>http://192.168.20.197:11814/?cmd=query business list</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1191,10 +1129,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>{rc,local}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>query progress</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1211,19 +1145,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>{ "rc": 0 }{ "ClusterName": "c1", "Desc": "" }</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>查询进度</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>查询进度响应</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{ClusterName, rc, [IP, HostName, Firework, [Disk],[CPU]...]}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1297,20 +1223,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>{"rc":0, "Detail":"","TaskID":"asd", "isFinish":true,"Status":"install/rollback","Progress":[{"Name":"Coord","TotalCount":7 "InstalledCount":100, "Desc":""}, {"Name":"Group1","TotalCount":3,"InstalledCount":50,"Desc":""},
-{"Name":"Group2","TotalCount":4,"InstalledCount":50,"Desc":""} ...]}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>http://192.168.20.197:11814/?cmd=scan host&amp;HostInfo={"ClusterName":"c1","HostInfo":[{"IP":"192.168.20.196","User":"root","Passwd":"sequoiad",SshPort:"22",AgentPort:"11790"}],"User":"root","Passwd":"sequoiadb",SshPort:"22",AgentPort:"11810"}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>http://192.168.20.197:11814/?cmd=query business template&amp;BusinessType=sequoiadb</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{ "rc": 0 }{ "DeployMod": "standalone", "WebName": "standalone", "BusinessType": "sequoiadb", "Property": [ { "Name": "replicanum", "Type": "int", "Default": "1", "Valid": "1", "Display": "edit box", "Edit": "false", "Desc": "", "Level": "0", "WebName": "replica_num" }, { "Name": "datagroupnum", "Type": "int", "Default": "1", "Valid": "1", "Display": "edit box", "Edit": "false", "Desc": "", "Level": "0", "WebName": "data_group_num" }, { "Name": "catalognum", "Type": "int", "Default": "1", "Valid": "1", "Display": "edit box", "Edit": "false", "Desc": "1", "Level": "0", "WebName": "catalog_num" }, { "Name": "coordnum", "Type": "int", "Default": "1", "Valid": "1", "Display": "edit box", "Edit": "false", "Desc": "", "Level": "0", "WebName": "coord_num" }, { "Name": "transactionon", "Type": "string", "Default": "false", "Valid": "true,false", "Display": "edit box", "Edit": "false", "Desc": "", "Level": "0", "WebName": "transactionon" } ] }{ "DeployMod": "distribution", "WebName": "distribution", "BusinessType": "sequoiadb", "Property": [ { "Name": "replicanum", "Type": "int", "Default": "3", "Valid": "1-7", "Display": "edit box", "Edit": "true", "Desc": "", "Level": "0", "WebName": "replica_num" }, { "Name": "datagroupnum", "Type": "int", "Default": "1", "Valid": "", "Display": "edit box", "Edit": "false", "Desc": "", "Level": "0", "WebName": "data_group_num" }, { "Name": "catalognum", "Type": "int", "Default": "1", "Valid": "", "Display": "edit box", "Edit": "false", "Desc": "1", "Level": "0", "WebName": "catalog_num" }, { "Name": "coordnum", "Type": "int", "Default": "0", "Valid": "0-7", "Display": "edit box", "Edit": "false", "Desc": "0 means one coord each host", "Level": "0", "WebName": "coord_num" }, { "Name": "transactionon", "Type": "string", "Default": "false", "Valid": "true,false", "Display": "edit box", "Edit": "false", "Desc": "", "Level": "0", "WebName": "transactionon" } ] }</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1543,6 +1460,135 @@
   </si>
   <si>
     <t>{"HostName":"", "IP":"", "User":"", "Passwd":"", "InstallPath":""}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>HostName=host1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://192.168.20.197:11814/?cmd=query host&amp;HostName=host1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>获取host列表</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>list host</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>获取host列表响应</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{ "Rc": 0 }{ "HostName": "rhelt10" }</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> http://192.168.20.197:11814/?cmd=list host&amp;ClusterName=c1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ClusterName=c1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ClusterName=c1(or BusinessName=b1)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{ "Rc": 0 }{ "_id": { "$oid": "54096ec6f1ee34d0b015a6ce" }, "HostName": "rhelt10", "ClusterName": "c1", "IP": "192.168.20.197", "User": "root", "Password": "sequoiadb", "OS": { "Distributor": "Ubuntu", "Release": "12.04", "Bit": 64 }, "OM": { "Status": 0, "Version": "" }, "Memory": { "Model": "", "Size": 2003, "Free": 916, "Unit": "M" }, "Disk": [ { "Name": "/dev/mapper/vgdata-lvdata1", "Mount": "/home/mount/", "Size": 32529, "Free": 6525, "Unit": "M", "Used": 1 } ], "CPU": [ { "ID": "", "Model": "", "Core": 1, "Freq": "2.00GHz" } ], "Net": [ { "Name": "lo", "Model": "", "Bandwidth": "", "IP": "127.0.0.1" }, { "Name": "eth0", "Model": "", "Bandwidth": "", "IP": "192.168.20.197" } ], "Service": [ { "Name": "", "Status": 0, "Version": "" } ], "Safety": { "Name": "", "Context": "", "Status": 0 }, "InstallPath": "/opt/sequoiadb/", "AgentPort": "11790" }</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>查询business列表</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>查询business列表响应</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>list business</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>192.168.20.197:11814/?cmd=list business&amp;ClusterName=c1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{ "Rc": 0 }{ "BusinessName": "b1" },{}...</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BusinessName=xxx</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{Rc}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://192.168.20.197:11814/?cmd=remove business&amp;BusinessName=b1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>删除集群响应</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Rc=ok, 已经存在</t>
+  </si>
+  <si>
+    <t>{ "Rc": 0 }{ "ClusterName": "c1", "Desc": "" }</t>
+  </si>
+  <si>
+    <t>[{IP, HostName, Ping:true, Ssh:false, HostName:"rhelt10", Rc}, ...]</t>
+  </si>
+  <si>
+    <t>Rc=ok</t>
+  </si>
+  <si>
+    <t>{[{IP, HostName, Rc, Firework, [Disk],[CPU]…}, ...]}</t>
+  </si>
+  <si>
+    <t>{ "Rc": 0 }{ "BusinessList": [ { "BusinessType": "sequoiadb", "BusinessDesc": "haha" }, { "BusinessType": "sequoiasql", "BusinessDesc": "haha" } ] }</t>
+  </si>
+  <si>
+    <t>{ "Rc": 0 }{ "DeployMod": "standalone", "WebName": "standalone", "BusinessType": "sequoiadb", "Property": [ { "Name": "replicanum", "Type": "int", "Default": "1", "Valid": "1", "Display": "edit box", "Edit": "false", "Desc": "", "Level": "0", "WebName": "replica_num" }, { "Name": "datagroupnum", "Type": "int", "Default": "1", "Valid": "1", "Display": "edit box", "Edit": "false", "Desc": "", "Level": "0", "WebName": "data_group_num" }, { "Name": "catalognum", "Type": "int", "Default": "1", "Valid": "1", "Display": "edit box", "Edit": "false", "Desc": "1", "Level": "0", "WebName": "catalog_num" }, { "Name": "coordnum", "Type": "int", "Default": "1", "Valid": "1", "Display": "edit box", "Edit": "false", "Desc": "", "Level": "0", "WebName": "coord_num" }, { "Name": "transactionon", "Type": "string", "Default": "false", "Valid": "true,false", "Display": "edit box", "Edit": "false", "Desc": "", "Level": "0", "WebName": "transactionon" } ] }{ "DeployMod": "distribution", "WebName": "distribution", "BusinessType": "sequoiadb", "Property": [ { "Name": "replicanum", "Type": "int", "Default": "3", "Valid": "1-7", "Display": "edit box", "Edit": "true", "Desc": "", "Level": "0", "WebName": "replica_num" }, { "Name": "datagroupnum", "Type": "int", "Default": "1", "Valid": "", "Display": "edit box", "Edit": "false", "Desc": "", "Level": "0", "WebName": "data_group_num" }, { "Name": "catalognum", "Type": "int", "Default": "1", "Valid": "", "Display": "edit box", "Edit": "false", "Desc": "1", "Level": "0", "WebName": "catalog_num" }, { "Name": "coordnum", "Type": "int", "Default": "0", "Valid": "0-7", "Display": "edit box", "Edit": "false", "Desc": "0 means one coord each host", "Level": "0", "WebName": "coord_num" }, { "Name": "transactionon", "Type": "string", "Default": "false", "Valid": "true,false", "Display": "edit box", "Edit": "false", "Desc": "", "Level": "0", "WebName": "transactionon" } ] }</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{Rc, ???}</t>
+  </si>
+  <si>
+    <t>{"Rc":0, "Detail":"","TaskID":"asd", "isFinish":true,"Status":"install/rollback","Progress":[{"Name":"Coord","TotalCount":7 "InstalledCount":100, "Desc":""}, {"Name":"Group1","TotalCount":3,"InstalledCount":50,"Desc":""},
+{"Name":"Group2","TotalCount":4,"InstalledCount":50,"Desc":""} ...]}</t>
+  </si>
+  <si>
+    <t>成功时：{Rc}
+校验失败时：{Rc,local} local为跳转文件login.html</t>
+  </si>
+  <si>
+    <t>{Rc,local}</t>
+  </si>
+  <si>
+    <t>{Rc,detail}</t>
+  </si>
+  <si>
+    <t>{ClusterName, Rc}</t>
+  </si>
+  <si>
+    <t>rest参数(响应最外层统一加上Rc)</t>
+  </si>
+  <si>
+    <t>删除host</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>remove host</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1791,7 +1837,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1847,10 +1893,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1877,6 +1919,10 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1895,14 +1941,21 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3106,7 +3159,7 @@
     <row r="14" spans="1:12">
       <c r="A14" s="14"/>
       <c r="B14" s="14" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="C14" s="14">
         <v>11811</v>
@@ -3128,7 +3181,7 @@
     <row r="15" spans="1:12">
       <c r="A15" s="14"/>
       <c r="B15" s="14" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="C15" s="14">
         <v>11812</v>
@@ -3150,7 +3203,7 @@
     <row r="16" spans="1:12">
       <c r="A16" s="14"/>
       <c r="B16" s="14" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
       <c r="C16" s="14">
         <v>11813</v>
@@ -3172,7 +3225,7 @@
     <row r="17" spans="1:12">
       <c r="A17" s="14"/>
       <c r="B17" s="14" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="C17" s="14">
         <v>11814</v>
@@ -3194,7 +3247,7 @@
     <row r="18" spans="1:12">
       <c r="A18" s="14"/>
       <c r="B18" s="14" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="C18" s="14">
         <v>3</v>
@@ -3218,7 +3271,7 @@
     <row r="19" spans="1:12">
       <c r="A19" s="14"/>
       <c r="B19" s="14" t="s">
-        <v>187</v>
+        <v>177</v>
       </c>
       <c r="C19" s="14" t="s">
         <v>95</v>
@@ -3242,7 +3295,7 @@
     <row r="20" spans="1:12">
       <c r="A20" s="14"/>
       <c r="B20" s="14" t="s">
-        <v>188</v>
+        <v>178</v>
       </c>
       <c r="C20" s="14">
         <v>64</v>
@@ -3255,7 +3308,7 @@
         <v>102</v>
       </c>
       <c r="G20" s="14" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="H20" s="14"/>
       <c r="I20" s="14"/>
@@ -3266,7 +3319,7 @@
     <row r="21" spans="1:12">
       <c r="A21" s="14"/>
       <c r="B21" s="14" t="s">
-        <v>189</v>
+        <v>179</v>
       </c>
       <c r="C21" s="14">
         <v>20</v>
@@ -3279,7 +3332,7 @@
         <v>102</v>
       </c>
       <c r="G21" s="14" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="H21" s="14"/>
       <c r="I21" s="14"/>
@@ -3290,7 +3343,7 @@
     <row r="22" spans="1:12">
       <c r="A22" s="14"/>
       <c r="B22" s="14" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="C22" s="17" t="s">
         <v>109</v>
@@ -3338,7 +3391,7 @@
     <row r="24" spans="1:12">
       <c r="A24" s="14"/>
       <c r="B24" s="16" t="s">
-        <v>191</v>
+        <v>181</v>
       </c>
       <c r="C24" s="11">
         <v>1</v>
@@ -3360,7 +3413,7 @@
     <row r="25" spans="1:12" s="19" customFormat="1">
       <c r="A25" s="16"/>
       <c r="B25" s="16" t="s">
-        <v>192</v>
+        <v>182</v>
       </c>
       <c r="C25" s="11">
         <v>10000</v>
@@ -3667,10 +3720,10 @@
   <dimension ref="A1:F74"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
-    <col min="1" max="1" width="26" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.75" style="3" customWidth="1"/>
-    <col min="3" max="3" width="45.125" style="10" customWidth="1"/>
-    <col min="4" max="4" width="52.25" style="10" customWidth="1"/>
+    <col min="1" max="1" width="22.375" style="10" customWidth="1"/>
+    <col min="2" max="2" width="22.625" style="3" customWidth="1"/>
+    <col min="3" max="3" width="54.125" style="10" customWidth="1"/>
+    <col min="4" max="4" width="57.375" style="10" customWidth="1"/>
     <col min="5" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
@@ -3689,10 +3742,10 @@
         <v>119</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>151</v>
+        <v>310</v>
       </c>
       <c r="D2" s="5" t="s">
         <v>1</v>
@@ -3702,16 +3755,16 @@
     </row>
     <row r="3" spans="1:6" ht="48">
       <c r="A3" s="9" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>227</v>
+        <v>210</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>223</v>
+        <v>207</v>
       </c>
       <c r="E3" s="4"/>
       <c r="F3" s="4"/>
@@ -3722,10 +3775,10 @@
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="9" t="s">
-        <v>179</v>
+        <v>309</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>130</v>
+        <v>297</v>
       </c>
       <c r="E4" s="4"/>
       <c r="F4" s="4"/>
@@ -3740,30 +3793,30 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="9" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>205</v>
+        <v>190</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>228</v>
+        <v>211</v>
       </c>
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="9" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="B7" s="4"/>
       <c r="C7" s="9" t="s">
-        <v>229</v>
+        <v>212</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>230</v>
+        <v>298</v>
       </c>
       <c r="E7" s="4"/>
       <c r="F7" s="4"/>
@@ -3776,72 +3829,68 @@
       <c r="E8" s="4"/>
       <c r="F8" s="4"/>
     </row>
-    <row r="9" spans="1:6" ht="60">
-      <c r="A9" s="9" t="s">
-        <v>122</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>207</v>
-      </c>
-      <c r="C9" s="9" t="s">
+    <row r="9" spans="1:6" s="45" customFormat="1">
+      <c r="A9" s="43" t="s">
+        <v>236</v>
+      </c>
+      <c r="B9" s="44" t="s">
         <v>239</v>
       </c>
-      <c r="D9" s="9" t="s">
-        <v>241</v>
-      </c>
-      <c r="E9" s="4"/>
-      <c r="F9" s="4"/>
-    </row>
-    <row r="10" spans="1:6" ht="24">
-      <c r="A10" s="9" t="s">
-        <v>123</v>
-      </c>
-      <c r="B10" s="4"/>
-      <c r="C10" s="9" t="s">
-        <v>196</v>
-      </c>
-      <c r="D10" s="9" t="s">
-        <v>197</v>
-      </c>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="9"/>
-      <c r="B11" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="C11" s="9"/>
-      <c r="D11" s="9"/>
-      <c r="E11" s="4"/>
-      <c r="F11" s="4"/>
+      <c r="C9" s="43" t="s">
+        <v>234</v>
+      </c>
+      <c r="D9" s="43" t="s">
+        <v>240</v>
+      </c>
+      <c r="E9" s="44"/>
+      <c r="F9" s="44"/>
+    </row>
+    <row r="10" spans="1:6" s="45" customFormat="1">
+      <c r="A10" s="43" t="s">
+        <v>296</v>
+      </c>
+      <c r="B10" s="44"/>
+      <c r="C10" s="43" t="s">
+        <v>294</v>
+      </c>
+      <c r="D10" s="43"/>
+      <c r="E10" s="44"/>
+      <c r="F10" s="44"/>
+    </row>
+    <row r="11" spans="1:6" s="49" customFormat="1">
+      <c r="A11" s="47"/>
+      <c r="B11" s="48"/>
+      <c r="C11" s="47"/>
+      <c r="D11" s="47"/>
+      <c r="E11" s="48"/>
+      <c r="F11" s="48"/>
     </row>
     <row r="12" spans="1:6" ht="60">
       <c r="A12" s="9" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>208</v>
+        <v>192</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>193</v>
+        <v>220</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>263</v>
+        <v>221</v>
       </c>
       <c r="E12" s="4"/>
       <c r="F12" s="4"/>
     </row>
-    <row r="13" spans="1:6" ht="102.75" customHeight="1">
+    <row r="13" spans="1:6" ht="24">
       <c r="A13" s="9" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B13" s="4"/>
       <c r="C13" s="9" t="s">
-        <v>194</v>
+        <v>299</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>262</v>
+        <v>300</v>
       </c>
       <c r="E13" s="4"/>
       <c r="F13" s="4"/>
@@ -3849,74 +3898,76 @@
     <row r="14" spans="1:6">
       <c r="A14" s="9"/>
       <c r="B14" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C14" s="9"/>
       <c r="D14" s="9"/>
       <c r="E14" s="4"/>
       <c r="F14" s="4"/>
     </row>
-    <row r="15" spans="1:6" ht="120" customHeight="1">
+    <row r="15" spans="1:6" ht="60">
       <c r="A15" s="9" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>209</v>
+        <v>193</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>253</v>
+        <v>183</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>264</v>
+        <v>242</v>
       </c>
       <c r="E15" s="4"/>
       <c r="F15" s="4"/>
     </row>
-    <row r="16" spans="1:6">
+    <row r="16" spans="1:6" ht="228">
       <c r="A16" s="9" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B16" s="4"/>
       <c r="C16" s="9" t="s">
-        <v>178</v>
-      </c>
-      <c r="D16" s="9"/>
+        <v>301</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>241</v>
+      </c>
       <c r="E16" s="4"/>
       <c r="F16" s="4"/>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="9"/>
       <c r="B17" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C17" s="9"/>
       <c r="D17" s="9"/>
       <c r="E17" s="4"/>
       <c r="F17" s="4"/>
     </row>
-    <row r="18" spans="1:6" ht="27">
+    <row r="18" spans="1:6" ht="204">
       <c r="A18" s="9" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>210</v>
+        <v>194</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>200</v>
-      </c>
-      <c r="D18" s="23" t="s">
-        <v>220</v>
+        <v>232</v>
+      </c>
+      <c r="D18" s="9" t="s">
+        <v>243</v>
       </c>
       <c r="E18" s="4"/>
       <c r="F18" s="4"/>
     </row>
-    <row r="19" spans="1:6" ht="24">
+    <row r="19" spans="1:6">
       <c r="A19" s="9" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B19" s="4"/>
       <c r="C19" s="9" t="s">
-        <v>233</v>
+        <v>309</v>
       </c>
       <c r="D19" s="9"/>
       <c r="E19" s="4"/>
@@ -3925,7 +3976,7 @@
     <row r="20" spans="1:6">
       <c r="A20" s="9"/>
       <c r="B20" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C20" s="9"/>
       <c r="D20" s="9"/>
@@ -3934,155 +3985,139 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="9" t="s">
-        <v>135</v>
+        <v>280</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>245</v>
-      </c>
-      <c r="C21" s="9"/>
+        <v>281</v>
+      </c>
+      <c r="C21" s="9" t="s">
+        <v>286</v>
+      </c>
       <c r="D21" s="9" t="s">
-        <v>221</v>
+        <v>284</v>
       </c>
       <c r="E21" s="4"/>
       <c r="F21" s="4"/>
     </row>
-    <row r="22" spans="1:6" ht="36">
+    <row r="22" spans="1:6">
       <c r="A22" s="9" t="s">
-        <v>136</v>
+        <v>282</v>
       </c>
       <c r="B22" s="4"/>
       <c r="C22" s="9" t="s">
-        <v>222</v>
-      </c>
-      <c r="D22" s="9" t="s">
-        <v>201</v>
-      </c>
+        <v>283</v>
+      </c>
+      <c r="D22" s="9"/>
       <c r="E22" s="4"/>
       <c r="F22" s="4"/>
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="9"/>
-      <c r="B23" s="4" t="s">
-        <v>133</v>
-      </c>
+      <c r="B23" s="4"/>
       <c r="C23" s="9"/>
       <c r="D23" s="9"/>
       <c r="E23" s="4"/>
       <c r="F23" s="4"/>
     </row>
-    <row r="24" spans="1:6" ht="24">
+    <row r="24" spans="1:6">
       <c r="A24" s="9" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>234</v>
+        <v>195</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>235</v>
+        <v>278</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>242</v>
+        <v>279</v>
       </c>
       <c r="E24" s="4"/>
       <c r="F24" s="4"/>
     </row>
-    <row r="25" spans="1:6" ht="240">
+    <row r="25" spans="1:6" ht="180">
       <c r="A25" s="9" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="B25" s="4"/>
       <c r="C25" s="9" t="s">
-        <v>195</v>
-      </c>
-      <c r="D25" s="9" t="s">
-        <v>243</v>
-      </c>
+        <v>287</v>
+      </c>
+      <c r="D25" s="9"/>
       <c r="E25" s="4"/>
       <c r="F25" s="4"/>
     </row>
     <row r="26" spans="1:6">
       <c r="A26" s="9"/>
-      <c r="B26" s="4" t="s">
-        <v>133</v>
-      </c>
+      <c r="B26" s="4"/>
       <c r="C26" s="9"/>
       <c r="D26" s="9"/>
       <c r="E26" s="4"/>
       <c r="F26" s="4"/>
     </row>
-    <row r="27" spans="1:6" ht="84">
+    <row r="27" spans="1:6">
       <c r="A27" s="9" t="s">
-        <v>139</v>
+        <v>311</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>211</v>
-      </c>
-      <c r="C27" s="9" t="s">
-        <v>236</v>
-      </c>
-      <c r="D27" s="9" t="s">
-        <v>244</v>
-      </c>
+        <v>312</v>
+      </c>
+      <c r="C27" s="9"/>
+      <c r="D27" s="9"/>
       <c r="E27" s="4"/>
       <c r="F27" s="4"/>
     </row>
-    <row r="28" spans="1:6" ht="120">
-      <c r="A28" s="9" t="s">
-        <v>140</v>
-      </c>
+    <row r="28" spans="1:6">
+      <c r="A28" s="9"/>
       <c r="B28" s="4"/>
-      <c r="C28" s="9" t="s">
-        <v>199</v>
-      </c>
-      <c r="D28" s="9" t="s">
-        <v>198</v>
-      </c>
+      <c r="C28" s="9"/>
+      <c r="D28" s="9"/>
       <c r="E28" s="4"/>
       <c r="F28" s="4"/>
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="9"/>
       <c r="B29" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C29" s="9"/>
       <c r="D29" s="9"/>
       <c r="E29" s="4"/>
       <c r="F29" s="4"/>
     </row>
-    <row r="30" spans="1:6" ht="144">
+    <row r="30" spans="1:6">
       <c r="A30" s="9" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>212</v>
-      </c>
-      <c r="C30" s="9" t="s">
-        <v>202</v>
-      </c>
+        <v>224</v>
+      </c>
+      <c r="C30" s="9"/>
       <c r="D30" s="9" t="s">
-        <v>270</v>
+        <v>205</v>
       </c>
       <c r="E30" s="4"/>
       <c r="F30" s="4"/>
     </row>
-    <row r="31" spans="1:6">
+    <row r="31" spans="1:6" ht="36">
       <c r="A31" s="9" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="B31" s="4"/>
       <c r="C31" s="9" t="s">
-        <v>148</v>
+        <v>206</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>120</v>
+        <v>302</v>
       </c>
       <c r="E31" s="4"/>
       <c r="F31" s="4"/>
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="9"/>
-      <c r="B32" s="4"/>
+      <c r="B32" s="4" t="s">
+        <v>132</v>
+      </c>
       <c r="C32" s="9"/>
       <c r="D32" s="9"/>
       <c r="E32" s="4"/>
@@ -4090,95 +4125,111 @@
     </row>
     <row r="33" spans="1:6" ht="24">
       <c r="A33" s="9" t="s">
-        <v>231</v>
+        <v>136</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>226</v>
+        <v>215</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>203</v>
+        <v>216</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>238</v>
+        <v>222</v>
       </c>
       <c r="E33" s="4"/>
       <c r="F33" s="4"/>
     </row>
-    <row r="34" spans="1:6" ht="96">
+    <row r="34" spans="1:6" ht="228">
       <c r="A34" s="9" t="s">
-        <v>232</v>
+        <v>137</v>
       </c>
       <c r="B34" s="4"/>
       <c r="C34" s="9" t="s">
-        <v>240</v>
-      </c>
-      <c r="D34" s="9"/>
+        <v>184</v>
+      </c>
+      <c r="D34" s="9" t="s">
+        <v>303</v>
+      </c>
       <c r="E34" s="4"/>
       <c r="F34" s="4"/>
     </row>
     <row r="35" spans="1:6">
       <c r="A35" s="9"/>
-      <c r="B35" s="4"/>
+      <c r="B35" s="4" t="s">
+        <v>132</v>
+      </c>
       <c r="C35" s="9"/>
       <c r="D35" s="9"/>
       <c r="E35" s="4"/>
       <c r="F35" s="4"/>
     </row>
-    <row r="36" spans="1:6" ht="24">
+    <row r="36" spans="1:6" ht="84">
       <c r="A36" s="9" t="s">
-        <v>258</v>
+        <v>138</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>254</v>
+        <v>196</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>255</v>
+        <v>217</v>
       </c>
       <c r="D36" s="9" t="s">
-        <v>256</v>
+        <v>223</v>
       </c>
       <c r="E36" s="4"/>
       <c r="F36" s="4"/>
     </row>
-    <row r="37" spans="1:6">
+    <row r="37" spans="1:6" ht="108">
       <c r="A37" s="9" t="s">
-        <v>259</v>
+        <v>139</v>
       </c>
       <c r="B37" s="4"/>
-      <c r="C37" s="9"/>
-      <c r="D37" s="9"/>
+      <c r="C37" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="D37" s="9" t="s">
+        <v>185</v>
+      </c>
       <c r="E37" s="4"/>
       <c r="F37" s="4"/>
     </row>
     <row r="38" spans="1:6">
       <c r="A38" s="9"/>
-      <c r="B38" s="4"/>
+      <c r="B38" s="4" t="s">
+        <v>132</v>
+      </c>
       <c r="C38" s="9"/>
       <c r="D38" s="9"/>
       <c r="E38" s="4"/>
       <c r="F38" s="4"/>
     </row>
-    <row r="39" spans="1:6" ht="24">
+    <row r="39" spans="1:6" ht="132">
       <c r="A39" s="9" t="s">
-        <v>257</v>
+        <v>140</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>260</v>
+        <v>197</v>
       </c>
       <c r="C39" s="9" t="s">
-        <v>255</v>
+        <v>187</v>
       </c>
       <c r="D39" s="9" t="s">
-        <v>261</v>
+        <v>249</v>
       </c>
       <c r="E39" s="4"/>
       <c r="F39" s="4"/>
     </row>
     <row r="40" spans="1:6">
-      <c r="A40" s="9"/>
+      <c r="A40" s="9" t="s">
+        <v>141</v>
+      </c>
       <c r="B40" s="4"/>
-      <c r="C40" s="9"/>
-      <c r="D40" s="9"/>
+      <c r="C40" s="9" t="s">
+        <v>304</v>
+      </c>
+      <c r="D40" s="9" t="s">
+        <v>120</v>
+      </c>
       <c r="E40" s="4"/>
       <c r="F40" s="4"/>
     </row>
@@ -4191,85 +4242,138 @@
       <c r="F41" s="4"/>
     </row>
     <row r="42" spans="1:6">
-      <c r="A42" s="9"/>
+      <c r="A42" s="9" t="s">
+        <v>288</v>
+      </c>
       <c r="B42" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="C42" s="9"/>
-      <c r="D42" s="9"/>
+        <v>290</v>
+      </c>
+      <c r="C42" s="9" t="s">
+        <v>285</v>
+      </c>
+      <c r="D42" s="9" t="s">
+        <v>291</v>
+      </c>
       <c r="E42" s="4"/>
       <c r="F42" s="4"/>
     </row>
     <row r="43" spans="1:6">
       <c r="A43" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="B43" s="4" t="s">
-        <v>145</v>
-      </c>
+        <v>289</v>
+      </c>
+      <c r="B43" s="4"/>
       <c r="C43" s="9" t="s">
-        <v>180</v>
+        <v>292</v>
       </c>
       <c r="D43" s="9"/>
       <c r="E43" s="4"/>
       <c r="F43" s="4"/>
     </row>
     <row r="44" spans="1:6">
-      <c r="A44" s="9" t="s">
-        <v>144</v>
-      </c>
-      <c r="B44" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="C44" s="9" t="s">
-        <v>181</v>
-      </c>
+      <c r="A44" s="9"/>
+      <c r="B44" s="4"/>
+      <c r="C44" s="9"/>
       <c r="D44" s="9"/>
       <c r="E44" s="4"/>
       <c r="F44" s="4"/>
     </row>
-    <row r="45" spans="1:6">
-      <c r="A45" s="43"/>
-      <c r="B45" s="44"/>
-      <c r="C45" s="43"/>
-      <c r="D45" s="43"/>
-      <c r="E45" s="44"/>
-      <c r="F45" s="44"/>
-    </row>
-    <row r="46" spans="1:6" s="4" customFormat="1">
-      <c r="A46" s="9"/>
-      <c r="C46" s="9"/>
-      <c r="D46" s="9"/>
-    </row>
-    <row r="47" spans="1:6" s="4" customFormat="1">
-      <c r="A47" s="9"/>
-      <c r="C47" s="9"/>
-      <c r="D47" s="9"/>
-    </row>
-    <row r="48" spans="1:6" s="4" customFormat="1">
-      <c r="A48" s="9"/>
-      <c r="C48" s="9"/>
-      <c r="D48" s="9"/>
-    </row>
-    <row r="49" spans="1:6" s="4" customFormat="1">
-      <c r="A49" s="9"/>
-      <c r="C49" s="9"/>
+    <row r="45" spans="1:6" s="46" customFormat="1">
+      <c r="A45" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C45" s="5" t="s">
+        <v>293</v>
+      </c>
+      <c r="D45" s="5" t="s">
+        <v>295</v>
+      </c>
+      <c r="E45" s="2"/>
+      <c r="F45" s="2"/>
+    </row>
+    <row r="46" spans="1:6" s="46" customFormat="1">
+      <c r="A46" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="B46" s="2"/>
+      <c r="C46" s="5" t="s">
+        <v>294</v>
+      </c>
+      <c r="D46" s="5"/>
+      <c r="E46" s="2"/>
+      <c r="F46" s="2"/>
+    </row>
+    <row r="47" spans="1:6" s="49" customFormat="1">
+      <c r="A47" s="47"/>
+      <c r="B47" s="48"/>
+      <c r="C47" s="47"/>
+      <c r="D47" s="47"/>
+      <c r="E47" s="48"/>
+      <c r="F47" s="48"/>
+    </row>
+    <row r="48" spans="1:6" ht="24">
+      <c r="A48" s="9" t="s">
+        <v>213</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="C48" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="D48" s="9" t="s">
+        <v>219</v>
+      </c>
+      <c r="E48" s="4"/>
+      <c r="F48" s="4"/>
+    </row>
+    <row r="49" spans="1:6" ht="84">
+      <c r="A49" s="9" t="s">
+        <v>214</v>
+      </c>
+      <c r="B49" s="4"/>
+      <c r="C49" s="9" t="s">
+        <v>305</v>
+      </c>
       <c r="D49" s="9"/>
-    </row>
-    <row r="50" spans="1:6" s="4" customFormat="1">
+      <c r="E49" s="4"/>
+      <c r="F49" s="4"/>
+    </row>
+    <row r="50" spans="1:6">
       <c r="A50" s="9"/>
+      <c r="B50" s="4"/>
       <c r="C50" s="9"/>
       <c r="D50" s="9"/>
-    </row>
-    <row r="51" spans="1:6" s="4" customFormat="1">
-      <c r="A51" s="9"/>
-      <c r="C51" s="9"/>
-      <c r="D51" s="9"/>
-    </row>
-    <row r="52" spans="1:6" s="4" customFormat="1">
-      <c r="A52" s="9"/>
+      <c r="E50" s="4"/>
+      <c r="F50" s="4"/>
+    </row>
+    <row r="51" spans="1:6">
+      <c r="A51" s="9" t="s">
+        <v>237</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>233</v>
+      </c>
+      <c r="C51" s="9" t="s">
+        <v>234</v>
+      </c>
+      <c r="D51" s="9" t="s">
+        <v>235</v>
+      </c>
+      <c r="E51" s="4"/>
+      <c r="F51" s="4"/>
+    </row>
+    <row r="52" spans="1:6" ht="24">
+      <c r="A52" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="B52" s="4"/>
       <c r="C52" s="9"/>
       <c r="D52" s="9"/>
+      <c r="E52" s="4"/>
+      <c r="F52" s="4"/>
     </row>
     <row r="53" spans="1:6" s="4" customFormat="1">
       <c r="A53" s="9"/>
@@ -4282,29 +4386,29 @@
       <c r="D54" s="9"/>
     </row>
     <row r="55" spans="1:6">
-      <c r="A55" s="45" t="s">
-        <v>153</v>
-      </c>
-      <c r="B55" s="46" t="s">
-        <v>206</v>
-      </c>
-      <c r="C55" s="45" t="s">
-        <v>147</v>
-      </c>
-      <c r="D55" s="45"/>
-      <c r="E55" s="46"/>
-      <c r="F55" s="46"/>
+      <c r="A55" s="35" t="s">
+        <v>149</v>
+      </c>
+      <c r="B55" s="36" t="s">
+        <v>191</v>
+      </c>
+      <c r="C55" s="35" t="s">
+        <v>145</v>
+      </c>
+      <c r="D55" s="35"/>
+      <c r="E55" s="36"/>
+      <c r="F55" s="36"/>
     </row>
     <row r="56" spans="1:6" ht="24">
       <c r="A56" s="9" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="B56" s="4"/>
       <c r="C56" s="9" t="s">
-        <v>170</v>
+        <v>306</v>
       </c>
       <c r="D56" s="9" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="E56" s="4"/>
       <c r="F56" s="4"/>
@@ -4319,54 +4423,54 @@
     </row>
     <row r="58" spans="1:6" ht="24">
       <c r="A58" s="9" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>224</v>
+        <v>208</v>
       </c>
       <c r="C58" s="9" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="D58" s="9" t="s">
-        <v>237</v>
+        <v>218</v>
       </c>
       <c r="E58" s="4"/>
       <c r="F58" s="4"/>
     </row>
     <row r="59" spans="1:6">
       <c r="A59" s="9" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="B59" s="4"/>
       <c r="C59" s="9" t="s">
-        <v>225</v>
+        <v>307</v>
       </c>
       <c r="D59" s="9"/>
       <c r="E59" s="4"/>
       <c r="F59" s="4"/>
     </row>
-    <row r="60" spans="1:6" ht="36">
+    <row r="60" spans="1:6" ht="24">
       <c r="A60" s="9" t="s">
-        <v>214</v>
+        <v>199</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>215</v>
+        <v>200</v>
       </c>
       <c r="C60" s="9" t="s">
-        <v>216</v>
+        <v>201</v>
       </c>
       <c r="D60" s="9" t="s">
-        <v>217</v>
+        <v>202</v>
       </c>
       <c r="E60" s="4"/>
       <c r="F60" s="4"/>
     </row>
     <row r="61" spans="1:6">
       <c r="A61" s="9" t="s">
-        <v>218</v>
+        <v>203</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>219</v>
+        <v>204</v>
       </c>
       <c r="C61" s="9"/>
       <c r="D61" s="9"/>
@@ -4381,95 +4485,95 @@
       <c r="E62" s="4"/>
       <c r="F62" s="4"/>
     </row>
-    <row r="63" spans="1:6">
-      <c r="A63" s="5" t="s">
+    <row r="63" spans="1:6" s="49" customFormat="1">
+      <c r="A63" s="47" t="s">
+        <v>155</v>
+      </c>
+      <c r="B63" s="48"/>
+      <c r="C63" s="47" t="s">
+        <v>308</v>
+      </c>
+      <c r="D63" s="47"/>
+      <c r="E63" s="48"/>
+      <c r="F63" s="48"/>
+    </row>
+    <row r="64" spans="1:6" s="49" customFormat="1" ht="24">
+      <c r="A64" s="47" t="s">
+        <v>156</v>
+      </c>
+      <c r="B64" s="48"/>
+      <c r="C64" s="47" t="s">
+        <v>307</v>
+      </c>
+      <c r="D64" s="47" t="s">
+        <v>146</v>
+      </c>
+      <c r="E64" s="48"/>
+      <c r="F64" s="48"/>
+    </row>
+    <row r="65" spans="1:6" s="49" customFormat="1" ht="24">
+      <c r="A65" s="47" t="s">
+        <v>153</v>
+      </c>
+      <c r="B65" s="48" t="s">
+        <v>158</v>
+      </c>
+      <c r="C65" s="47" t="s">
+        <v>154</v>
+      </c>
+      <c r="D65" s="47"/>
+      <c r="E65" s="48"/>
+      <c r="F65" s="48"/>
+    </row>
+    <row r="66" spans="1:6" s="49" customFormat="1" ht="48">
+      <c r="A66" s="47" t="s">
+        <v>157</v>
+      </c>
+      <c r="B66" s="48" t="s">
+        <v>158</v>
+      </c>
+      <c r="C66" s="47" t="s">
+        <v>161</v>
+      </c>
+      <c r="D66" s="47" t="s">
+        <v>162</v>
+      </c>
+      <c r="E66" s="48"/>
+      <c r="F66" s="48"/>
+    </row>
+    <row r="67" spans="1:6" s="49" customFormat="1" ht="36">
+      <c r="A67" s="47" t="s">
+        <v>159</v>
+      </c>
+      <c r="B67" s="48" t="s">
+        <v>158</v>
+      </c>
+      <c r="C67" s="47" t="s">
         <v>160</v>
       </c>
-      <c r="B63" s="2"/>
-      <c r="C63" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="D63" s="5"/>
-      <c r="E63" s="2"/>
-      <c r="F63" s="2"/>
-    </row>
-    <row r="64" spans="1:6" ht="24">
-      <c r="A64" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="B64" s="2"/>
-      <c r="C64" s="5" t="s">
-        <v>225</v>
-      </c>
-      <c r="D64" s="5" t="s">
-        <v>149</v>
-      </c>
-      <c r="E64" s="2"/>
-      <c r="F64" s="2"/>
-    </row>
-    <row r="65" spans="1:6" ht="24">
-      <c r="A65" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="B65" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="C65" s="5" t="s">
-        <v>158</v>
-      </c>
-      <c r="D65" s="5"/>
-      <c r="E65" s="2"/>
-      <c r="F65" s="2"/>
-    </row>
-    <row r="66" spans="1:6" ht="60">
-      <c r="A66" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="B66" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="C66" s="5" t="s">
-        <v>166</v>
-      </c>
-      <c r="D66" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="E66" s="2"/>
-      <c r="F66" s="2"/>
-    </row>
-    <row r="67" spans="1:6" ht="48">
-      <c r="A67" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="B67" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="C67" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="D67" s="5"/>
-      <c r="E67" s="2"/>
-      <c r="F67" s="2"/>
-    </row>
-    <row r="68" spans="1:6" s="21" customFormat="1">
-      <c r="A68" s="25" t="s">
-        <v>152</v>
-      </c>
-      <c r="B68" s="26"/>
-      <c r="C68" s="25"/>
-      <c r="D68" s="25" t="s">
-        <v>150</v>
-      </c>
-      <c r="E68" s="26"/>
-      <c r="F68" s="26"/>
-    </row>
-    <row r="69" spans="1:6">
-      <c r="A69" s="5"/>
-      <c r="B69" s="2"/>
-      <c r="C69" s="5"/>
-      <c r="D69" s="5"/>
-      <c r="E69" s="2"/>
-      <c r="F69" s="2"/>
+      <c r="D67" s="47"/>
+      <c r="E67" s="48"/>
+      <c r="F67" s="48"/>
+    </row>
+    <row r="68" spans="1:6" s="21" customFormat="1" ht="24">
+      <c r="A68" s="50" t="s">
+        <v>148</v>
+      </c>
+      <c r="B68" s="51"/>
+      <c r="C68" s="50"/>
+      <c r="D68" s="50" t="s">
+        <v>147</v>
+      </c>
+      <c r="E68" s="51"/>
+      <c r="F68" s="51"/>
+    </row>
+    <row r="69" spans="1:6" s="49" customFormat="1">
+      <c r="A69" s="47"/>
+      <c r="B69" s="48"/>
+      <c r="C69" s="47"/>
+      <c r="D69" s="47"/>
+      <c r="E69" s="48"/>
+      <c r="F69" s="48"/>
     </row>
     <row r="70" spans="1:6">
       <c r="A70" s="9"/>
@@ -4530,18 +4634,18 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="40.5">
       <c r="B8" s="23" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="C8" s="24" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
     </row>
   </sheetData>
@@ -4563,195 +4667,195 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="25" t="s">
+        <v>227</v>
+      </c>
+      <c r="B1" s="25" t="s">
+        <v>225</v>
+      </c>
+      <c r="C1" s="26" t="s">
+        <v>226</v>
+      </c>
+      <c r="D1" s="26" t="s">
+        <v>247</v>
+      </c>
+      <c r="E1" s="26" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="67.5">
+      <c r="A2" s="28" t="s">
+        <v>231</v>
+      </c>
+      <c r="B2" s="29" t="s">
+        <v>245</v>
+      </c>
+      <c r="C2" s="28" t="s">
+        <v>229</v>
+      </c>
+      <c r="D2" s="28" t="s">
+        <v>228</v>
+      </c>
+      <c r="E2" s="30" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="29"/>
+      <c r="B3" s="29"/>
+      <c r="C3" s="28"/>
+      <c r="D3" s="28"/>
+      <c r="E3" s="28"/>
+    </row>
+    <row r="4" spans="1:5" ht="27">
+      <c r="A4" s="29" t="s">
+        <v>244</v>
+      </c>
+      <c r="B4" s="29" t="s">
+        <v>44</v>
+      </c>
+      <c r="C4" s="28" t="s">
+        <v>277</v>
+      </c>
+      <c r="D4" s="28" t="s">
+        <v>246</v>
+      </c>
+      <c r="E4" s="30" t="s">
         <v>248</v>
       </c>
-      <c r="B1" s="27" t="s">
-        <v>246</v>
-      </c>
-      <c r="C1" s="28" t="s">
-        <v>247</v>
-      </c>
-      <c r="D1" s="28" t="s">
-        <v>268</v>
-      </c>
-      <c r="E1" s="28" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="67.5">
-      <c r="A2" s="30" t="s">
-        <v>252</v>
-      </c>
-      <c r="B2" s="31" t="s">
-        <v>266</v>
-      </c>
-      <c r="C2" s="30" t="s">
-        <v>250</v>
-      </c>
-      <c r="D2" s="30" t="s">
-        <v>249</v>
-      </c>
-      <c r="E2" s="32" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="31"/>
-      <c r="B3" s="31"/>
-      <c r="C3" s="30"/>
-      <c r="D3" s="30"/>
-      <c r="E3" s="30"/>
-    </row>
-    <row r="4" spans="1:5" ht="27">
-      <c r="A4" s="31" t="s">
-        <v>265</v>
-      </c>
-      <c r="B4" s="31" t="s">
-        <v>44</v>
-      </c>
-      <c r="C4" s="30" t="s">
-        <v>298</v>
-      </c>
-      <c r="D4" s="30" t="s">
-        <v>267</v>
-      </c>
-      <c r="E4" s="32" t="s">
-        <v>269</v>
-      </c>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="31"/>
-      <c r="B5" s="31"/>
-      <c r="C5" s="30"/>
-      <c r="D5" s="30"/>
-      <c r="E5" s="30"/>
+      <c r="A5" s="29"/>
+      <c r="B5" s="29"/>
+      <c r="C5" s="28"/>
+      <c r="D5" s="28"/>
+      <c r="E5" s="28"/>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="31"/>
-      <c r="B6" s="31"/>
-      <c r="C6" s="30"/>
-      <c r="D6" s="30"/>
-      <c r="E6" s="30"/>
+      <c r="A6" s="29"/>
+      <c r="B6" s="29"/>
+      <c r="C6" s="28"/>
+      <c r="D6" s="28"/>
+      <c r="E6" s="28"/>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7" s="31"/>
-      <c r="B7" s="31"/>
-      <c r="C7" s="30"/>
-      <c r="D7" s="30"/>
-      <c r="E7" s="30"/>
+      <c r="A7" s="29"/>
+      <c r="B7" s="29"/>
+      <c r="C7" s="28"/>
+      <c r="D7" s="28"/>
+      <c r="E7" s="28"/>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" s="31"/>
-      <c r="B8" s="31"/>
-      <c r="C8" s="30"/>
-      <c r="D8" s="30"/>
-      <c r="E8" s="30"/>
+      <c r="A8" s="29"/>
+      <c r="B8" s="29"/>
+      <c r="C8" s="28"/>
+      <c r="D8" s="28"/>
+      <c r="E8" s="28"/>
     </row>
     <row r="9" spans="1:5">
-      <c r="A9" s="31"/>
-      <c r="B9" s="31"/>
-      <c r="C9" s="30"/>
-      <c r="D9" s="30"/>
-      <c r="E9" s="30"/>
+      <c r="A9" s="29"/>
+      <c r="B9" s="29"/>
+      <c r="C9" s="28"/>
+      <c r="D9" s="28"/>
+      <c r="E9" s="28"/>
     </row>
     <row r="10" spans="1:5">
-      <c r="A10" s="31"/>
-      <c r="B10" s="31"/>
-      <c r="C10" s="30"/>
-      <c r="D10" s="30"/>
-      <c r="E10" s="30"/>
+      <c r="A10" s="29"/>
+      <c r="B10" s="29"/>
+      <c r="C10" s="28"/>
+      <c r="D10" s="28"/>
+      <c r="E10" s="28"/>
     </row>
     <row r="11" spans="1:5">
-      <c r="A11" s="31"/>
-      <c r="B11" s="31"/>
-      <c r="C11" s="30"/>
-      <c r="D11" s="30"/>
-      <c r="E11" s="30"/>
+      <c r="A11" s="29"/>
+      <c r="B11" s="29"/>
+      <c r="C11" s="28"/>
+      <c r="D11" s="28"/>
+      <c r="E11" s="28"/>
     </row>
     <row r="12" spans="1:5">
-      <c r="A12" s="31"/>
-      <c r="B12" s="31"/>
-      <c r="C12" s="30"/>
-      <c r="D12" s="30"/>
-      <c r="E12" s="30"/>
+      <c r="A12" s="29"/>
+      <c r="B12" s="29"/>
+      <c r="C12" s="28"/>
+      <c r="D12" s="28"/>
+      <c r="E12" s="28"/>
     </row>
     <row r="13" spans="1:5">
-      <c r="A13" s="31"/>
-      <c r="B13" s="31"/>
-      <c r="C13" s="30"/>
-      <c r="D13" s="30"/>
-      <c r="E13" s="30"/>
+      <c r="A13" s="29"/>
+      <c r="B13" s="29"/>
+      <c r="C13" s="28"/>
+      <c r="D13" s="28"/>
+      <c r="E13" s="28"/>
     </row>
     <row r="14" spans="1:5">
-      <c r="A14" s="31"/>
-      <c r="B14" s="31"/>
-      <c r="C14" s="30"/>
-      <c r="D14" s="30"/>
-      <c r="E14" s="30"/>
+      <c r="A14" s="29"/>
+      <c r="B14" s="29"/>
+      <c r="C14" s="28"/>
+      <c r="D14" s="28"/>
+      <c r="E14" s="28"/>
     </row>
     <row r="15" spans="1:5">
-      <c r="A15" s="31"/>
-      <c r="B15" s="31"/>
-      <c r="C15" s="30"/>
-      <c r="D15" s="30"/>
-      <c r="E15" s="30"/>
+      <c r="A15" s="29"/>
+      <c r="B15" s="29"/>
+      <c r="C15" s="28"/>
+      <c r="D15" s="28"/>
+      <c r="E15" s="28"/>
     </row>
     <row r="16" spans="1:5">
-      <c r="A16" s="31"/>
-      <c r="B16" s="31"/>
-      <c r="C16" s="30"/>
-      <c r="D16" s="30"/>
-      <c r="E16" s="30"/>
+      <c r="A16" s="29"/>
+      <c r="B16" s="29"/>
+      <c r="C16" s="28"/>
+      <c r="D16" s="28"/>
+      <c r="E16" s="28"/>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="31"/>
-      <c r="B17" s="31"/>
-      <c r="C17" s="30"/>
-      <c r="D17" s="30"/>
-      <c r="E17" s="30"/>
+      <c r="A17" s="29"/>
+      <c r="B17" s="29"/>
+      <c r="C17" s="28"/>
+      <c r="D17" s="28"/>
+      <c r="E17" s="28"/>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="31"/>
-      <c r="B18" s="31"/>
-      <c r="C18" s="30"/>
-      <c r="D18" s="30"/>
-      <c r="E18" s="30"/>
+      <c r="A18" s="29"/>
+      <c r="B18" s="29"/>
+      <c r="C18" s="28"/>
+      <c r="D18" s="28"/>
+      <c r="E18" s="28"/>
     </row>
     <row r="19" spans="1:5">
-      <c r="A19" s="31"/>
-      <c r="B19" s="31"/>
-      <c r="C19" s="30"/>
-      <c r="D19" s="30"/>
-      <c r="E19" s="30"/>
+      <c r="A19" s="29"/>
+      <c r="B19" s="29"/>
+      <c r="C19" s="28"/>
+      <c r="D19" s="28"/>
+      <c r="E19" s="28"/>
     </row>
     <row r="20" spans="1:5">
-      <c r="A20" s="31"/>
-      <c r="B20" s="31"/>
-      <c r="C20" s="30"/>
-      <c r="D20" s="30"/>
-      <c r="E20" s="30"/>
+      <c r="A20" s="29"/>
+      <c r="B20" s="29"/>
+      <c r="C20" s="28"/>
+      <c r="D20" s="28"/>
+      <c r="E20" s="28"/>
     </row>
     <row r="21" spans="1:5">
-      <c r="A21" s="31"/>
-      <c r="B21" s="31"/>
-      <c r="C21" s="30"/>
-      <c r="D21" s="30"/>
-      <c r="E21" s="30"/>
+      <c r="A21" s="29"/>
+      <c r="B21" s="29"/>
+      <c r="C21" s="28"/>
+      <c r="D21" s="28"/>
+      <c r="E21" s="28"/>
     </row>
     <row r="22" spans="1:5">
-      <c r="A22" s="31"/>
-      <c r="B22" s="31"/>
-      <c r="C22" s="30"/>
-      <c r="D22" s="30"/>
-      <c r="E22" s="30"/>
+      <c r="A22" s="29"/>
+      <c r="B22" s="29"/>
+      <c r="C22" s="28"/>
+      <c r="D22" s="28"/>
+      <c r="E22" s="28"/>
     </row>
     <row r="23" spans="1:5">
-      <c r="A23" s="31"/>
-      <c r="B23" s="31"/>
-      <c r="C23" s="30"/>
-      <c r="D23" s="30"/>
-      <c r="E23" s="30"/>
+      <c r="A23" s="29"/>
+      <c r="B23" s="29"/>
+      <c r="C23" s="28"/>
+      <c r="D23" s="28"/>
+      <c r="E23" s="28"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -4772,163 +4876,163 @@
   <sheetData>
     <row r="1" spans="1:4" ht="27">
       <c r="A1" s="23" t="s">
-        <v>273</v>
+        <v>252</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="27">
       <c r="A2" s="23" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="26" t="s">
+        <v>269</v>
+      </c>
+      <c r="B4" s="26" t="s">
+        <v>270</v>
+      </c>
+      <c r="C4" s="26"/>
+      <c r="D4" s="26"/>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="31" t="s">
+        <v>253</v>
+      </c>
+      <c r="B5" s="27" t="s">
+        <v>268</v>
+      </c>
+      <c r="C5" s="27"/>
+      <c r="D5" s="27"/>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="31" t="s">
+        <v>254</v>
+      </c>
+      <c r="B6" s="27" t="s">
+        <v>251</v>
+      </c>
+      <c r="C6" s="27"/>
+      <c r="D6" s="27"/>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="31" t="s">
+        <v>255</v>
+      </c>
+      <c r="B7" s="27" t="s">
         <v>271</v>
       </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="28" t="s">
-        <v>290</v>
-      </c>
-      <c r="B4" s="28" t="s">
-        <v>291</v>
-      </c>
-      <c r="C4" s="28"/>
-      <c r="D4" s="28"/>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="33" t="s">
+      <c r="C7" s="27"/>
+      <c r="D7" s="27"/>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="31" t="s">
+        <v>256</v>
+      </c>
+      <c r="B8" s="27" t="s">
+        <v>272</v>
+      </c>
+      <c r="C8" s="27"/>
+      <c r="D8" s="27"/>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="31" t="s">
+        <v>257</v>
+      </c>
+      <c r="B9" s="27" t="s">
+        <v>273</v>
+      </c>
+      <c r="C9" s="27"/>
+      <c r="D9" s="27"/>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="31" t="s">
+        <v>258</v>
+      </c>
+      <c r="B10" s="27" t="s">
+        <v>273</v>
+      </c>
+      <c r="C10" s="27"/>
+      <c r="D10" s="27"/>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="31" t="s">
+        <v>259</v>
+      </c>
+      <c r="B11" s="27" t="s">
+        <v>273</v>
+      </c>
+      <c r="C11" s="27"/>
+      <c r="D11" s="27"/>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="31" t="s">
+        <v>260</v>
+      </c>
+      <c r="B12" s="27" t="s">
         <v>274</v>
       </c>
-      <c r="B5" s="29" t="s">
-        <v>289</v>
-      </c>
-      <c r="C5" s="29"/>
-      <c r="D5" s="29"/>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" s="33" t="s">
+      <c r="C12" s="27"/>
+      <c r="D12" s="27"/>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="31" t="s">
+        <v>265</v>
+      </c>
+      <c r="B13" s="27" t="s">
         <v>275</v>
       </c>
-      <c r="B6" s="29" t="s">
-        <v>272</v>
-      </c>
-      <c r="C6" s="29"/>
-      <c r="D6" s="29"/>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" s="33" t="s">
+      <c r="C13" s="27"/>
+      <c r="D13" s="27"/>
+    </row>
+    <row r="14" spans="1:4" ht="27">
+      <c r="A14" s="31" t="s">
+        <v>266</v>
+      </c>
+      <c r="B14" s="27" t="s">
         <v>276</v>
       </c>
-      <c r="B7" s="29" t="s">
-        <v>292</v>
-      </c>
-      <c r="C7" s="29"/>
-      <c r="D7" s="29"/>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" s="33" t="s">
-        <v>277</v>
-      </c>
-      <c r="B8" s="29" t="s">
-        <v>293</v>
-      </c>
-      <c r="C8" s="29"/>
-      <c r="D8" s="29"/>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" s="33" t="s">
-        <v>278</v>
-      </c>
-      <c r="B9" s="29" t="s">
-        <v>294</v>
-      </c>
-      <c r="C9" s="29"/>
-      <c r="D9" s="29"/>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" s="33" t="s">
-        <v>279</v>
-      </c>
-      <c r="B10" s="29" t="s">
-        <v>294</v>
-      </c>
-      <c r="C10" s="29"/>
-      <c r="D10" s="29"/>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11" s="33" t="s">
-        <v>280</v>
-      </c>
-      <c r="B11" s="29" t="s">
-        <v>294</v>
-      </c>
-      <c r="C11" s="29"/>
-      <c r="D11" s="29"/>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12" s="33" t="s">
-        <v>281</v>
-      </c>
-      <c r="B12" s="29" t="s">
-        <v>295</v>
-      </c>
-      <c r="C12" s="29"/>
-      <c r="D12" s="29"/>
-    </row>
-    <row r="13" spans="1:4">
-      <c r="A13" s="33" t="s">
-        <v>286</v>
-      </c>
-      <c r="B13" s="29" t="s">
-        <v>296</v>
-      </c>
-      <c r="C13" s="29"/>
-      <c r="D13" s="29"/>
-    </row>
-    <row r="14" spans="1:4" ht="27">
-      <c r="A14" s="33" t="s">
-        <v>287</v>
-      </c>
-      <c r="B14" s="29" t="s">
-        <v>297</v>
-      </c>
-      <c r="C14" s="29"/>
-      <c r="D14" s="29"/>
+      <c r="C14" s="27"/>
+      <c r="D14" s="27"/>
     </row>
     <row r="15" spans="1:4">
-      <c r="A15" s="34" t="s">
-        <v>288</v>
-      </c>
-      <c r="B15" s="35" t="s">
-        <v>283</v>
-      </c>
-      <c r="C15" s="35"/>
-      <c r="D15" s="35"/>
+      <c r="A15" s="32" t="s">
+        <v>267</v>
+      </c>
+      <c r="B15" s="33" t="s">
+        <v>262</v>
+      </c>
+      <c r="C15" s="33"/>
+      <c r="D15" s="33"/>
     </row>
     <row r="16" spans="1:4">
-      <c r="A16" s="36" t="s">
-        <v>282</v>
-      </c>
-      <c r="B16" s="35" t="s">
-        <v>283</v>
-      </c>
-      <c r="C16" s="35"/>
-      <c r="D16" s="35"/>
+      <c r="A16" s="34" t="s">
+        <v>261</v>
+      </c>
+      <c r="B16" s="33" t="s">
+        <v>262</v>
+      </c>
+      <c r="C16" s="33"/>
+      <c r="D16" s="33"/>
     </row>
     <row r="17" spans="1:4">
-      <c r="A17" s="36" t="s">
-        <v>284</v>
-      </c>
-      <c r="B17" s="35" t="s">
-        <v>283</v>
-      </c>
-      <c r="C17" s="35"/>
-      <c r="D17" s="35"/>
+      <c r="A17" s="34" t="s">
+        <v>263</v>
+      </c>
+      <c r="B17" s="33" t="s">
+        <v>262</v>
+      </c>
+      <c r="C17" s="33"/>
+      <c r="D17" s="33"/>
     </row>
     <row r="18" spans="1:4">
-      <c r="A18" s="36" t="s">
-        <v>285</v>
-      </c>
-      <c r="B18" s="35" t="s">
-        <v>283</v>
-      </c>
-      <c r="C18" s="35"/>
-      <c r="D18" s="35"/>
+      <c r="A18" s="34" t="s">
+        <v>264</v>
+      </c>
+      <c r="B18" s="33" t="s">
+        <v>262</v>
+      </c>
+      <c r="C18" s="33"/>
+      <c r="D18" s="33"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/internal_doc/03.开发设计/OM_web接口.xlsx
+++ b/internal_doc/03.开发设计/OM_web接口.xlsx
@@ -281,7 +281,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="313">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="321">
   <si>
     <t>需求</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1269,10 +1269,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>host_info={ClusterName:cls1, HostInfo:[{IP, HostName, User, Passwd, SshPort:xxx, AgentPort:xxx, InstallPath:xxx, Firework, [Disk],[CPU]…}, ...], User:xxx, Passwd:xxx, SshPort:xxx, AgentPort:xxx, InstallPath:xxx}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>query business</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1286,14 +1282,6 @@
   </si>
   <si>
     <t>删除集群</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>根据clusterName查询业务</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>根据clusterName查询业务响应</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1503,14 +1491,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>查询business列表</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>查询business列表响应</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>list business</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1589,6 +1569,61 @@
   </si>
   <si>
     <t>remove host</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>查询集群下所有business</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>查询集群下所有business响应</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>查询业务</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>查询业务响应</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>查询主机运行状态</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>query host status</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>查询主机运行状态响应</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>HostInfo={ClusterName:cls1, HostInfo:[{IP, HostName, User, Passwd, SshPort:xxx, AgentPort:xxx, InstallPath:xxx, Firework, [Disk],[CPU]…}, ...], User:xxx, Passwd:xxx, SshPort:xxx, AgentPort:xxx, InstallPath:xxx}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>HostInfo={[{HostName:"h1"}, {HostName:"h2"}]}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://192.168.20.197:11814/?cmd=query host status&amp;HostInfo={[{HostName:"h1"}, {HostName:"h2"}]}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{HostInfo:[{HostName:aa, "CPU":"90%", "Memory": { "Model": "", "Size": 2003, "Free": 916, "Unit": "M" }, "Disk":[{ "Name"
+: "/dev/sda1", "Mount": "/", "Size": 32529, "Free": 6525, "Unit": "M", "Used": 1 }]}, {...}, ...]}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{HostName:aa, "CPU":"90%", "Memory": { "Model": "", "Size": 2003, "Free": 916, "Unit": "M" }, "Disk":[{ "Name"
+: "/dev/sda1", "Mount": "/", "Size": 32529, "Free": 6525, "Unit": "M", "Used": 1 }]}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"HostInfo":[{HostName:aa, "User":"root", "Passwd"sequoiadb", "Disk":[{ "Name"
+: "/dev/sda1", "Mount": "/"}]}, {...}, ...]}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1923,6 +1958,21 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1941,21 +1991,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2367,7 +2402,7 @@
       </c>
     </row>
     <row r="3" spans="1:8">
-      <c r="A3" s="37" t="s">
+      <c r="A3" s="46" t="s">
         <v>12</v>
       </c>
       <c r="B3" s="4" t="s">
@@ -2385,7 +2420,7 @@
       <c r="H3" s="4"/>
     </row>
     <row r="4" spans="1:8" ht="13.5">
-      <c r="A4" s="38"/>
+      <c r="A4" s="47"/>
       <c r="B4" s="4" t="s">
         <v>5</v>
       </c>
@@ -2401,7 +2436,7 @@
       <c r="H4" s="4"/>
     </row>
     <row r="5" spans="1:8" ht="13.5">
-      <c r="A5" s="38"/>
+      <c r="A5" s="47"/>
       <c r="B5" s="4" t="s">
         <v>8</v>
       </c>
@@ -2417,7 +2452,7 @@
       <c r="H5" s="4"/>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" s="39"/>
+      <c r="A6" s="48"/>
       <c r="B6" s="4" t="s">
         <v>13</v>
       </c>
@@ -2433,7 +2468,7 @@
       <c r="H6" s="4"/>
     </row>
     <row r="7" spans="1:8" ht="24">
-      <c r="A7" s="40" t="s">
+      <c r="A7" s="49" t="s">
         <v>24</v>
       </c>
       <c r="B7" s="4" t="s">
@@ -2451,7 +2486,7 @@
       <c r="H7" s="4"/>
     </row>
     <row r="8" spans="1:8" ht="36">
-      <c r="A8" s="41"/>
+      <c r="A8" s="50"/>
       <c r="B8" s="4" t="s">
         <v>17</v>
       </c>
@@ -2469,7 +2504,7 @@
       <c r="H8" s="4"/>
     </row>
     <row r="9" spans="1:8" ht="72">
-      <c r="A9" s="41"/>
+      <c r="A9" s="50"/>
       <c r="B9" s="4" t="s">
         <v>18</v>
       </c>
@@ -2487,7 +2522,7 @@
       <c r="H9" s="4"/>
     </row>
     <row r="10" spans="1:8" ht="24">
-      <c r="A10" s="42"/>
+      <c r="A10" s="51"/>
       <c r="B10" s="4" t="s">
         <v>21</v>
       </c>
@@ -2525,7 +2560,7 @@
       <c r="H11" s="4"/>
     </row>
     <row r="12" spans="1:8" ht="24">
-      <c r="A12" s="40" t="s">
+      <c r="A12" s="49" t="s">
         <v>26</v>
       </c>
       <c r="B12" s="4" t="s">
@@ -2543,7 +2578,7 @@
       <c r="H12" s="4"/>
     </row>
     <row r="13" spans="1:8">
-      <c r="A13" s="41"/>
+      <c r="A13" s="50"/>
       <c r="B13" s="4" t="s">
         <v>32</v>
       </c>
@@ -2559,7 +2594,7 @@
       <c r="H13" s="4"/>
     </row>
     <row r="14" spans="1:8" ht="24">
-      <c r="A14" s="41"/>
+      <c r="A14" s="50"/>
       <c r="B14" s="4" t="s">
         <v>33</v>
       </c>
@@ -2577,7 +2612,7 @@
       <c r="H14" s="4"/>
     </row>
     <row r="15" spans="1:8">
-      <c r="A15" s="41"/>
+      <c r="A15" s="50"/>
       <c r="B15" s="4" t="s">
         <v>35</v>
       </c>
@@ -2593,7 +2628,7 @@
       <c r="H15" s="4"/>
     </row>
     <row r="16" spans="1:8">
-      <c r="A16" s="41"/>
+      <c r="A16" s="50"/>
       <c r="B16" s="4" t="s">
         <v>57</v>
       </c>
@@ -2605,7 +2640,7 @@
       <c r="H16" s="4"/>
     </row>
     <row r="17" spans="1:8" ht="48">
-      <c r="A17" s="41"/>
+      <c r="A17" s="50"/>
       <c r="B17" s="4" t="s">
         <v>30</v>
       </c>
@@ -2623,7 +2658,7 @@
       <c r="H17" s="4"/>
     </row>
     <row r="18" spans="1:8">
-      <c r="A18" s="41"/>
+      <c r="A18" s="50"/>
       <c r="B18" s="4" t="s">
         <v>38</v>
       </c>
@@ -2639,7 +2674,7 @@
       <c r="H18" s="4"/>
     </row>
     <row r="19" spans="1:8">
-      <c r="A19" s="41"/>
+      <c r="A19" s="50"/>
       <c r="B19" s="4" t="s">
         <v>41</v>
       </c>
@@ -2655,7 +2690,7 @@
       <c r="H19" s="4"/>
     </row>
     <row r="20" spans="1:8">
-      <c r="A20" s="41"/>
+      <c r="A20" s="50"/>
       <c r="B20" s="4" t="s">
         <v>40</v>
       </c>
@@ -2671,7 +2706,7 @@
       <c r="H20" s="4"/>
     </row>
     <row r="21" spans="1:8" ht="24">
-      <c r="A21" s="41"/>
+      <c r="A21" s="50"/>
       <c r="B21" s="4" t="s">
         <v>44</v>
       </c>
@@ -2689,7 +2724,7 @@
       <c r="H21" s="4"/>
     </row>
     <row r="22" spans="1:8" ht="24">
-      <c r="A22" s="41"/>
+      <c r="A22" s="50"/>
       <c r="B22" s="4" t="s">
         <v>47</v>
       </c>
@@ -2705,7 +2740,7 @@
       <c r="H22" s="4"/>
     </row>
     <row r="23" spans="1:8" ht="24">
-      <c r="A23" s="41"/>
+      <c r="A23" s="50"/>
       <c r="B23" s="4" t="s">
         <v>49</v>
       </c>
@@ -3717,7 +3752,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F74"/>
+  <dimension ref="A1:F79"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="22.375" style="10" customWidth="1"/>
@@ -3745,7 +3780,7 @@
         <v>133</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="D2" s="5" t="s">
         <v>1</v>
@@ -3775,10 +3810,10 @@
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="9" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="E4" s="4"/>
       <c r="F4" s="4"/>
@@ -3816,7 +3851,7 @@
         <v>212</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="E7" s="4"/>
       <c r="F7" s="4"/>
@@ -3829,41 +3864,41 @@
       <c r="E8" s="4"/>
       <c r="F8" s="4"/>
     </row>
-    <row r="9" spans="1:6" s="45" customFormat="1">
-      <c r="A9" s="43" t="s">
+    <row r="9" spans="1:6" s="39" customFormat="1">
+      <c r="A9" s="37" t="s">
+        <v>235</v>
+      </c>
+      <c r="B9" s="38" t="s">
         <v>236</v>
       </c>
-      <c r="B9" s="44" t="s">
-        <v>239</v>
-      </c>
-      <c r="C9" s="43" t="s">
-        <v>234</v>
-      </c>
-      <c r="D9" s="43" t="s">
-        <v>240</v>
-      </c>
-      <c r="E9" s="44"/>
-      <c r="F9" s="44"/>
-    </row>
-    <row r="10" spans="1:6" s="45" customFormat="1">
-      <c r="A10" s="43" t="s">
-        <v>296</v>
-      </c>
-      <c r="B10" s="44"/>
-      <c r="C10" s="43" t="s">
-        <v>294</v>
-      </c>
-      <c r="D10" s="43"/>
-      <c r="E10" s="44"/>
-      <c r="F10" s="44"/>
-    </row>
-    <row r="11" spans="1:6" s="49" customFormat="1">
-      <c r="A11" s="47"/>
-      <c r="B11" s="48"/>
-      <c r="C11" s="47"/>
-      <c r="D11" s="47"/>
-      <c r="E11" s="48"/>
-      <c r="F11" s="48"/>
+      <c r="C9" s="37" t="s">
+        <v>233</v>
+      </c>
+      <c r="D9" s="37" t="s">
+        <v>237</v>
+      </c>
+      <c r="E9" s="38"/>
+      <c r="F9" s="38"/>
+    </row>
+    <row r="10" spans="1:6" s="39" customFormat="1">
+      <c r="A10" s="37" t="s">
+        <v>291</v>
+      </c>
+      <c r="B10" s="38"/>
+      <c r="C10" s="37" t="s">
+        <v>289</v>
+      </c>
+      <c r="D10" s="37"/>
+      <c r="E10" s="38"/>
+      <c r="F10" s="38"/>
+    </row>
+    <row r="11" spans="1:6" s="43" customFormat="1">
+      <c r="A11" s="41"/>
+      <c r="B11" s="42"/>
+      <c r="C11" s="41"/>
+      <c r="D11" s="41"/>
+      <c r="E11" s="42"/>
+      <c r="F11" s="42"/>
     </row>
     <row r="12" spans="1:6" ht="60">
       <c r="A12" s="9" t="s">
@@ -3887,10 +3922,10 @@
       </c>
       <c r="B13" s="4"/>
       <c r="C13" s="9" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="E13" s="4"/>
       <c r="F13" s="4"/>
@@ -3916,7 +3951,7 @@
         <v>183</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="E15" s="4"/>
       <c r="F15" s="4"/>
@@ -3927,10 +3962,10 @@
       </c>
       <c r="B16" s="4"/>
       <c r="C16" s="9" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="E16" s="4"/>
       <c r="F16" s="4"/>
@@ -3953,10 +3988,10 @@
         <v>194</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>232</v>
+        <v>315</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="E18" s="4"/>
       <c r="F18" s="4"/>
@@ -3967,7 +4002,7 @@
       </c>
       <c r="B19" s="4"/>
       <c r="C19" s="9" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="D19" s="9"/>
       <c r="E19" s="4"/>
@@ -3975,77 +4010,77 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="9"/>
-      <c r="B20" s="4" t="s">
-        <v>132</v>
-      </c>
+      <c r="B20" s="4"/>
       <c r="C20" s="9"/>
       <c r="D20" s="9"/>
       <c r="E20" s="4"/>
       <c r="F20" s="4"/>
     </row>
-    <row r="21" spans="1:6">
-      <c r="A21" s="9" t="s">
-        <v>280</v>
-      </c>
-      <c r="B21" s="4" t="s">
-        <v>281</v>
-      </c>
-      <c r="C21" s="9" t="s">
-        <v>286</v>
-      </c>
-      <c r="D21" s="9" t="s">
-        <v>284</v>
-      </c>
-      <c r="E21" s="4"/>
-      <c r="F21" s="4"/>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22" s="9" t="s">
-        <v>282</v>
-      </c>
-      <c r="B22" s="4"/>
-      <c r="C22" s="9" t="s">
-        <v>283</v>
-      </c>
-      <c r="D22" s="9"/>
-      <c r="E22" s="4"/>
-      <c r="F22" s="4"/>
+    <row r="21" spans="1:6" s="40" customFormat="1" ht="24">
+      <c r="A21" s="5" t="s">
+        <v>312</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>316</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>317</v>
+      </c>
+      <c r="E21" s="2"/>
+      <c r="F21" s="2"/>
+    </row>
+    <row r="22" spans="1:6" s="40" customFormat="1" ht="60">
+      <c r="A22" s="5" t="s">
+        <v>314</v>
+      </c>
+      <c r="B22" s="2"/>
+      <c r="C22" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="D22" s="5"/>
+      <c r="E22" s="2"/>
+      <c r="F22" s="2"/>
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="9"/>
-      <c r="B23" s="4"/>
+      <c r="B23" s="4" t="s">
+        <v>132</v>
+      </c>
       <c r="C23" s="9"/>
       <c r="D23" s="9"/>
       <c r="E23" s="4"/>
       <c r="F23" s="4"/>
     </row>
-    <row r="24" spans="1:6">
-      <c r="A24" s="9" t="s">
-        <v>128</v>
-      </c>
-      <c r="B24" s="4" t="s">
-        <v>195</v>
-      </c>
-      <c r="C24" s="9" t="s">
+    <row r="24" spans="1:6" s="40" customFormat="1">
+      <c r="A24" s="5" t="s">
+        <v>277</v>
+      </c>
+      <c r="B24" s="2" t="s">
         <v>278</v>
       </c>
-      <c r="D24" s="9" t="s">
+      <c r="C24" s="5" t="s">
+        <v>283</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="E24" s="2"/>
+      <c r="F24" s="2"/>
+    </row>
+    <row r="25" spans="1:6" s="40" customFormat="1">
+      <c r="A25" s="5" t="s">
         <v>279</v>
       </c>
-      <c r="E24" s="4"/>
-      <c r="F24" s="4"/>
-    </row>
-    <row r="25" spans="1:6" ht="180">
-      <c r="A25" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="B25" s="4"/>
-      <c r="C25" s="9" t="s">
-        <v>287</v>
-      </c>
-      <c r="D25" s="9"/>
-      <c r="E25" s="4"/>
-      <c r="F25" s="4"/>
+      <c r="B25" s="2"/>
+      <c r="C25" s="5" t="s">
+        <v>280</v>
+      </c>
+      <c r="D25" s="5"/>
+      <c r="E25" s="2"/>
+      <c r="F25" s="2"/>
     </row>
     <row r="26" spans="1:6">
       <c r="A26" s="9"/>
@@ -4055,31 +4090,37 @@
       <c r="E26" s="4"/>
       <c r="F26" s="4"/>
     </row>
-    <row r="27" spans="1:6">
-      <c r="A27" s="9" t="s">
-        <v>311</v>
-      </c>
-      <c r="B27" s="4" t="s">
-        <v>312</v>
-      </c>
-      <c r="C27" s="9"/>
-      <c r="D27" s="9"/>
-      <c r="E27" s="4"/>
-      <c r="F27" s="4"/>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28" s="9"/>
-      <c r="B28" s="4"/>
-      <c r="C28" s="9"/>
-      <c r="D28" s="9"/>
-      <c r="E28" s="4"/>
-      <c r="F28" s="4"/>
+    <row r="27" spans="1:6" s="40" customFormat="1">
+      <c r="A27" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>275</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>276</v>
+      </c>
+      <c r="E27" s="2"/>
+      <c r="F27" s="2"/>
+    </row>
+    <row r="28" spans="1:6" s="40" customFormat="1" ht="180">
+      <c r="A28" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="B28" s="2"/>
+      <c r="C28" s="5" t="s">
+        <v>284</v>
+      </c>
+      <c r="D28" s="5"/>
+      <c r="E28" s="2"/>
+      <c r="F28" s="2"/>
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="9"/>
-      <c r="B29" s="4" t="s">
-        <v>132</v>
-      </c>
+      <c r="B29" s="4"/>
       <c r="C29" s="9"/>
       <c r="D29" s="9"/>
       <c r="E29" s="4"/>
@@ -4087,29 +4128,21 @@
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="9" t="s">
-        <v>134</v>
+        <v>306</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>224</v>
+        <v>307</v>
       </c>
       <c r="C30" s="9"/>
-      <c r="D30" s="9" t="s">
-        <v>205</v>
-      </c>
+      <c r="D30" s="9"/>
       <c r="E30" s="4"/>
       <c r="F30" s="4"/>
     </row>
-    <row r="31" spans="1:6" ht="36">
-      <c r="A31" s="9" t="s">
-        <v>135</v>
-      </c>
+    <row r="31" spans="1:6">
+      <c r="A31" s="9"/>
       <c r="B31" s="4"/>
-      <c r="C31" s="9" t="s">
-        <v>206</v>
-      </c>
-      <c r="D31" s="9" t="s">
-        <v>302</v>
-      </c>
+      <c r="C31" s="9"/>
+      <c r="D31" s="9"/>
       <c r="E31" s="4"/>
       <c r="F31" s="4"/>
     </row>
@@ -4123,32 +4156,30 @@
       <c r="E32" s="4"/>
       <c r="F32" s="4"/>
     </row>
-    <row r="33" spans="1:6" ht="24">
+    <row r="33" spans="1:6">
       <c r="A33" s="9" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>215</v>
-      </c>
-      <c r="C33" s="9" t="s">
-        <v>216</v>
-      </c>
+        <v>224</v>
+      </c>
+      <c r="C33" s="9"/>
       <c r="D33" s="9" t="s">
-        <v>222</v>
+        <v>205</v>
       </c>
       <c r="E33" s="4"/>
       <c r="F33" s="4"/>
     </row>
-    <row r="34" spans="1:6" ht="228">
+    <row r="34" spans="1:6" ht="36">
       <c r="A34" s="9" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B34" s="4"/>
       <c r="C34" s="9" t="s">
-        <v>184</v>
+        <v>206</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="E34" s="4"/>
       <c r="F34" s="4"/>
@@ -4163,32 +4194,32 @@
       <c r="E35" s="4"/>
       <c r="F35" s="4"/>
     </row>
-    <row r="36" spans="1:6" ht="84">
+    <row r="36" spans="1:6" ht="24">
       <c r="A36" s="9" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>196</v>
+        <v>215</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D36" s="9" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E36" s="4"/>
       <c r="F36" s="4"/>
     </row>
-    <row r="37" spans="1:6" ht="108">
+    <row r="37" spans="1:6" ht="228">
       <c r="A37" s="9" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B37" s="4"/>
       <c r="C37" s="9" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="D37" s="9" t="s">
-        <v>185</v>
+        <v>298</v>
       </c>
       <c r="E37" s="4"/>
       <c r="F37" s="4"/>
@@ -4203,69 +4234,73 @@
       <c r="E38" s="4"/>
       <c r="F38" s="4"/>
     </row>
-    <row r="39" spans="1:6" ht="132">
+    <row r="39" spans="1:6" ht="84">
       <c r="A39" s="9" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C39" s="9" t="s">
-        <v>187</v>
+        <v>217</v>
       </c>
       <c r="D39" s="9" t="s">
-        <v>249</v>
+        <v>223</v>
       </c>
       <c r="E39" s="4"/>
       <c r="F39" s="4"/>
     </row>
-    <row r="40" spans="1:6">
+    <row r="40" spans="1:6" ht="108">
       <c r="A40" s="9" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B40" s="4"/>
       <c r="C40" s="9" t="s">
-        <v>304</v>
+        <v>186</v>
       </c>
       <c r="D40" s="9" t="s">
-        <v>120</v>
+        <v>185</v>
       </c>
       <c r="E40" s="4"/>
       <c r="F40" s="4"/>
     </row>
     <row r="41" spans="1:6">
       <c r="A41" s="9"/>
-      <c r="B41" s="4"/>
+      <c r="B41" s="4" t="s">
+        <v>132</v>
+      </c>
       <c r="C41" s="9"/>
       <c r="D41" s="9"/>
       <c r="E41" s="4"/>
       <c r="F41" s="4"/>
     </row>
-    <row r="42" spans="1:6">
+    <row r="42" spans="1:6" ht="132">
       <c r="A42" s="9" t="s">
-        <v>288</v>
+        <v>140</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>290</v>
+        <v>197</v>
       </c>
       <c r="C42" s="9" t="s">
-        <v>285</v>
+        <v>187</v>
       </c>
       <c r="D42" s="9" t="s">
-        <v>291</v>
+        <v>246</v>
       </c>
       <c r="E42" s="4"/>
       <c r="F42" s="4"/>
     </row>
     <row r="43" spans="1:6">
       <c r="A43" s="9" t="s">
-        <v>289</v>
+        <v>141</v>
       </c>
       <c r="B43" s="4"/>
       <c r="C43" s="9" t="s">
-        <v>292</v>
-      </c>
-      <c r="D43" s="9"/>
+        <v>299</v>
+      </c>
+      <c r="D43" s="9" t="s">
+        <v>120</v>
+      </c>
       <c r="E43" s="4"/>
       <c r="F43" s="4"/>
     </row>
@@ -4277,69 +4312,67 @@
       <c r="E44" s="4"/>
       <c r="F44" s="4"/>
     </row>
-    <row r="45" spans="1:6" s="46" customFormat="1">
+    <row r="45" spans="1:6" s="40" customFormat="1">
       <c r="A45" s="5" t="s">
-        <v>142</v>
+        <v>308</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>144</v>
+        <v>285</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>293</v>
+        <v>282</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>295</v>
+        <v>286</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" s="2"/>
     </row>
-    <row r="46" spans="1:6" s="46" customFormat="1">
+    <row r="46" spans="1:6" s="40" customFormat="1">
       <c r="A46" s="5" t="s">
-        <v>143</v>
+        <v>309</v>
       </c>
       <c r="B46" s="2"/>
       <c r="C46" s="5" t="s">
-        <v>294</v>
+        <v>287</v>
       </c>
       <c r="D46" s="5"/>
       <c r="E46" s="2"/>
       <c r="F46" s="2"/>
     </row>
-    <row r="47" spans="1:6" s="49" customFormat="1">
-      <c r="A47" s="47"/>
-      <c r="B47" s="48"/>
-      <c r="C47" s="47"/>
-      <c r="D47" s="47"/>
-      <c r="E47" s="48"/>
-      <c r="F47" s="48"/>
-    </row>
-    <row r="48" spans="1:6" ht="24">
-      <c r="A48" s="9" t="s">
-        <v>213</v>
-      </c>
-      <c r="B48" s="4" t="s">
-        <v>209</v>
-      </c>
-      <c r="C48" s="9" t="s">
-        <v>188</v>
-      </c>
-      <c r="D48" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="E48" s="4"/>
-      <c r="F48" s="4"/>
-    </row>
-    <row r="49" spans="1:6" ht="84">
-      <c r="A49" s="9" t="s">
-        <v>214</v>
-      </c>
-      <c r="B49" s="4"/>
-      <c r="C49" s="9" t="s">
-        <v>305</v>
-      </c>
-      <c r="D49" s="9"/>
-      <c r="E49" s="4"/>
-      <c r="F49" s="4"/>
+    <row r="47" spans="1:6" s="43" customFormat="1">
+      <c r="A47" s="41"/>
+      <c r="B47" s="42"/>
+      <c r="C47" s="41"/>
+      <c r="D47" s="41"/>
+      <c r="E47" s="42"/>
+      <c r="F47" s="42"/>
+    </row>
+    <row r="48" spans="1:6" s="40" customFormat="1">
+      <c r="A48" s="5" t="s">
+        <v>310</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="C48" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="D48" s="5" t="s">
+        <v>234</v>
+      </c>
+      <c r="E48" s="2"/>
+      <c r="F48" s="2"/>
+    </row>
+    <row r="49" spans="1:6" s="40" customFormat="1">
+      <c r="A49" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="B49" s="2"/>
+      <c r="C49" s="5"/>
+      <c r="D49" s="5"/>
+      <c r="E49" s="2"/>
+      <c r="F49" s="2"/>
     </row>
     <row r="50" spans="1:6">
       <c r="A50" s="9"/>
@@ -4349,67 +4382,75 @@
       <c r="E50" s="4"/>
       <c r="F50" s="4"/>
     </row>
-    <row r="51" spans="1:6">
-      <c r="A51" s="9" t="s">
-        <v>237</v>
-      </c>
-      <c r="B51" s="4" t="s">
-        <v>233</v>
-      </c>
-      <c r="C51" s="9" t="s">
-        <v>234</v>
-      </c>
-      <c r="D51" s="9" t="s">
-        <v>235</v>
-      </c>
-      <c r="E51" s="4"/>
-      <c r="F51" s="4"/>
-    </row>
-    <row r="52" spans="1:6" ht="24">
-      <c r="A52" s="9" t="s">
-        <v>238</v>
-      </c>
-      <c r="B52" s="4"/>
-      <c r="C52" s="9"/>
-      <c r="D52" s="9"/>
-      <c r="E52" s="4"/>
-      <c r="F52" s="4"/>
-    </row>
-    <row r="53" spans="1:6" s="4" customFormat="1">
-      <c r="A53" s="9"/>
-      <c r="C53" s="9"/>
-      <c r="D53" s="9"/>
-    </row>
-    <row r="54" spans="1:6" s="4" customFormat="1">
-      <c r="A54" s="9"/>
-      <c r="C54" s="9"/>
-      <c r="D54" s="9"/>
-    </row>
-    <row r="55" spans="1:6">
-      <c r="A55" s="35" t="s">
-        <v>149</v>
-      </c>
-      <c r="B55" s="36" t="s">
-        <v>191</v>
-      </c>
-      <c r="C55" s="35" t="s">
-        <v>145</v>
-      </c>
-      <c r="D55" s="35"/>
-      <c r="E55" s="36"/>
-      <c r="F55" s="36"/>
-    </row>
-    <row r="56" spans="1:6" ht="24">
+    <row r="51" spans="1:6" s="40" customFormat="1">
+      <c r="A51" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C51" s="5" t="s">
+        <v>288</v>
+      </c>
+      <c r="D51" s="5" t="s">
+        <v>290</v>
+      </c>
+      <c r="E51" s="2"/>
+      <c r="F51" s="2"/>
+    </row>
+    <row r="52" spans="1:6" s="40" customFormat="1">
+      <c r="A52" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="B52" s="2"/>
+      <c r="C52" s="5" t="s">
+        <v>289</v>
+      </c>
+      <c r="D52" s="5"/>
+      <c r="E52" s="2"/>
+      <c r="F52" s="2"/>
+    </row>
+    <row r="53" spans="1:6" s="43" customFormat="1">
+      <c r="A53" s="41"/>
+      <c r="B53" s="42"/>
+      <c r="C53" s="41"/>
+      <c r="D53" s="41"/>
+      <c r="E53" s="42"/>
+      <c r="F53" s="42"/>
+    </row>
+    <row r="54" spans="1:6" s="43" customFormat="1">
+      <c r="A54" s="41"/>
+      <c r="B54" s="42"/>
+      <c r="C54" s="41"/>
+      <c r="D54" s="41"/>
+      <c r="E54" s="42"/>
+      <c r="F54" s="42"/>
+    </row>
+    <row r="55" spans="1:6" ht="24">
+      <c r="A55" s="9" t="s">
+        <v>213</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="C55" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="D55" s="9" t="s">
+        <v>219</v>
+      </c>
+      <c r="E55" s="4"/>
+      <c r="F55" s="4"/>
+    </row>
+    <row r="56" spans="1:6" ht="84">
       <c r="A56" s="9" t="s">
-        <v>150</v>
+        <v>214</v>
       </c>
       <c r="B56" s="4"/>
       <c r="C56" s="9" t="s">
-        <v>306</v>
-      </c>
-      <c r="D56" s="9" t="s">
-        <v>151</v>
-      </c>
+        <v>300</v>
+      </c>
+      <c r="D56" s="9"/>
       <c r="E56" s="4"/>
       <c r="F56" s="4"/>
     </row>
@@ -4421,59 +4462,41 @@
       <c r="E57" s="4"/>
       <c r="F57" s="4"/>
     </row>
-    <row r="58" spans="1:6" ht="24">
-      <c r="A58" s="9" t="s">
-        <v>163</v>
-      </c>
-      <c r="B58" s="4" t="s">
-        <v>208</v>
-      </c>
-      <c r="C58" s="9" t="s">
-        <v>198</v>
-      </c>
-      <c r="D58" s="9" t="s">
-        <v>218</v>
-      </c>
-      <c r="E58" s="4"/>
-      <c r="F58" s="4"/>
-    </row>
-    <row r="59" spans="1:6">
-      <c r="A59" s="9" t="s">
-        <v>164</v>
-      </c>
-      <c r="B59" s="4"/>
-      <c r="C59" s="9" t="s">
-        <v>307</v>
-      </c>
+    <row r="58" spans="1:6" s="4" customFormat="1">
+      <c r="A58" s="9"/>
+      <c r="C58" s="9"/>
+      <c r="D58" s="9"/>
+    </row>
+    <row r="59" spans="1:6" s="4" customFormat="1">
+      <c r="A59" s="9"/>
+      <c r="C59" s="9"/>
       <c r="D59" s="9"/>
-      <c r="E59" s="4"/>
-      <c r="F59" s="4"/>
-    </row>
-    <row r="60" spans="1:6" ht="24">
-      <c r="A60" s="9" t="s">
-        <v>199</v>
-      </c>
-      <c r="B60" s="4" t="s">
-        <v>200</v>
-      </c>
-      <c r="C60" s="9" t="s">
-        <v>201</v>
-      </c>
-      <c r="D60" s="9" t="s">
-        <v>202</v>
-      </c>
-      <c r="E60" s="4"/>
-      <c r="F60" s="4"/>
-    </row>
-    <row r="61" spans="1:6">
+    </row>
+    <row r="60" spans="1:6">
+      <c r="A60" s="35" t="s">
+        <v>149</v>
+      </c>
+      <c r="B60" s="36" t="s">
+        <v>191</v>
+      </c>
+      <c r="C60" s="35" t="s">
+        <v>145</v>
+      </c>
+      <c r="D60" s="35"/>
+      <c r="E60" s="36"/>
+      <c r="F60" s="36"/>
+    </row>
+    <row r="61" spans="1:6" ht="24">
       <c r="A61" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="B61" s="4" t="s">
-        <v>204</v>
-      </c>
-      <c r="C61" s="9"/>
-      <c r="D61" s="9"/>
+        <v>150</v>
+      </c>
+      <c r="B61" s="4"/>
+      <c r="C61" s="9" t="s">
+        <v>301</v>
+      </c>
+      <c r="D61" s="9" t="s">
+        <v>151</v>
+      </c>
       <c r="E61" s="4"/>
       <c r="F61" s="4"/>
     </row>
@@ -4485,135 +4508,199 @@
       <c r="E62" s="4"/>
       <c r="F62" s="4"/>
     </row>
-    <row r="63" spans="1:6" s="49" customFormat="1">
-      <c r="A63" s="47" t="s">
+    <row r="63" spans="1:6" ht="24">
+      <c r="A63" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="B63" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="C63" s="9" t="s">
+        <v>198</v>
+      </c>
+      <c r="D63" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="E63" s="4"/>
+      <c r="F63" s="4"/>
+    </row>
+    <row r="64" spans="1:6">
+      <c r="A64" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="B64" s="4"/>
+      <c r="C64" s="9" t="s">
+        <v>302</v>
+      </c>
+      <c r="D64" s="9"/>
+      <c r="E64" s="4"/>
+      <c r="F64" s="4"/>
+    </row>
+    <row r="65" spans="1:6" ht="24">
+      <c r="A65" s="9" t="s">
+        <v>199</v>
+      </c>
+      <c r="B65" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="C65" s="9" t="s">
+        <v>201</v>
+      </c>
+      <c r="D65" s="9" t="s">
+        <v>202</v>
+      </c>
+      <c r="E65" s="4"/>
+      <c r="F65" s="4"/>
+    </row>
+    <row r="66" spans="1:6">
+      <c r="A66" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="B66" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C66" s="9"/>
+      <c r="D66" s="9"/>
+      <c r="E66" s="4"/>
+      <c r="F66" s="4"/>
+    </row>
+    <row r="67" spans="1:6">
+      <c r="A67" s="9"/>
+      <c r="B67" s="4"/>
+      <c r="C67" s="9"/>
+      <c r="D67" s="9"/>
+      <c r="E67" s="4"/>
+      <c r="F67" s="4"/>
+    </row>
+    <row r="68" spans="1:6" s="43" customFormat="1">
+      <c r="A68" s="41" t="s">
         <v>155</v>
       </c>
-      <c r="B63" s="48"/>
-      <c r="C63" s="47" t="s">
-        <v>308</v>
-      </c>
-      <c r="D63" s="47"/>
-      <c r="E63" s="48"/>
-      <c r="F63" s="48"/>
-    </row>
-    <row r="64" spans="1:6" s="49" customFormat="1" ht="24">
-      <c r="A64" s="47" t="s">
+      <c r="B68" s="42"/>
+      <c r="C68" s="41" t="s">
+        <v>303</v>
+      </c>
+      <c r="D68" s="41"/>
+      <c r="E68" s="42"/>
+      <c r="F68" s="42"/>
+    </row>
+    <row r="69" spans="1:6" s="43" customFormat="1" ht="24">
+      <c r="A69" s="41" t="s">
         <v>156</v>
       </c>
-      <c r="B64" s="48"/>
-      <c r="C64" s="47" t="s">
-        <v>307</v>
-      </c>
-      <c r="D64" s="47" t="s">
+      <c r="B69" s="42"/>
+      <c r="C69" s="41" t="s">
+        <v>302</v>
+      </c>
+      <c r="D69" s="41" t="s">
         <v>146</v>
       </c>
-      <c r="E64" s="48"/>
-      <c r="F64" s="48"/>
-    </row>
-    <row r="65" spans="1:6" s="49" customFormat="1" ht="24">
-      <c r="A65" s="47" t="s">
+      <c r="E69" s="42"/>
+      <c r="F69" s="42"/>
+    </row>
+    <row r="70" spans="1:6" s="43" customFormat="1" ht="24">
+      <c r="A70" s="41" t="s">
         <v>153</v>
       </c>
-      <c r="B65" s="48" t="s">
+      <c r="B70" s="42" t="s">
         <v>158</v>
       </c>
-      <c r="C65" s="47" t="s">
+      <c r="C70" s="41" t="s">
         <v>154</v>
       </c>
-      <c r="D65" s="47"/>
-      <c r="E65" s="48"/>
-      <c r="F65" s="48"/>
-    </row>
-    <row r="66" spans="1:6" s="49" customFormat="1" ht="48">
-      <c r="A66" s="47" t="s">
+      <c r="D70" s="41"/>
+      <c r="E70" s="42"/>
+      <c r="F70" s="42"/>
+    </row>
+    <row r="71" spans="1:6" s="43" customFormat="1" ht="48">
+      <c r="A71" s="41" t="s">
         <v>157</v>
       </c>
-      <c r="B66" s="48" t="s">
+      <c r="B71" s="42" t="s">
         <v>158</v>
       </c>
-      <c r="C66" s="47" t="s">
+      <c r="C71" s="41" t="s">
         <v>161</v>
       </c>
-      <c r="D66" s="47" t="s">
+      <c r="D71" s="41" t="s">
         <v>162</v>
       </c>
-      <c r="E66" s="48"/>
-      <c r="F66" s="48"/>
-    </row>
-    <row r="67" spans="1:6" s="49" customFormat="1" ht="36">
-      <c r="A67" s="47" t="s">
+      <c r="E71" s="42"/>
+      <c r="F71" s="42"/>
+    </row>
+    <row r="72" spans="1:6" s="43" customFormat="1" ht="36">
+      <c r="A72" s="41" t="s">
         <v>159</v>
       </c>
-      <c r="B67" s="48" t="s">
+      <c r="B72" s="42" t="s">
         <v>158</v>
       </c>
-      <c r="C67" s="47" t="s">
+      <c r="C72" s="41" t="s">
         <v>160</v>
       </c>
-      <c r="D67" s="47"/>
-      <c r="E67" s="48"/>
-      <c r="F67" s="48"/>
-    </row>
-    <row r="68" spans="1:6" s="21" customFormat="1" ht="24">
-      <c r="A68" s="50" t="s">
+      <c r="D72" s="41"/>
+      <c r="E72" s="42"/>
+      <c r="F72" s="42"/>
+    </row>
+    <row r="73" spans="1:6" s="21" customFormat="1" ht="24">
+      <c r="A73" s="44" t="s">
         <v>148</v>
       </c>
-      <c r="B68" s="51"/>
-      <c r="C68" s="50"/>
-      <c r="D68" s="50" t="s">
+      <c r="B73" s="45"/>
+      <c r="C73" s="44"/>
+      <c r="D73" s="44" t="s">
         <v>147</v>
       </c>
-      <c r="E68" s="51"/>
-      <c r="F68" s="51"/>
-    </row>
-    <row r="69" spans="1:6" s="49" customFormat="1">
-      <c r="A69" s="47"/>
-      <c r="B69" s="48"/>
-      <c r="C69" s="47"/>
-      <c r="D69" s="47"/>
-      <c r="E69" s="48"/>
-      <c r="F69" s="48"/>
-    </row>
-    <row r="70" spans="1:6">
-      <c r="A70" s="9"/>
-      <c r="B70" s="4"/>
-      <c r="C70" s="9"/>
-      <c r="D70" s="9"/>
-      <c r="E70" s="4"/>
-      <c r="F70" s="4"/>
-    </row>
-    <row r="71" spans="1:6">
-      <c r="A71" s="9"/>
-      <c r="B71" s="4"/>
-      <c r="C71" s="9"/>
-      <c r="D71" s="9"/>
-      <c r="E71" s="4"/>
-      <c r="F71" s="4"/>
-    </row>
-    <row r="72" spans="1:6">
-      <c r="A72" s="9"/>
-      <c r="B72" s="4"/>
-      <c r="C72" s="9"/>
-      <c r="D72" s="9"/>
-      <c r="E72" s="4"/>
-      <c r="F72" s="4"/>
-    </row>
-    <row r="73" spans="1:6">
-      <c r="A73" s="9"/>
-      <c r="B73" s="4"/>
-      <c r="C73" s="9"/>
-      <c r="D73" s="9"/>
-      <c r="E73" s="4"/>
-      <c r="F73" s="4"/>
-    </row>
-    <row r="74" spans="1:6">
-      <c r="A74" s="9"/>
-      <c r="B74" s="4"/>
-      <c r="C74" s="9"/>
-      <c r="D74" s="9"/>
-      <c r="E74" s="4"/>
-      <c r="F74" s="4"/>
+      <c r="E73" s="45"/>
+      <c r="F73" s="45"/>
+    </row>
+    <row r="74" spans="1:6" s="43" customFormat="1">
+      <c r="A74" s="41"/>
+      <c r="B74" s="42"/>
+      <c r="C74" s="41"/>
+      <c r="D74" s="41"/>
+      <c r="E74" s="42"/>
+      <c r="F74" s="42"/>
+    </row>
+    <row r="75" spans="1:6">
+      <c r="A75" s="9"/>
+      <c r="B75" s="4"/>
+      <c r="C75" s="9"/>
+      <c r="D75" s="9"/>
+      <c r="E75" s="4"/>
+      <c r="F75" s="4"/>
+    </row>
+    <row r="76" spans="1:6">
+      <c r="A76" s="9"/>
+      <c r="B76" s="4"/>
+      <c r="C76" s="9"/>
+      <c r="D76" s="9"/>
+      <c r="E76" s="4"/>
+      <c r="F76" s="4"/>
+    </row>
+    <row r="77" spans="1:6">
+      <c r="A77" s="9"/>
+      <c r="B77" s="4"/>
+      <c r="C77" s="9"/>
+      <c r="D77" s="9"/>
+      <c r="E77" s="4"/>
+      <c r="F77" s="4"/>
+    </row>
+    <row r="78" spans="1:6">
+      <c r="A78" s="9"/>
+      <c r="B78" s="4"/>
+      <c r="C78" s="9"/>
+      <c r="D78" s="9"/>
+      <c r="E78" s="4"/>
+      <c r="F78" s="4"/>
+    </row>
+    <row r="79" spans="1:6">
+      <c r="A79" s="9"/>
+      <c r="B79" s="4"/>
+      <c r="C79" s="9"/>
+      <c r="D79" s="9"/>
+      <c r="E79" s="4"/>
+      <c r="F79" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -4677,7 +4764,7 @@
         <v>226</v>
       </c>
       <c r="D1" s="26" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="E1" s="26" t="s">
         <v>51</v>
@@ -4688,7 +4775,7 @@
         <v>231</v>
       </c>
       <c r="B2" s="29" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="C2" s="28" t="s">
         <v>229</v>
@@ -4709,19 +4796,19 @@
     </row>
     <row r="4" spans="1:5" ht="27">
       <c r="A4" s="29" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="B4" s="29" t="s">
         <v>44</v>
       </c>
       <c r="C4" s="28" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="D4" s="28" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="E4" s="30" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -4745,11 +4832,17 @@
       <c r="D7" s="28"/>
       <c r="E7" s="28"/>
     </row>
-    <row r="8" spans="1:5">
-      <c r="A8" s="29"/>
+    <row r="8" spans="1:5" ht="108">
+      <c r="A8" s="29" t="s">
+        <v>312</v>
+      </c>
       <c r="B8" s="29"/>
-      <c r="C8" s="28"/>
-      <c r="D8" s="28"/>
+      <c r="C8" s="28" t="s">
+        <v>320</v>
+      </c>
+      <c r="D8" s="28" t="s">
+        <v>319</v>
+      </c>
       <c r="E8" s="28"/>
     </row>
     <row r="9" spans="1:5">
@@ -4876,160 +4969,160 @@
   <sheetData>
     <row r="1" spans="1:4" ht="27">
       <c r="A1" s="23" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="27">
       <c r="A2" s="23" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="26" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="B4" s="26" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="C4" s="26"/>
       <c r="D4" s="26"/>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="31" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="B5" s="27" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="C5" s="27"/>
       <c r="D5" s="27"/>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="31" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="B6" s="27" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="C6" s="27"/>
       <c r="D6" s="27"/>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="31" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="B7" s="27" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="C7" s="27"/>
       <c r="D7" s="27"/>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="31" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="B8" s="27" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="C8" s="27"/>
       <c r="D8" s="27"/>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="31" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="B9" s="27" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="C9" s="27"/>
       <c r="D9" s="27"/>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="31" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="B10" s="27" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="C10" s="27"/>
       <c r="D10" s="27"/>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="31" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="B11" s="27" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="C11" s="27"/>
       <c r="D11" s="27"/>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="31" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="B12" s="27" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="C12" s="27"/>
       <c r="D12" s="27"/>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="31" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="B13" s="27" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="C13" s="27"/>
       <c r="D13" s="27"/>
     </row>
     <row r="14" spans="1:4" ht="27">
       <c r="A14" s="31" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="B14" s="27" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="C14" s="27"/>
       <c r="D14" s="27"/>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="32" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="B15" s="33" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="C15" s="33"/>
       <c r="D15" s="33"/>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="34" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="B16" s="33" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="C16" s="33"/>
       <c r="D16" s="33"/>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="34" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="B17" s="33" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="C17" s="33"/>
       <c r="D17" s="33"/>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="34" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="B18" s="33" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="C18" s="33"/>
       <c r="D18" s="33"/>

--- a/internal_doc/03.开发设计/OM_web接口.xlsx
+++ b/internal_doc/03.开发设计/OM_web接口.xlsx
@@ -1604,14 +1604,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>HostInfo={[{HostName:"h1"}, {HostName:"h2"}]}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>http://192.168.20.197:11814/?cmd=query host status&amp;HostInfo={[{HostName:"h1"}, {HostName:"h2"}]}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>{HostInfo:[{HostName:aa, "CPU":"90%", "Memory": { "Model": "", "Size": 2003, "Free": 916, "Unit": "M" }, "Disk":[{ "Name"
 : "/dev/sda1", "Mount": "/", "Size": 32529, "Free": 6525, "Unit": "M", "Used": 1 }]}, {...}, ...]}</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1624,6 +1616,14 @@
   <si>
     <t>{"HostInfo":[{HostName:aa, "User":"root", "Passwd"sequoiadb", "Disk":[{ "Name"
 : "/dev/sda1", "Mount": "/"}]}, {...}, ...]}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://192.168.20.197:11814/?cmd=query host status&amp;HostInfo={HostInfo:[{HostName:"rhelt10"}]}'</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>HostInfo={HostInfo:[{HostName:"rhelt10"}]}'</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -4024,10 +4024,10 @@
         <v>313</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" s="2"/>
@@ -4038,7 +4038,7 @@
       </c>
       <c r="B22" s="2"/>
       <c r="C22" s="5" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="D22" s="5"/>
       <c r="E22" s="2"/>
@@ -4838,10 +4838,10 @@
       </c>
       <c r="B8" s="29"/>
       <c r="C8" s="28" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="D8" s="28" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="E8" s="28"/>
     </row>

--- a/internal_doc/03.开发设计/OM_web接口.xlsx
+++ b/internal_doc/03.开发设计/OM_web接口.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="6510" activeTab="3"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="6510" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="需求" sheetId="1" r:id="rId1"/>
@@ -281,7 +281,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="321">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="325">
   <si>
     <t>需求</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1309,10 +1309,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>删除host命令</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>update hostname</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1624,6 +1620,26 @@
   </si>
   <si>
     <t>HostInfo={HostInfo:[{HostName:"rhelt10"}]}'</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>删除host命令</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>删除业务</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>remove business</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"AuthUser":"","AuthPasswd":"","Config":[{"datagroupname":"","dbpath":"/home/mount/testdata/coord/11820","svcname":"11820","diaglevel":"3","role":"coord","logfilesz":"64","logfilenum":"20","transactionon":"false","preferedinstance":"A","numpagecleaners":"1","pagecleaninterval":"1000","hjbuf":"128","logbuffsize":"1024","maxprefpool":"200","maxreplsync":"10","numpreload":"0","sortbuf":"512","syncstrategy":"none","HostName":"rhelt10","User":"root","Passwd":"sequoiadb"}, ...]}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{Rc，0}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3780,7 +3796,7 @@
         <v>133</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D2" s="5" t="s">
         <v>1</v>
@@ -3810,10 +3826,10 @@
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="9" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="E4" s="4"/>
       <c r="F4" s="4"/>
@@ -3851,7 +3867,7 @@
         <v>212</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E7" s="4"/>
       <c r="F7" s="4"/>
@@ -3882,11 +3898,11 @@
     </row>
     <row r="10" spans="1:6" s="39" customFormat="1">
       <c r="A10" s="37" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B10" s="38"/>
       <c r="C10" s="37" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D10" s="37"/>
       <c r="E10" s="38"/>
@@ -3922,10 +3938,10 @@
       </c>
       <c r="B13" s="4"/>
       <c r="C13" s="9" t="s">
+        <v>293</v>
+      </c>
+      <c r="D13" s="9" t="s">
         <v>294</v>
-      </c>
-      <c r="D13" s="9" t="s">
-        <v>295</v>
       </c>
       <c r="E13" s="4"/>
       <c r="F13" s="4"/>
@@ -3962,7 +3978,7 @@
       </c>
       <c r="B16" s="4"/>
       <c r="C16" s="9" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="D16" s="9" t="s">
         <v>238</v>
@@ -3988,7 +4004,7 @@
         <v>194</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="D18" s="9" t="s">
         <v>240</v>
@@ -4002,7 +4018,7 @@
       </c>
       <c r="B19" s="4"/>
       <c r="C19" s="9" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D19" s="9"/>
       <c r="E19" s="4"/>
@@ -4018,27 +4034,27 @@
     </row>
     <row r="21" spans="1:6" s="40" customFormat="1" ht="24">
       <c r="A21" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="B21" s="2" t="s">
         <v>312</v>
       </c>
-      <c r="B21" s="2" t="s">
-        <v>313</v>
-      </c>
       <c r="C21" s="5" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" s="2"/>
     </row>
     <row r="22" spans="1:6" s="40" customFormat="1" ht="60">
       <c r="A22" s="5" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B22" s="2"/>
       <c r="C22" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="D22" s="5"/>
       <c r="E22" s="2"/>
@@ -4056,27 +4072,27 @@
     </row>
     <row r="24" spans="1:6" s="40" customFormat="1">
       <c r="A24" s="5" t="s">
+        <v>276</v>
+      </c>
+      <c r="B24" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="B24" s="2" t="s">
-        <v>278</v>
-      </c>
       <c r="C24" s="5" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" s="2"/>
     </row>
     <row r="25" spans="1:6" s="40" customFormat="1">
       <c r="A25" s="5" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B25" s="2"/>
       <c r="C25" s="5" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="D25" s="5"/>
       <c r="E25" s="2"/>
@@ -4098,10 +4114,10 @@
         <v>195</v>
       </c>
       <c r="C27" s="5" t="s">
+        <v>274</v>
+      </c>
+      <c r="D27" s="5" t="s">
         <v>275</v>
-      </c>
-      <c r="D27" s="5" t="s">
-        <v>276</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" s="2"/>
@@ -4112,7 +4128,7 @@
       </c>
       <c r="B28" s="2"/>
       <c r="C28" s="5" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="D28" s="5"/>
       <c r="E28" s="2"/>
@@ -4128,10 +4144,10 @@
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="9" t="s">
+        <v>305</v>
+      </c>
+      <c r="B30" s="4" t="s">
         <v>306</v>
-      </c>
-      <c r="B30" s="4" t="s">
-        <v>307</v>
       </c>
       <c r="C30" s="9"/>
       <c r="D30" s="9"/>
@@ -4179,7 +4195,7 @@
         <v>206</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E34" s="4"/>
       <c r="F34" s="4"/>
@@ -4219,7 +4235,7 @@
         <v>184</v>
       </c>
       <c r="D37" s="9" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="E37" s="4"/>
       <c r="F37" s="4"/>
@@ -4285,7 +4301,7 @@
         <v>187</v>
       </c>
       <c r="D42" s="9" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="E42" s="4"/>
       <c r="F42" s="4"/>
@@ -4296,7 +4312,7 @@
       </c>
       <c r="B43" s="4"/>
       <c r="C43" s="9" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D43" s="9" t="s">
         <v>120</v>
@@ -4314,27 +4330,27 @@
     </row>
     <row r="45" spans="1:6" s="40" customFormat="1">
       <c r="A45" s="5" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B45" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="C45" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="D45" s="5" t="s">
         <v>285</v>
-      </c>
-      <c r="C45" s="5" t="s">
-        <v>282</v>
-      </c>
-      <c r="D45" s="5" t="s">
-        <v>286</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" s="2"/>
     </row>
     <row r="46" spans="1:6" s="40" customFormat="1">
       <c r="A46" s="5" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B46" s="2"/>
       <c r="C46" s="5" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D46" s="5"/>
       <c r="E46" s="2"/>
@@ -4350,7 +4366,7 @@
     </row>
     <row r="48" spans="1:6" s="40" customFormat="1">
       <c r="A48" s="5" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>232</v>
@@ -4366,7 +4382,7 @@
     </row>
     <row r="49" spans="1:6" s="40" customFormat="1">
       <c r="A49" s="5" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B49" s="2"/>
       <c r="C49" s="5"/>
@@ -4390,10 +4406,10 @@
         <v>144</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" s="2"/>
@@ -4404,7 +4420,7 @@
       </c>
       <c r="B52" s="2"/>
       <c r="C52" s="5" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D52" s="5"/>
       <c r="E52" s="2"/>
@@ -4448,7 +4464,7 @@
       </c>
       <c r="B56" s="4"/>
       <c r="C56" s="9" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D56" s="9"/>
       <c r="E56" s="4"/>
@@ -4492,7 +4508,7 @@
       </c>
       <c r="B61" s="4"/>
       <c r="C61" s="9" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D61" s="9" t="s">
         <v>151</v>
@@ -4530,7 +4546,7 @@
       </c>
       <c r="B64" s="4"/>
       <c r="C64" s="9" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="D64" s="9"/>
       <c r="E64" s="4"/>
@@ -4578,7 +4594,7 @@
       </c>
       <c r="B68" s="42"/>
       <c r="C68" s="41" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D68" s="41"/>
       <c r="E68" s="42"/>
@@ -4590,7 +4606,7 @@
       </c>
       <c r="B69" s="42"/>
       <c r="C69" s="41" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="D69" s="41" t="s">
         <v>146</v>
@@ -4743,7 +4759,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="34.25" customWidth="1"/>
@@ -4764,7 +4780,7 @@
         <v>226</v>
       </c>
       <c r="D1" s="26" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="E1" s="26" t="s">
         <v>51</v>
@@ -4775,7 +4791,7 @@
         <v>231</v>
       </c>
       <c r="B2" s="29" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C2" s="28" t="s">
         <v>229</v>
@@ -4796,19 +4812,19 @@
     </row>
     <row r="4" spans="1:5" ht="27">
       <c r="A4" s="29" t="s">
-        <v>241</v>
+        <v>320</v>
       </c>
       <c r="B4" s="29" t="s">
         <v>44</v>
       </c>
       <c r="C4" s="28" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D4" s="28" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E4" s="30" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -4816,13 +4832,21 @@
       <c r="B5" s="29"/>
       <c r="C5" s="28"/>
       <c r="D5" s="28"/>
-      <c r="E5" s="28"/>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" s="29"/>
-      <c r="B6" s="29"/>
-      <c r="C6" s="28"/>
-      <c r="D6" s="28"/>
+      <c r="E5" s="30"/>
+    </row>
+    <row r="6" spans="1:5" ht="162">
+      <c r="A6" s="29" t="s">
+        <v>321</v>
+      </c>
+      <c r="B6" s="29" t="s">
+        <v>322</v>
+      </c>
+      <c r="C6" s="28" t="s">
+        <v>323</v>
+      </c>
+      <c r="D6" s="28" t="s">
+        <v>324</v>
+      </c>
       <c r="E6" s="28"/>
     </row>
     <row r="7" spans="1:5">
@@ -4832,24 +4856,24 @@
       <c r="D7" s="28"/>
       <c r="E7" s="28"/>
     </row>
-    <row r="8" spans="1:5" ht="108">
-      <c r="A8" s="29" t="s">
-        <v>312</v>
-      </c>
+    <row r="8" spans="1:5">
+      <c r="A8" s="29"/>
       <c r="B8" s="29"/>
-      <c r="C8" s="28" t="s">
-        <v>318</v>
-      </c>
-      <c r="D8" s="28" t="s">
+      <c r="C8" s="28"/>
+      <c r="D8" s="28"/>
+      <c r="E8" s="28"/>
+    </row>
+    <row r="9" spans="1:5" ht="108">
+      <c r="A9" s="29" t="s">
+        <v>311</v>
+      </c>
+      <c r="B9" s="29"/>
+      <c r="C9" s="28" t="s">
         <v>317</v>
       </c>
-      <c r="E8" s="28"/>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9" s="29"/>
-      <c r="B9" s="29"/>
-      <c r="C9" s="28"/>
-      <c r="D9" s="28"/>
+      <c r="D9" s="28" t="s">
+        <v>316</v>
+      </c>
       <c r="E9" s="28"/>
     </row>
     <row r="10" spans="1:5">
@@ -4949,6 +4973,13 @@
       <c r="C23" s="28"/>
       <c r="D23" s="28"/>
       <c r="E23" s="28"/>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="29"/>
+      <c r="B24" s="29"/>
+      <c r="C24" s="28"/>
+      <c r="D24" s="28"/>
+      <c r="E24" s="28"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -4969,160 +5000,160 @@
   <sheetData>
     <row r="1" spans="1:4" ht="27">
       <c r="A1" s="23" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="27">
       <c r="A2" s="23" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="26" t="s">
+        <v>265</v>
+      </c>
+      <c r="B4" s="26" t="s">
         <v>266</v>
-      </c>
-      <c r="B4" s="26" t="s">
-        <v>267</v>
       </c>
       <c r="C4" s="26"/>
       <c r="D4" s="26"/>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="31" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B5" s="27" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C5" s="27"/>
       <c r="D5" s="27"/>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="31" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B6" s="27" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C6" s="27"/>
       <c r="D6" s="27"/>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="31" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B7" s="27" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C7" s="27"/>
       <c r="D7" s="27"/>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="31" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B8" s="27" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C8" s="27"/>
       <c r="D8" s="27"/>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="31" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B9" s="27" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C9" s="27"/>
       <c r="D9" s="27"/>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="31" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B10" s="27" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C10" s="27"/>
       <c r="D10" s="27"/>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="31" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B11" s="27" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C11" s="27"/>
       <c r="D11" s="27"/>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="31" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B12" s="27" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C12" s="27"/>
       <c r="D12" s="27"/>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="31" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B13" s="27" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C13" s="27"/>
       <c r="D13" s="27"/>
     </row>
     <row r="14" spans="1:4" ht="27">
       <c r="A14" s="31" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B14" s="27" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C14" s="27"/>
       <c r="D14" s="27"/>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="32" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B15" s="33" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C15" s="33"/>
       <c r="D15" s="33"/>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="34" t="s">
+        <v>257</v>
+      </c>
+      <c r="B16" s="33" t="s">
         <v>258</v>
-      </c>
-      <c r="B16" s="33" t="s">
-        <v>259</v>
       </c>
       <c r="C16" s="33"/>
       <c r="D16" s="33"/>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="34" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B17" s="33" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C17" s="33"/>
       <c r="D17" s="33"/>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="34" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B18" s="33" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C18" s="33"/>
       <c r="D18" s="33"/>

--- a/internal_doc/03.开发设计/OM_web接口.xlsx
+++ b/internal_doc/03.开发设计/OM_web接口.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="6510" activeTab="5"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="6510" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="需求" sheetId="1" r:id="rId1"/>
@@ -281,7 +281,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="325">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="326">
   <si>
     <t>需求</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1277,10 +1277,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>http://192.168.20.197:11814/?cmd=query business&amp;ClusterName=cl</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>删除集群</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1475,10 +1471,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>ClusterName=c1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>ClusterName=c1(or BusinessName=b1)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1568,14 +1560,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>查询集群下所有business</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>查询集群下所有business响应</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>查询业务</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1640,6 +1624,26 @@
   </si>
   <si>
     <t>{Rc，0}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>查询已安装business响应</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>查询已安装business</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ClusterName=c1（或者HostName=rhlet10）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BusinessName=cl</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://192.168.20.197:11814/?cmd=query business&amp;BusinessName=cl</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3796,7 +3800,7 @@
         <v>133</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="D2" s="5" t="s">
         <v>1</v>
@@ -3826,10 +3830,10 @@
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="9" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="E4" s="4"/>
       <c r="F4" s="4"/>
@@ -3867,7 +3871,7 @@
         <v>212</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="E7" s="4"/>
       <c r="F7" s="4"/>
@@ -3882,27 +3886,27 @@
     </row>
     <row r="9" spans="1:6" s="39" customFormat="1">
       <c r="A9" s="37" t="s">
+        <v>234</v>
+      </c>
+      <c r="B9" s="38" t="s">
         <v>235</v>
-      </c>
-      <c r="B9" s="38" t="s">
-        <v>236</v>
       </c>
       <c r="C9" s="37" t="s">
         <v>233</v>
       </c>
       <c r="D9" s="37" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E9" s="38"/>
       <c r="F9" s="38"/>
     </row>
     <row r="10" spans="1:6" s="39" customFormat="1">
       <c r="A10" s="37" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="B10" s="38"/>
       <c r="C10" s="37" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="D10" s="37"/>
       <c r="E10" s="38"/>
@@ -3938,10 +3942,10 @@
       </c>
       <c r="B13" s="4"/>
       <c r="C13" s="9" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="E13" s="4"/>
       <c r="F13" s="4"/>
@@ -3967,7 +3971,7 @@
         <v>183</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E15" s="4"/>
       <c r="F15" s="4"/>
@@ -3978,10 +3982,10 @@
       </c>
       <c r="B16" s="4"/>
       <c r="C16" s="9" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E16" s="4"/>
       <c r="F16" s="4"/>
@@ -4004,10 +4008,10 @@
         <v>194</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E18" s="4"/>
       <c r="F18" s="4"/>
@@ -4018,7 +4022,7 @@
       </c>
       <c r="B19" s="4"/>
       <c r="C19" s="9" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="D19" s="9"/>
       <c r="E19" s="4"/>
@@ -4034,27 +4038,27 @@
     </row>
     <row r="21" spans="1:6" s="40" customFormat="1" ht="24">
       <c r="A21" s="5" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" s="2"/>
     </row>
     <row r="22" spans="1:6" s="40" customFormat="1" ht="60">
       <c r="A22" s="5" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="B22" s="2"/>
       <c r="C22" s="5" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="D22" s="5"/>
       <c r="E22" s="2"/>
@@ -4072,27 +4076,27 @@
     </row>
     <row r="24" spans="1:6" s="40" customFormat="1">
       <c r="A24" s="5" t="s">
+        <v>275</v>
+      </c>
+      <c r="B24" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="B24" s="2" t="s">
-        <v>277</v>
-      </c>
       <c r="C24" s="5" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" s="2"/>
     </row>
     <row r="25" spans="1:6" s="40" customFormat="1">
       <c r="A25" s="5" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B25" s="2"/>
       <c r="C25" s="5" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D25" s="5"/>
       <c r="E25" s="2"/>
@@ -4114,10 +4118,10 @@
         <v>195</v>
       </c>
       <c r="C27" s="5" t="s">
+        <v>273</v>
+      </c>
+      <c r="D27" s="5" t="s">
         <v>274</v>
-      </c>
-      <c r="D27" s="5" t="s">
-        <v>275</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" s="2"/>
@@ -4128,7 +4132,7 @@
       </c>
       <c r="B28" s="2"/>
       <c r="C28" s="5" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="D28" s="5"/>
       <c r="E28" s="2"/>
@@ -4144,10 +4148,10 @@
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="9" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="C30" s="9"/>
       <c r="D30" s="9"/>
@@ -4195,7 +4199,7 @@
         <v>206</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="E34" s="4"/>
       <c r="F34" s="4"/>
@@ -4235,7 +4239,7 @@
         <v>184</v>
       </c>
       <c r="D37" s="9" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="E37" s="4"/>
       <c r="F37" s="4"/>
@@ -4301,7 +4305,7 @@
         <v>187</v>
       </c>
       <c r="D42" s="9" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="E42" s="4"/>
       <c r="F42" s="4"/>
@@ -4312,7 +4316,7 @@
       </c>
       <c r="B43" s="4"/>
       <c r="C43" s="9" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="D43" s="9" t="s">
         <v>120</v>
@@ -4330,27 +4334,27 @@
     </row>
     <row r="45" spans="1:6" s="40" customFormat="1">
       <c r="A45" s="5" t="s">
-        <v>307</v>
+        <v>322</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>281</v>
+        <v>323</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" s="2"/>
     </row>
     <row r="46" spans="1:6" s="40" customFormat="1">
       <c r="A46" s="5" t="s">
-        <v>308</v>
+        <v>321</v>
       </c>
       <c r="B46" s="2"/>
       <c r="C46" s="5" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="D46" s="5"/>
       <c r="E46" s="2"/>
@@ -4366,23 +4370,23 @@
     </row>
     <row r="48" spans="1:6" s="40" customFormat="1">
       <c r="A48" s="5" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>232</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>233</v>
+        <v>324</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>234</v>
+        <v>325</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" s="2"/>
     </row>
     <row r="49" spans="1:6" s="40" customFormat="1">
       <c r="A49" s="5" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="B49" s="2"/>
       <c r="C49" s="5"/>
@@ -4406,10 +4410,10 @@
         <v>144</v>
       </c>
       <c r="C51" s="5" t="s">
+        <v>285</v>
+      </c>
+      <c r="D51" s="5" t="s">
         <v>287</v>
-      </c>
-      <c r="D51" s="5" t="s">
-        <v>289</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" s="2"/>
@@ -4420,7 +4424,7 @@
       </c>
       <c r="B52" s="2"/>
       <c r="C52" s="5" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="D52" s="5"/>
       <c r="E52" s="2"/>
@@ -4464,7 +4468,7 @@
       </c>
       <c r="B56" s="4"/>
       <c r="C56" s="9" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="D56" s="9"/>
       <c r="E56" s="4"/>
@@ -4508,7 +4512,7 @@
       </c>
       <c r="B61" s="4"/>
       <c r="C61" s="9" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="D61" s="9" t="s">
         <v>151</v>
@@ -4546,7 +4550,7 @@
       </c>
       <c r="B64" s="4"/>
       <c r="C64" s="9" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="D64" s="9"/>
       <c r="E64" s="4"/>
@@ -4594,7 +4598,7 @@
       </c>
       <c r="B68" s="42"/>
       <c r="C68" s="41" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="D68" s="41"/>
       <c r="E68" s="42"/>
@@ -4606,7 +4610,7 @@
       </c>
       <c r="B69" s="42"/>
       <c r="C69" s="41" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="D69" s="41" t="s">
         <v>146</v>
@@ -4780,7 +4784,7 @@
         <v>226</v>
       </c>
       <c r="D1" s="26" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E1" s="26" t="s">
         <v>51</v>
@@ -4791,7 +4795,7 @@
         <v>231</v>
       </c>
       <c r="B2" s="29" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C2" s="28" t="s">
         <v>229</v>
@@ -4812,19 +4816,19 @@
     </row>
     <row r="4" spans="1:5" ht="27">
       <c r="A4" s="29" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="B4" s="29" t="s">
         <v>44</v>
       </c>
       <c r="C4" s="28" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D4" s="28" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E4" s="30" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -4836,16 +4840,16 @@
     </row>
     <row r="6" spans="1:5" ht="162">
       <c r="A6" s="29" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="B6" s="29" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="C6" s="28" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="D6" s="28" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="E6" s="28"/>
     </row>
@@ -4865,14 +4869,14 @@
     </row>
     <row r="9" spans="1:5" ht="108">
       <c r="A9" s="29" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="B9" s="29"/>
       <c r="C9" s="28" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="D9" s="28" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="E9" s="28"/>
     </row>
@@ -5000,160 +5004,160 @@
   <sheetData>
     <row r="1" spans="1:4" ht="27">
       <c r="A1" s="23" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="27">
       <c r="A2" s="23" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="26" t="s">
+        <v>264</v>
+      </c>
+      <c r="B4" s="26" t="s">
         <v>265</v>
-      </c>
-      <c r="B4" s="26" t="s">
-        <v>266</v>
       </c>
       <c r="C4" s="26"/>
       <c r="D4" s="26"/>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="31" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B5" s="27" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C5" s="27"/>
       <c r="D5" s="27"/>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="31" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B6" s="27" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C6" s="27"/>
       <c r="D6" s="27"/>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="31" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B7" s="27" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C7" s="27"/>
       <c r="D7" s="27"/>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="31" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B8" s="27" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C8" s="27"/>
       <c r="D8" s="27"/>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="31" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B9" s="27" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C9" s="27"/>
       <c r="D9" s="27"/>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="31" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B10" s="27" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C10" s="27"/>
       <c r="D10" s="27"/>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="31" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B11" s="27" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C11" s="27"/>
       <c r="D11" s="27"/>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="31" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B12" s="27" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C12" s="27"/>
       <c r="D12" s="27"/>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="31" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B13" s="27" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C13" s="27"/>
       <c r="D13" s="27"/>
     </row>
     <row r="14" spans="1:4" ht="27">
       <c r="A14" s="31" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B14" s="27" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C14" s="27"/>
       <c r="D14" s="27"/>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="32" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B15" s="33" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C15" s="33"/>
       <c r="D15" s="33"/>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="34" t="s">
+        <v>256</v>
+      </c>
+      <c r="B16" s="33" t="s">
         <v>257</v>
-      </c>
-      <c r="B16" s="33" t="s">
-        <v>258</v>
       </c>
       <c r="C16" s="33"/>
       <c r="D16" s="33"/>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="34" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B17" s="33" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C17" s="33"/>
       <c r="D17" s="33"/>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="34" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B18" s="33" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C18" s="33"/>
       <c r="D18" s="33"/>

--- a/internal_doc/03.开发设计/OM_web接口.xlsx
+++ b/internal_doc/03.开发设计/OM_web接口.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="6510" activeTab="3"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="6510" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="需求" sheetId="1" r:id="rId1"/>
@@ -281,7 +281,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="326">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="331">
   <si>
     <t>需求</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1644,6 +1644,26 @@
   </si>
   <si>
     <t>http://192.168.20.197:11814/?cmd=query business&amp;BusinessName=cl</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>agent查询task请求</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>query task</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Agent-&gt;OM</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{HostName:"",AgentPort:""}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{TaskType:"add business",TaskID:1, TaskStatus:"install", TaskDetail:{{"BusinessType":"sequoiadb","BusinessName":"b1", "DeployMod":"xx", "ClusterName":"c1", "Config":[{"HostName": "host1", "User":"root", "Passwd":"root", "datagroupname": "", "dbpath": "/home/db2/standalone/11830", "svcname": "11830", ...}]}}}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -4763,13 +4783,13 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E24"/>
+  <dimension ref="A1:E25"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="34.25" customWidth="1"/>
     <col min="2" max="2" width="17.25" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="44.25" style="23" customWidth="1"/>
-    <col min="4" max="4" width="30.5" style="23" customWidth="1"/>
+    <col min="4" max="4" width="42.375" style="23" customWidth="1"/>
     <col min="5" max="5" width="37.375" style="23" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4895,17 +4915,35 @@
       <c r="E11" s="28"/>
     </row>
     <row r="12" spans="1:5">
-      <c r="A12" s="29"/>
-      <c r="B12" s="29"/>
-      <c r="C12" s="28"/>
-      <c r="D12" s="28"/>
-      <c r="E12" s="28"/>
-    </row>
-    <row r="13" spans="1:5">
-      <c r="A13" s="29"/>
-      <c r="B13" s="29"/>
-      <c r="C13" s="28"/>
-      <c r="D13" s="28"/>
+      <c r="A12" s="25" t="s">
+        <v>328</v>
+      </c>
+      <c r="B12" s="25" t="s">
+        <v>225</v>
+      </c>
+      <c r="C12" s="26" t="s">
+        <v>226</v>
+      </c>
+      <c r="D12" s="26" t="s">
+        <v>242</v>
+      </c>
+      <c r="E12" s="26" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="135">
+      <c r="A13" s="29" t="s">
+        <v>326</v>
+      </c>
+      <c r="B13" s="29" t="s">
+        <v>327</v>
+      </c>
+      <c r="C13" s="28" t="s">
+        <v>329</v>
+      </c>
+      <c r="D13" s="28" t="s">
+        <v>330</v>
+      </c>
       <c r="E13" s="28"/>
     </row>
     <row r="14" spans="1:5">
@@ -4984,6 +5022,13 @@
       <c r="C24" s="28"/>
       <c r="D24" s="28"/>
       <c r="E24" s="28"/>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="29"/>
+      <c r="B25" s="29"/>
+      <c r="C25" s="28"/>
+      <c r="D25" s="28"/>
+      <c r="E25" s="28"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/internal_doc/03.开发设计/OM_web接口.xlsx
+++ b/internal_doc/03.开发设计/OM_web接口.xlsx
@@ -4,16 +4,15 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="6510" activeTab="5"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="6510" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="需求" sheetId="1" r:id="rId1"/>
     <sheet name="问题确认" sheetId="2" r:id="rId2"/>
     <sheet name="表结构设计" sheetId="3" r:id="rId3"/>
     <sheet name="消息定义" sheetId="4" r:id="rId4"/>
-    <sheet name="Sheet1" sheetId="5" r:id="rId5"/>
-    <sheet name="agent接口" sheetId="6" r:id="rId6"/>
-    <sheet name="Sheet3" sheetId="7" r:id="rId7"/>
+    <sheet name="agent接口" sheetId="6" r:id="rId5"/>
+    <sheet name="Sheet3" sheetId="7" r:id="rId6"/>
   </sheets>
   <calcPr calcId="124519"/>
 </workbook>
@@ -281,7 +280,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="331">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="327">
   <si>
     <t>需求</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -811,14 +810,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>INT32 catMainController::_ensureMetadata()</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>创建cs, cl</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t/>
   </si>
   <si>
@@ -961,14 +952,6 @@
   </si>
   <si>
     <t>cmd=xxx</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>msgBuildQueryMsg( &amp;pContent, &amp;contentSize, OM_BASIC_CHECK_REQ, 0, 0, 0, -1, &amp;bsonRequest, NULL, NULL, NULL )</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>pContent在什么情况下可以释放</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1671,7 +1654,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="20">
+  <fonts count="19">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1767,14 +1750,6 @@
       <color theme="2" tint="-0.499984740745262"/>
       <name val="宋体"/>
       <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -1906,13 +1881,10 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1967,7 +1939,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1979,30 +1950,30 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2032,9 +2003,8 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Warning Text" xfId="1" builtinId="11"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -2442,7 +2412,7 @@
       </c>
     </row>
     <row r="3" spans="1:8">
-      <c r="A3" s="46" t="s">
+      <c r="A3" s="45" t="s">
         <v>12</v>
       </c>
       <c r="B3" s="4" t="s">
@@ -2460,7 +2430,7 @@
       <c r="H3" s="4"/>
     </row>
     <row r="4" spans="1:8" ht="13.5">
-      <c r="A4" s="47"/>
+      <c r="A4" s="46"/>
       <c r="B4" s="4" t="s">
         <v>5</v>
       </c>
@@ -2476,7 +2446,7 @@
       <c r="H4" s="4"/>
     </row>
     <row r="5" spans="1:8" ht="13.5">
-      <c r="A5" s="47"/>
+      <c r="A5" s="46"/>
       <c r="B5" s="4" t="s">
         <v>8</v>
       </c>
@@ -2492,7 +2462,7 @@
       <c r="H5" s="4"/>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" s="48"/>
+      <c r="A6" s="47"/>
       <c r="B6" s="4" t="s">
         <v>13</v>
       </c>
@@ -2508,7 +2478,7 @@
       <c r="H6" s="4"/>
     </row>
     <row r="7" spans="1:8" ht="24">
-      <c r="A7" s="49" t="s">
+      <c r="A7" s="48" t="s">
         <v>24</v>
       </c>
       <c r="B7" s="4" t="s">
@@ -2526,7 +2496,7 @@
       <c r="H7" s="4"/>
     </row>
     <row r="8" spans="1:8" ht="36">
-      <c r="A8" s="50"/>
+      <c r="A8" s="49"/>
       <c r="B8" s="4" t="s">
         <v>17</v>
       </c>
@@ -2544,7 +2514,7 @@
       <c r="H8" s="4"/>
     </row>
     <row r="9" spans="1:8" ht="72">
-      <c r="A9" s="50"/>
+      <c r="A9" s="49"/>
       <c r="B9" s="4" t="s">
         <v>18</v>
       </c>
@@ -2562,7 +2532,7 @@
       <c r="H9" s="4"/>
     </row>
     <row r="10" spans="1:8" ht="24">
-      <c r="A10" s="51"/>
+      <c r="A10" s="50"/>
       <c r="B10" s="4" t="s">
         <v>21</v>
       </c>
@@ -2600,7 +2570,7 @@
       <c r="H11" s="4"/>
     </row>
     <row r="12" spans="1:8" ht="24">
-      <c r="A12" s="49" t="s">
+      <c r="A12" s="48" t="s">
         <v>26</v>
       </c>
       <c r="B12" s="4" t="s">
@@ -2618,7 +2588,7 @@
       <c r="H12" s="4"/>
     </row>
     <row r="13" spans="1:8">
-      <c r="A13" s="50"/>
+      <c r="A13" s="49"/>
       <c r="B13" s="4" t="s">
         <v>32</v>
       </c>
@@ -2634,7 +2604,7 @@
       <c r="H13" s="4"/>
     </row>
     <row r="14" spans="1:8" ht="24">
-      <c r="A14" s="50"/>
+      <c r="A14" s="49"/>
       <c r="B14" s="4" t="s">
         <v>33</v>
       </c>
@@ -2652,7 +2622,7 @@
       <c r="H14" s="4"/>
     </row>
     <row r="15" spans="1:8">
-      <c r="A15" s="50"/>
+      <c r="A15" s="49"/>
       <c r="B15" s="4" t="s">
         <v>35</v>
       </c>
@@ -2668,7 +2638,7 @@
       <c r="H15" s="4"/>
     </row>
     <row r="16" spans="1:8">
-      <c r="A16" s="50"/>
+      <c r="A16" s="49"/>
       <c r="B16" s="4" t="s">
         <v>57</v>
       </c>
@@ -2680,7 +2650,7 @@
       <c r="H16" s="4"/>
     </row>
     <row r="17" spans="1:8" ht="48">
-      <c r="A17" s="50"/>
+      <c r="A17" s="49"/>
       <c r="B17" s="4" t="s">
         <v>30</v>
       </c>
@@ -2698,7 +2668,7 @@
       <c r="H17" s="4"/>
     </row>
     <row r="18" spans="1:8">
-      <c r="A18" s="50"/>
+      <c r="A18" s="49"/>
       <c r="B18" s="4" t="s">
         <v>38</v>
       </c>
@@ -2714,7 +2684,7 @@
       <c r="H18" s="4"/>
     </row>
     <row r="19" spans="1:8">
-      <c r="A19" s="50"/>
+      <c r="A19" s="49"/>
       <c r="B19" s="4" t="s">
         <v>41</v>
       </c>
@@ -2730,7 +2700,7 @@
       <c r="H19" s="4"/>
     </row>
     <row r="20" spans="1:8">
-      <c r="A20" s="50"/>
+      <c r="A20" s="49"/>
       <c r="B20" s="4" t="s">
         <v>40</v>
       </c>
@@ -2746,7 +2716,7 @@
       <c r="H20" s="4"/>
     </row>
     <row r="21" spans="1:8" ht="24">
-      <c r="A21" s="50"/>
+      <c r="A21" s="49"/>
       <c r="B21" s="4" t="s">
         <v>44</v>
       </c>
@@ -2764,7 +2734,7 @@
       <c r="H21" s="4"/>
     </row>
     <row r="22" spans="1:8" ht="24">
-      <c r="A22" s="50"/>
+      <c r="A22" s="49"/>
       <c r="B22" s="4" t="s">
         <v>47</v>
       </c>
@@ -2780,7 +2750,7 @@
       <c r="H22" s="4"/>
     </row>
     <row r="23" spans="1:8" ht="24">
-      <c r="A23" s="50"/>
+      <c r="A23" s="49"/>
       <c r="B23" s="4" t="s">
         <v>49</v>
       </c>
@@ -3234,7 +3204,7 @@
     <row r="14" spans="1:12">
       <c r="A14" s="14"/>
       <c r="B14" s="14" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="C14" s="14">
         <v>11811</v>
@@ -3256,7 +3226,7 @@
     <row r="15" spans="1:12">
       <c r="A15" s="14"/>
       <c r="B15" s="14" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="C15" s="14">
         <v>11812</v>
@@ -3278,7 +3248,7 @@
     <row r="16" spans="1:12">
       <c r="A16" s="14"/>
       <c r="B16" s="14" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="C16" s="14">
         <v>11813</v>
@@ -3300,7 +3270,7 @@
     <row r="17" spans="1:12">
       <c r="A17" s="14"/>
       <c r="B17" s="14" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="C17" s="14">
         <v>11814</v>
@@ -3322,7 +3292,7 @@
     <row r="18" spans="1:12">
       <c r="A18" s="14"/>
       <c r="B18" s="14" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="C18" s="14">
         <v>3</v>
@@ -3346,7 +3316,7 @@
     <row r="19" spans="1:12">
       <c r="A19" s="14"/>
       <c r="B19" s="14" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="C19" s="14" t="s">
         <v>95</v>
@@ -3370,7 +3340,7 @@
     <row r="20" spans="1:12">
       <c r="A20" s="14"/>
       <c r="B20" s="14" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="C20" s="14">
         <v>64</v>
@@ -3383,7 +3353,7 @@
         <v>102</v>
       </c>
       <c r="G20" s="14" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="H20" s="14"/>
       <c r="I20" s="14"/>
@@ -3394,7 +3364,7 @@
     <row r="21" spans="1:12">
       <c r="A21" s="14"/>
       <c r="B21" s="14" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="C21" s="14">
         <v>20</v>
@@ -3407,7 +3377,7 @@
         <v>102</v>
       </c>
       <c r="G21" s="14" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="H21" s="14"/>
       <c r="I21" s="14"/>
@@ -3418,7 +3388,7 @@
     <row r="22" spans="1:12">
       <c r="A22" s="14"/>
       <c r="B22" s="14" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="C22" s="17" t="s">
         <v>109</v>
@@ -3466,7 +3436,7 @@
     <row r="24" spans="1:12">
       <c r="A24" s="14"/>
       <c r="B24" s="16" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="C24" s="11">
         <v>1</v>
@@ -3488,7 +3458,7 @@
     <row r="25" spans="1:12" s="19" customFormat="1">
       <c r="A25" s="16"/>
       <c r="B25" s="16" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="C25" s="11">
         <v>10000</v>
@@ -3817,10 +3787,10 @@
         <v>119</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="D2" s="5" t="s">
         <v>1</v>
@@ -3830,16 +3800,16 @@
     </row>
     <row r="3" spans="1:6" ht="48">
       <c r="A3" s="9" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="E3" s="4"/>
       <c r="F3" s="4"/>
@@ -3850,10 +3820,10 @@
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="9" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E4" s="4"/>
       <c r="F4" s="4"/>
@@ -3868,30 +3838,30 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="C6" s="9" t="s">
         <v>165</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>190</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>167</v>
-      </c>
       <c r="D6" s="9" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="9" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B7" s="4"/>
       <c r="C7" s="9" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="E7" s="4"/>
       <c r="F7" s="4"/>
@@ -3904,54 +3874,54 @@
       <c r="E8" s="4"/>
       <c r="F8" s="4"/>
     </row>
-    <row r="9" spans="1:6" s="39" customFormat="1">
-      <c r="A9" s="37" t="s">
-        <v>234</v>
-      </c>
-      <c r="B9" s="38" t="s">
-        <v>235</v>
-      </c>
-      <c r="C9" s="37" t="s">
-        <v>233</v>
-      </c>
-      <c r="D9" s="37" t="s">
-        <v>236</v>
-      </c>
-      <c r="E9" s="38"/>
-      <c r="F9" s="38"/>
-    </row>
-    <row r="10" spans="1:6" s="39" customFormat="1">
-      <c r="A10" s="37" t="s">
-        <v>288</v>
-      </c>
-      <c r="B10" s="38"/>
-      <c r="C10" s="37" t="s">
-        <v>286</v>
-      </c>
-      <c r="D10" s="37"/>
-      <c r="E10" s="38"/>
-      <c r="F10" s="38"/>
-    </row>
-    <row r="11" spans="1:6" s="43" customFormat="1">
-      <c r="A11" s="41"/>
-      <c r="B11" s="42"/>
-      <c r="C11" s="41"/>
-      <c r="D11" s="41"/>
-      <c r="E11" s="42"/>
-      <c r="F11" s="42"/>
+    <row r="9" spans="1:6" s="38" customFormat="1">
+      <c r="A9" s="36" t="s">
+        <v>230</v>
+      </c>
+      <c r="B9" s="37" t="s">
+        <v>231</v>
+      </c>
+      <c r="C9" s="36" t="s">
+        <v>229</v>
+      </c>
+      <c r="D9" s="36" t="s">
+        <v>232</v>
+      </c>
+      <c r="E9" s="37"/>
+      <c r="F9" s="37"/>
+    </row>
+    <row r="10" spans="1:6" s="38" customFormat="1">
+      <c r="A10" s="36" t="s">
+        <v>284</v>
+      </c>
+      <c r="B10" s="37"/>
+      <c r="C10" s="36" t="s">
+        <v>282</v>
+      </c>
+      <c r="D10" s="36"/>
+      <c r="E10" s="37"/>
+      <c r="F10" s="37"/>
+    </row>
+    <row r="11" spans="1:6" s="42" customFormat="1">
+      <c r="A11" s="40"/>
+      <c r="B11" s="41"/>
+      <c r="C11" s="40"/>
+      <c r="D11" s="40"/>
+      <c r="E11" s="41"/>
+      <c r="F11" s="41"/>
     </row>
     <row r="12" spans="1:6" ht="60">
       <c r="A12" s="9" t="s">
         <v>122</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="E12" s="4"/>
       <c r="F12" s="4"/>
@@ -3962,10 +3932,10 @@
       </c>
       <c r="B13" s="4"/>
       <c r="C13" s="9" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="E13" s="4"/>
       <c r="F13" s="4"/>
@@ -3973,7 +3943,7 @@
     <row r="14" spans="1:6">
       <c r="A14" s="9"/>
       <c r="B14" s="4" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C14" s="9"/>
       <c r="D14" s="9"/>
@@ -3985,13 +3955,13 @@
         <v>124</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="E15" s="4"/>
       <c r="F15" s="4"/>
@@ -4002,10 +3972,10 @@
       </c>
       <c r="B16" s="4"/>
       <c r="C16" s="9" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="E16" s="4"/>
       <c r="F16" s="4"/>
@@ -4013,7 +3983,7 @@
     <row r="17" spans="1:6">
       <c r="A17" s="9"/>
       <c r="B17" s="4" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C17" s="9"/>
       <c r="D17" s="9"/>
@@ -4025,13 +3995,13 @@
         <v>126</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="E18" s="4"/>
       <c r="F18" s="4"/>
@@ -4042,7 +4012,7 @@
       </c>
       <c r="B19" s="4"/>
       <c r="C19" s="9" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="D19" s="9"/>
       <c r="E19" s="4"/>
@@ -4056,29 +4026,29 @@
       <c r="E20" s="4"/>
       <c r="F20" s="4"/>
     </row>
-    <row r="21" spans="1:6" s="40" customFormat="1" ht="24">
+    <row r="21" spans="1:6" s="39" customFormat="1" ht="24">
       <c r="A21" s="5" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" s="2"/>
     </row>
-    <row r="22" spans="1:6" s="40" customFormat="1" ht="60">
+    <row r="22" spans="1:6" s="39" customFormat="1" ht="60">
       <c r="A22" s="5" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="B22" s="2"/>
       <c r="C22" s="5" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="D22" s="5"/>
       <c r="E22" s="2"/>
@@ -4087,36 +4057,36 @@
     <row r="23" spans="1:6">
       <c r="A23" s="9"/>
       <c r="B23" s="4" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C23" s="9"/>
       <c r="D23" s="9"/>
       <c r="E23" s="4"/>
       <c r="F23" s="4"/>
     </row>
-    <row r="24" spans="1:6" s="40" customFormat="1">
+    <row r="24" spans="1:6" s="39" customFormat="1">
       <c r="A24" s="5" t="s">
+        <v>271</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>276</v>
+      </c>
+      <c r="D24" s="5" t="s">
         <v>275</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>280</v>
-      </c>
-      <c r="D24" s="5" t="s">
-        <v>279</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" s="2"/>
     </row>
-    <row r="25" spans="1:6" s="40" customFormat="1">
+    <row r="25" spans="1:6" s="39" customFormat="1">
       <c r="A25" s="5" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="B25" s="2"/>
       <c r="C25" s="5" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="D25" s="5"/>
       <c r="E25" s="2"/>
@@ -4130,29 +4100,29 @@
       <c r="E26" s="4"/>
       <c r="F26" s="4"/>
     </row>
-    <row r="27" spans="1:6" s="40" customFormat="1">
+    <row r="27" spans="1:6" s="39" customFormat="1">
       <c r="A27" s="5" t="s">
         <v>128</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" s="2"/>
     </row>
-    <row r="28" spans="1:6" s="40" customFormat="1" ht="180">
+    <row r="28" spans="1:6" s="39" customFormat="1" ht="180">
       <c r="A28" s="5" t="s">
         <v>129</v>
       </c>
       <c r="B28" s="2"/>
       <c r="C28" s="5" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="D28" s="5"/>
       <c r="E28" s="2"/>
@@ -4168,10 +4138,10 @@
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="9" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="C30" s="9"/>
       <c r="D30" s="9"/>
@@ -4189,7 +4159,7 @@
     <row r="32" spans="1:6">
       <c r="A32" s="9"/>
       <c r="B32" s="4" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C32" s="9"/>
       <c r="D32" s="9"/>
@@ -4198,28 +4168,28 @@
     </row>
     <row r="33" spans="1:6">
       <c r="A33" s="9" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="C33" s="9"/>
       <c r="D33" s="9" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="E33" s="4"/>
       <c r="F33" s="4"/>
     </row>
     <row r="34" spans="1:6" ht="36">
       <c r="A34" s="9" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B34" s="4"/>
       <c r="C34" s="9" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="E34" s="4"/>
       <c r="F34" s="4"/>
@@ -4227,7 +4197,7 @@
     <row r="35" spans="1:6">
       <c r="A35" s="9"/>
       <c r="B35" s="4" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C35" s="9"/>
       <c r="D35" s="9"/>
@@ -4236,30 +4206,30 @@
     </row>
     <row r="36" spans="1:6" ht="24">
       <c r="A36" s="9" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="D36" s="9" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="E36" s="4"/>
       <c r="F36" s="4"/>
     </row>
     <row r="37" spans="1:6" ht="228">
       <c r="A37" s="9" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B37" s="4"/>
       <c r="C37" s="9" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="D37" s="9" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="E37" s="4"/>
       <c r="F37" s="4"/>
@@ -4267,7 +4237,7 @@
     <row r="38" spans="1:6">
       <c r="A38" s="9"/>
       <c r="B38" s="4" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C38" s="9"/>
       <c r="D38" s="9"/>
@@ -4276,30 +4246,30 @@
     </row>
     <row r="39" spans="1:6" ht="84">
       <c r="A39" s="9" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="C39" s="9" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="D39" s="9" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="E39" s="4"/>
       <c r="F39" s="4"/>
     </row>
     <row r="40" spans="1:6" ht="108">
       <c r="A40" s="9" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B40" s="4"/>
       <c r="C40" s="9" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="D40" s="9" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="E40" s="4"/>
       <c r="F40" s="4"/>
@@ -4307,7 +4277,7 @@
     <row r="41" spans="1:6">
       <c r="A41" s="9"/>
       <c r="B41" s="4" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C41" s="9"/>
       <c r="D41" s="9"/>
@@ -4316,27 +4286,27 @@
     </row>
     <row r="42" spans="1:6" ht="132">
       <c r="A42" s="9" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="C42" s="9" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="D42" s="9" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="E42" s="4"/>
       <c r="F42" s="4"/>
     </row>
     <row r="43" spans="1:6">
       <c r="A43" s="9" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B43" s="4"/>
       <c r="C43" s="9" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="D43" s="9" t="s">
         <v>120</v>
@@ -4352,61 +4322,61 @@
       <c r="E44" s="4"/>
       <c r="F44" s="4"/>
     </row>
-    <row r="45" spans="1:6" s="40" customFormat="1">
+    <row r="45" spans="1:6" s="39" customFormat="1">
       <c r="A45" s="5" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" s="2"/>
     </row>
-    <row r="46" spans="1:6" s="40" customFormat="1">
+    <row r="46" spans="1:6" s="39" customFormat="1">
       <c r="A46" s="5" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="B46" s="2"/>
       <c r="C46" s="5" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="D46" s="5"/>
       <c r="E46" s="2"/>
       <c r="F46" s="2"/>
     </row>
-    <row r="47" spans="1:6" s="43" customFormat="1">
-      <c r="A47" s="41"/>
-      <c r="B47" s="42"/>
-      <c r="C47" s="41"/>
-      <c r="D47" s="41"/>
-      <c r="E47" s="42"/>
-      <c r="F47" s="42"/>
-    </row>
-    <row r="48" spans="1:6" s="40" customFormat="1">
+    <row r="47" spans="1:6" s="42" customFormat="1">
+      <c r="A47" s="40"/>
+      <c r="B47" s="41"/>
+      <c r="C47" s="40"/>
+      <c r="D47" s="40"/>
+      <c r="E47" s="41"/>
+      <c r="F47" s="41"/>
+    </row>
+    <row r="48" spans="1:6" s="39" customFormat="1">
       <c r="A48" s="5" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" s="2"/>
     </row>
-    <row r="49" spans="1:6" s="40" customFormat="1">
+    <row r="49" spans="1:6" s="39" customFormat="1">
       <c r="A49" s="5" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="B49" s="2"/>
       <c r="C49" s="5"/>
@@ -4422,73 +4392,73 @@
       <c r="E50" s="4"/>
       <c r="F50" s="4"/>
     </row>
-    <row r="51" spans="1:6" s="40" customFormat="1">
+    <row r="51" spans="1:6" s="39" customFormat="1">
       <c r="A51" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="B51" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="B51" s="2" t="s">
-        <v>144</v>
-      </c>
       <c r="C51" s="5" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" s="2"/>
     </row>
-    <row r="52" spans="1:6" s="40" customFormat="1">
+    <row r="52" spans="1:6" s="39" customFormat="1">
       <c r="A52" s="5" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B52" s="2"/>
       <c r="C52" s="5" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="D52" s="5"/>
       <c r="E52" s="2"/>
       <c r="F52" s="2"/>
     </row>
-    <row r="53" spans="1:6" s="43" customFormat="1">
-      <c r="A53" s="41"/>
-      <c r="B53" s="42"/>
-      <c r="C53" s="41"/>
-      <c r="D53" s="41"/>
-      <c r="E53" s="42"/>
-      <c r="F53" s="42"/>
-    </row>
-    <row r="54" spans="1:6" s="43" customFormat="1">
-      <c r="A54" s="41"/>
-      <c r="B54" s="42"/>
-      <c r="C54" s="41"/>
-      <c r="D54" s="41"/>
-      <c r="E54" s="42"/>
-      <c r="F54" s="42"/>
+    <row r="53" spans="1:6" s="42" customFormat="1">
+      <c r="A53" s="40"/>
+      <c r="B53" s="41"/>
+      <c r="C53" s="40"/>
+      <c r="D53" s="40"/>
+      <c r="E53" s="41"/>
+      <c r="F53" s="41"/>
+    </row>
+    <row r="54" spans="1:6" s="42" customFormat="1">
+      <c r="A54" s="40"/>
+      <c r="B54" s="41"/>
+      <c r="C54" s="40"/>
+      <c r="D54" s="40"/>
+      <c r="E54" s="41"/>
+      <c r="F54" s="41"/>
     </row>
     <row r="55" spans="1:6" ht="24">
       <c r="A55" s="9" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="C55" s="9" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="D55" s="9" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="E55" s="4"/>
       <c r="F55" s="4"/>
     </row>
     <row r="56" spans="1:6" ht="84">
       <c r="A56" s="9" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="B56" s="4"/>
       <c r="C56" s="9" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="D56" s="9"/>
       <c r="E56" s="4"/>
@@ -4513,29 +4483,29 @@
       <c r="D59" s="9"/>
     </row>
     <row r="60" spans="1:6">
-      <c r="A60" s="35" t="s">
-        <v>149</v>
-      </c>
-      <c r="B60" s="36" t="s">
-        <v>191</v>
-      </c>
-      <c r="C60" s="35" t="s">
-        <v>145</v>
-      </c>
-      <c r="D60" s="35"/>
-      <c r="E60" s="36"/>
-      <c r="F60" s="36"/>
+      <c r="A60" s="34" t="s">
+        <v>147</v>
+      </c>
+      <c r="B60" s="35" t="s">
+        <v>187</v>
+      </c>
+      <c r="C60" s="34" t="s">
+        <v>143</v>
+      </c>
+      <c r="D60" s="34"/>
+      <c r="E60" s="35"/>
+      <c r="F60" s="35"/>
     </row>
     <row r="61" spans="1:6" ht="24">
       <c r="A61" s="9" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B61" s="4"/>
       <c r="C61" s="9" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="D61" s="9" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="E61" s="4"/>
       <c r="F61" s="4"/>
@@ -4550,27 +4520,27 @@
     </row>
     <row r="63" spans="1:6" ht="24">
       <c r="A63" s="9" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="C63" s="9" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="D63" s="9" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="E63" s="4"/>
       <c r="F63" s="4"/>
     </row>
     <row r="64" spans="1:6">
       <c r="A64" s="9" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B64" s="4"/>
       <c r="C64" s="9" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="D64" s="9"/>
       <c r="E64" s="4"/>
@@ -4578,26 +4548,26 @@
     </row>
     <row r="65" spans="1:6" ht="24">
       <c r="A65" s="9" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="C65" s="9" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="D65" s="9" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="E65" s="4"/>
       <c r="F65" s="4"/>
     </row>
     <row r="66" spans="1:6">
       <c r="A66" s="9" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="C66" s="9"/>
       <c r="D66" s="9"/>
@@ -4612,95 +4582,95 @@
       <c r="E67" s="4"/>
       <c r="F67" s="4"/>
     </row>
-    <row r="68" spans="1:6" s="43" customFormat="1">
-      <c r="A68" s="41" t="s">
+    <row r="68" spans="1:6" s="42" customFormat="1">
+      <c r="A68" s="40" t="s">
+        <v>153</v>
+      </c>
+      <c r="B68" s="41"/>
+      <c r="C68" s="40" t="s">
+        <v>296</v>
+      </c>
+      <c r="D68" s="40"/>
+      <c r="E68" s="41"/>
+      <c r="F68" s="41"/>
+    </row>
+    <row r="69" spans="1:6" s="42" customFormat="1" ht="24">
+      <c r="A69" s="40" t="s">
+        <v>154</v>
+      </c>
+      <c r="B69" s="41"/>
+      <c r="C69" s="40" t="s">
+        <v>295</v>
+      </c>
+      <c r="D69" s="40" t="s">
+        <v>144</v>
+      </c>
+      <c r="E69" s="41"/>
+      <c r="F69" s="41"/>
+    </row>
+    <row r="70" spans="1:6" s="42" customFormat="1" ht="24">
+      <c r="A70" s="40" t="s">
+        <v>151</v>
+      </c>
+      <c r="B70" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="C70" s="40" t="s">
+        <v>152</v>
+      </c>
+      <c r="D70" s="40"/>
+      <c r="E70" s="41"/>
+      <c r="F70" s="41"/>
+    </row>
+    <row r="71" spans="1:6" s="42" customFormat="1" ht="48">
+      <c r="A71" s="40" t="s">
         <v>155</v>
       </c>
-      <c r="B68" s="42"/>
-      <c r="C68" s="41" t="s">
-        <v>300</v>
-      </c>
-      <c r="D68" s="41"/>
-      <c r="E68" s="42"/>
-      <c r="F68" s="42"/>
-    </row>
-    <row r="69" spans="1:6" s="43" customFormat="1" ht="24">
-      <c r="A69" s="41" t="s">
+      <c r="B71" s="41" t="s">
         <v>156</v>
       </c>
-      <c r="B69" s="42"/>
-      <c r="C69" s="41" t="s">
-        <v>299</v>
-      </c>
-      <c r="D69" s="41" t="s">
+      <c r="C71" s="40" t="s">
+        <v>159</v>
+      </c>
+      <c r="D71" s="40" t="s">
+        <v>160</v>
+      </c>
+      <c r="E71" s="41"/>
+      <c r="F71" s="41"/>
+    </row>
+    <row r="72" spans="1:6" s="42" customFormat="1" ht="36">
+      <c r="A72" s="40" t="s">
+        <v>157</v>
+      </c>
+      <c r="B72" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="C72" s="40" t="s">
+        <v>158</v>
+      </c>
+      <c r="D72" s="40"/>
+      <c r="E72" s="41"/>
+      <c r="F72" s="41"/>
+    </row>
+    <row r="73" spans="1:6" s="21" customFormat="1" ht="24">
+      <c r="A73" s="43" t="s">
         <v>146</v>
       </c>
-      <c r="E69" s="42"/>
-      <c r="F69" s="42"/>
-    </row>
-    <row r="70" spans="1:6" s="43" customFormat="1" ht="24">
-      <c r="A70" s="41" t="s">
-        <v>153</v>
-      </c>
-      <c r="B70" s="42" t="s">
-        <v>158</v>
-      </c>
-      <c r="C70" s="41" t="s">
-        <v>154</v>
-      </c>
-      <c r="D70" s="41"/>
-      <c r="E70" s="42"/>
-      <c r="F70" s="42"/>
-    </row>
-    <row r="71" spans="1:6" s="43" customFormat="1" ht="48">
-      <c r="A71" s="41" t="s">
-        <v>157</v>
-      </c>
-      <c r="B71" s="42" t="s">
-        <v>158</v>
-      </c>
-      <c r="C71" s="41" t="s">
-        <v>161</v>
-      </c>
-      <c r="D71" s="41" t="s">
-        <v>162</v>
-      </c>
-      <c r="E71" s="42"/>
-      <c r="F71" s="42"/>
-    </row>
-    <row r="72" spans="1:6" s="43" customFormat="1" ht="36">
-      <c r="A72" s="41" t="s">
-        <v>159</v>
-      </c>
-      <c r="B72" s="42" t="s">
-        <v>158</v>
-      </c>
-      <c r="C72" s="41" t="s">
-        <v>160</v>
-      </c>
-      <c r="D72" s="41"/>
-      <c r="E72" s="42"/>
-      <c r="F72" s="42"/>
-    </row>
-    <row r="73" spans="1:6" s="21" customFormat="1" ht="24">
-      <c r="A73" s="44" t="s">
-        <v>148</v>
-      </c>
-      <c r="B73" s="45"/>
-      <c r="C73" s="44"/>
-      <c r="D73" s="44" t="s">
-        <v>147</v>
-      </c>
-      <c r="E73" s="45"/>
-      <c r="F73" s="45"/>
-    </row>
-    <row r="74" spans="1:6" s="43" customFormat="1">
-      <c r="A74" s="41"/>
-      <c r="B74" s="42"/>
-      <c r="C74" s="41"/>
-      <c r="D74" s="41"/>
-      <c r="E74" s="42"/>
-      <c r="F74" s="42"/>
+      <c r="B73" s="44"/>
+      <c r="C73" s="43"/>
+      <c r="D73" s="43" t="s">
+        <v>145</v>
+      </c>
+      <c r="E73" s="44"/>
+      <c r="F73" s="44"/>
+    </row>
+    <row r="74" spans="1:6" s="42" customFormat="1">
+      <c r="A74" s="40"/>
+      <c r="B74" s="41"/>
+      <c r="C74" s="40"/>
+      <c r="D74" s="40"/>
+      <c r="E74" s="41"/>
+      <c r="F74" s="41"/>
     </row>
     <row r="75" spans="1:6">
       <c r="A75" s="9"/>
@@ -4750,38 +4720,6 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
-  <cols>
-    <col min="1" max="1" width="11.375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="47.125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="30.125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" t="s">
-        <v>131</v>
-      </c>
-      <c r="B1" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="40.5">
-      <c r="B8" s="23" t="s">
-        <v>168</v>
-      </c>
-      <c r="C8" s="24" t="s">
-        <v>169</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E25"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
@@ -4794,241 +4732,241 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="24" t="s">
+        <v>223</v>
+      </c>
+      <c r="B1" s="24" t="s">
+        <v>221</v>
+      </c>
+      <c r="C1" s="25" t="s">
+        <v>222</v>
+      </c>
+      <c r="D1" s="25" t="s">
+        <v>238</v>
+      </c>
+      <c r="E1" s="25" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="67.5">
+      <c r="A2" s="27" t="s">
         <v>227</v>
       </c>
-      <c r="B1" s="25" t="s">
+      <c r="B2" s="28" t="s">
+        <v>236</v>
+      </c>
+      <c r="C2" s="27" t="s">
         <v>225</v>
       </c>
-      <c r="C1" s="26" t="s">
+      <c r="D2" s="27" t="s">
+        <v>224</v>
+      </c>
+      <c r="E2" s="29" t="s">
         <v>226</v>
       </c>
-      <c r="D1" s="26" t="s">
-        <v>242</v>
-      </c>
-      <c r="E1" s="26" t="s">
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="28"/>
+      <c r="B3" s="28"/>
+      <c r="C3" s="27"/>
+      <c r="D3" s="27"/>
+      <c r="E3" s="27"/>
+    </row>
+    <row r="4" spans="1:5" ht="27">
+      <c r="A4" s="28" t="s">
+        <v>312</v>
+      </c>
+      <c r="B4" s="28" t="s">
+        <v>44</v>
+      </c>
+      <c r="C4" s="27" t="s">
+        <v>268</v>
+      </c>
+      <c r="D4" s="27" t="s">
+        <v>237</v>
+      </c>
+      <c r="E4" s="29" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="28"/>
+      <c r="B5" s="28"/>
+      <c r="C5" s="27"/>
+      <c r="D5" s="27"/>
+      <c r="E5" s="29"/>
+    </row>
+    <row r="6" spans="1:5" ht="162">
+      <c r="A6" s="28" t="s">
+        <v>313</v>
+      </c>
+      <c r="B6" s="28" t="s">
+        <v>314</v>
+      </c>
+      <c r="C6" s="27" t="s">
+        <v>315</v>
+      </c>
+      <c r="D6" s="27" t="s">
+        <v>316</v>
+      </c>
+      <c r="E6" s="27"/>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="28"/>
+      <c r="B7" s="28"/>
+      <c r="C7" s="27"/>
+      <c r="D7" s="27"/>
+      <c r="E7" s="27"/>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="28"/>
+      <c r="B8" s="28"/>
+      <c r="C8" s="27"/>
+      <c r="D8" s="27"/>
+      <c r="E8" s="27"/>
+    </row>
+    <row r="9" spans="1:5" ht="108">
+      <c r="A9" s="28" t="s">
+        <v>303</v>
+      </c>
+      <c r="B9" s="28"/>
+      <c r="C9" s="27" t="s">
+        <v>309</v>
+      </c>
+      <c r="D9" s="27" t="s">
+        <v>308</v>
+      </c>
+      <c r="E9" s="27"/>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="28"/>
+      <c r="B10" s="28"/>
+      <c r="C10" s="27"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="27"/>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="28"/>
+      <c r="B11" s="28"/>
+      <c r="C11" s="27"/>
+      <c r="D11" s="27"/>
+      <c r="E11" s="27"/>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="24" t="s">
+        <v>324</v>
+      </c>
+      <c r="B12" s="24" t="s">
+        <v>221</v>
+      </c>
+      <c r="C12" s="25" t="s">
+        <v>222</v>
+      </c>
+      <c r="D12" s="25" t="s">
+        <v>238</v>
+      </c>
+      <c r="E12" s="25" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="67.5">
-      <c r="A2" s="28" t="s">
-        <v>231</v>
-      </c>
-      <c r="B2" s="29" t="s">
-        <v>240</v>
-      </c>
-      <c r="C2" s="28" t="s">
-        <v>229</v>
-      </c>
-      <c r="D2" s="28" t="s">
-        <v>228</v>
-      </c>
-      <c r="E2" s="30" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="29"/>
-      <c r="B3" s="29"/>
-      <c r="C3" s="28"/>
-      <c r="D3" s="28"/>
-      <c r="E3" s="28"/>
-    </row>
-    <row r="4" spans="1:5" ht="27">
-      <c r="A4" s="29" t="s">
-        <v>316</v>
-      </c>
-      <c r="B4" s="29" t="s">
-        <v>44</v>
-      </c>
-      <c r="C4" s="28" t="s">
-        <v>272</v>
-      </c>
-      <c r="D4" s="28" t="s">
-        <v>241</v>
-      </c>
-      <c r="E4" s="30" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="29"/>
-      <c r="B5" s="29"/>
-      <c r="C5" s="28"/>
-      <c r="D5" s="28"/>
-      <c r="E5" s="30"/>
-    </row>
-    <row r="6" spans="1:5" ht="162">
-      <c r="A6" s="29" t="s">
-        <v>317</v>
-      </c>
-      <c r="B6" s="29" t="s">
-        <v>318</v>
-      </c>
-      <c r="C6" s="28" t="s">
-        <v>319</v>
-      </c>
-      <c r="D6" s="28" t="s">
-        <v>320</v>
-      </c>
-      <c r="E6" s="28"/>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7" s="29"/>
-      <c r="B7" s="29"/>
-      <c r="C7" s="28"/>
-      <c r="D7" s="28"/>
-      <c r="E7" s="28"/>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" s="29"/>
-      <c r="B8" s="29"/>
-      <c r="C8" s="28"/>
-      <c r="D8" s="28"/>
-      <c r="E8" s="28"/>
-    </row>
-    <row r="9" spans="1:5" ht="108">
-      <c r="A9" s="29" t="s">
-        <v>307</v>
-      </c>
-      <c r="B9" s="29"/>
-      <c r="C9" s="28" t="s">
-        <v>313</v>
-      </c>
-      <c r="D9" s="28" t="s">
-        <v>312</v>
-      </c>
-      <c r="E9" s="28"/>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10" s="29"/>
-      <c r="B10" s="29"/>
-      <c r="C10" s="28"/>
-      <c r="D10" s="28"/>
-      <c r="E10" s="28"/>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11" s="29"/>
-      <c r="B11" s="29"/>
-      <c r="C11" s="28"/>
-      <c r="D11" s="28"/>
-      <c r="E11" s="28"/>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12" s="25" t="s">
-        <v>328</v>
-      </c>
-      <c r="B12" s="25" t="s">
-        <v>225</v>
-      </c>
-      <c r="C12" s="26" t="s">
-        <v>226</v>
-      </c>
-      <c r="D12" s="26" t="s">
-        <v>242</v>
-      </c>
-      <c r="E12" s="26" t="s">
-        <v>51</v>
-      </c>
-    </row>
     <row r="13" spans="1:5" ht="135">
-      <c r="A13" s="29" t="s">
+      <c r="A13" s="28" t="s">
+        <v>322</v>
+      </c>
+      <c r="B13" s="28" t="s">
+        <v>323</v>
+      </c>
+      <c r="C13" s="27" t="s">
+        <v>325</v>
+      </c>
+      <c r="D13" s="27" t="s">
         <v>326</v>
       </c>
-      <c r="B13" s="29" t="s">
-        <v>327</v>
-      </c>
-      <c r="C13" s="28" t="s">
-        <v>329</v>
-      </c>
-      <c r="D13" s="28" t="s">
-        <v>330</v>
-      </c>
-      <c r="E13" s="28"/>
+      <c r="E13" s="27"/>
     </row>
     <row r="14" spans="1:5">
-      <c r="A14" s="29"/>
-      <c r="B14" s="29"/>
-      <c r="C14" s="28"/>
-      <c r="D14" s="28"/>
-      <c r="E14" s="28"/>
+      <c r="A14" s="28"/>
+      <c r="B14" s="28"/>
+      <c r="C14" s="27"/>
+      <c r="D14" s="27"/>
+      <c r="E14" s="27"/>
     </row>
     <row r="15" spans="1:5">
-      <c r="A15" s="29"/>
-      <c r="B15" s="29"/>
-      <c r="C15" s="28"/>
-      <c r="D15" s="28"/>
-      <c r="E15" s="28"/>
+      <c r="A15" s="28"/>
+      <c r="B15" s="28"/>
+      <c r="C15" s="27"/>
+      <c r="D15" s="27"/>
+      <c r="E15" s="27"/>
     </row>
     <row r="16" spans="1:5">
-      <c r="A16" s="29"/>
-      <c r="B16" s="29"/>
-      <c r="C16" s="28"/>
-      <c r="D16" s="28"/>
-      <c r="E16" s="28"/>
+      <c r="A16" s="28"/>
+      <c r="B16" s="28"/>
+      <c r="C16" s="27"/>
+      <c r="D16" s="27"/>
+      <c r="E16" s="27"/>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="29"/>
-      <c r="B17" s="29"/>
-      <c r="C17" s="28"/>
-      <c r="D17" s="28"/>
-      <c r="E17" s="28"/>
+      <c r="A17" s="28"/>
+      <c r="B17" s="28"/>
+      <c r="C17" s="27"/>
+      <c r="D17" s="27"/>
+      <c r="E17" s="27"/>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="29"/>
-      <c r="B18" s="29"/>
-      <c r="C18" s="28"/>
-      <c r="D18" s="28"/>
-      <c r="E18" s="28"/>
+      <c r="A18" s="28"/>
+      <c r="B18" s="28"/>
+      <c r="C18" s="27"/>
+      <c r="D18" s="27"/>
+      <c r="E18" s="27"/>
     </row>
     <row r="19" spans="1:5">
-      <c r="A19" s="29"/>
-      <c r="B19" s="29"/>
-      <c r="C19" s="28"/>
-      <c r="D19" s="28"/>
-      <c r="E19" s="28"/>
+      <c r="A19" s="28"/>
+      <c r="B19" s="28"/>
+      <c r="C19" s="27"/>
+      <c r="D19" s="27"/>
+      <c r="E19" s="27"/>
     </row>
     <row r="20" spans="1:5">
-      <c r="A20" s="29"/>
-      <c r="B20" s="29"/>
-      <c r="C20" s="28"/>
-      <c r="D20" s="28"/>
-      <c r="E20" s="28"/>
+      <c r="A20" s="28"/>
+      <c r="B20" s="28"/>
+      <c r="C20" s="27"/>
+      <c r="D20" s="27"/>
+      <c r="E20" s="27"/>
     </row>
     <row r="21" spans="1:5">
-      <c r="A21" s="29"/>
-      <c r="B21" s="29"/>
-      <c r="C21" s="28"/>
-      <c r="D21" s="28"/>
-      <c r="E21" s="28"/>
+      <c r="A21" s="28"/>
+      <c r="B21" s="28"/>
+      <c r="C21" s="27"/>
+      <c r="D21" s="27"/>
+      <c r="E21" s="27"/>
     </row>
     <row r="22" spans="1:5">
-      <c r="A22" s="29"/>
-      <c r="B22" s="29"/>
-      <c r="C22" s="28"/>
-      <c r="D22" s="28"/>
-      <c r="E22" s="28"/>
+      <c r="A22" s="28"/>
+      <c r="B22" s="28"/>
+      <c r="C22" s="27"/>
+      <c r="D22" s="27"/>
+      <c r="E22" s="27"/>
     </row>
     <row r="23" spans="1:5">
-      <c r="A23" s="29"/>
-      <c r="B23" s="29"/>
-      <c r="C23" s="28"/>
-      <c r="D23" s="28"/>
-      <c r="E23" s="28"/>
+      <c r="A23" s="28"/>
+      <c r="B23" s="28"/>
+      <c r="C23" s="27"/>
+      <c r="D23" s="27"/>
+      <c r="E23" s="27"/>
     </row>
     <row r="24" spans="1:5">
-      <c r="A24" s="29"/>
-      <c r="B24" s="29"/>
-      <c r="C24" s="28"/>
-      <c r="D24" s="28"/>
-      <c r="E24" s="28"/>
+      <c r="A24" s="28"/>
+      <c r="B24" s="28"/>
+      <c r="C24" s="27"/>
+      <c r="D24" s="27"/>
+      <c r="E24" s="27"/>
     </row>
     <row r="25" spans="1:5">
-      <c r="A25" s="29"/>
-      <c r="B25" s="29"/>
-      <c r="C25" s="28"/>
-      <c r="D25" s="28"/>
-      <c r="E25" s="28"/>
+      <c r="A25" s="28"/>
+      <c r="B25" s="28"/>
+      <c r="C25" s="27"/>
+      <c r="D25" s="27"/>
+      <c r="E25" s="27"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -5037,7 +4975,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H18"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
@@ -5049,163 +4987,163 @@
   <sheetData>
     <row r="1" spans="1:4" ht="27">
       <c r="A1" s="23" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="27">
       <c r="A2" s="23" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="25" t="s">
+        <v>260</v>
+      </c>
+      <c r="B4" s="25" t="s">
+        <v>261</v>
+      </c>
+      <c r="C4" s="25"/>
+      <c r="D4" s="25"/>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="30" t="s">
+        <v>244</v>
+      </c>
+      <c r="B5" s="26" t="s">
+        <v>259</v>
+      </c>
+      <c r="C5" s="26"/>
+      <c r="D5" s="26"/>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="30" t="s">
         <v>245</v>
       </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="26" t="s">
+      <c r="B6" s="26" t="s">
+        <v>242</v>
+      </c>
+      <c r="C6" s="26"/>
+      <c r="D6" s="26"/>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="30" t="s">
+        <v>246</v>
+      </c>
+      <c r="B7" s="26" t="s">
+        <v>262</v>
+      </c>
+      <c r="C7" s="26"/>
+      <c r="D7" s="26"/>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="30" t="s">
+        <v>247</v>
+      </c>
+      <c r="B8" s="26" t="s">
+        <v>263</v>
+      </c>
+      <c r="C8" s="26"/>
+      <c r="D8" s="26"/>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="30" t="s">
+        <v>248</v>
+      </c>
+      <c r="B9" s="26" t="s">
         <v>264</v>
       </c>
-      <c r="B4" s="26" t="s">
+      <c r="C9" s="26"/>
+      <c r="D9" s="26"/>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="30" t="s">
+        <v>249</v>
+      </c>
+      <c r="B10" s="26" t="s">
+        <v>264</v>
+      </c>
+      <c r="C10" s="26"/>
+      <c r="D10" s="26"/>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="30" t="s">
+        <v>250</v>
+      </c>
+      <c r="B11" s="26" t="s">
+        <v>264</v>
+      </c>
+      <c r="C11" s="26"/>
+      <c r="D11" s="26"/>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="30" t="s">
+        <v>251</v>
+      </c>
+      <c r="B12" s="26" t="s">
         <v>265</v>
       </c>
-      <c r="C4" s="26"/>
-      <c r="D4" s="26"/>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="31" t="s">
-        <v>248</v>
-      </c>
-      <c r="B5" s="27" t="s">
-        <v>263</v>
-      </c>
-      <c r="C5" s="27"/>
-      <c r="D5" s="27"/>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" s="31" t="s">
-        <v>249</v>
-      </c>
-      <c r="B6" s="27" t="s">
-        <v>246</v>
-      </c>
-      <c r="C6" s="27"/>
-      <c r="D6" s="27"/>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" s="31" t="s">
-        <v>250</v>
-      </c>
-      <c r="B7" s="27" t="s">
+      <c r="C12" s="26"/>
+      <c r="D12" s="26"/>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="30" t="s">
+        <v>256</v>
+      </c>
+      <c r="B13" s="26" t="s">
         <v>266</v>
       </c>
-      <c r="C7" s="27"/>
-      <c r="D7" s="27"/>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" s="31" t="s">
-        <v>251</v>
-      </c>
-      <c r="B8" s="27" t="s">
+      <c r="C13" s="26"/>
+      <c r="D13" s="26"/>
+    </row>
+    <row r="14" spans="1:4" ht="27">
+      <c r="A14" s="30" t="s">
+        <v>257</v>
+      </c>
+      <c r="B14" s="26" t="s">
         <v>267</v>
       </c>
-      <c r="C8" s="27"/>
-      <c r="D8" s="27"/>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" s="31" t="s">
+      <c r="C14" s="26"/>
+      <c r="D14" s="26"/>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="31" t="s">
+        <v>258</v>
+      </c>
+      <c r="B15" s="32" t="s">
+        <v>253</v>
+      </c>
+      <c r="C15" s="32"/>
+      <c r="D15" s="32"/>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="33" t="s">
         <v>252</v>
       </c>
-      <c r="B9" s="27" t="s">
-        <v>268</v>
-      </c>
-      <c r="C9" s="27"/>
-      <c r="D9" s="27"/>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" s="31" t="s">
+      <c r="B16" s="32" t="s">
         <v>253</v>
       </c>
-      <c r="B10" s="27" t="s">
-        <v>268</v>
-      </c>
-      <c r="C10" s="27"/>
-      <c r="D10" s="27"/>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11" s="31" t="s">
+      <c r="C16" s="32"/>
+      <c r="D16" s="32"/>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" s="33" t="s">
         <v>254</v>
       </c>
-      <c r="B11" s="27" t="s">
-        <v>268</v>
-      </c>
-      <c r="C11" s="27"/>
-      <c r="D11" s="27"/>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12" s="31" t="s">
+      <c r="B17" s="32" t="s">
+        <v>253</v>
+      </c>
+      <c r="C17" s="32"/>
+      <c r="D17" s="32"/>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" s="33" t="s">
         <v>255</v>
       </c>
-      <c r="B12" s="27" t="s">
-        <v>269</v>
-      </c>
-      <c r="C12" s="27"/>
-      <c r="D12" s="27"/>
-    </row>
-    <row r="13" spans="1:4">
-      <c r="A13" s="31" t="s">
-        <v>260</v>
-      </c>
-      <c r="B13" s="27" t="s">
-        <v>270</v>
-      </c>
-      <c r="C13" s="27"/>
-      <c r="D13" s="27"/>
-    </row>
-    <row r="14" spans="1:4" ht="27">
-      <c r="A14" s="31" t="s">
-        <v>261</v>
-      </c>
-      <c r="B14" s="27" t="s">
-        <v>271</v>
-      </c>
-      <c r="C14" s="27"/>
-      <c r="D14" s="27"/>
-    </row>
-    <row r="15" spans="1:4">
-      <c r="A15" s="32" t="s">
-        <v>262</v>
-      </c>
-      <c r="B15" s="33" t="s">
-        <v>257</v>
-      </c>
-      <c r="C15" s="33"/>
-      <c r="D15" s="33"/>
-    </row>
-    <row r="16" spans="1:4">
-      <c r="A16" s="34" t="s">
-        <v>256</v>
-      </c>
-      <c r="B16" s="33" t="s">
-        <v>257</v>
-      </c>
-      <c r="C16" s="33"/>
-      <c r="D16" s="33"/>
-    </row>
-    <row r="17" spans="1:4">
-      <c r="A17" s="34" t="s">
-        <v>258</v>
-      </c>
-      <c r="B17" s="33" t="s">
-        <v>257</v>
-      </c>
-      <c r="C17" s="33"/>
-      <c r="D17" s="33"/>
-    </row>
-    <row r="18" spans="1:4">
-      <c r="A18" s="34" t="s">
-        <v>259</v>
-      </c>
-      <c r="B18" s="33" t="s">
-        <v>257</v>
-      </c>
-      <c r="C18" s="33"/>
-      <c r="D18" s="33"/>
+      <c r="B18" s="32" t="s">
+        <v>253</v>
+      </c>
+      <c r="C18" s="32"/>
+      <c r="D18" s="32"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/internal_doc/03.开发设计/OM_web接口.xlsx
+++ b/internal_doc/03.开发设计/OM_web接口.xlsx
@@ -1515,138 +1515,139 @@
     <t>{Rc, ???}</t>
   </si>
   <si>
+    <t>成功时：{Rc}
+校验失败时：{Rc,local} local为跳转文件login.html</t>
+  </si>
+  <si>
+    <t>{Rc,local}</t>
+  </si>
+  <si>
+    <t>{Rc,detail}</t>
+  </si>
+  <si>
+    <t>{ClusterName, Rc}</t>
+  </si>
+  <si>
+    <t>rest参数(响应最外层统一加上Rc)</t>
+  </si>
+  <si>
+    <t>删除host</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>remove host</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>查询业务</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>查询业务响应</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>查询主机运行状态</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>query host status</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>查询主机运行状态响应</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>HostInfo={ClusterName:cls1, HostInfo:[{IP, HostName, User, Passwd, SshPort:xxx, AgentPort:xxx, InstallPath:xxx, Firework, [Disk],[CPU]…}, ...], User:xxx, Passwd:xxx, SshPort:xxx, AgentPort:xxx, InstallPath:xxx}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{HostInfo:[{HostName:aa, "CPU":"90%", "Memory": { "Model": "", "Size": 2003, "Free": 916, "Unit": "M" }, "Disk":[{ "Name"
+: "/dev/sda1", "Mount": "/", "Size": 32529, "Free": 6525, "Unit": "M", "Used": 1 }]}, {...}, ...]}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{HostName:aa, "CPU":"90%", "Memory": { "Model": "", "Size": 2003, "Free": 916, "Unit": "M" }, "Disk":[{ "Name"
+: "/dev/sda1", "Mount": "/", "Size": 32529, "Free": 6525, "Unit": "M", "Used": 1 }]}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"HostInfo":[{HostName:aa, "User":"root", "Passwd"sequoiadb", "Disk":[{ "Name"
+: "/dev/sda1", "Mount": "/"}]}, {...}, ...]}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://192.168.20.197:11814/?cmd=query host status&amp;HostInfo={HostInfo:[{HostName:"rhelt10"}]}'</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>HostInfo={HostInfo:[{HostName:"rhelt10"}]}'</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>删除host命令</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>删除业务</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>remove business</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"AuthUser":"","AuthPasswd":"","Config":[{"datagroupname":"","dbpath":"/home/mount/testdata/coord/11820","svcname":"11820","diaglevel":"3","role":"coord","logfilesz":"64","logfilenum":"20","transactionon":"false","preferedinstance":"A","numpagecleaners":"1","pagecleaninterval":"1000","hjbuf":"128","logbuffsize":"1024","maxprefpool":"200","maxreplsync":"10","numpreload":"0","sortbuf":"512","syncstrategy":"none","HostName":"rhelt10","User":"root","Passwd":"sequoiadb"}, ...]}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{Rc，0}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>查询已安装business响应</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>查询已安装business</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ClusterName=c1（或者HostName=rhlet10）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BusinessName=cl</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://192.168.20.197:11814/?cmd=query business&amp;BusinessName=cl</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>agent查询task请求</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Agent-&gt;OM</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{HostName:"",AgentPort:""}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{TaskType:"add business",TaskID:1, TaskStatus:"install", TaskDetail:{{"BusinessType":"sequoiadb","BusinessName":"b1", "DeployMod":"xx", "ClusterName":"c1", "Config":[{"HostName": "host1", "User":"root", "Passwd":"root", "datagroupname": "", "dbpath": "/home/db2/standalone/11830", "svcname": "11830", ...}]}}}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>{"Rc":0, "Detail":"","TaskID":"asd", "isFinish":true,"Status":"install/rollback","Progress":[{"Name":"Coord","TotalCount":7 "InstalledCount":100, "Desc":""}, {"Name":"Group1","TotalCount":3,"InstalledCount":50,"Desc":""},
 {"Name":"Group2","TotalCount":4,"InstalledCount":50,"Desc":""} ...]}</t>
-  </si>
-  <si>
-    <t>成功时：{Rc}
-校验失败时：{Rc,local} local为跳转文件login.html</t>
-  </si>
-  <si>
-    <t>{Rc,local}</t>
-  </si>
-  <si>
-    <t>{Rc,detail}</t>
-  </si>
-  <si>
-    <t>{ClusterName, Rc}</t>
-  </si>
-  <si>
-    <t>rest参数(响应最外层统一加上Rc)</t>
-  </si>
-  <si>
-    <t>删除host</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>remove host</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>查询业务</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>查询业务响应</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>查询主机运行状态</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>query host status</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>查询主机运行状态响应</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>HostInfo={ClusterName:cls1, HostInfo:[{IP, HostName, User, Passwd, SshPort:xxx, AgentPort:xxx, InstallPath:xxx, Firework, [Disk],[CPU]…}, ...], User:xxx, Passwd:xxx, SshPort:xxx, AgentPort:xxx, InstallPath:xxx}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{HostInfo:[{HostName:aa, "CPU":"90%", "Memory": { "Model": "", "Size": 2003, "Free": 916, "Unit": "M" }, "Disk":[{ "Name"
-: "/dev/sda1", "Mount": "/", "Size": 32529, "Free": 6525, "Unit": "M", "Used": 1 }]}, {...}, ...]}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{HostName:aa, "CPU":"90%", "Memory": { "Model": "", "Size": 2003, "Free": 916, "Unit": "M" }, "Disk":[{ "Name"
-: "/dev/sda1", "Mount": "/", "Size": 32529, "Free": 6525, "Unit": "M", "Used": 1 }]}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"HostInfo":[{HostName:aa, "User":"root", "Passwd"sequoiadb", "Disk":[{ "Name"
-: "/dev/sda1", "Mount": "/"}]}, {...}, ...]}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>http://192.168.20.197:11814/?cmd=query host status&amp;HostInfo={HostInfo:[{HostName:"rhelt10"}]}'</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>HostInfo={HostInfo:[{HostName:"rhelt10"}]}'</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>删除host命令</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>删除业务</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>remove business</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"AuthUser":"","AuthPasswd":"","Config":[{"datagroupname":"","dbpath":"/home/mount/testdata/coord/11820","svcname":"11820","diaglevel":"3","role":"coord","logfilesz":"64","logfilenum":"20","transactionon":"false","preferedinstance":"A","numpagecleaners":"1","pagecleaninterval":"1000","hjbuf":"128","logbuffsize":"1024","maxprefpool":"200","maxreplsync":"10","numpreload":"0","sortbuf":"512","syncstrategy":"none","HostName":"rhelt10","User":"root","Passwd":"sequoiadb"}, ...]}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{Rc，0}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>查询已安装business响应</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>查询已安装business</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ClusterName=c1（或者HostName=rhlet10）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BusinessName=cl</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>http://192.168.20.197:11814/?cmd=query business&amp;BusinessName=cl</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>agent查询task请求</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>query task</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Agent-&gt;OM</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{HostName:"",AgentPort:""}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{TaskType:"add business",TaskID:1, TaskStatus:"install", TaskDetail:{{"BusinessType":"sequoiadb","BusinessName":"b1", "DeployMod":"xx", "ClusterName":"c1", "Config":[{"HostName": "host1", "User":"root", "Passwd":"root", "datagroupname": "", "dbpath": "/home/db2/standalone/11830", "svcname": "11830", ...}]}}}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3790,7 +3791,7 @@
         <v>131</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="D2" s="5" t="s">
         <v>1</v>
@@ -3820,7 +3821,7 @@
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="9" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D4" s="9" t="s">
         <v>285</v>
@@ -3998,7 +3999,7 @@
         <v>190</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="D18" s="9" t="s">
         <v>235</v>
@@ -4012,7 +4013,7 @@
       </c>
       <c r="B19" s="4"/>
       <c r="C19" s="9" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D19" s="9"/>
       <c r="E19" s="4"/>
@@ -4028,27 +4029,27 @@
     </row>
     <row r="21" spans="1:6" s="39" customFormat="1" ht="24">
       <c r="A21" s="5" t="s">
+        <v>302</v>
+      </c>
+      <c r="B21" s="2" t="s">
         <v>303</v>
       </c>
-      <c r="B21" s="2" t="s">
-        <v>304</v>
-      </c>
       <c r="C21" s="5" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" s="2"/>
     </row>
     <row r="22" spans="1:6" s="39" customFormat="1" ht="60">
       <c r="A22" s="5" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B22" s="2"/>
       <c r="C22" s="5" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="D22" s="5"/>
       <c r="E22" s="2"/>
@@ -4138,10 +4139,10 @@
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="9" t="s">
+        <v>298</v>
+      </c>
+      <c r="B30" s="4" t="s">
         <v>299</v>
-      </c>
-      <c r="B30" s="4" t="s">
-        <v>300</v>
       </c>
       <c r="C30" s="9"/>
       <c r="D30" s="9"/>
@@ -4324,13 +4325,13 @@
     </row>
     <row r="45" spans="1:6" s="39" customFormat="1">
       <c r="A45" s="5" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>278</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="D45" s="5" t="s">
         <v>279</v>
@@ -4340,7 +4341,7 @@
     </row>
     <row r="46" spans="1:6" s="39" customFormat="1">
       <c r="A46" s="5" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B46" s="2"/>
       <c r="C46" s="5" t="s">
@@ -4360,23 +4361,23 @@
     </row>
     <row r="48" spans="1:6" s="39" customFormat="1">
       <c r="A48" s="5" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>228</v>
       </c>
       <c r="C48" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="D48" s="5" t="s">
         <v>320</v>
-      </c>
-      <c r="D48" s="5" t="s">
-        <v>321</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" s="2"/>
     </row>
     <row r="49" spans="1:6" s="39" customFormat="1">
       <c r="A49" s="5" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B49" s="2"/>
       <c r="C49" s="5"/>
@@ -4458,7 +4459,7 @@
       </c>
       <c r="B56" s="4"/>
       <c r="C56" s="9" t="s">
-        <v>293</v>
+        <v>325</v>
       </c>
       <c r="D56" s="9"/>
       <c r="E56" s="4"/>
@@ -4502,7 +4503,7 @@
       </c>
       <c r="B61" s="4"/>
       <c r="C61" s="9" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D61" s="9" t="s">
         <v>149</v>
@@ -4540,7 +4541,7 @@
       </c>
       <c r="B64" s="4"/>
       <c r="C64" s="9" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="D64" s="9"/>
       <c r="E64" s="4"/>
@@ -4588,7 +4589,7 @@
       </c>
       <c r="B68" s="41"/>
       <c r="C68" s="40" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="D68" s="40"/>
       <c r="E68" s="41"/>
@@ -4600,7 +4601,7 @@
       </c>
       <c r="B69" s="41"/>
       <c r="C69" s="40" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="D69" s="40" t="s">
         <v>144</v>
@@ -4774,7 +4775,7 @@
     </row>
     <row r="4" spans="1:5" ht="27">
       <c r="A4" s="28" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B4" s="28" t="s">
         <v>44</v>
@@ -4798,16 +4799,16 @@
     </row>
     <row r="6" spans="1:5" ht="162">
       <c r="A6" s="28" t="s">
+        <v>312</v>
+      </c>
+      <c r="B6" s="28" t="s">
         <v>313</v>
       </c>
-      <c r="B6" s="28" t="s">
+      <c r="C6" s="27" t="s">
         <v>314</v>
       </c>
-      <c r="C6" s="27" t="s">
+      <c r="D6" s="27" t="s">
         <v>315</v>
-      </c>
-      <c r="D6" s="27" t="s">
-        <v>316</v>
       </c>
       <c r="E6" s="27"/>
     </row>
@@ -4825,16 +4826,16 @@
       <c r="D8" s="27"/>
       <c r="E8" s="27"/>
     </row>
-    <row r="9" spans="1:5" ht="108">
+    <row r="9" spans="1:5" ht="81">
       <c r="A9" s="28" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B9" s="28"/>
       <c r="C9" s="27" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="D9" s="27" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="E9" s="27"/>
     </row>
@@ -4854,7 +4855,7 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="24" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="B12" s="24" t="s">
         <v>221</v>
@@ -4871,16 +4872,16 @@
     </row>
     <row r="13" spans="1:5" ht="135">
       <c r="A13" s="28" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B13" s="28" t="s">
+        <v>326</v>
+      </c>
+      <c r="C13" s="27" t="s">
         <v>323</v>
       </c>
-      <c r="C13" s="27" t="s">
-        <v>325</v>
-      </c>
       <c r="D13" s="27" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E13" s="27"/>
     </row>

--- a/internal_doc/03.开发设计/OM_web接口.xlsx
+++ b/internal_doc/03.开发设计/OM_web接口.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="6510" activeTab="4"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="6510" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="需求" sheetId="1" r:id="rId1"/>
@@ -280,7 +280,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="327">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="331">
   <si>
     <t>需求</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1648,6 +1648,22 @@
   </si>
   <si>
     <t>query task</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>HostName=host1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>删除host响应</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://192.168.20.197:11814/?cmd=remove host&amp;HostName=host1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{ "Rc": 0 }</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -4144,15 +4160,23 @@
       <c r="B30" s="4" t="s">
         <v>299</v>
       </c>
-      <c r="C30" s="9"/>
-      <c r="D30" s="9"/>
+      <c r="C30" s="9" t="s">
+        <v>327</v>
+      </c>
+      <c r="D30" s="9" t="s">
+        <v>329</v>
+      </c>
       <c r="E30" s="4"/>
       <c r="F30" s="4"/>
     </row>
     <row r="31" spans="1:6">
-      <c r="A31" s="9"/>
+      <c r="A31" s="9" t="s">
+        <v>328</v>
+      </c>
       <c r="B31" s="4"/>
-      <c r="C31" s="9"/>
+      <c r="C31" s="9" t="s">
+        <v>330</v>
+      </c>
       <c r="D31" s="9"/>
       <c r="E31" s="4"/>
       <c r="F31" s="4"/>

--- a/internal_doc/03.开发设计/OM_web接口.xlsx
+++ b/internal_doc/03.开发设计/OM_web接口.xlsx
@@ -280,7 +280,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="331">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="398" uniqueCount="332">
   <si>
     <t>需求</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1563,11 +1563,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>{HostInfo:[{HostName:aa, "CPU":"90%", "Memory": { "Model": "", "Size": 2003, "Free": 916, "Unit": "M" }, "Disk":[{ "Name"
-: "/dev/sda1", "Mount": "/", "Size": 32529, "Free": 6525, "Unit": "M", "Used": 1 }]}, {...}, ...]}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>{HostName:aa, "CPU":"90%", "Memory": { "Model": "", "Size": 2003, "Free": 916, "Unit": "M" }, "Disk":[{ "Name"
 : "/dev/sda1", "Mount": "/", "Size": 32529, "Free": 6525, "Unit": "M", "Used": 1 }]}</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1664,6 +1659,19 @@
   </si>
   <si>
     <t>{ "Rc": 0 }</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{HostInfo:[{HostName:aa, "CPU":{"User": 185754680,"Sys":46538870,"Idle": 23682187910, "Other": 66205170}, "Memory": { "Model": "", "Size": 2003, "Free": 916, "Unit": "M" }, "Disk":[{ "Name"
+: "/dev/sda1", "Mount": "/", "Size": 32529, "Free": 6525, "Unit": "M", "Used": 1 }]}, {...}, ...], "Net":{"CalendarTime": 1411549162, "Netcards": [{"Name": "eth1","RXBytes": 14757385393,"RXPackets": 44979129,"RXErrors": 0,"RXDrops": 0,"TXBytes": 14757385393,"TXPackets": 44979129,"TXErrors": 0,"TXDrops": 0 }]}}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>计算CPU利用率和网络流量需要取两次的结果进行运算才能得到，运算规则如下：
+CPU 利用率： (1-(Idle2-Idle1)/(User2+Sys2+Idle2+Other2-User1-Sys1-Idle1-Other1)) * 100%
+网络流量：
+入口流量（字节/s）: (RXBytes2-RXBytes1)/(CalendarTime2-CalendarTime1)
+出口流量（字节/s）: (TXBytes2-TXBytes1)/(CalendarTime2-CalendarTime1)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -4051,23 +4059,25 @@
         <v>303</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" s="2"/>
     </row>
-    <row r="22" spans="1:6" s="39" customFormat="1" ht="60">
+    <row r="22" spans="1:6" s="39" customFormat="1" ht="132">
       <c r="A22" s="5" t="s">
         <v>304</v>
       </c>
       <c r="B22" s="2"/>
       <c r="C22" s="5" t="s">
-        <v>306</v>
-      </c>
-      <c r="D22" s="5"/>
+        <v>330</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>331</v>
+      </c>
       <c r="E22" s="2"/>
       <c r="F22" s="2"/>
     </row>
@@ -4161,21 +4171,21 @@
         <v>299</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E30" s="4"/>
       <c r="F30" s="4"/>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="9" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B31" s="4"/>
       <c r="C31" s="9" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="D31" s="9"/>
       <c r="E31" s="4"/>
@@ -4349,13 +4359,13 @@
     </row>
     <row r="45" spans="1:6" s="39" customFormat="1">
       <c r="A45" s="5" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>278</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D45" s="5" t="s">
         <v>279</v>
@@ -4365,7 +4375,7 @@
     </row>
     <row r="46" spans="1:6" s="39" customFormat="1">
       <c r="A46" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B46" s="2"/>
       <c r="C46" s="5" t="s">
@@ -4391,10 +4401,10 @@
         <v>228</v>
       </c>
       <c r="C48" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="D48" s="5" t="s">
         <v>319</v>
-      </c>
-      <c r="D48" s="5" t="s">
-        <v>320</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" s="2"/>
@@ -4483,7 +4493,7 @@
       </c>
       <c r="B56" s="4"/>
       <c r="C56" s="9" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D56" s="9"/>
       <c r="E56" s="4"/>
@@ -4799,7 +4809,7 @@
     </row>
     <row r="4" spans="1:5" ht="27">
       <c r="A4" s="28" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B4" s="28" t="s">
         <v>44</v>
@@ -4823,16 +4833,16 @@
     </row>
     <row r="6" spans="1:5" ht="162">
       <c r="A6" s="28" t="s">
+        <v>311</v>
+      </c>
+      <c r="B6" s="28" t="s">
         <v>312</v>
       </c>
-      <c r="B6" s="28" t="s">
+      <c r="C6" s="27" t="s">
         <v>313</v>
       </c>
-      <c r="C6" s="27" t="s">
+      <c r="D6" s="27" t="s">
         <v>314</v>
-      </c>
-      <c r="D6" s="27" t="s">
-        <v>315</v>
       </c>
       <c r="E6" s="27"/>
     </row>
@@ -4856,10 +4866,10 @@
       </c>
       <c r="B9" s="28"/>
       <c r="C9" s="27" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="D9" s="27" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="E9" s="27"/>
     </row>
@@ -4879,7 +4889,7 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="24" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B12" s="24" t="s">
         <v>221</v>
@@ -4896,16 +4906,16 @@
     </row>
     <row r="13" spans="1:5" ht="135">
       <c r="A13" s="28" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B13" s="28" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C13" s="27" t="s">
+        <v>322</v>
+      </c>
+      <c r="D13" s="27" t="s">
         <v>323</v>
-      </c>
-      <c r="D13" s="27" t="s">
-        <v>324</v>
       </c>
       <c r="E13" s="27"/>
     </row>

--- a/internal_doc/03.开发设计/OM_web接口.xlsx
+++ b/internal_doc/03.开发设计/OM_web接口.xlsx
@@ -280,7 +280,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="398" uniqueCount="332">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="337">
   <si>
     <t>需求</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1672,6 +1672,26 @@
 网络流量：
 入口流量（字节/s）: (RXBytes2-RXBytes1)/(CalendarTime2-CalendarTime1)
 出口流量（字节/s）: (TXBytes2-TXBytes1)/(CalendarTime2-CalendarTime1)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>预估容量</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>预估容量响应</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"replica_num":"","group_num":"", "HostInfo":{}}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>HostInfo可有可无</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{ValidSize:3, TotalSize:10, Redundancy:2}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3787,7 +3807,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F79"/>
+  <dimension ref="A1:F81"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="22.375" style="10" customWidth="1"/>
@@ -4464,264 +4484,274 @@
       <c r="F53" s="41"/>
     </row>
     <row r="54" spans="1:6" s="42" customFormat="1">
-      <c r="A54" s="40"/>
-      <c r="B54" s="41"/>
-      <c r="C54" s="40"/>
-      <c r="D54" s="40"/>
+      <c r="A54" s="5" t="s">
+        <v>332</v>
+      </c>
+      <c r="B54" s="2"/>
+      <c r="C54" s="5" t="s">
+        <v>334</v>
+      </c>
+      <c r="D54" s="5" t="s">
+        <v>335</v>
+      </c>
       <c r="E54" s="41"/>
       <c r="F54" s="41"/>
     </row>
-    <row r="55" spans="1:6" ht="24">
-      <c r="A55" s="9" t="s">
+    <row r="55" spans="1:6" s="42" customFormat="1">
+      <c r="A55" s="5" t="s">
+        <v>333</v>
+      </c>
+      <c r="B55" s="2"/>
+      <c r="C55" s="5" t="s">
+        <v>336</v>
+      </c>
+      <c r="D55" s="5"/>
+      <c r="E55" s="41"/>
+      <c r="F55" s="41"/>
+    </row>
+    <row r="56" spans="1:6" s="42" customFormat="1">
+      <c r="A56" s="40"/>
+      <c r="B56" s="41"/>
+      <c r="C56" s="40"/>
+      <c r="D56" s="40"/>
+      <c r="E56" s="41"/>
+      <c r="F56" s="41"/>
+    </row>
+    <row r="57" spans="1:6" ht="24">
+      <c r="A57" s="9" t="s">
         <v>209</v>
       </c>
-      <c r="B55" s="4" t="s">
+      <c r="B57" s="4" t="s">
         <v>205</v>
       </c>
-      <c r="C55" s="9" t="s">
+      <c r="C57" s="9" t="s">
         <v>184</v>
       </c>
-      <c r="D55" s="9" t="s">
+      <c r="D57" s="9" t="s">
         <v>215</v>
       </c>
-      <c r="E55" s="4"/>
-      <c r="F55" s="4"/>
-    </row>
-    <row r="56" spans="1:6" ht="84">
-      <c r="A56" s="9" t="s">
-        <v>210</v>
-      </c>
-      <c r="B56" s="4"/>
-      <c r="C56" s="9" t="s">
-        <v>324</v>
-      </c>
-      <c r="D56" s="9"/>
-      <c r="E56" s="4"/>
-      <c r="F56" s="4"/>
-    </row>
-    <row r="57" spans="1:6">
-      <c r="A57" s="9"/>
-      <c r="B57" s="4"/>
-      <c r="C57" s="9"/>
-      <c r="D57" s="9"/>
       <c r="E57" s="4"/>
       <c r="F57" s="4"/>
     </row>
-    <row r="58" spans="1:6" s="4" customFormat="1">
-      <c r="A58" s="9"/>
-      <c r="C58" s="9"/>
+    <row r="58" spans="1:6" ht="84">
+      <c r="A58" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="B58" s="4"/>
+      <c r="C58" s="9" t="s">
+        <v>324</v>
+      </c>
       <c r="D58" s="9"/>
-    </row>
-    <row r="59" spans="1:6" s="4" customFormat="1">
+      <c r="E58" s="4"/>
+      <c r="F58" s="4"/>
+    </row>
+    <row r="59" spans="1:6">
       <c r="A59" s="9"/>
+      <c r="B59" s="4"/>
       <c r="C59" s="9"/>
       <c r="D59" s="9"/>
-    </row>
-    <row r="60" spans="1:6">
-      <c r="A60" s="34" t="s">
+      <c r="E59" s="4"/>
+      <c r="F59" s="4"/>
+    </row>
+    <row r="60" spans="1:6" s="4" customFormat="1">
+      <c r="A60" s="9"/>
+      <c r="C60" s="9"/>
+      <c r="D60" s="9"/>
+    </row>
+    <row r="61" spans="1:6" s="4" customFormat="1">
+      <c r="A61" s="9"/>
+      <c r="C61" s="9"/>
+      <c r="D61" s="9"/>
+    </row>
+    <row r="62" spans="1:6">
+      <c r="A62" s="34" t="s">
         <v>147</v>
       </c>
-      <c r="B60" s="35" t="s">
+      <c r="B62" s="35" t="s">
         <v>187</v>
       </c>
-      <c r="C60" s="34" t="s">
+      <c r="C62" s="34" t="s">
         <v>143</v>
       </c>
-      <c r="D60" s="34"/>
-      <c r="E60" s="35"/>
-      <c r="F60" s="35"/>
-    </row>
-    <row r="61" spans="1:6" ht="24">
-      <c r="A61" s="9" t="s">
-        <v>148</v>
-      </c>
-      <c r="B61" s="4"/>
-      <c r="C61" s="9" t="s">
-        <v>293</v>
-      </c>
-      <c r="D61" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="E61" s="4"/>
-      <c r="F61" s="4"/>
-    </row>
-    <row r="62" spans="1:6">
-      <c r="A62" s="9"/>
-      <c r="B62" s="4"/>
-      <c r="C62" s="9"/>
-      <c r="D62" s="9"/>
-      <c r="E62" s="4"/>
-      <c r="F62" s="4"/>
+      <c r="D62" s="34"/>
+      <c r="E62" s="35"/>
+      <c r="F62" s="35"/>
     </row>
     <row r="63" spans="1:6" ht="24">
       <c r="A63" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="B63" s="4" t="s">
-        <v>204</v>
-      </c>
+        <v>148</v>
+      </c>
+      <c r="B63" s="4"/>
       <c r="C63" s="9" t="s">
-        <v>194</v>
+        <v>293</v>
       </c>
       <c r="D63" s="9" t="s">
-        <v>214</v>
+        <v>149</v>
       </c>
       <c r="E63" s="4"/>
       <c r="F63" s="4"/>
     </row>
     <row r="64" spans="1:6">
-      <c r="A64" s="9" t="s">
-        <v>162</v>
-      </c>
+      <c r="A64" s="9"/>
       <c r="B64" s="4"/>
-      <c r="C64" s="9" t="s">
-        <v>294</v>
-      </c>
+      <c r="C64" s="9"/>
       <c r="D64" s="9"/>
       <c r="E64" s="4"/>
       <c r="F64" s="4"/>
     </row>
     <row r="65" spans="1:6" ht="24">
       <c r="A65" s="9" t="s">
-        <v>195</v>
+        <v>161</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="C65" s="9" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="D65" s="9" t="s">
-        <v>198</v>
+        <v>214</v>
       </c>
       <c r="E65" s="4"/>
       <c r="F65" s="4"/>
     </row>
     <row r="66" spans="1:6">
       <c r="A66" s="9" t="s">
-        <v>199</v>
-      </c>
-      <c r="B66" s="4" t="s">
-        <v>200</v>
-      </c>
-      <c r="C66" s="9"/>
+        <v>162</v>
+      </c>
+      <c r="B66" s="4"/>
+      <c r="C66" s="9" t="s">
+        <v>294</v>
+      </c>
       <c r="D66" s="9"/>
       <c r="E66" s="4"/>
       <c r="F66" s="4"/>
     </row>
-    <row r="67" spans="1:6">
-      <c r="A67" s="9"/>
-      <c r="B67" s="4"/>
-      <c r="C67" s="9"/>
-      <c r="D67" s="9"/>
+    <row r="67" spans="1:6" ht="24">
+      <c r="A67" s="9" t="s">
+        <v>195</v>
+      </c>
+      <c r="B67" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="C67" s="9" t="s">
+        <v>197</v>
+      </c>
+      <c r="D67" s="9" t="s">
+        <v>198</v>
+      </c>
       <c r="E67" s="4"/>
       <c r="F67" s="4"/>
     </row>
-    <row r="68" spans="1:6" s="42" customFormat="1">
-      <c r="A68" s="40" t="s">
+    <row r="68" spans="1:6">
+      <c r="A68" s="9" t="s">
+        <v>199</v>
+      </c>
+      <c r="B68" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="C68" s="9"/>
+      <c r="D68" s="9"/>
+      <c r="E68" s="4"/>
+      <c r="F68" s="4"/>
+    </row>
+    <row r="69" spans="1:6">
+      <c r="A69" s="9"/>
+      <c r="B69" s="4"/>
+      <c r="C69" s="9"/>
+      <c r="D69" s="9"/>
+      <c r="E69" s="4"/>
+      <c r="F69" s="4"/>
+    </row>
+    <row r="70" spans="1:6" s="42" customFormat="1">
+      <c r="A70" s="40" t="s">
         <v>153</v>
       </c>
-      <c r="B68" s="41"/>
-      <c r="C68" s="40" t="s">
+      <c r="B70" s="41"/>
+      <c r="C70" s="40" t="s">
         <v>295</v>
-      </c>
-      <c r="D68" s="40"/>
-      <c r="E68" s="41"/>
-      <c r="F68" s="41"/>
-    </row>
-    <row r="69" spans="1:6" s="42" customFormat="1" ht="24">
-      <c r="A69" s="40" t="s">
-        <v>154</v>
-      </c>
-      <c r="B69" s="41"/>
-      <c r="C69" s="40" t="s">
-        <v>294</v>
-      </c>
-      <c r="D69" s="40" t="s">
-        <v>144</v>
-      </c>
-      <c r="E69" s="41"/>
-      <c r="F69" s="41"/>
-    </row>
-    <row r="70" spans="1:6" s="42" customFormat="1" ht="24">
-      <c r="A70" s="40" t="s">
-        <v>151</v>
-      </c>
-      <c r="B70" s="41" t="s">
-        <v>156</v>
-      </c>
-      <c r="C70" s="40" t="s">
-        <v>152</v>
       </c>
       <c r="D70" s="40"/>
       <c r="E70" s="41"/>
       <c r="F70" s="41"/>
     </row>
-    <row r="71" spans="1:6" s="42" customFormat="1" ht="48">
+    <row r="71" spans="1:6" s="42" customFormat="1" ht="24">
       <c r="A71" s="40" t="s">
-        <v>155</v>
-      </c>
-      <c r="B71" s="41" t="s">
-        <v>156</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="B71" s="41"/>
       <c r="C71" s="40" t="s">
-        <v>159</v>
+        <v>294</v>
       </c>
       <c r="D71" s="40" t="s">
-        <v>160</v>
+        <v>144</v>
       </c>
       <c r="E71" s="41"/>
       <c r="F71" s="41"/>
     </row>
-    <row r="72" spans="1:6" s="42" customFormat="1" ht="36">
+    <row r="72" spans="1:6" s="42" customFormat="1" ht="24">
       <c r="A72" s="40" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="B72" s="41" t="s">
         <v>156</v>
       </c>
       <c r="C72" s="40" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="D72" s="40"/>
       <c r="E72" s="41"/>
       <c r="F72" s="41"/>
     </row>
-    <row r="73" spans="1:6" s="21" customFormat="1" ht="24">
-      <c r="A73" s="43" t="s">
-        <v>146</v>
-      </c>
-      <c r="B73" s="44"/>
-      <c r="C73" s="43"/>
-      <c r="D73" s="43" t="s">
-        <v>145</v>
-      </c>
-      <c r="E73" s="44"/>
-      <c r="F73" s="44"/>
-    </row>
-    <row r="74" spans="1:6" s="42" customFormat="1">
-      <c r="A74" s="40"/>
-      <c r="B74" s="41"/>
-      <c r="C74" s="40"/>
+    <row r="73" spans="1:6" s="42" customFormat="1" ht="48">
+      <c r="A73" s="40" t="s">
+        <v>155</v>
+      </c>
+      <c r="B73" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="C73" s="40" t="s">
+        <v>159</v>
+      </c>
+      <c r="D73" s="40" t="s">
+        <v>160</v>
+      </c>
+      <c r="E73" s="41"/>
+      <c r="F73" s="41"/>
+    </row>
+    <row r="74" spans="1:6" s="42" customFormat="1" ht="36">
+      <c r="A74" s="40" t="s">
+        <v>157</v>
+      </c>
+      <c r="B74" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="C74" s="40" t="s">
+        <v>158</v>
+      </c>
       <c r="D74" s="40"/>
       <c r="E74" s="41"/>
       <c r="F74" s="41"/>
     </row>
-    <row r="75" spans="1:6">
-      <c r="A75" s="9"/>
-      <c r="B75" s="4"/>
-      <c r="C75" s="9"/>
-      <c r="D75" s="9"/>
-      <c r="E75" s="4"/>
-      <c r="F75" s="4"/>
-    </row>
-    <row r="76" spans="1:6">
-      <c r="A76" s="9"/>
-      <c r="B76" s="4"/>
-      <c r="C76" s="9"/>
-      <c r="D76" s="9"/>
-      <c r="E76" s="4"/>
-      <c r="F76" s="4"/>
+    <row r="75" spans="1:6" s="21" customFormat="1" ht="24">
+      <c r="A75" s="43" t="s">
+        <v>146</v>
+      </c>
+      <c r="B75" s="44"/>
+      <c r="C75" s="43"/>
+      <c r="D75" s="43" t="s">
+        <v>145</v>
+      </c>
+      <c r="E75" s="44"/>
+      <c r="F75" s="44"/>
+    </row>
+    <row r="76" spans="1:6" s="42" customFormat="1">
+      <c r="A76" s="40"/>
+      <c r="B76" s="41"/>
+      <c r="C76" s="40"/>
+      <c r="D76" s="40"/>
+      <c r="E76" s="41"/>
+      <c r="F76" s="41"/>
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="9"/>
@@ -4746,6 +4776,22 @@
       <c r="D79" s="9"/>
       <c r="E79" s="4"/>
       <c r="F79" s="4"/>
+    </row>
+    <row r="80" spans="1:6">
+      <c r="A80" s="9"/>
+      <c r="B80" s="4"/>
+      <c r="C80" s="9"/>
+      <c r="D80" s="9"/>
+      <c r="E80" s="4"/>
+      <c r="F80" s="4"/>
+    </row>
+    <row r="81" spans="1:6">
+      <c r="A81" s="9"/>
+      <c r="B81" s="4"/>
+      <c r="C81" s="9"/>
+      <c r="D81" s="9"/>
+      <c r="E81" s="4"/>
+      <c r="F81" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/internal_doc/03.开发设计/OM_web接口.xlsx
+++ b/internal_doc/03.开发设计/OM_web接口.xlsx
@@ -1028,10 +1028,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>{"TaskID":"asd"}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>create cluster</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1198,10 +1194,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>http://192.168.20.197:11814/?cmd=query progress&amp;Task={"TaskID":"12345"}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>HostInfo={ClusterName:cls1,HostInfo:[{IP/HostName:xxx, User:xxx, Passwd:xxx, SshPort:xxx, AgentPort:xxx}, ...],User:usr1,Passwd:Passwd1, SshPort:xxx, AgentPort:xxx}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1637,11 +1629,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>{"Rc":0, "Detail":"","TaskID":"asd", "isFinish":true,"Status":"install/rollback","Progress":[{"Name":"Coord","TotalCount":7 "InstalledCount":100, "Desc":""}, {"Name":"Group1","TotalCount":3,"InstalledCount":50,"Desc":""},
-{"Name":"Group2","TotalCount":4,"InstalledCount":50,"Desc":""} ...]}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>query task</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1692,6 +1679,18 @@
   </si>
   <si>
     <t>{ValidSize:3, TotalSize:10, Redundancy:2}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{ "TaskID": 1, "TaskType": "add business", "IsEnable": true, "IsFinish": true, "Status": "rollback", "Progress": [ { "Name": "Coord", "TotalCount": 1, "InstalledCount": 1, "Desc": "Finish installing coord[rhelt10:11820]" }, { "Name": "Catalog", "TotalCount": 1, "InstalledCount": 1, "Desc": "Finish installing catalog[rhelt10:11830]" }, { "Name": "DATAGROUP1", "TotalCount": 1, "InstalledCount": 0, "Desc": "Installing data node[rhelt10:11840]" } ], "ErrMsg": "" }</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://192.168.20.197:11814/?cmd=query progress&amp;TaskID=1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TaskID=1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3835,7 +3834,7 @@
         <v>131</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="D2" s="5" t="s">
         <v>1</v>
@@ -3848,13 +3847,13 @@
         <v>150</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E3" s="4"/>
       <c r="F3" s="4"/>
@@ -3865,10 +3864,10 @@
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="9" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="E4" s="4"/>
       <c r="F4" s="4"/>
@@ -3886,13 +3885,13 @@
         <v>163</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C6" s="9" t="s">
         <v>165</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
@@ -3903,10 +3902,10 @@
       </c>
       <c r="B7" s="4"/>
       <c r="C7" s="9" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="E7" s="4"/>
       <c r="F7" s="4"/>
@@ -3921,27 +3920,27 @@
     </row>
     <row r="9" spans="1:6" s="38" customFormat="1">
       <c r="A9" s="36" t="s">
+        <v>228</v>
+      </c>
+      <c r="B9" s="37" t="s">
+        <v>229</v>
+      </c>
+      <c r="C9" s="36" t="s">
+        <v>227</v>
+      </c>
+      <c r="D9" s="36" t="s">
         <v>230</v>
-      </c>
-      <c r="B9" s="37" t="s">
-        <v>231</v>
-      </c>
-      <c r="C9" s="36" t="s">
-        <v>229</v>
-      </c>
-      <c r="D9" s="36" t="s">
-        <v>232</v>
       </c>
       <c r="E9" s="37"/>
       <c r="F9" s="37"/>
     </row>
     <row r="10" spans="1:6" s="38" customFormat="1">
       <c r="A10" s="36" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="B10" s="37"/>
       <c r="C10" s="36" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="D10" s="36"/>
       <c r="E10" s="37"/>
@@ -3960,13 +3959,13 @@
         <v>122</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E12" s="4"/>
       <c r="F12" s="4"/>
@@ -3977,10 +3976,10 @@
       </c>
       <c r="B13" s="4"/>
       <c r="C13" s="9" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="E13" s="4"/>
       <c r="F13" s="4"/>
@@ -4000,13 +3999,13 @@
         <v>124</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C15" s="9" t="s">
         <v>179</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E15" s="4"/>
       <c r="F15" s="4"/>
@@ -4017,10 +4016,10 @@
       </c>
       <c r="B16" s="4"/>
       <c r="C16" s="9" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="E16" s="4"/>
       <c r="F16" s="4"/>
@@ -4040,13 +4039,13 @@
         <v>126</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E18" s="4"/>
       <c r="F18" s="4"/>
@@ -4057,7 +4056,7 @@
       </c>
       <c r="B19" s="4"/>
       <c r="C19" s="9" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="D19" s="9"/>
       <c r="E19" s="4"/>
@@ -4073,30 +4072,30 @@
     </row>
     <row r="21" spans="1:6" s="39" customFormat="1" ht="24">
       <c r="A21" s="5" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" s="2"/>
     </row>
     <row r="22" spans="1:6" s="39" customFormat="1" ht="132">
       <c r="A22" s="5" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="B22" s="2"/>
       <c r="C22" s="5" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" s="2"/>
@@ -4113,27 +4112,27 @@
     </row>
     <row r="24" spans="1:6" s="39" customFormat="1">
       <c r="A24" s="5" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" s="2"/>
     </row>
     <row r="25" spans="1:6" s="39" customFormat="1">
       <c r="A25" s="5" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B25" s="2"/>
       <c r="C25" s="5" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="D25" s="5"/>
       <c r="E25" s="2"/>
@@ -4152,13 +4151,13 @@
         <v>128</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" s="2"/>
@@ -4169,7 +4168,7 @@
       </c>
       <c r="B28" s="2"/>
       <c r="C28" s="5" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="D28" s="5"/>
       <c r="E28" s="2"/>
@@ -4185,27 +4184,27 @@
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="9" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="E30" s="4"/>
       <c r="F30" s="4"/>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="9" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="B31" s="4"/>
       <c r="C31" s="9" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="D31" s="9"/>
       <c r="E31" s="4"/>
@@ -4226,11 +4225,11 @@
         <v>132</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C33" s="9"/>
       <c r="D33" s="9" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E33" s="4"/>
       <c r="F33" s="4"/>
@@ -4241,10 +4240,10 @@
       </c>
       <c r="B34" s="4"/>
       <c r="C34" s="9" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="E34" s="4"/>
       <c r="F34" s="4"/>
@@ -4264,13 +4263,13 @@
         <v>134</v>
       </c>
       <c r="B36" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="C36" s="9" t="s">
         <v>211</v>
       </c>
-      <c r="C36" s="9" t="s">
-        <v>212</v>
-      </c>
       <c r="D36" s="9" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="E36" s="4"/>
       <c r="F36" s="4"/>
@@ -4284,7 +4283,7 @@
         <v>180</v>
       </c>
       <c r="D37" s="9" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="E37" s="4"/>
       <c r="F37" s="4"/>
@@ -4304,13 +4303,13 @@
         <v>136</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C39" s="9" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D39" s="9" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="E39" s="4"/>
       <c r="F39" s="4"/>
@@ -4344,13 +4343,13 @@
         <v>138</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C42" s="9" t="s">
         <v>183</v>
       </c>
       <c r="D42" s="9" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="E42" s="4"/>
       <c r="F42" s="4"/>
@@ -4361,7 +4360,7 @@
       </c>
       <c r="B43" s="4"/>
       <c r="C43" s="9" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="D43" s="9" t="s">
         <v>120</v>
@@ -4379,27 +4378,27 @@
     </row>
     <row r="45" spans="1:6" s="39" customFormat="1">
       <c r="A45" s="5" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" s="2"/>
     </row>
     <row r="46" spans="1:6" s="39" customFormat="1">
       <c r="A46" s="5" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="B46" s="2"/>
       <c r="C46" s="5" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="D46" s="5"/>
       <c r="E46" s="2"/>
@@ -4415,23 +4414,23 @@
     </row>
     <row r="48" spans="1:6" s="39" customFormat="1">
       <c r="A48" s="5" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" s="2"/>
     </row>
     <row r="49" spans="1:6" s="39" customFormat="1">
       <c r="A49" s="5" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B49" s="2"/>
       <c r="C49" s="5"/>
@@ -4455,10 +4454,10 @@
         <v>142</v>
       </c>
       <c r="C51" s="5" t="s">
+        <v>279</v>
+      </c>
+      <c r="D51" s="5" t="s">
         <v>281</v>
-      </c>
-      <c r="D51" s="5" t="s">
-        <v>283</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" s="2"/>
@@ -4469,7 +4468,7 @@
       </c>
       <c r="B52" s="2"/>
       <c r="C52" s="5" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="D52" s="5"/>
       <c r="E52" s="2"/>
@@ -4485,25 +4484,25 @@
     </row>
     <row r="54" spans="1:6" s="42" customFormat="1">
       <c r="A54" s="5" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="B54" s="2"/>
       <c r="C54" s="5" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="D54" s="5" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="E54" s="41"/>
       <c r="F54" s="41"/>
     </row>
     <row r="55" spans="1:6" s="42" customFormat="1">
       <c r="A55" s="5" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="B55" s="2"/>
       <c r="C55" s="5" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="D55" s="5"/>
       <c r="E55" s="41"/>
@@ -4517,29 +4516,29 @@
       <c r="E56" s="41"/>
       <c r="F56" s="41"/>
     </row>
-    <row r="57" spans="1:6" ht="24">
+    <row r="57" spans="1:6">
       <c r="A57" s="9" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C57" s="9" t="s">
-        <v>184</v>
+        <v>336</v>
       </c>
       <c r="D57" s="9" t="s">
-        <v>215</v>
+        <v>335</v>
       </c>
       <c r="E57" s="4"/>
       <c r="F57" s="4"/>
     </row>
-    <row r="58" spans="1:6" ht="84">
+    <row r="58" spans="1:6" ht="96">
       <c r="A58" s="9" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B58" s="4"/>
       <c r="C58" s="9" t="s">
-        <v>324</v>
+        <v>334</v>
       </c>
       <c r="D58" s="9"/>
       <c r="E58" s="4"/>
@@ -4568,7 +4567,7 @@
         <v>147</v>
       </c>
       <c r="B62" s="35" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C62" s="34" t="s">
         <v>143</v>
@@ -4583,7 +4582,7 @@
       </c>
       <c r="B63" s="4"/>
       <c r="C63" s="9" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="D63" s="9" t="s">
         <v>149</v>
@@ -4604,13 +4603,13 @@
         <v>161</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C65" s="9" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D65" s="9" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E65" s="4"/>
       <c r="F65" s="4"/>
@@ -4621,7 +4620,7 @@
       </c>
       <c r="B66" s="4"/>
       <c r="C66" s="9" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="D66" s="9"/>
       <c r="E66" s="4"/>
@@ -4629,26 +4628,26 @@
     </row>
     <row r="67" spans="1:6" ht="24">
       <c r="A67" s="9" t="s">
+        <v>194</v>
+      </c>
+      <c r="B67" s="4" t="s">
         <v>195</v>
       </c>
-      <c r="B67" s="4" t="s">
+      <c r="C67" s="9" t="s">
         <v>196</v>
       </c>
-      <c r="C67" s="9" t="s">
+      <c r="D67" s="9" t="s">
         <v>197</v>
-      </c>
-      <c r="D67" s="9" t="s">
-        <v>198</v>
       </c>
       <c r="E67" s="4"/>
       <c r="F67" s="4"/>
     </row>
     <row r="68" spans="1:6">
       <c r="A68" s="9" t="s">
+        <v>198</v>
+      </c>
+      <c r="B68" s="4" t="s">
         <v>199</v>
-      </c>
-      <c r="B68" s="4" t="s">
-        <v>200</v>
       </c>
       <c r="C68" s="9"/>
       <c r="D68" s="9"/>
@@ -4669,7 +4668,7 @@
       </c>
       <c r="B70" s="41"/>
       <c r="C70" s="40" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="D70" s="40"/>
       <c r="E70" s="41"/>
@@ -4681,7 +4680,7 @@
       </c>
       <c r="B71" s="41"/>
       <c r="C71" s="40" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="D71" s="40" t="s">
         <v>144</v>
@@ -4814,16 +4813,16 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="24" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B1" s="24" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C1" s="25" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="D1" s="25" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="E1" s="25" t="s">
         <v>51</v>
@@ -4831,19 +4830,19 @@
     </row>
     <row r="2" spans="1:5" ht="67.5">
       <c r="A2" s="27" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B2" s="28" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C2" s="27" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D2" s="27" t="s">
+        <v>222</v>
+      </c>
+      <c r="E2" s="29" t="s">
         <v>224</v>
-      </c>
-      <c r="E2" s="29" t="s">
-        <v>226</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -4855,19 +4854,19 @@
     </row>
     <row r="4" spans="1:5" ht="27">
       <c r="A4" s="28" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="B4" s="28" t="s">
         <v>44</v>
       </c>
       <c r="C4" s="27" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="D4" s="27" t="s">
+        <v>235</v>
+      </c>
+      <c r="E4" s="29" t="s">
         <v>237</v>
-      </c>
-      <c r="E4" s="29" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -4879,16 +4878,16 @@
     </row>
     <row r="6" spans="1:5" ht="162">
       <c r="A6" s="28" t="s">
+        <v>309</v>
+      </c>
+      <c r="B6" s="28" t="s">
+        <v>310</v>
+      </c>
+      <c r="C6" s="27" t="s">
         <v>311</v>
       </c>
-      <c r="B6" s="28" t="s">
+      <c r="D6" s="27" t="s">
         <v>312</v>
-      </c>
-      <c r="C6" s="27" t="s">
-        <v>313</v>
-      </c>
-      <c r="D6" s="27" t="s">
-        <v>314</v>
       </c>
       <c r="E6" s="27"/>
     </row>
@@ -4908,14 +4907,14 @@
     </row>
     <row r="9" spans="1:5" ht="81">
       <c r="A9" s="28" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="B9" s="28"/>
       <c r="C9" s="27" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="D9" s="27" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="E9" s="27"/>
     </row>
@@ -4935,16 +4934,16 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="24" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="B12" s="24" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C12" s="25" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="D12" s="25" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="E12" s="25" t="s">
         <v>51</v>
@@ -4952,16 +4951,16 @@
     </row>
     <row r="13" spans="1:5" ht="135">
       <c r="A13" s="28" t="s">
+        <v>318</v>
+      </c>
+      <c r="B13" s="28" t="s">
+        <v>322</v>
+      </c>
+      <c r="C13" s="27" t="s">
         <v>320</v>
       </c>
-      <c r="B13" s="28" t="s">
-        <v>325</v>
-      </c>
-      <c r="C13" s="27" t="s">
-        <v>322</v>
-      </c>
       <c r="D13" s="27" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="E13" s="27"/>
     </row>
@@ -5068,160 +5067,160 @@
   <sheetData>
     <row r="1" spans="1:4" ht="27">
       <c r="A1" s="23" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="27">
       <c r="A2" s="23" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="25" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B4" s="25" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C4" s="25"/>
       <c r="D4" s="25"/>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="30" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B5" s="26" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C5" s="26"/>
       <c r="D5" s="26"/>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="30" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="B6" s="26" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C6" s="26"/>
       <c r="D6" s="26"/>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="30" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B7" s="26" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C7" s="26"/>
       <c r="D7" s="26"/>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="30" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B8" s="26" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C8" s="26"/>
       <c r="D8" s="26"/>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="30" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B9" s="26" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C9" s="26"/>
       <c r="D9" s="26"/>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="30" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B10" s="26" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C10" s="26"/>
       <c r="D10" s="26"/>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="30" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B11" s="26" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C11" s="26"/>
       <c r="D11" s="26"/>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="30" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B12" s="26" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="C12" s="26"/>
       <c r="D12" s="26"/>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="30" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B13" s="26" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="C13" s="26"/>
       <c r="D13" s="26"/>
     </row>
     <row r="14" spans="1:4" ht="27">
       <c r="A14" s="30" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B14" s="26" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="C14" s="26"/>
       <c r="D14" s="26"/>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="31" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="B15" s="32" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="C15" s="32"/>
       <c r="D15" s="32"/>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="33" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B16" s="32" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="C16" s="32"/>
       <c r="D16" s="32"/>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="33" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B17" s="32" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="C17" s="32"/>
       <c r="D17" s="32"/>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="33" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B18" s="32" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="C18" s="32"/>
       <c r="D18" s="32"/>

--- a/internal_doc/03.开发设计/OM_web接口.xlsx
+++ b/internal_doc/03.开发设计/OM_web接口.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="6510" activeTab="3"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="6510" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="需求" sheetId="1" r:id="rId1"/>
@@ -280,7 +280,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="337">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="404" uniqueCount="338">
   <si>
     <t>需求</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1462,10 +1462,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>{ "Rc": 0 }{ "BusinessName": "b1" },{}...</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>BusinessName=xxx</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1557,11 +1553,6 @@
   <si>
     <t>{HostName:aa, "CPU":"90%", "Memory": { "Model": "", "Size": 2003, "Free": 916, "Unit": "M" }, "Disk":[{ "Name"
 : "/dev/sda1", "Mount": "/", "Size": 32529, "Free": 6525, "Unit": "M", "Used": 1 }]}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"HostInfo":[{HostName:aa, "User":"root", "Passwd"sequoiadb", "Disk":[{ "Name"
-: "/dev/sda1", "Mount": "/"}]}, {...}, ...]}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1670,18 +1661,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>{"replica_num":"","group_num":"", "HostInfo":{}}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>HostInfo可有可无</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{ValidSize:3, TotalSize:10, Redundancy:2}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>{ "TaskID": 1, "TaskType": "add business", "IsEnable": true, "IsFinish": true, "Status": "rollback", "Progress": [ { "Name": "Coord", "TotalCount": 1, "InstalledCount": 1, "Desc": "Finish installing coord[rhelt10:11820]" }, { "Name": "Catalog", "TotalCount": 1, "InstalledCount": 1, "Desc": "Finish installing catalog[rhelt10:11830]" }, { "Name": "DATAGROUP1", "TotalCount": 1, "InstalledCount": 0, "Desc": "Installing data node[rhelt10:11840]" } ], "ErrMsg": "" }</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1691,6 +1670,32 @@
   </si>
   <si>
     <t>TaskID=1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{ "Rc": 0 }{ "BusinessName": "b1", "BusinessType": "" }</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"BusinessName": "b1", "BusinessType": "sequoiadb", "DeployMod": "distribution", "ClusterName": "c1" }</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://192.168.20.197:11814/?cmd=predict capacity&amp;TemplateInfo={ClusterName:"c1", Property:[{Name:"replicanum", Value:"2"}, {Name:"datagroupnum", Value:"2"}], HostInfo:[{HostName:"rhelt10"}]}
+HostInfo可有可无</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{ClusterName:"c1", Property:[{Name:"replicanum", Value:"2"}, {Name:"datagroupnum", Value:"2"}], HostInfo:[{HostName:"rhelt10"}]}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{ "TotalSize": 6525, "ValidSize": 3262, "RedundancyRate": 1 }</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"HostInfo":[{HostName:aa, "Disk":[{ "Name"
+: "/dev/sda1", "Mount": "/"}]}], "Net":{"Name":"eth1"}}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3834,7 +3839,7 @@
         <v>131</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="D2" s="5" t="s">
         <v>1</v>
@@ -3864,10 +3869,10 @@
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="9" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="E4" s="4"/>
       <c r="F4" s="4"/>
@@ -3905,7 +3910,7 @@
         <v>207</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="E7" s="4"/>
       <c r="F7" s="4"/>
@@ -3936,11 +3941,11 @@
     </row>
     <row r="10" spans="1:6" s="38" customFormat="1">
       <c r="A10" s="36" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B10" s="37"/>
       <c r="C10" s="36" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="D10" s="36"/>
       <c r="E10" s="37"/>
@@ -3976,10 +3981,10 @@
       </c>
       <c r="B13" s="4"/>
       <c r="C13" s="9" t="s">
+        <v>284</v>
+      </c>
+      <c r="D13" s="9" t="s">
         <v>285</v>
-      </c>
-      <c r="D13" s="9" t="s">
-        <v>286</v>
       </c>
       <c r="E13" s="4"/>
       <c r="F13" s="4"/>
@@ -4016,7 +4021,7 @@
       </c>
       <c r="B16" s="4"/>
       <c r="C16" s="9" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D16" s="9" t="s">
         <v>231</v>
@@ -4042,7 +4047,7 @@
         <v>189</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D18" s="9" t="s">
         <v>233</v>
@@ -4056,7 +4061,7 @@
       </c>
       <c r="B19" s="4"/>
       <c r="C19" s="9" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D19" s="9"/>
       <c r="E19" s="4"/>
@@ -4072,30 +4077,30 @@
     </row>
     <row r="21" spans="1:6" s="39" customFormat="1" ht="24">
       <c r="A21" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="B21" s="2" t="s">
         <v>300</v>
       </c>
-      <c r="B21" s="2" t="s">
-        <v>301</v>
-      </c>
       <c r="C21" s="5" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" s="2"/>
     </row>
     <row r="22" spans="1:6" s="39" customFormat="1" ht="132">
       <c r="A22" s="5" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B22" s="2"/>
       <c r="C22" s="5" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" s="2"/>
@@ -4184,27 +4189,27 @@
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="9" t="s">
+        <v>295</v>
+      </c>
+      <c r="B30" s="4" t="s">
         <v>296</v>
       </c>
-      <c r="B30" s="4" t="s">
-        <v>297</v>
-      </c>
       <c r="C30" s="9" t="s">
+        <v>321</v>
+      </c>
+      <c r="D30" s="9" t="s">
         <v>323</v>
-      </c>
-      <c r="D30" s="9" t="s">
-        <v>325</v>
       </c>
       <c r="E30" s="4"/>
       <c r="F30" s="4"/>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="9" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="B31" s="4"/>
       <c r="C31" s="9" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="D31" s="9"/>
       <c r="E31" s="4"/>
@@ -4243,7 +4248,7 @@
         <v>201</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E34" s="4"/>
       <c r="F34" s="4"/>
@@ -4283,7 +4288,7 @@
         <v>180</v>
       </c>
       <c r="D37" s="9" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="E37" s="4"/>
       <c r="F37" s="4"/>
@@ -4360,7 +4365,7 @@
       </c>
       <c r="B43" s="4"/>
       <c r="C43" s="9" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D43" s="9" t="s">
         <v>120</v>
@@ -4378,13 +4383,13 @@
     </row>
     <row r="45" spans="1:6" s="39" customFormat="1">
       <c r="A45" s="5" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>276</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="D45" s="5" t="s">
         <v>277</v>
@@ -4394,11 +4399,11 @@
     </row>
     <row r="46" spans="1:6" s="39" customFormat="1">
       <c r="A46" s="5" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="B46" s="2"/>
       <c r="C46" s="5" t="s">
-        <v>278</v>
+        <v>332</v>
       </c>
       <c r="D46" s="5"/>
       <c r="E46" s="2"/>
@@ -4414,26 +4419,28 @@
     </row>
     <row r="48" spans="1:6" s="39" customFormat="1">
       <c r="A48" s="5" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>226</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" s="2"/>
     </row>
-    <row r="49" spans="1:6" s="39" customFormat="1">
+    <row r="49" spans="1:6" s="39" customFormat="1" ht="24">
       <c r="A49" s="5" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B49" s="2"/>
-      <c r="C49" s="5"/>
+      <c r="C49" s="5" t="s">
+        <v>333</v>
+      </c>
       <c r="D49" s="5"/>
       <c r="E49" s="2"/>
       <c r="F49" s="2"/>
@@ -4454,10 +4461,10 @@
         <v>142</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" s="2"/>
@@ -4468,7 +4475,7 @@
       </c>
       <c r="B52" s="2"/>
       <c r="C52" s="5" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="D52" s="5"/>
       <c r="E52" s="2"/>
@@ -4482,27 +4489,27 @@
       <c r="E53" s="41"/>
       <c r="F53" s="41"/>
     </row>
-    <row r="54" spans="1:6" s="42" customFormat="1">
+    <row r="54" spans="1:6" s="42" customFormat="1" ht="60">
       <c r="A54" s="5" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="B54" s="2"/>
       <c r="C54" s="5" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="D54" s="5" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="E54" s="41"/>
       <c r="F54" s="41"/>
     </row>
     <row r="55" spans="1:6" s="42" customFormat="1">
       <c r="A55" s="5" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="B55" s="2"/>
       <c r="C55" s="5" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="D55" s="5"/>
       <c r="E55" s="41"/>
@@ -4524,10 +4531,10 @@
         <v>204</v>
       </c>
       <c r="C57" s="9" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="D57" s="9" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="E57" s="4"/>
       <c r="F57" s="4"/>
@@ -4538,7 +4545,7 @@
       </c>
       <c r="B58" s="4"/>
       <c r="C58" s="9" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="D58" s="9"/>
       <c r="E58" s="4"/>
@@ -4582,7 +4589,7 @@
       </c>
       <c r="B63" s="4"/>
       <c r="C63" s="9" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D63" s="9" t="s">
         <v>149</v>
@@ -4620,7 +4627,7 @@
       </c>
       <c r="B66" s="4"/>
       <c r="C66" s="9" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="D66" s="9"/>
       <c r="E66" s="4"/>
@@ -4668,7 +4675,7 @@
       </c>
       <c r="B70" s="41"/>
       <c r="C70" s="40" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D70" s="40"/>
       <c r="E70" s="41"/>
@@ -4680,7 +4687,7 @@
       </c>
       <c r="B71" s="41"/>
       <c r="C71" s="40" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="D71" s="40" t="s">
         <v>144</v>
@@ -4854,7 +4861,7 @@
     </row>
     <row r="4" spans="1:5" ht="27">
       <c r="A4" s="28" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="B4" s="28" t="s">
         <v>44</v>
@@ -4878,16 +4885,16 @@
     </row>
     <row r="6" spans="1:5" ht="162">
       <c r="A6" s="28" t="s">
+        <v>307</v>
+      </c>
+      <c r="B6" s="28" t="s">
+        <v>308</v>
+      </c>
+      <c r="C6" s="27" t="s">
         <v>309</v>
       </c>
-      <c r="B6" s="28" t="s">
+      <c r="D6" s="27" t="s">
         <v>310</v>
-      </c>
-      <c r="C6" s="27" t="s">
-        <v>311</v>
-      </c>
-      <c r="D6" s="27" t="s">
-        <v>312</v>
       </c>
       <c r="E6" s="27"/>
     </row>
@@ -4907,14 +4914,14 @@
     </row>
     <row r="9" spans="1:5" ht="81">
       <c r="A9" s="28" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B9" s="28"/>
       <c r="C9" s="27" t="s">
-        <v>305</v>
+        <v>337</v>
       </c>
       <c r="D9" s="27" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E9" s="27"/>
     </row>
@@ -4934,7 +4941,7 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="24" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="B12" s="24" t="s">
         <v>219</v>
@@ -4951,16 +4958,16 @@
     </row>
     <row r="13" spans="1:5" ht="135">
       <c r="A13" s="28" t="s">
+        <v>316</v>
+      </c>
+      <c r="B13" s="28" t="s">
+        <v>320</v>
+      </c>
+      <c r="C13" s="27" t="s">
         <v>318</v>
       </c>
-      <c r="B13" s="28" t="s">
-        <v>322</v>
-      </c>
-      <c r="C13" s="27" t="s">
-        <v>320</v>
-      </c>
       <c r="D13" s="27" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="E13" s="27"/>
     </row>

--- a/internal_doc/03.开发设计/OM_web接口.xlsx
+++ b/internal_doc/03.开发设计/OM_web接口.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="6510" activeTab="4"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="6510" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="需求" sheetId="1" r:id="rId1"/>
@@ -13,6 +13,8 @@
     <sheet name="消息定义" sheetId="4" r:id="rId4"/>
     <sheet name="agent接口" sheetId="6" r:id="rId5"/>
     <sheet name="Sheet3" sheetId="7" r:id="rId6"/>
+    <sheet name="Sheet1" sheetId="8" r:id="rId7"/>
+    <sheet name="与agent消息(new)" sheetId="9" r:id="rId8"/>
   </sheets>
   <calcPr calcId="124519"/>
 </workbook>
@@ -280,7 +282,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="404" uniqueCount="338">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="472" uniqueCount="390">
   <si>
     <t>需求</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1021,10 +1023,6 @@
   </si>
   <si>
     <t>{BusinessType, BusinessName,ClusterType, ClusterName, "Config":[{dbpath, svcname…} },...],"Property": [{ "Name": "username", "Type": "string", "Default": "sdbadmin", "Valid": "", "Display": "edit box", "Edit": "true", "Desc": "", "Level": "0", "WebName": "user_name",... }, ...] }</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{BusinessType, BusinessName,ClusterType, ClusterName, "Config":[{"HostName":"host1","datagroupname":"", "dbpath":"/home/db2//standalone/11830", "svcname":"11830", ...}, ...] }]}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1222,10 +1220,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>OM-&gt;Agent</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>{Rc}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1698,12 +1692,456 @@
 : "/dev/sda1", "Mount": "/"}]}], "Net":{"Name":"eth1"}}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>command</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+    OM_BSON_FIELD_CLUSTER_NAME:"c1",
+    OM_BSON_FIELD_SDB_USER:"usr",
+    OM_BSON_FIELD_SDB_PASSWD:"passwd",
+    OM_BSON_FIELD_SDB_USERGROUP:"usr_group",
+    OM_BSON_FIELD_PATCKET_PATH:"path",
+    OM_BSON_FIELD_HOST_INFO:
+    [
+    {
+        OM_HOST_FIELD_NAME:"host",
+        OM_HOST_FIELD_CLUSTERNAME:"c1",
+        OM_HOST_FIELD_IP:"ip"...
+    }
+    , ...
+    ]
+}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>taskinfo(key=OM_TASKINFO_FIELD_INFO)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>resultinfo(key=OM_TASKINFO_FIELD_RESULTINFO)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[
+{
+    OM_HOST_FIELD_IP:"ip",
+    OM_HOST_FIELD_NAME:"host",
+    OM_TASKINFO_FIELD_STATUS:1,
+    OM_TASKINFO_FIELD_STATUS_DESC:"desc",
+    OM_REST_RES_RETCODE:0,
+    OM_REST_RES_DETAIL:"detail",
+    OM_TASKINFO_FIELD_FLOW:"flow"
+}
+]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[
+{
+    OM_BSON_FIELD_HOST_NAME:"host1",
+    OM_CONF_DETAIL_SVCNAME:"",
+    OM_CONF_DETAIL_ROLE:"",
+    OM_CONF_DETAIL_DATAGROUPNAME:"",
+    OM_TASKINFO_FIELD_STATUS:1,
+    OM_TASKINFO_FIELD_STATUS_DESC:"desc",
+    OM_REST_RES_RETCODE:0,
+    OM_REST_RES_DETAIL:"detail",
+    OM_TASKINFO_FIELD_FLOW:"flow"
+}
+]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{BusinessType, BusinessName,ClusterType, ClusterName, "Config":[{"HostName":"host1","datagroupname":"", "dbpath":"/home/db2//standalone/11830", "svcname":"11830", ...}, ...] }]}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+    OM_BSON_BUSINESS_TYPE:type,
+    OM_BSON_FIELD_CLUSTER_NAME:"c1",
+    OM_BSON_BUSINESS_NAME:"b1",
+    OM_BSON_DEPLOY_MOD:"mode",
+    OM_BSON_FIELD_CONFIG:
+    [
+    {
+        OM_BSON_FIELD_HOST_NAME:"host",
+        OM_BSON_FIELD_HOST_USER:"",
+        OM_BSON_FIELD_HOST_PASSWD:"",
+        OM_BSON_FIELD_HOST_SSHPORT:"",
+        svcname:"",
+    }
+    ]
+}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">{
+    OM_BSON_BUSINESS_TYPE:type,
+    OM_BSON_FIELD_CLUSTER_NAME:"c1",
+    OM_BSON_BUSINESS_NAME:"b1",
+    OM_BSON_DEPLOY_MOD:"mode",
+    OM_BSON_FIELD_CONFIG:
+    [
+    {
+        </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>OM_BSON_FIELD_HOST_NAME:"host",
+        OM_BSON_FIELD_HOST_USER:"",
+        OM_BSON_FIELD_HOST_PASSWD:"",
+        OM_BSON_FIELD_HOST_SSHPORT:"",</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+        svcname:"",
+    }
+    ]
+}</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>OM与Agent消息</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>参数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>样例</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>扫描主机请求</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>扫描主机响应</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>说明</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>消息结构不变</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+  HostInfo:
+  [
+    {
+      errno:0,
+      detail:"",
+      IP:"192.168.20.197"
+      Status:"finish"
+      HostName:"rhelt10"
+    }
+  ]
+}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>检测主机--基本检测</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>删除</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pre-check host</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">{
+  HostInfo:
+  [
+    {
+      errno:返回码
+      detail:错误描述
+      IP: IP地址 
+      Status:"ping/ssh/getinfo/finish"
+      HostName: 该机器上的HostName
+    },…
+  ]
+}
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">{
+  HostInfo:
+  [
+    {
+      IP/HostName:主机IP或主机名
+      User:root用户名
+      Passwd:root密码
+      SshPort:ssh端口号
+    },…
+  ]
+}
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>检测主机--检测前请求</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>检测主机--检测前响应</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+  HostInfo:
+  [
+    {
+      errno:
+      detail:
+      IP:主机IP
+      AgentService:已成功安装的agent端口号
+    },…
+  ]
+}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>检测主机--检测主机请求</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+  HostInfo:
+  [
+    {
+      IP:主机IP
+      HostName:主机名
+      User:root用户名
+      Passwd:root密码
+    },…
+  ]
+}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>检测主机--检测主机响应</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不变</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>检测主机--检测后请求</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>post-check host</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>检测主机--检测后响应</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>通知agent退出，通知本机agent删除临时包，跟以前一样</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>跟以前一样</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>添加主机--任务通知请求</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>notify agent</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+  TaskID:任务ID
+}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>添加主机--任务通知响应</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>按照内部消息返回flag=0即为成功;
+非0为失败并在返回的BSON中填上detail</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">agent通过TaskID向OM发送查询请求（与查表请求格式一样），表结构参见OM架构设计--Task表结构;这里只描述不同的两个字段：
+Info：
+{
+    OM_BSON_FIELD_CLUSTER_NAME:"c1",
+    OM_BSON_FIELD_SDB_USER:"usr",
+    OM_BSON_FIELD_SDB_PASSWD:"passwd",
+    OM_BSON_FIELD_SDB_USERGROUP:"usr_group",
+    OM_BSON_FIELD_PATCKET_PATH:"path",
+    OM_BSON_FIELD_HOST_INFO:
+    [
+    {
+        OM_HOST_FIELD_NAME:"host",
+        OM_HOST_FIELD_CLUSTERNAME:"c1",
+        OM_HOST_FIELD_IP:"ip"...
+    }
+    , ...
+    ]
+}
+ResultInfo:
+{
+  [
+    {
+    OM_HOST_FIELD_IP:"ip",
+    OM_HOST_FIELD_NAME:"host",
+    OM_TASKINFO_FIELD_STATUS:1,
+    OM_TASKINFO_FIELD_STATUS_DESC:"desc",
+    OM_REST_RES_RETCODE:0,
+    OM_REST_RES_DETAIL:"detail",
+    OM_TASKINFO_FIELD_FLOW:null
+    }
+  ]
+}
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>update task</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+  TaskID:
+  Status:
+  Progress:
+  ResultInfo:
+}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>以内部的Query命令发，命令字为update task
+ResultInfo不同任务类型格式不一样：
+task为添加机器时，ResultInfo:
+[
+{
+    OM_HOST_FIELD_IP:"ip",
+    OM_HOST_FIELD_NAME:"host",
+    OM_TASKINFO_FIELD_STATUS:1,
+    OM_TASKINFO_FIELD_STATUS_DESC:"desc",
+    OM_REST_RES_RETCODE:0,
+    OM_REST_RES_DETAIL:"detail",
+    OM_TASKINFO_FIELD_FLOW:"flow"
+}
+]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>agent更新ADD_HOST任务进度请求(agent-&gt;om)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>agent更新ADD_HOST任务进度响应(om-&gt;agent)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>无</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>flag==0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>agent更新ADD_BUSINESS任务进度请求(agent-&gt;om)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>agent更新ADD_BUSINESS任务进度响应(om-&gt;agent)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>agent更新REMOVE_BUSINESS任务进度请求(agent-&gt;om)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>agent更新REMOVE_BUSINESS任务进度响应(om-&gt;agent)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>以内部的Query命令发，命令字为update task
+ResultInfo不同任务类型格式不一样：
+task为添加业务时，ResultInfo:
+[
+{
+    OM_BSON_FIELD_HOST_NAME:"host1",
+    OM_CONF_DETAIL_SVCNAME:"",
+    OM_CONF_DETAIL_ROLE:"",
+    OM_CONF_DETAIL_DATAGROUPNAME:"",
+    OM_TASKINFO_FIELD_STATUS:1,
+    OM_TASKINFO_FIELD_STATUS_DESC:"desc",
+    OM_REST_RES_RETCODE:0,
+    OM_REST_RES_DETAIL:"detail",
+    OM_TASKINFO_FIELD_FLOW:null
+}
+]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>以内部的Query命令发，命令字为update task
+ResultInfo不同任务类型格式不一样：
+task为删除业务时，ResultInfo:
+[
+{
+    OM_BSON_FIELD_HOST_NAME:"host1",
+    OM_CONF_DETAIL_SVCNAME:"",
+    OM_CONF_DETAIL_ROLE:"",
+    OM_CONF_DETAIL_DATAGROUPNAME:"",
+    OM_TASKINFO_FIELD_STATUS:1,
+    OM_TASKINFO_FIELD_STATUS_DESC:"desc",
+    OM_REST_RES_RETCODE:0,
+    OM_REST_RES_DETAIL:"detail",
+    OM_TASKINFO_FIELD_FLOW:"flow"
+}
+]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="19">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1848,6 +2286,30 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="2" tint="-0.499984740745262"/>
+      <name val="宋体"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="2" tint="-0.499984740745262"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF00B050"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -1864,7 +2326,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
+        <fgColor theme="3" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1933,7 +2395,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1995,13 +2457,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -2050,6 +2505,40 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2461,7 +2950,7 @@
       </c>
     </row>
     <row r="3" spans="1:8">
-      <c r="A3" s="45" t="s">
+      <c r="A3" s="42" t="s">
         <v>12</v>
       </c>
       <c r="B3" s="4" t="s">
@@ -2479,7 +2968,7 @@
       <c r="H3" s="4"/>
     </row>
     <row r="4" spans="1:8" ht="13.5">
-      <c r="A4" s="46"/>
+      <c r="A4" s="43"/>
       <c r="B4" s="4" t="s">
         <v>5</v>
       </c>
@@ -2495,7 +2984,7 @@
       <c r="H4" s="4"/>
     </row>
     <row r="5" spans="1:8" ht="13.5">
-      <c r="A5" s="46"/>
+      <c r="A5" s="43"/>
       <c r="B5" s="4" t="s">
         <v>8</v>
       </c>
@@ -2511,7 +3000,7 @@
       <c r="H5" s="4"/>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" s="47"/>
+      <c r="A6" s="44"/>
       <c r="B6" s="4" t="s">
         <v>13</v>
       </c>
@@ -2527,7 +3016,7 @@
       <c r="H6" s="4"/>
     </row>
     <row r="7" spans="1:8" ht="24">
-      <c r="A7" s="48" t="s">
+      <c r="A7" s="45" t="s">
         <v>24</v>
       </c>
       <c r="B7" s="4" t="s">
@@ -2545,7 +3034,7 @@
       <c r="H7" s="4"/>
     </row>
     <row r="8" spans="1:8" ht="36">
-      <c r="A8" s="49"/>
+      <c r="A8" s="46"/>
       <c r="B8" s="4" t="s">
         <v>17</v>
       </c>
@@ -2563,7 +3052,7 @@
       <c r="H8" s="4"/>
     </row>
     <row r="9" spans="1:8" ht="72">
-      <c r="A9" s="49"/>
+      <c r="A9" s="46"/>
       <c r="B9" s="4" t="s">
         <v>18</v>
       </c>
@@ -2581,7 +3070,7 @@
       <c r="H9" s="4"/>
     </row>
     <row r="10" spans="1:8" ht="24">
-      <c r="A10" s="50"/>
+      <c r="A10" s="47"/>
       <c r="B10" s="4" t="s">
         <v>21</v>
       </c>
@@ -2619,7 +3108,7 @@
       <c r="H11" s="4"/>
     </row>
     <row r="12" spans="1:8" ht="24">
-      <c r="A12" s="48" t="s">
+      <c r="A12" s="45" t="s">
         <v>26</v>
       </c>
       <c r="B12" s="4" t="s">
@@ -2637,7 +3126,7 @@
       <c r="H12" s="4"/>
     </row>
     <row r="13" spans="1:8">
-      <c r="A13" s="49"/>
+      <c r="A13" s="46"/>
       <c r="B13" s="4" t="s">
         <v>32</v>
       </c>
@@ -2653,7 +3142,7 @@
       <c r="H13" s="4"/>
     </row>
     <row r="14" spans="1:8" ht="24">
-      <c r="A14" s="49"/>
+      <c r="A14" s="46"/>
       <c r="B14" s="4" t="s">
         <v>33</v>
       </c>
@@ -2671,7 +3160,7 @@
       <c r="H14" s="4"/>
     </row>
     <row r="15" spans="1:8">
-      <c r="A15" s="49"/>
+      <c r="A15" s="46"/>
       <c r="B15" s="4" t="s">
         <v>35</v>
       </c>
@@ -2687,7 +3176,7 @@
       <c r="H15" s="4"/>
     </row>
     <row r="16" spans="1:8">
-      <c r="A16" s="49"/>
+      <c r="A16" s="46"/>
       <c r="B16" s="4" t="s">
         <v>57</v>
       </c>
@@ -2699,7 +3188,7 @@
       <c r="H16" s="4"/>
     </row>
     <row r="17" spans="1:8" ht="48">
-      <c r="A17" s="49"/>
+      <c r="A17" s="46"/>
       <c r="B17" s="4" t="s">
         <v>30</v>
       </c>
@@ -2717,7 +3206,7 @@
       <c r="H17" s="4"/>
     </row>
     <row r="18" spans="1:8">
-      <c r="A18" s="49"/>
+      <c r="A18" s="46"/>
       <c r="B18" s="4" t="s">
         <v>38</v>
       </c>
@@ -2733,7 +3222,7 @@
       <c r="H18" s="4"/>
     </row>
     <row r="19" spans="1:8">
-      <c r="A19" s="49"/>
+      <c r="A19" s="46"/>
       <c r="B19" s="4" t="s">
         <v>41</v>
       </c>
@@ -2749,7 +3238,7 @@
       <c r="H19" s="4"/>
     </row>
     <row r="20" spans="1:8">
-      <c r="A20" s="49"/>
+      <c r="A20" s="46"/>
       <c r="B20" s="4" t="s">
         <v>40</v>
       </c>
@@ -2765,7 +3254,7 @@
       <c r="H20" s="4"/>
     </row>
     <row r="21" spans="1:8" ht="24">
-      <c r="A21" s="49"/>
+      <c r="A21" s="46"/>
       <c r="B21" s="4" t="s">
         <v>44</v>
       </c>
@@ -2783,7 +3272,7 @@
       <c r="H21" s="4"/>
     </row>
     <row r="22" spans="1:8" ht="24">
-      <c r="A22" s="49"/>
+      <c r="A22" s="46"/>
       <c r="B22" s="4" t="s">
         <v>47</v>
       </c>
@@ -2799,7 +3288,7 @@
       <c r="H22" s="4"/>
     </row>
     <row r="23" spans="1:8" ht="24">
-      <c r="A23" s="49"/>
+      <c r="A23" s="46"/>
       <c r="B23" s="4" t="s">
         <v>49</v>
       </c>
@@ -3839,7 +4328,7 @@
         <v>131</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="D2" s="5" t="s">
         <v>1</v>
@@ -3852,13 +4341,13 @@
         <v>150</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E3" s="4"/>
       <c r="F3" s="4"/>
@@ -3869,10 +4358,10 @@
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="9" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="E4" s="4"/>
       <c r="F4" s="4"/>
@@ -3890,13 +4379,13 @@
         <v>163</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C6" s="9" t="s">
         <v>165</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
@@ -3907,10 +4396,10 @@
       </c>
       <c r="B7" s="4"/>
       <c r="C7" s="9" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="E7" s="4"/>
       <c r="F7" s="4"/>
@@ -3923,54 +4412,54 @@
       <c r="E8" s="4"/>
       <c r="F8" s="4"/>
     </row>
-    <row r="9" spans="1:6" s="38" customFormat="1">
-      <c r="A9" s="36" t="s">
+    <row r="9" spans="1:6" s="35" customFormat="1">
+      <c r="A9" s="33" t="s">
+        <v>226</v>
+      </c>
+      <c r="B9" s="34" t="s">
+        <v>227</v>
+      </c>
+      <c r="C9" s="33" t="s">
+        <v>225</v>
+      </c>
+      <c r="D9" s="33" t="s">
         <v>228</v>
       </c>
-      <c r="B9" s="37" t="s">
-        <v>229</v>
-      </c>
-      <c r="C9" s="36" t="s">
-        <v>227</v>
-      </c>
-      <c r="D9" s="36" t="s">
-        <v>230</v>
-      </c>
-      <c r="E9" s="37"/>
-      <c r="F9" s="37"/>
-    </row>
-    <row r="10" spans="1:6" s="38" customFormat="1">
-      <c r="A10" s="36" t="s">
-        <v>281</v>
-      </c>
-      <c r="B10" s="37"/>
-      <c r="C10" s="36" t="s">
+      <c r="E9" s="34"/>
+      <c r="F9" s="34"/>
+    </row>
+    <row r="10" spans="1:6" s="35" customFormat="1">
+      <c r="A10" s="33" t="s">
         <v>279</v>
       </c>
-      <c r="D10" s="36"/>
-      <c r="E10" s="37"/>
-      <c r="F10" s="37"/>
-    </row>
-    <row r="11" spans="1:6" s="42" customFormat="1">
-      <c r="A11" s="40"/>
-      <c r="B11" s="41"/>
-      <c r="C11" s="40"/>
-      <c r="D11" s="40"/>
-      <c r="E11" s="41"/>
-      <c r="F11" s="41"/>
+      <c r="B10" s="34"/>
+      <c r="C10" s="33" t="s">
+        <v>277</v>
+      </c>
+      <c r="D10" s="33"/>
+      <c r="E10" s="34"/>
+      <c r="F10" s="34"/>
+    </row>
+    <row r="11" spans="1:6" s="39" customFormat="1">
+      <c r="A11" s="37"/>
+      <c r="B11" s="38"/>
+      <c r="C11" s="37"/>
+      <c r="D11" s="37"/>
+      <c r="E11" s="38"/>
+      <c r="F11" s="38"/>
     </row>
     <row r="12" spans="1:6" ht="60">
       <c r="A12" s="9" t="s">
         <v>122</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C12" s="9" t="s">
+        <v>213</v>
+      </c>
+      <c r="D12" s="9" t="s">
         <v>214</v>
-      </c>
-      <c r="D12" s="9" t="s">
-        <v>215</v>
       </c>
       <c r="E12" s="4"/>
       <c r="F12" s="4"/>
@@ -3981,10 +4470,10 @@
       </c>
       <c r="B13" s="4"/>
       <c r="C13" s="9" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="E13" s="4"/>
       <c r="F13" s="4"/>
@@ -4004,13 +4493,13 @@
         <v>124</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C15" s="9" t="s">
         <v>179</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="E15" s="4"/>
       <c r="F15" s="4"/>
@@ -4021,10 +4510,10 @@
       </c>
       <c r="B16" s="4"/>
       <c r="C16" s="9" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="E16" s="4"/>
       <c r="F16" s="4"/>
@@ -4044,13 +4533,13 @@
         <v>126</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="E18" s="4"/>
       <c r="F18" s="4"/>
@@ -4061,7 +4550,7 @@
       </c>
       <c r="B19" s="4"/>
       <c r="C19" s="9" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="D19" s="9"/>
       <c r="E19" s="4"/>
@@ -4075,32 +4564,32 @@
       <c r="E20" s="4"/>
       <c r="F20" s="4"/>
     </row>
-    <row r="21" spans="1:6" s="39" customFormat="1" ht="24">
+    <row r="21" spans="1:6" s="36" customFormat="1" ht="24">
       <c r="A21" s="5" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" s="2"/>
     </row>
-    <row r="22" spans="1:6" s="39" customFormat="1" ht="132">
+    <row r="22" spans="1:6" s="36" customFormat="1" ht="132">
       <c r="A22" s="5" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B22" s="2"/>
       <c r="C22" s="5" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" s="2"/>
@@ -4115,29 +4604,29 @@
       <c r="E23" s="4"/>
       <c r="F23" s="4"/>
     </row>
-    <row r="24" spans="1:6" s="39" customFormat="1">
+    <row r="24" spans="1:6" s="36" customFormat="1">
       <c r="A24" s="5" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" s="2"/>
     </row>
-    <row r="25" spans="1:6" s="39" customFormat="1">
+    <row r="25" spans="1:6" s="36" customFormat="1">
       <c r="A25" s="5" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B25" s="2"/>
       <c r="C25" s="5" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="D25" s="5"/>
       <c r="E25" s="2"/>
@@ -4151,29 +4640,29 @@
       <c r="E26" s="4"/>
       <c r="F26" s="4"/>
     </row>
-    <row r="27" spans="1:6" s="39" customFormat="1">
+    <row r="27" spans="1:6" s="36" customFormat="1">
       <c r="A27" s="5" t="s">
         <v>128</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" s="2"/>
     </row>
-    <row r="28" spans="1:6" s="39" customFormat="1" ht="180">
+    <row r="28" spans="1:6" s="36" customFormat="1" ht="180">
       <c r="A28" s="5" t="s">
         <v>129</v>
       </c>
       <c r="B28" s="2"/>
       <c r="C28" s="5" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="D28" s="5"/>
       <c r="E28" s="2"/>
@@ -4189,27 +4678,27 @@
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="9" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C30" s="9" t="s">
+        <v>319</v>
+      </c>
+      <c r="D30" s="9" t="s">
         <v>321</v>
-      </c>
-      <c r="D30" s="9" t="s">
-        <v>323</v>
       </c>
       <c r="E30" s="4"/>
       <c r="F30" s="4"/>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="9" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="B31" s="4"/>
       <c r="C31" s="9" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D31" s="9"/>
       <c r="E31" s="4"/>
@@ -4230,11 +4719,11 @@
         <v>132</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C33" s="9"/>
       <c r="D33" s="9" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E33" s="4"/>
       <c r="F33" s="4"/>
@@ -4245,10 +4734,10 @@
       </c>
       <c r="B34" s="4"/>
       <c r="C34" s="9" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="E34" s="4"/>
       <c r="F34" s="4"/>
@@ -4268,13 +4757,13 @@
         <v>134</v>
       </c>
       <c r="B36" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="C36" s="9" t="s">
         <v>210</v>
       </c>
-      <c r="C36" s="9" t="s">
-        <v>211</v>
-      </c>
       <c r="D36" s="9" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E36" s="4"/>
       <c r="F36" s="4"/>
@@ -4288,7 +4777,7 @@
         <v>180</v>
       </c>
       <c r="D37" s="9" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="E37" s="4"/>
       <c r="F37" s="4"/>
@@ -4308,13 +4797,13 @@
         <v>136</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C39" s="9" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D39" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E39" s="4"/>
       <c r="F39" s="4"/>
@@ -4348,13 +4837,13 @@
         <v>138</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C42" s="9" t="s">
-        <v>183</v>
+        <v>342</v>
       </c>
       <c r="D42" s="9" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="E42" s="4"/>
       <c r="F42" s="4"/>
@@ -4365,7 +4854,7 @@
       </c>
       <c r="B43" s="4"/>
       <c r="C43" s="9" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="D43" s="9" t="s">
         <v>120</v>
@@ -4381,65 +4870,65 @@
       <c r="E44" s="4"/>
       <c r="F44" s="4"/>
     </row>
-    <row r="45" spans="1:6" s="39" customFormat="1">
+    <row r="45" spans="1:6" s="36" customFormat="1">
       <c r="A45" s="5" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" s="2"/>
     </row>
-    <row r="46" spans="1:6" s="39" customFormat="1">
+    <row r="46" spans="1:6" s="36" customFormat="1">
       <c r="A46" s="5" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="B46" s="2"/>
       <c r="C46" s="5" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="D46" s="5"/>
       <c r="E46" s="2"/>
       <c r="F46" s="2"/>
     </row>
-    <row r="47" spans="1:6" s="42" customFormat="1">
-      <c r="A47" s="40"/>
-      <c r="B47" s="41"/>
-      <c r="C47" s="40"/>
-      <c r="D47" s="40"/>
-      <c r="E47" s="41"/>
-      <c r="F47" s="41"/>
-    </row>
-    <row r="48" spans="1:6" s="39" customFormat="1">
+    <row r="47" spans="1:6" s="39" customFormat="1">
+      <c r="A47" s="37"/>
+      <c r="B47" s="38"/>
+      <c r="C47" s="37"/>
+      <c r="D47" s="37"/>
+      <c r="E47" s="38"/>
+      <c r="F47" s="38"/>
+    </row>
+    <row r="48" spans="1:6" s="36" customFormat="1">
       <c r="A48" s="5" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" s="2"/>
     </row>
-    <row r="49" spans="1:6" s="39" customFormat="1" ht="24">
+    <row r="49" spans="1:6" s="36" customFormat="1" ht="24">
       <c r="A49" s="5" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="B49" s="2"/>
       <c r="C49" s="5" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="D49" s="5"/>
       <c r="E49" s="2"/>
@@ -4453,7 +4942,7 @@
       <c r="E50" s="4"/>
       <c r="F50" s="4"/>
     </row>
-    <row r="51" spans="1:6" s="39" customFormat="1">
+    <row r="51" spans="1:6" s="36" customFormat="1">
       <c r="A51" s="5" t="s">
         <v>140</v>
       </c>
@@ -4461,91 +4950,91 @@
         <v>142</v>
       </c>
       <c r="C51" s="5" t="s">
+        <v>276</v>
+      </c>
+      <c r="D51" s="5" t="s">
         <v>278</v>
-      </c>
-      <c r="D51" s="5" t="s">
-        <v>280</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" s="2"/>
     </row>
-    <row r="52" spans="1:6" s="39" customFormat="1">
+    <row r="52" spans="1:6" s="36" customFormat="1">
       <c r="A52" s="5" t="s">
         <v>141</v>
       </c>
       <c r="B52" s="2"/>
       <c r="C52" s="5" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D52" s="5"/>
       <c r="E52" s="2"/>
       <c r="F52" s="2"/>
     </row>
-    <row r="53" spans="1:6" s="42" customFormat="1">
-      <c r="A53" s="40"/>
-      <c r="B53" s="41"/>
-      <c r="C53" s="40"/>
-      <c r="D53" s="40"/>
-      <c r="E53" s="41"/>
-      <c r="F53" s="41"/>
-    </row>
-    <row r="54" spans="1:6" s="42" customFormat="1" ht="60">
+    <row r="53" spans="1:6" s="39" customFormat="1">
+      <c r="A53" s="37"/>
+      <c r="B53" s="38"/>
+      <c r="C53" s="37"/>
+      <c r="D53" s="37"/>
+      <c r="E53" s="38"/>
+      <c r="F53" s="38"/>
+    </row>
+    <row r="54" spans="1:6" s="39" customFormat="1" ht="60">
       <c r="A54" s="5" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="B54" s="2"/>
       <c r="C54" s="5" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="D54" s="5" t="s">
-        <v>334</v>
-      </c>
-      <c r="E54" s="41"/>
-      <c r="F54" s="41"/>
-    </row>
-    <row r="55" spans="1:6" s="42" customFormat="1">
+        <v>332</v>
+      </c>
+      <c r="E54" s="38"/>
+      <c r="F54" s="38"/>
+    </row>
+    <row r="55" spans="1:6" s="39" customFormat="1">
       <c r="A55" s="5" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="B55" s="2"/>
       <c r="C55" s="5" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="D55" s="5"/>
-      <c r="E55" s="41"/>
-      <c r="F55" s="41"/>
-    </row>
-    <row r="56" spans="1:6" s="42" customFormat="1">
-      <c r="A56" s="40"/>
-      <c r="B56" s="41"/>
-      <c r="C56" s="40"/>
-      <c r="D56" s="40"/>
-      <c r="E56" s="41"/>
-      <c r="F56" s="41"/>
+      <c r="E55" s="38"/>
+      <c r="F55" s="38"/>
+    </row>
+    <row r="56" spans="1:6" s="39" customFormat="1">
+      <c r="A56" s="37"/>
+      <c r="B56" s="38"/>
+      <c r="C56" s="37"/>
+      <c r="D56" s="37"/>
+      <c r="E56" s="38"/>
+      <c r="F56" s="38"/>
     </row>
     <row r="57" spans="1:6">
       <c r="A57" s="9" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C57" s="9" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="D57" s="9" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="E57" s="4"/>
       <c r="F57" s="4"/>
     </row>
     <row r="58" spans="1:6" ht="96">
       <c r="A58" s="9" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B58" s="4"/>
       <c r="C58" s="9" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="D58" s="9"/>
       <c r="E58" s="4"/>
@@ -4570,18 +5059,18 @@
       <c r="D61" s="9"/>
     </row>
     <row r="62" spans="1:6">
-      <c r="A62" s="34" t="s">
+      <c r="A62" s="31" t="s">
         <v>147</v>
       </c>
-      <c r="B62" s="35" t="s">
-        <v>186</v>
-      </c>
-      <c r="C62" s="34" t="s">
+      <c r="B62" s="32" t="s">
+        <v>185</v>
+      </c>
+      <c r="C62" s="31" t="s">
         <v>143</v>
       </c>
-      <c r="D62" s="34"/>
-      <c r="E62" s="35"/>
-      <c r="F62" s="35"/>
+      <c r="D62" s="31"/>
+      <c r="E62" s="32"/>
+      <c r="F62" s="32"/>
     </row>
     <row r="63" spans="1:6" ht="24">
       <c r="A63" s="9" t="s">
@@ -4589,7 +5078,7 @@
       </c>
       <c r="B63" s="4"/>
       <c r="C63" s="9" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="D63" s="9" t="s">
         <v>149</v>
@@ -4610,13 +5099,13 @@
         <v>161</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C65" s="9" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D65" s="9" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E65" s="4"/>
       <c r="F65" s="4"/>
@@ -4627,7 +5116,7 @@
       </c>
       <c r="B66" s="4"/>
       <c r="C66" s="9" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="D66" s="9"/>
       <c r="E66" s="4"/>
@@ -4635,26 +5124,26 @@
     </row>
     <row r="67" spans="1:6" ht="24">
       <c r="A67" s="9" t="s">
+        <v>193</v>
+      </c>
+      <c r="B67" s="4" t="s">
         <v>194</v>
       </c>
-      <c r="B67" s="4" t="s">
+      <c r="C67" s="9" t="s">
         <v>195</v>
       </c>
-      <c r="C67" s="9" t="s">
+      <c r="D67" s="9" t="s">
         <v>196</v>
-      </c>
-      <c r="D67" s="9" t="s">
-        <v>197</v>
       </c>
       <c r="E67" s="4"/>
       <c r="F67" s="4"/>
     </row>
     <row r="68" spans="1:6">
       <c r="A68" s="9" t="s">
+        <v>197</v>
+      </c>
+      <c r="B68" s="4" t="s">
         <v>198</v>
-      </c>
-      <c r="B68" s="4" t="s">
-        <v>199</v>
       </c>
       <c r="C68" s="9"/>
       <c r="D68" s="9"/>
@@ -4669,95 +5158,95 @@
       <c r="E69" s="4"/>
       <c r="F69" s="4"/>
     </row>
-    <row r="70" spans="1:6" s="42" customFormat="1">
-      <c r="A70" s="40" t="s">
+    <row r="70" spans="1:6" s="39" customFormat="1">
+      <c r="A70" s="37" t="s">
         <v>153</v>
       </c>
-      <c r="B70" s="41"/>
-      <c r="C70" s="40" t="s">
-        <v>292</v>
-      </c>
-      <c r="D70" s="40"/>
-      <c r="E70" s="41"/>
-      <c r="F70" s="41"/>
-    </row>
-    <row r="71" spans="1:6" s="42" customFormat="1" ht="24">
-      <c r="A71" s="40" t="s">
+      <c r="B70" s="38"/>
+      <c r="C70" s="37" t="s">
+        <v>290</v>
+      </c>
+      <c r="D70" s="37"/>
+      <c r="E70" s="38"/>
+      <c r="F70" s="38"/>
+    </row>
+    <row r="71" spans="1:6" s="39" customFormat="1" ht="24">
+      <c r="A71" s="37" t="s">
         <v>154</v>
       </c>
-      <c r="B71" s="41"/>
-      <c r="C71" s="40" t="s">
-        <v>291</v>
-      </c>
-      <c r="D71" s="40" t="s">
+      <c r="B71" s="38"/>
+      <c r="C71" s="37" t="s">
+        <v>289</v>
+      </c>
+      <c r="D71" s="37" t="s">
         <v>144</v>
       </c>
-      <c r="E71" s="41"/>
-      <c r="F71" s="41"/>
-    </row>
-    <row r="72" spans="1:6" s="42" customFormat="1" ht="24">
-      <c r="A72" s="40" t="s">
+      <c r="E71" s="38"/>
+      <c r="F71" s="38"/>
+    </row>
+    <row r="72" spans="1:6" s="39" customFormat="1" ht="24">
+      <c r="A72" s="37" t="s">
         <v>151</v>
       </c>
-      <c r="B72" s="41" t="s">
+      <c r="B72" s="38" t="s">
         <v>156</v>
       </c>
-      <c r="C72" s="40" t="s">
+      <c r="C72" s="37" t="s">
         <v>152</v>
       </c>
-      <c r="D72" s="40"/>
-      <c r="E72" s="41"/>
-      <c r="F72" s="41"/>
-    </row>
-    <row r="73" spans="1:6" s="42" customFormat="1" ht="48">
-      <c r="A73" s="40" t="s">
+      <c r="D72" s="37"/>
+      <c r="E72" s="38"/>
+      <c r="F72" s="38"/>
+    </row>
+    <row r="73" spans="1:6" s="39" customFormat="1" ht="48">
+      <c r="A73" s="37" t="s">
         <v>155</v>
       </c>
-      <c r="B73" s="41" t="s">
+      <c r="B73" s="38" t="s">
         <v>156</v>
       </c>
-      <c r="C73" s="40" t="s">
+      <c r="C73" s="37" t="s">
         <v>159</v>
       </c>
-      <c r="D73" s="40" t="s">
+      <c r="D73" s="37" t="s">
         <v>160</v>
       </c>
-      <c r="E73" s="41"/>
-      <c r="F73" s="41"/>
-    </row>
-    <row r="74" spans="1:6" s="42" customFormat="1" ht="36">
-      <c r="A74" s="40" t="s">
+      <c r="E73" s="38"/>
+      <c r="F73" s="38"/>
+    </row>
+    <row r="74" spans="1:6" s="39" customFormat="1" ht="36">
+      <c r="A74" s="37" t="s">
         <v>157</v>
       </c>
-      <c r="B74" s="41" t="s">
+      <c r="B74" s="38" t="s">
         <v>156</v>
       </c>
-      <c r="C74" s="40" t="s">
+      <c r="C74" s="37" t="s">
         <v>158</v>
       </c>
-      <c r="D74" s="40"/>
-      <c r="E74" s="41"/>
-      <c r="F74" s="41"/>
+      <c r="D74" s="37"/>
+      <c r="E74" s="38"/>
+      <c r="F74" s="38"/>
     </row>
     <row r="75" spans="1:6" s="21" customFormat="1" ht="24">
-      <c r="A75" s="43" t="s">
+      <c r="A75" s="40" t="s">
         <v>146</v>
       </c>
-      <c r="B75" s="44"/>
-      <c r="C75" s="43"/>
-      <c r="D75" s="43" t="s">
+      <c r="B75" s="41"/>
+      <c r="C75" s="40"/>
+      <c r="D75" s="40" t="s">
         <v>145</v>
       </c>
-      <c r="E75" s="44"/>
-      <c r="F75" s="44"/>
-    </row>
-    <row r="76" spans="1:6" s="42" customFormat="1">
-      <c r="A76" s="40"/>
-      <c r="B76" s="41"/>
-      <c r="C76" s="40"/>
-      <c r="D76" s="40"/>
-      <c r="E76" s="41"/>
-      <c r="F76" s="41"/>
+      <c r="E75" s="41"/>
+      <c r="F75" s="41"/>
+    </row>
+    <row r="76" spans="1:6" s="39" customFormat="1">
+      <c r="A76" s="37"/>
+      <c r="B76" s="38"/>
+      <c r="C76" s="37"/>
+      <c r="D76" s="37"/>
+      <c r="E76" s="38"/>
+      <c r="F76" s="38"/>
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="9"/>
@@ -4808,7 +5297,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:E38"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="34.25" customWidth="1"/>
@@ -4820,240 +5309,331 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="24" t="s">
-        <v>221</v>
+        <v>345</v>
       </c>
       <c r="B1" s="24" t="s">
+        <v>218</v>
+      </c>
+      <c r="C1" s="25" t="s">
         <v>219</v>
       </c>
-      <c r="C1" s="25" t="s">
-        <v>220</v>
-      </c>
       <c r="D1" s="25" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="E1" s="25" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="67.5">
-      <c r="A2" s="27" t="s">
-        <v>225</v>
-      </c>
-      <c r="B2" s="28" t="s">
+    <row r="2" spans="1:5" s="57" customFormat="1">
+      <c r="A2" s="52"/>
+      <c r="B2" s="52"/>
+      <c r="C2" s="51"/>
+      <c r="D2" s="51"/>
+      <c r="E2" s="51"/>
+    </row>
+    <row r="3" spans="1:5" s="57" customFormat="1">
+      <c r="A3" s="52"/>
+      <c r="B3" s="52"/>
+      <c r="C3" s="51"/>
+      <c r="D3" s="51"/>
+      <c r="E3" s="51"/>
+    </row>
+    <row r="4" spans="1:5" s="57" customFormat="1">
+      <c r="A4" s="52"/>
+      <c r="B4" s="52"/>
+      <c r="C4" s="51"/>
+      <c r="D4" s="51"/>
+      <c r="E4" s="51"/>
+    </row>
+    <row r="5" spans="1:5" s="57" customFormat="1">
+      <c r="A5" s="52"/>
+      <c r="B5" s="52"/>
+      <c r="C5" s="51"/>
+      <c r="D5" s="51"/>
+      <c r="E5" s="51"/>
+    </row>
+    <row r="6" spans="1:5" s="57" customFormat="1">
+      <c r="A6" s="52"/>
+      <c r="B6" s="52"/>
+      <c r="C6" s="51"/>
+      <c r="D6" s="51"/>
+      <c r="E6" s="51"/>
+    </row>
+    <row r="7" spans="1:5" s="57" customFormat="1">
+      <c r="A7" s="52"/>
+      <c r="B7" s="52"/>
+      <c r="C7" s="51"/>
+      <c r="D7" s="51"/>
+      <c r="E7" s="51"/>
+    </row>
+    <row r="8" spans="1:5" s="57" customFormat="1">
+      <c r="A8" s="52"/>
+      <c r="B8" s="52"/>
+      <c r="C8" s="51"/>
+      <c r="D8" s="51"/>
+      <c r="E8" s="51"/>
+    </row>
+    <row r="9" spans="1:5" s="57" customFormat="1">
+      <c r="A9" s="52"/>
+      <c r="B9" s="52"/>
+      <c r="C9" s="51"/>
+      <c r="D9" s="51"/>
+      <c r="E9" s="51"/>
+    </row>
+    <row r="10" spans="1:5" s="57" customFormat="1">
+      <c r="A10" s="52"/>
+      <c r="B10" s="52"/>
+      <c r="C10" s="51"/>
+      <c r="D10" s="51"/>
+      <c r="E10" s="51"/>
+    </row>
+    <row r="11" spans="1:5" s="57" customFormat="1">
+      <c r="A11" s="52"/>
+      <c r="B11" s="52"/>
+      <c r="C11" s="51"/>
+      <c r="D11" s="51"/>
+      <c r="E11" s="51"/>
+    </row>
+    <row r="12" spans="1:5" s="57" customFormat="1">
+      <c r="A12" s="52"/>
+      <c r="B12" s="52"/>
+      <c r="C12" s="51"/>
+      <c r="D12" s="51"/>
+      <c r="E12" s="51"/>
+    </row>
+    <row r="13" spans="1:5" s="57" customFormat="1">
+      <c r="A13" s="52"/>
+      <c r="B13" s="52"/>
+      <c r="C13" s="51"/>
+      <c r="D13" s="51"/>
+      <c r="E13" s="51"/>
+    </row>
+    <row r="14" spans="1:5" s="57" customFormat="1">
+      <c r="A14" s="52"/>
+      <c r="B14" s="52"/>
+      <c r="C14" s="51"/>
+      <c r="D14" s="51"/>
+      <c r="E14" s="51"/>
+    </row>
+    <row r="15" spans="1:5" ht="67.5">
+      <c r="A15" s="51" t="s">
+        <v>223</v>
+      </c>
+      <c r="B15" s="52" t="s">
+        <v>232</v>
+      </c>
+      <c r="C15" s="51" t="s">
+        <v>221</v>
+      </c>
+      <c r="D15" s="51" t="s">
+        <v>220</v>
+      </c>
+      <c r="E15" s="53" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="52"/>
+      <c r="B16" s="52"/>
+      <c r="C16" s="51"/>
+      <c r="D16" s="51"/>
+      <c r="E16" s="51"/>
+    </row>
+    <row r="17" spans="1:5" ht="27">
+      <c r="A17" s="52" t="s">
+        <v>304</v>
+      </c>
+      <c r="B17" s="52" t="s">
+        <v>44</v>
+      </c>
+      <c r="C17" s="51" t="s">
+        <v>264</v>
+      </c>
+      <c r="D17" s="51" t="s">
+        <v>233</v>
+      </c>
+      <c r="E17" s="53" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="52"/>
+      <c r="B18" s="52"/>
+      <c r="C18" s="51"/>
+      <c r="D18" s="51"/>
+      <c r="E18" s="53"/>
+    </row>
+    <row r="19" spans="1:5" ht="162">
+      <c r="A19" s="54" t="s">
+        <v>305</v>
+      </c>
+      <c r="B19" s="55" t="s">
+        <v>306</v>
+      </c>
+      <c r="C19" s="56" t="s">
+        <v>307</v>
+      </c>
+      <c r="D19" s="56" t="s">
+        <v>308</v>
+      </c>
+      <c r="E19" s="56"/>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="52"/>
+      <c r="B20" s="52"/>
+      <c r="C20" s="51"/>
+      <c r="D20" s="51"/>
+      <c r="E20" s="51"/>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="52"/>
+      <c r="B21" s="52"/>
+      <c r="C21" s="51"/>
+      <c r="D21" s="51"/>
+      <c r="E21" s="51"/>
+    </row>
+    <row r="22" spans="1:5" ht="81">
+      <c r="A22" s="52" t="s">
+        <v>297</v>
+      </c>
+      <c r="B22" s="52"/>
+      <c r="C22" s="51" t="s">
+        <v>335</v>
+      </c>
+      <c r="D22" s="51" t="s">
+        <v>301</v>
+      </c>
+      <c r="E22" s="51"/>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="52"/>
+      <c r="B23" s="52"/>
+      <c r="C23" s="51"/>
+      <c r="D23" s="51"/>
+      <c r="E23" s="51"/>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="52"/>
+      <c r="B24" s="52"/>
+      <c r="C24" s="51"/>
+      <c r="D24" s="51"/>
+      <c r="E24" s="51"/>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="52" t="s">
+        <v>315</v>
+      </c>
+      <c r="B25" s="52" t="s">
+        <v>218</v>
+      </c>
+      <c r="C25" s="51" t="s">
+        <v>219</v>
+      </c>
+      <c r="D25" s="51" t="s">
         <v>234</v>
       </c>
-      <c r="C2" s="27" t="s">
-        <v>223</v>
-      </c>
-      <c r="D2" s="27" t="s">
-        <v>222</v>
-      </c>
-      <c r="E2" s="29" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="28"/>
-      <c r="B3" s="28"/>
-      <c r="C3" s="27"/>
-      <c r="D3" s="27"/>
-      <c r="E3" s="27"/>
-    </row>
-    <row r="4" spans="1:5" ht="27">
-      <c r="A4" s="28" t="s">
-        <v>306</v>
-      </c>
-      <c r="B4" s="28" t="s">
-        <v>44</v>
-      </c>
-      <c r="C4" s="27" t="s">
-        <v>266</v>
-      </c>
-      <c r="D4" s="27" t="s">
-        <v>235</v>
-      </c>
-      <c r="E4" s="29" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="28"/>
-      <c r="B5" s="28"/>
-      <c r="C5" s="27"/>
-      <c r="D5" s="27"/>
-      <c r="E5" s="29"/>
-    </row>
-    <row r="6" spans="1:5" ht="162">
-      <c r="A6" s="28" t="s">
-        <v>307</v>
-      </c>
-      <c r="B6" s="28" t="s">
-        <v>308</v>
-      </c>
-      <c r="C6" s="27" t="s">
-        <v>309</v>
-      </c>
-      <c r="D6" s="27" t="s">
-        <v>310</v>
-      </c>
-      <c r="E6" s="27"/>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7" s="28"/>
-      <c r="B7" s="28"/>
-      <c r="C7" s="27"/>
-      <c r="D7" s="27"/>
-      <c r="E7" s="27"/>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" s="28"/>
-      <c r="B8" s="28"/>
-      <c r="C8" s="27"/>
-      <c r="D8" s="27"/>
-      <c r="E8" s="27"/>
-    </row>
-    <row r="9" spans="1:5" ht="81">
-      <c r="A9" s="28" t="s">
-        <v>299</v>
-      </c>
-      <c r="B9" s="28"/>
-      <c r="C9" s="27" t="s">
-        <v>337</v>
-      </c>
-      <c r="D9" s="27" t="s">
-        <v>303</v>
-      </c>
-      <c r="E9" s="27"/>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10" s="28"/>
-      <c r="B10" s="28"/>
-      <c r="C10" s="27"/>
-      <c r="D10" s="27"/>
-      <c r="E10" s="27"/>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11" s="28"/>
-      <c r="B11" s="28"/>
-      <c r="C11" s="27"/>
-      <c r="D11" s="27"/>
-      <c r="E11" s="27"/>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12" s="24" t="s">
+      <c r="E25" s="51" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" ht="135">
+      <c r="A26" s="52" t="s">
+        <v>314</v>
+      </c>
+      <c r="B26" s="52" t="s">
+        <v>318</v>
+      </c>
+      <c r="C26" s="51" t="s">
+        <v>316</v>
+      </c>
+      <c r="D26" s="51" t="s">
         <v>317</v>
       </c>
-      <c r="B12" s="24" t="s">
-        <v>219</v>
-      </c>
-      <c r="C12" s="25" t="s">
-        <v>220</v>
-      </c>
-      <c r="D12" s="25" t="s">
-        <v>236</v>
-      </c>
-      <c r="E12" s="25" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" ht="135">
-      <c r="A13" s="28" t="s">
-        <v>316</v>
-      </c>
-      <c r="B13" s="28" t="s">
-        <v>320</v>
-      </c>
-      <c r="C13" s="27" t="s">
-        <v>318</v>
-      </c>
-      <c r="D13" s="27" t="s">
-        <v>319</v>
-      </c>
-      <c r="E13" s="27"/>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14" s="28"/>
-      <c r="B14" s="28"/>
-      <c r="C14" s="27"/>
-      <c r="D14" s="27"/>
-      <c r="E14" s="27"/>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15" s="28"/>
-      <c r="B15" s="28"/>
-      <c r="C15" s="27"/>
-      <c r="D15" s="27"/>
-      <c r="E15" s="27"/>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="A16" s="28"/>
-      <c r="B16" s="28"/>
-      <c r="C16" s="27"/>
-      <c r="D16" s="27"/>
-      <c r="E16" s="27"/>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="28"/>
-      <c r="B17" s="28"/>
-      <c r="C17" s="27"/>
-      <c r="D17" s="27"/>
-      <c r="E17" s="27"/>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="28"/>
-      <c r="B18" s="28"/>
-      <c r="C18" s="27"/>
-      <c r="D18" s="27"/>
-      <c r="E18" s="27"/>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="28"/>
-      <c r="B19" s="28"/>
-      <c r="C19" s="27"/>
-      <c r="D19" s="27"/>
-      <c r="E19" s="27"/>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="28"/>
-      <c r="B20" s="28"/>
-      <c r="C20" s="27"/>
-      <c r="D20" s="27"/>
-      <c r="E20" s="27"/>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="28"/>
-      <c r="B21" s="28"/>
-      <c r="C21" s="27"/>
-      <c r="D21" s="27"/>
-      <c r="E21" s="27"/>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="28"/>
-      <c r="B22" s="28"/>
-      <c r="C22" s="27"/>
-      <c r="D22" s="27"/>
-      <c r="E22" s="27"/>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="28"/>
-      <c r="B23" s="28"/>
-      <c r="C23" s="27"/>
-      <c r="D23" s="27"/>
-      <c r="E23" s="27"/>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="28"/>
-      <c r="B24" s="28"/>
-      <c r="C24" s="27"/>
-      <c r="D24" s="27"/>
-      <c r="E24" s="27"/>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="28"/>
-      <c r="B25" s="28"/>
-      <c r="C25" s="27"/>
-      <c r="D25" s="27"/>
-      <c r="E25" s="27"/>
+      <c r="E26" s="51"/>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="52"/>
+      <c r="B27" s="52"/>
+      <c r="C27" s="51"/>
+      <c r="D27" s="51"/>
+      <c r="E27" s="51"/>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="52"/>
+      <c r="B28" s="52"/>
+      <c r="C28" s="51"/>
+      <c r="D28" s="51"/>
+      <c r="E28" s="51"/>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="52"/>
+      <c r="B29" s="52"/>
+      <c r="C29" s="51"/>
+      <c r="D29" s="51"/>
+      <c r="E29" s="51"/>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="52"/>
+      <c r="B30" s="52"/>
+      <c r="C30" s="51"/>
+      <c r="D30" s="51"/>
+      <c r="E30" s="51"/>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="52"/>
+      <c r="B31" s="52"/>
+      <c r="C31" s="51"/>
+      <c r="D31" s="51"/>
+      <c r="E31" s="51"/>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="52"/>
+      <c r="B32" s="52"/>
+      <c r="C32" s="51"/>
+      <c r="D32" s="51"/>
+      <c r="E32" s="51"/>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="52"/>
+      <c r="B33" s="52"/>
+      <c r="C33" s="51"/>
+      <c r="D33" s="51"/>
+      <c r="E33" s="51"/>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="52"/>
+      <c r="B34" s="52"/>
+      <c r="C34" s="51"/>
+      <c r="D34" s="51"/>
+      <c r="E34" s="51"/>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="52"/>
+      <c r="B35" s="52"/>
+      <c r="C35" s="51"/>
+      <c r="D35" s="51"/>
+      <c r="E35" s="51"/>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="52"/>
+      <c r="B36" s="52"/>
+      <c r="C36" s="51"/>
+      <c r="D36" s="51"/>
+      <c r="E36" s="51"/>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="52"/>
+      <c r="B37" s="52"/>
+      <c r="C37" s="51"/>
+      <c r="D37" s="51"/>
+      <c r="E37" s="51"/>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="52"/>
+      <c r="B38" s="52"/>
+      <c r="C38" s="51"/>
+      <c r="D38" s="51"/>
+      <c r="E38" s="51"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -5074,163 +5654,619 @@
   <sheetData>
     <row r="1" spans="1:4" ht="27">
       <c r="A1" s="23" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="27">
       <c r="A2" s="23" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="25" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="B4" s="25" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C4" s="25"/>
       <c r="D4" s="25"/>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" s="30" t="s">
-        <v>242</v>
+      <c r="A5" s="27" t="s">
+        <v>240</v>
       </c>
       <c r="B5" s="26" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="C5" s="26"/>
       <c r="D5" s="26"/>
     </row>
     <row r="6" spans="1:4">
-      <c r="A6" s="30" t="s">
-        <v>243</v>
+      <c r="A6" s="27" t="s">
+        <v>241</v>
       </c>
       <c r="B6" s="26" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C6" s="26"/>
       <c r="D6" s="26"/>
     </row>
     <row r="7" spans="1:4">
-      <c r="A7" s="30" t="s">
-        <v>244</v>
+      <c r="A7" s="27" t="s">
+        <v>242</v>
       </c>
       <c r="B7" s="26" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C7" s="26"/>
       <c r="D7" s="26"/>
     </row>
     <row r="8" spans="1:4">
-      <c r="A8" s="30" t="s">
-        <v>245</v>
+      <c r="A8" s="27" t="s">
+        <v>243</v>
       </c>
       <c r="B8" s="26" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C8" s="26"/>
       <c r="D8" s="26"/>
     </row>
     <row r="9" spans="1:4">
-      <c r="A9" s="30" t="s">
-        <v>246</v>
+      <c r="A9" s="27" t="s">
+        <v>244</v>
       </c>
       <c r="B9" s="26" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C9" s="26"/>
       <c r="D9" s="26"/>
     </row>
     <row r="10" spans="1:4">
-      <c r="A10" s="30" t="s">
-        <v>247</v>
+      <c r="A10" s="27" t="s">
+        <v>245</v>
       </c>
       <c r="B10" s="26" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C10" s="26"/>
       <c r="D10" s="26"/>
     </row>
     <row r="11" spans="1:4">
-      <c r="A11" s="30" t="s">
-        <v>248</v>
+      <c r="A11" s="27" t="s">
+        <v>246</v>
       </c>
       <c r="B11" s="26" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C11" s="26"/>
       <c r="D11" s="26"/>
     </row>
     <row r="12" spans="1:4">
-      <c r="A12" s="30" t="s">
-        <v>249</v>
+      <c r="A12" s="27" t="s">
+        <v>247</v>
       </c>
       <c r="B12" s="26" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C12" s="26"/>
       <c r="D12" s="26"/>
     </row>
     <row r="13" spans="1:4">
-      <c r="A13" s="30" t="s">
-        <v>254</v>
+      <c r="A13" s="27" t="s">
+        <v>252</v>
       </c>
       <c r="B13" s="26" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C13" s="26"/>
       <c r="D13" s="26"/>
     </row>
     <row r="14" spans="1:4" ht="27">
-      <c r="A14" s="30" t="s">
-        <v>255</v>
+      <c r="A14" s="27" t="s">
+        <v>253</v>
       </c>
       <c r="B14" s="26" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="C14" s="26"/>
       <c r="D14" s="26"/>
     </row>
     <row r="15" spans="1:4">
-      <c r="A15" s="31" t="s">
-        <v>256</v>
-      </c>
-      <c r="B15" s="32" t="s">
+      <c r="A15" s="28" t="s">
+        <v>254</v>
+      </c>
+      <c r="B15" s="29" t="s">
+        <v>249</v>
+      </c>
+      <c r="C15" s="29"/>
+      <c r="D15" s="29"/>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="30" t="s">
+        <v>248</v>
+      </c>
+      <c r="B16" s="29" t="s">
+        <v>249</v>
+      </c>
+      <c r="C16" s="29"/>
+      <c r="D16" s="29"/>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" s="30" t="s">
+        <v>250</v>
+      </c>
+      <c r="B17" s="29" t="s">
+        <v>249</v>
+      </c>
+      <c r="C17" s="29"/>
+      <c r="D17" s="29"/>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" s="30" t="s">
         <v>251</v>
       </c>
-      <c r="C15" s="32"/>
-      <c r="D15" s="32"/>
-    </row>
-    <row r="16" spans="1:4">
-      <c r="A16" s="33" t="s">
-        <v>250</v>
-      </c>
-      <c r="B16" s="32" t="s">
-        <v>251</v>
-      </c>
-      <c r="C16" s="32"/>
-      <c r="D16" s="32"/>
-    </row>
-    <row r="17" spans="1:4">
-      <c r="A17" s="33" t="s">
-        <v>252</v>
-      </c>
-      <c r="B17" s="32" t="s">
-        <v>251</v>
-      </c>
-      <c r="C17" s="32"/>
-      <c r="D17" s="32"/>
-    </row>
-    <row r="18" spans="1:4">
-      <c r="A18" s="33" t="s">
-        <v>253</v>
-      </c>
-      <c r="B18" s="32" t="s">
-        <v>251</v>
-      </c>
-      <c r="C18" s="32"/>
-      <c r="D18" s="32"/>
+      <c r="B18" s="29" t="s">
+        <v>249</v>
+      </c>
+      <c r="C18" s="29"/>
+      <c r="D18" s="29"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C17"/>
+  <sheetFormatPr defaultRowHeight="12"/>
+  <cols>
+    <col min="1" max="1" width="16.625" style="3" customWidth="1"/>
+    <col min="2" max="2" width="49.875" style="3" customWidth="1"/>
+    <col min="3" max="3" width="55.375" style="3" customWidth="1"/>
+    <col min="4" max="5" width="9" style="3"/>
+    <col min="6" max="6" width="34" style="3" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="48" t="s">
+        <v>336</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="93" customHeight="1">
+      <c r="A2" s="50" t="s">
+        <v>188</v>
+      </c>
+      <c r="B2" s="49" t="s">
+        <v>337</v>
+      </c>
+      <c r="C2" s="49" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="123.75" customHeight="1">
+      <c r="A3" s="50" t="s">
+        <v>191</v>
+      </c>
+      <c r="B3" s="49" t="s">
+        <v>344</v>
+      </c>
+      <c r="C3" s="49" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="204">
+      <c r="A4" s="50" t="s">
+        <v>306</v>
+      </c>
+      <c r="B4" s="49" t="s">
+        <v>343</v>
+      </c>
+      <c r="C4" s="49" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="4"/>
+      <c r="B5" s="4"/>
+      <c r="C5" s="4"/>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="4"/>
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="4"/>
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="4"/>
+      <c r="B8" s="4"/>
+      <c r="C8" s="4"/>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="4"/>
+      <c r="B9" s="4"/>
+      <c r="C9" s="4"/>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" s="4"/>
+      <c r="B10" s="4"/>
+      <c r="C10" s="4"/>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" s="4"/>
+      <c r="B11" s="4"/>
+      <c r="C11" s="4"/>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" s="4"/>
+      <c r="B12" s="4"/>
+      <c r="C12" s="4"/>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" s="4"/>
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" s="4"/>
+      <c r="B14" s="4"/>
+      <c r="C14" s="4"/>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" s="4"/>
+      <c r="B15" s="4"/>
+      <c r="C15" s="4"/>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" s="4"/>
+      <c r="B16" s="4"/>
+      <c r="C16" s="4"/>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" s="4"/>
+      <c r="B17" s="4"/>
+      <c r="C17" s="4"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E28"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
+  <cols>
+    <col min="1" max="1" width="22.375" style="23" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="37" customWidth="1"/>
+    <col min="4" max="4" width="46.5" style="23" customWidth="1"/>
+    <col min="5" max="5" width="28.375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="5" t="s">
+        <v>345</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>350</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="9" t="s">
+        <v>348</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="C2" s="4"/>
+      <c r="D2" s="9" t="s">
+        <v>351</v>
+      </c>
+      <c r="E2" s="4"/>
+    </row>
+    <row r="3" spans="1:5" ht="156">
+      <c r="A3" s="9" t="s">
+        <v>349</v>
+      </c>
+      <c r="B3" s="4"/>
+      <c r="C3" s="9" t="s">
+        <v>357</v>
+      </c>
+      <c r="D3" s="9"/>
+      <c r="E3" s="9" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="59"/>
+      <c r="B4" s="60"/>
+      <c r="C4" s="59"/>
+      <c r="D4" s="59"/>
+      <c r="E4" s="59"/>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="11" t="s">
+        <v>353</v>
+      </c>
+      <c r="B5" s="18"/>
+      <c r="C5" s="18" t="s">
+        <v>356</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>354</v>
+      </c>
+      <c r="E5" s="18"/>
+    </row>
+    <row r="6" spans="1:5" ht="144">
+      <c r="A6" s="9" t="s">
+        <v>359</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>355</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>358</v>
+      </c>
+      <c r="D6" s="9"/>
+      <c r="E6" s="4"/>
+    </row>
+    <row r="7" spans="1:5" ht="132">
+      <c r="A7" s="9" t="s">
+        <v>360</v>
+      </c>
+      <c r="B7" s="4"/>
+      <c r="C7" s="9" t="s">
+        <v>361</v>
+      </c>
+      <c r="D7" s="9"/>
+      <c r="E7" s="4"/>
+    </row>
+    <row r="8" spans="1:5" ht="132">
+      <c r="A8" s="9" t="s">
+        <v>362</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>363</v>
+      </c>
+      <c r="D8" s="9"/>
+      <c r="E8" s="4"/>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="9" t="s">
+        <v>364</v>
+      </c>
+      <c r="B9" s="4"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="58" t="s">
+        <v>365</v>
+      </c>
+      <c r="E9" s="4"/>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="9" t="s">
+        <v>366</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>367</v>
+      </c>
+      <c r="C10" s="4"/>
+      <c r="D10" s="58" t="s">
+        <v>369</v>
+      </c>
+      <c r="E10" s="4"/>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="9" t="s">
+        <v>368</v>
+      </c>
+      <c r="B11" s="4"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="58" t="s">
+        <v>370</v>
+      </c>
+      <c r="E11" s="4"/>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="61"/>
+      <c r="B12" s="62"/>
+      <c r="C12" s="62"/>
+      <c r="D12" s="63"/>
+      <c r="E12" s="62"/>
+    </row>
+    <row r="13" spans="1:5" ht="409.5">
+      <c r="A13" s="9" t="s">
+        <v>371</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>373</v>
+      </c>
+      <c r="D13" s="58" t="s">
+        <v>376</v>
+      </c>
+      <c r="E13" s="4"/>
+    </row>
+    <row r="14" spans="1:5" ht="24">
+      <c r="A14" s="9" t="s">
+        <v>374</v>
+      </c>
+      <c r="B14" s="4"/>
+      <c r="C14" s="4"/>
+      <c r="D14" s="58" t="s">
+        <v>375</v>
+      </c>
+      <c r="E14" s="4"/>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="61"/>
+      <c r="B15" s="62"/>
+      <c r="C15" s="62"/>
+      <c r="D15" s="63"/>
+      <c r="E15" s="62"/>
+    </row>
+    <row r="16" spans="1:5" ht="168">
+      <c r="A16" s="9" t="s">
+        <v>380</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>377</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>378</v>
+      </c>
+      <c r="D16" s="58" t="s">
+        <v>379</v>
+      </c>
+      <c r="E16" s="4"/>
+    </row>
+    <row r="17" spans="1:5" ht="24">
+      <c r="A17" s="9" t="s">
+        <v>381</v>
+      </c>
+      <c r="B17" s="4"/>
+      <c r="C17" s="4" t="s">
+        <v>382</v>
+      </c>
+      <c r="D17" s="58" t="s">
+        <v>383</v>
+      </c>
+      <c r="E17" s="4"/>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="61"/>
+      <c r="B18" s="62"/>
+      <c r="C18" s="62"/>
+      <c r="D18" s="63"/>
+      <c r="E18" s="62"/>
+    </row>
+    <row r="19" spans="1:5" ht="192">
+      <c r="A19" s="9" t="s">
+        <v>384</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>377</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>378</v>
+      </c>
+      <c r="D19" s="58" t="s">
+        <v>388</v>
+      </c>
+      <c r="E19" s="4"/>
+    </row>
+    <row r="20" spans="1:5" ht="24">
+      <c r="A20" s="9" t="s">
+        <v>385</v>
+      </c>
+      <c r="B20" s="4"/>
+      <c r="C20" s="4" t="s">
+        <v>382</v>
+      </c>
+      <c r="D20" s="58" t="s">
+        <v>383</v>
+      </c>
+      <c r="E20" s="4"/>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="61"/>
+      <c r="B21" s="62"/>
+      <c r="C21" s="62"/>
+      <c r="D21" s="63"/>
+      <c r="E21" s="62"/>
+    </row>
+    <row r="22" spans="1:5" ht="192">
+      <c r="A22" s="9" t="s">
+        <v>386</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>377</v>
+      </c>
+      <c r="C22" s="9" t="s">
+        <v>378</v>
+      </c>
+      <c r="D22" s="58" t="s">
+        <v>389</v>
+      </c>
+      <c r="E22" s="4"/>
+    </row>
+    <row r="23" spans="1:5" ht="24">
+      <c r="A23" s="9" t="s">
+        <v>387</v>
+      </c>
+      <c r="B23" s="4"/>
+      <c r="C23" s="4" t="s">
+        <v>382</v>
+      </c>
+      <c r="D23" s="58" t="s">
+        <v>383</v>
+      </c>
+      <c r="E23" s="4"/>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="61"/>
+      <c r="B24" s="62"/>
+      <c r="C24" s="62"/>
+      <c r="D24" s="63"/>
+      <c r="E24" s="62"/>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="9"/>
+      <c r="B25" s="4"/>
+      <c r="C25" s="4"/>
+      <c r="D25" s="58"/>
+      <c r="E25" s="4"/>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="9"/>
+      <c r="B26" s="4"/>
+      <c r="C26" s="4"/>
+      <c r="D26" s="58"/>
+      <c r="E26" s="4"/>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="9"/>
+      <c r="B27" s="4"/>
+      <c r="C27" s="4"/>
+      <c r="D27" s="9"/>
+      <c r="E27" s="4"/>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="9"/>
+      <c r="B28" s="4"/>
+      <c r="C28" s="4"/>
+      <c r="D28" s="9"/>
+      <c r="E28" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/internal_doc/03.开发设计/OM_web接口.xlsx
+++ b/internal_doc/03.开发设计/OM_web接口.xlsx
@@ -2050,23 +2050,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>以内部的Query命令发，命令字为update task
-ResultInfo不同任务类型格式不一样：
-task为添加机器时，ResultInfo:
-[
-{
-    OM_HOST_FIELD_IP:"ip",
-    OM_HOST_FIELD_NAME:"host",
-    OM_TASKINFO_FIELD_STATUS:1,
-    OM_TASKINFO_FIELD_STATUS_DESC:"desc",
-    OM_REST_RES_RETCODE:0,
-    OM_REST_RES_DETAIL:"detail",
-    OM_TASKINFO_FIELD_FLOW:"flow"
-}
-]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>agent更新ADD_HOST任务进度请求(agent-&gt;om)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2131,7 +2114,24 @@
     OM_TASKINFO_FIELD_STATUS_DESC:"desc",
     OM_REST_RES_RETCODE:0,
     OM_REST_RES_DETAIL:"detail",
-    OM_TASKINFO_FIELD_FLOW:"flow"
+    OM_TASKINFO_FIELD_FLOW:null
+}
+]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>以内部的Query命令发，命令字为update task
+ResultInfo不同任务类型格式不一样：
+task为添加机器时，ResultInfo:
+[
+{
+    OM_HOST_FIELD_IP:"ip",
+    OM_HOST_FIELD_NAME:"host",
+    OM_TASKINFO_FIELD_STATUS:1,
+    OM_TASKINFO_FIELD_STATUS_DESC:"desc",
+    OM_REST_RES_RETCODE:0,
+    OM_REST_RES_DETAIL:"detail",
+    OM_TASKINFO_FIELD_FLOW:null
 }
 ]</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -6137,7 +6137,7 @@
     </row>
     <row r="16" spans="1:5" ht="168">
       <c r="A16" s="9" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>377</v>
@@ -6146,20 +6146,20 @@
         <v>378</v>
       </c>
       <c r="D16" s="58" t="s">
-        <v>379</v>
+        <v>389</v>
       </c>
       <c r="E16" s="4"/>
     </row>
     <row r="17" spans="1:5" ht="24">
       <c r="A17" s="9" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B17" s="4"/>
       <c r="C17" s="4" t="s">
+        <v>381</v>
+      </c>
+      <c r="D17" s="58" t="s">
         <v>382</v>
-      </c>
-      <c r="D17" s="58" t="s">
-        <v>383</v>
       </c>
       <c r="E17" s="4"/>
     </row>
@@ -6172,7 +6172,7 @@
     </row>
     <row r="19" spans="1:5" ht="192">
       <c r="A19" s="9" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>377</v>
@@ -6181,20 +6181,20 @@
         <v>378</v>
       </c>
       <c r="D19" s="58" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="E19" s="4"/>
     </row>
     <row r="20" spans="1:5" ht="24">
       <c r="A20" s="9" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B20" s="4"/>
       <c r="C20" s="4" t="s">
+        <v>381</v>
+      </c>
+      <c r="D20" s="58" t="s">
         <v>382</v>
-      </c>
-      <c r="D20" s="58" t="s">
-        <v>383</v>
       </c>
       <c r="E20" s="4"/>
     </row>
@@ -6207,7 +6207,7 @@
     </row>
     <row r="22" spans="1:5" ht="192">
       <c r="A22" s="9" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>377</v>
@@ -6216,20 +6216,20 @@
         <v>378</v>
       </c>
       <c r="D22" s="58" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="E22" s="4"/>
     </row>
     <row r="23" spans="1:5" ht="24">
       <c r="A23" s="9" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B23" s="4"/>
       <c r="C23" s="4" t="s">
+        <v>381</v>
+      </c>
+      <c r="D23" s="58" t="s">
         <v>382</v>
-      </c>
-      <c r="D23" s="58" t="s">
-        <v>383</v>
       </c>
       <c r="E23" s="4"/>
     </row>

--- a/internal_doc/03.开发设计/OM_web接口.xlsx
+++ b/internal_doc/03.开发设计/OM_web接口.xlsx
@@ -1982,10 +1982,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>notify agent</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>{
   TaskID:任务ID
 }</t>
@@ -2134,6 +2130,10 @@
     OM_TASKINFO_FIELD_FLOW:null
 }
 ]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>notify task</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2488,24 +2488,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -2540,80 +2522,30 @@
     <xf numFmtId="0" fontId="21" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -2625,7 +2557,7 @@
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="C7EDCC"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -2950,7 +2882,7 @@
       </c>
     </row>
     <row r="3" spans="1:8">
-      <c r="A3" s="42" t="s">
+      <c r="A3" s="58" t="s">
         <v>12</v>
       </c>
       <c r="B3" s="4" t="s">
@@ -2968,7 +2900,7 @@
       <c r="H3" s="4"/>
     </row>
     <row r="4" spans="1:8" ht="13.5">
-      <c r="A4" s="43"/>
+      <c r="A4" s="59"/>
       <c r="B4" s="4" t="s">
         <v>5</v>
       </c>
@@ -2984,7 +2916,7 @@
       <c r="H4" s="4"/>
     </row>
     <row r="5" spans="1:8" ht="13.5">
-      <c r="A5" s="43"/>
+      <c r="A5" s="59"/>
       <c r="B5" s="4" t="s">
         <v>8</v>
       </c>
@@ -3000,7 +2932,7 @@
       <c r="H5" s="4"/>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" s="44"/>
+      <c r="A6" s="60"/>
       <c r="B6" s="4" t="s">
         <v>13</v>
       </c>
@@ -3016,7 +2948,7 @@
       <c r="H6" s="4"/>
     </row>
     <row r="7" spans="1:8" ht="24">
-      <c r="A7" s="45" t="s">
+      <c r="A7" s="61" t="s">
         <v>24</v>
       </c>
       <c r="B7" s="4" t="s">
@@ -3034,7 +2966,7 @@
       <c r="H7" s="4"/>
     </row>
     <row r="8" spans="1:8" ht="36">
-      <c r="A8" s="46"/>
+      <c r="A8" s="62"/>
       <c r="B8" s="4" t="s">
         <v>17</v>
       </c>
@@ -3052,7 +2984,7 @@
       <c r="H8" s="4"/>
     </row>
     <row r="9" spans="1:8" ht="72">
-      <c r="A9" s="46"/>
+      <c r="A9" s="62"/>
       <c r="B9" s="4" t="s">
         <v>18</v>
       </c>
@@ -3070,7 +3002,7 @@
       <c r="H9" s="4"/>
     </row>
     <row r="10" spans="1:8" ht="24">
-      <c r="A10" s="47"/>
+      <c r="A10" s="63"/>
       <c r="B10" s="4" t="s">
         <v>21</v>
       </c>
@@ -3108,7 +3040,7 @@
       <c r="H11" s="4"/>
     </row>
     <row r="12" spans="1:8" ht="24">
-      <c r="A12" s="45" t="s">
+      <c r="A12" s="61" t="s">
         <v>26</v>
       </c>
       <c r="B12" s="4" t="s">
@@ -3126,7 +3058,7 @@
       <c r="H12" s="4"/>
     </row>
     <row r="13" spans="1:8">
-      <c r="A13" s="46"/>
+      <c r="A13" s="62"/>
       <c r="B13" s="4" t="s">
         <v>32</v>
       </c>
@@ -3142,7 +3074,7 @@
       <c r="H13" s="4"/>
     </row>
     <row r="14" spans="1:8" ht="24">
-      <c r="A14" s="46"/>
+      <c r="A14" s="62"/>
       <c r="B14" s="4" t="s">
         <v>33</v>
       </c>
@@ -3160,7 +3092,7 @@
       <c r="H14" s="4"/>
     </row>
     <row r="15" spans="1:8">
-      <c r="A15" s="46"/>
+      <c r="A15" s="62"/>
       <c r="B15" s="4" t="s">
         <v>35</v>
       </c>
@@ -3176,7 +3108,7 @@
       <c r="H15" s="4"/>
     </row>
     <row r="16" spans="1:8">
-      <c r="A16" s="46"/>
+      <c r="A16" s="62"/>
       <c r="B16" s="4" t="s">
         <v>57</v>
       </c>
@@ -3188,7 +3120,7 @@
       <c r="H16" s="4"/>
     </row>
     <row r="17" spans="1:8" ht="48">
-      <c r="A17" s="46"/>
+      <c r="A17" s="62"/>
       <c r="B17" s="4" t="s">
         <v>30</v>
       </c>
@@ -3206,7 +3138,7 @@
       <c r="H17" s="4"/>
     </row>
     <row r="18" spans="1:8">
-      <c r="A18" s="46"/>
+      <c r="A18" s="62"/>
       <c r="B18" s="4" t="s">
         <v>38</v>
       </c>
@@ -3222,7 +3154,7 @@
       <c r="H18" s="4"/>
     </row>
     <row r="19" spans="1:8">
-      <c r="A19" s="46"/>
+      <c r="A19" s="62"/>
       <c r="B19" s="4" t="s">
         <v>41</v>
       </c>
@@ -3238,7 +3170,7 @@
       <c r="H19" s="4"/>
     </row>
     <row r="20" spans="1:8">
-      <c r="A20" s="46"/>
+      <c r="A20" s="62"/>
       <c r="B20" s="4" t="s">
         <v>40</v>
       </c>
@@ -3254,7 +3186,7 @@
       <c r="H20" s="4"/>
     </row>
     <row r="21" spans="1:8" ht="24">
-      <c r="A21" s="46"/>
+      <c r="A21" s="62"/>
       <c r="B21" s="4" t="s">
         <v>44</v>
       </c>
@@ -3272,7 +3204,7 @@
       <c r="H21" s="4"/>
     </row>
     <row r="22" spans="1:8" ht="24">
-      <c r="A22" s="46"/>
+      <c r="A22" s="62"/>
       <c r="B22" s="4" t="s">
         <v>47</v>
       </c>
@@ -3288,7 +3220,7 @@
       <c r="H22" s="4"/>
     </row>
     <row r="23" spans="1:8" ht="24">
-      <c r="A23" s="46"/>
+      <c r="A23" s="62"/>
       <c r="B23" s="4" t="s">
         <v>49</v>
       </c>
@@ -5324,316 +5256,316 @@
         <v>51</v>
       </c>
     </row>
-    <row r="2" spans="1:5" s="57" customFormat="1">
-      <c r="A2" s="52"/>
-      <c r="B2" s="52"/>
-      <c r="C2" s="51"/>
-      <c r="D2" s="51"/>
-      <c r="E2" s="51"/>
-    </row>
-    <row r="3" spans="1:5" s="57" customFormat="1">
-      <c r="A3" s="52"/>
-      <c r="B3" s="52"/>
-      <c r="C3" s="51"/>
-      <c r="D3" s="51"/>
-      <c r="E3" s="51"/>
-    </row>
-    <row r="4" spans="1:5" s="57" customFormat="1">
-      <c r="A4" s="52"/>
-      <c r="B4" s="52"/>
-      <c r="C4" s="51"/>
-      <c r="D4" s="51"/>
-      <c r="E4" s="51"/>
-    </row>
-    <row r="5" spans="1:5" s="57" customFormat="1">
-      <c r="A5" s="52"/>
-      <c r="B5" s="52"/>
-      <c r="C5" s="51"/>
-      <c r="D5" s="51"/>
-      <c r="E5" s="51"/>
-    </row>
-    <row r="6" spans="1:5" s="57" customFormat="1">
-      <c r="A6" s="52"/>
-      <c r="B6" s="52"/>
-      <c r="C6" s="51"/>
-      <c r="D6" s="51"/>
-      <c r="E6" s="51"/>
-    </row>
-    <row r="7" spans="1:5" s="57" customFormat="1">
-      <c r="A7" s="52"/>
-      <c r="B7" s="52"/>
-      <c r="C7" s="51"/>
-      <c r="D7" s="51"/>
-      <c r="E7" s="51"/>
-    </row>
-    <row r="8" spans="1:5" s="57" customFormat="1">
-      <c r="A8" s="52"/>
-      <c r="B8" s="52"/>
-      <c r="C8" s="51"/>
-      <c r="D8" s="51"/>
-      <c r="E8" s="51"/>
-    </row>
-    <row r="9" spans="1:5" s="57" customFormat="1">
-      <c r="A9" s="52"/>
-      <c r="B9" s="52"/>
-      <c r="C9" s="51"/>
-      <c r="D9" s="51"/>
-      <c r="E9" s="51"/>
-    </row>
-    <row r="10" spans="1:5" s="57" customFormat="1">
-      <c r="A10" s="52"/>
-      <c r="B10" s="52"/>
-      <c r="C10" s="51"/>
-      <c r="D10" s="51"/>
-      <c r="E10" s="51"/>
-    </row>
-    <row r="11" spans="1:5" s="57" customFormat="1">
-      <c r="A11" s="52"/>
-      <c r="B11" s="52"/>
-      <c r="C11" s="51"/>
-      <c r="D11" s="51"/>
-      <c r="E11" s="51"/>
-    </row>
-    <row r="12" spans="1:5" s="57" customFormat="1">
-      <c r="A12" s="52"/>
-      <c r="B12" s="52"/>
-      <c r="C12" s="51"/>
-      <c r="D12" s="51"/>
-      <c r="E12" s="51"/>
-    </row>
-    <row r="13" spans="1:5" s="57" customFormat="1">
-      <c r="A13" s="52"/>
-      <c r="B13" s="52"/>
-      <c r="C13" s="51"/>
-      <c r="D13" s="51"/>
-      <c r="E13" s="51"/>
-    </row>
-    <row r="14" spans="1:5" s="57" customFormat="1">
-      <c r="A14" s="52"/>
-      <c r="B14" s="52"/>
-      <c r="C14" s="51"/>
-      <c r="D14" s="51"/>
-      <c r="E14" s="51"/>
+    <row r="2" spans="1:5" s="51" customFormat="1">
+      <c r="A2" s="46"/>
+      <c r="B2" s="46"/>
+      <c r="C2" s="45"/>
+      <c r="D2" s="45"/>
+      <c r="E2" s="45"/>
+    </row>
+    <row r="3" spans="1:5" s="51" customFormat="1">
+      <c r="A3" s="46"/>
+      <c r="B3" s="46"/>
+      <c r="C3" s="45"/>
+      <c r="D3" s="45"/>
+      <c r="E3" s="45"/>
+    </row>
+    <row r="4" spans="1:5" s="51" customFormat="1">
+      <c r="A4" s="46"/>
+      <c r="B4" s="46"/>
+      <c r="C4" s="45"/>
+      <c r="D4" s="45"/>
+      <c r="E4" s="45"/>
+    </row>
+    <row r="5" spans="1:5" s="51" customFormat="1">
+      <c r="A5" s="46"/>
+      <c r="B5" s="46"/>
+      <c r="C5" s="45"/>
+      <c r="D5" s="45"/>
+      <c r="E5" s="45"/>
+    </row>
+    <row r="6" spans="1:5" s="51" customFormat="1">
+      <c r="A6" s="46"/>
+      <c r="B6" s="46"/>
+      <c r="C6" s="45"/>
+      <c r="D6" s="45"/>
+      <c r="E6" s="45"/>
+    </row>
+    <row r="7" spans="1:5" s="51" customFormat="1">
+      <c r="A7" s="46"/>
+      <c r="B7" s="46"/>
+      <c r="C7" s="45"/>
+      <c r="D7" s="45"/>
+      <c r="E7" s="45"/>
+    </row>
+    <row r="8" spans="1:5" s="51" customFormat="1">
+      <c r="A8" s="46"/>
+      <c r="B8" s="46"/>
+      <c r="C8" s="45"/>
+      <c r="D8" s="45"/>
+      <c r="E8" s="45"/>
+    </row>
+    <row r="9" spans="1:5" s="51" customFormat="1">
+      <c r="A9" s="46"/>
+      <c r="B9" s="46"/>
+      <c r="C9" s="45"/>
+      <c r="D9" s="45"/>
+      <c r="E9" s="45"/>
+    </row>
+    <row r="10" spans="1:5" s="51" customFormat="1">
+      <c r="A10" s="46"/>
+      <c r="B10" s="46"/>
+      <c r="C10" s="45"/>
+      <c r="D10" s="45"/>
+      <c r="E10" s="45"/>
+    </row>
+    <row r="11" spans="1:5" s="51" customFormat="1">
+      <c r="A11" s="46"/>
+      <c r="B11" s="46"/>
+      <c r="C11" s="45"/>
+      <c r="D11" s="45"/>
+      <c r="E11" s="45"/>
+    </row>
+    <row r="12" spans="1:5" s="51" customFormat="1">
+      <c r="A12" s="46"/>
+      <c r="B12" s="46"/>
+      <c r="C12" s="45"/>
+      <c r="D12" s="45"/>
+      <c r="E12" s="45"/>
+    </row>
+    <row r="13" spans="1:5" s="51" customFormat="1">
+      <c r="A13" s="46"/>
+      <c r="B13" s="46"/>
+      <c r="C13" s="45"/>
+      <c r="D13" s="45"/>
+      <c r="E13" s="45"/>
+    </row>
+    <row r="14" spans="1:5" s="51" customFormat="1">
+      <c r="A14" s="46"/>
+      <c r="B14" s="46"/>
+      <c r="C14" s="45"/>
+      <c r="D14" s="45"/>
+      <c r="E14" s="45"/>
     </row>
     <row r="15" spans="1:5" ht="67.5">
-      <c r="A15" s="51" t="s">
+      <c r="A15" s="45" t="s">
         <v>223</v>
       </c>
-      <c r="B15" s="52" t="s">
+      <c r="B15" s="46" t="s">
         <v>232</v>
       </c>
-      <c r="C15" s="51" t="s">
+      <c r="C15" s="45" t="s">
         <v>221</v>
       </c>
-      <c r="D15" s="51" t="s">
+      <c r="D15" s="45" t="s">
         <v>220</v>
       </c>
-      <c r="E15" s="53" t="s">
+      <c r="E15" s="47" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="16" spans="1:5">
-      <c r="A16" s="52"/>
-      <c r="B16" s="52"/>
-      <c r="C16" s="51"/>
-      <c r="D16" s="51"/>
-      <c r="E16" s="51"/>
+      <c r="A16" s="46"/>
+      <c r="B16" s="46"/>
+      <c r="C16" s="45"/>
+      <c r="D16" s="45"/>
+      <c r="E16" s="45"/>
     </row>
     <row r="17" spans="1:5" ht="27">
-      <c r="A17" s="52" t="s">
+      <c r="A17" s="46" t="s">
         <v>304</v>
       </c>
-      <c r="B17" s="52" t="s">
+      <c r="B17" s="46" t="s">
         <v>44</v>
       </c>
-      <c r="C17" s="51" t="s">
+      <c r="C17" s="45" t="s">
         <v>264</v>
       </c>
-      <c r="D17" s="51" t="s">
+      <c r="D17" s="45" t="s">
         <v>233</v>
       </c>
-      <c r="E17" s="53" t="s">
+      <c r="E17" s="47" t="s">
         <v>235</v>
       </c>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="52"/>
-      <c r="B18" s="52"/>
-      <c r="C18" s="51"/>
-      <c r="D18" s="51"/>
-      <c r="E18" s="53"/>
+      <c r="A18" s="46"/>
+      <c r="B18" s="46"/>
+      <c r="C18" s="45"/>
+      <c r="D18" s="45"/>
+      <c r="E18" s="47"/>
     </row>
     <row r="19" spans="1:5" ht="162">
-      <c r="A19" s="54" t="s">
+      <c r="A19" s="48" t="s">
         <v>305</v>
       </c>
-      <c r="B19" s="55" t="s">
+      <c r="B19" s="49" t="s">
         <v>306</v>
       </c>
-      <c r="C19" s="56" t="s">
+      <c r="C19" s="50" t="s">
         <v>307</v>
       </c>
-      <c r="D19" s="56" t="s">
+      <c r="D19" s="50" t="s">
         <v>308</v>
       </c>
-      <c r="E19" s="56"/>
+      <c r="E19" s="50"/>
     </row>
     <row r="20" spans="1:5">
-      <c r="A20" s="52"/>
-      <c r="B20" s="52"/>
-      <c r="C20" s="51"/>
-      <c r="D20" s="51"/>
-      <c r="E20" s="51"/>
+      <c r="A20" s="46"/>
+      <c r="B20" s="46"/>
+      <c r="C20" s="45"/>
+      <c r="D20" s="45"/>
+      <c r="E20" s="45"/>
     </row>
     <row r="21" spans="1:5">
-      <c r="A21" s="52"/>
-      <c r="B21" s="52"/>
-      <c r="C21" s="51"/>
-      <c r="D21" s="51"/>
-      <c r="E21" s="51"/>
+      <c r="A21" s="46"/>
+      <c r="B21" s="46"/>
+      <c r="C21" s="45"/>
+      <c r="D21" s="45"/>
+      <c r="E21" s="45"/>
     </row>
     <row r="22" spans="1:5" ht="81">
-      <c r="A22" s="52" t="s">
+      <c r="A22" s="46" t="s">
         <v>297</v>
       </c>
-      <c r="B22" s="52"/>
-      <c r="C22" s="51" t="s">
+      <c r="B22" s="46"/>
+      <c r="C22" s="45" t="s">
         <v>335</v>
       </c>
-      <c r="D22" s="51" t="s">
+      <c r="D22" s="45" t="s">
         <v>301</v>
       </c>
-      <c r="E22" s="51"/>
+      <c r="E22" s="45"/>
     </row>
     <row r="23" spans="1:5">
-      <c r="A23" s="52"/>
-      <c r="B23" s="52"/>
-      <c r="C23" s="51"/>
-      <c r="D23" s="51"/>
-      <c r="E23" s="51"/>
+      <c r="A23" s="46"/>
+      <c r="B23" s="46"/>
+      <c r="C23" s="45"/>
+      <c r="D23" s="45"/>
+      <c r="E23" s="45"/>
     </row>
     <row r="24" spans="1:5">
-      <c r="A24" s="52"/>
-      <c r="B24" s="52"/>
-      <c r="C24" s="51"/>
-      <c r="D24" s="51"/>
-      <c r="E24" s="51"/>
+      <c r="A24" s="46"/>
+      <c r="B24" s="46"/>
+      <c r="C24" s="45"/>
+      <c r="D24" s="45"/>
+      <c r="E24" s="45"/>
     </row>
     <row r="25" spans="1:5">
-      <c r="A25" s="52" t="s">
+      <c r="A25" s="46" t="s">
         <v>315</v>
       </c>
-      <c r="B25" s="52" t="s">
+      <c r="B25" s="46" t="s">
         <v>218</v>
       </c>
-      <c r="C25" s="51" t="s">
+      <c r="C25" s="45" t="s">
         <v>219</v>
       </c>
-      <c r="D25" s="51" t="s">
+      <c r="D25" s="45" t="s">
         <v>234</v>
       </c>
-      <c r="E25" s="51" t="s">
+      <c r="E25" s="45" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="135">
-      <c r="A26" s="52" t="s">
+      <c r="A26" s="46" t="s">
         <v>314</v>
       </c>
-      <c r="B26" s="52" t="s">
+      <c r="B26" s="46" t="s">
         <v>318</v>
       </c>
-      <c r="C26" s="51" t="s">
+      <c r="C26" s="45" t="s">
         <v>316</v>
       </c>
-      <c r="D26" s="51" t="s">
+      <c r="D26" s="45" t="s">
         <v>317</v>
       </c>
-      <c r="E26" s="51"/>
+      <c r="E26" s="45"/>
     </row>
     <row r="27" spans="1:5">
-      <c r="A27" s="52"/>
-      <c r="B27" s="52"/>
-      <c r="C27" s="51"/>
-      <c r="D27" s="51"/>
-      <c r="E27" s="51"/>
+      <c r="A27" s="46"/>
+      <c r="B27" s="46"/>
+      <c r="C27" s="45"/>
+      <c r="D27" s="45"/>
+      <c r="E27" s="45"/>
     </row>
     <row r="28" spans="1:5">
-      <c r="A28" s="52"/>
-      <c r="B28" s="52"/>
-      <c r="C28" s="51"/>
-      <c r="D28" s="51"/>
-      <c r="E28" s="51"/>
+      <c r="A28" s="46"/>
+      <c r="B28" s="46"/>
+      <c r="C28" s="45"/>
+      <c r="D28" s="45"/>
+      <c r="E28" s="45"/>
     </row>
     <row r="29" spans="1:5">
-      <c r="A29" s="52"/>
-      <c r="B29" s="52"/>
-      <c r="C29" s="51"/>
-      <c r="D29" s="51"/>
-      <c r="E29" s="51"/>
+      <c r="A29" s="46"/>
+      <c r="B29" s="46"/>
+      <c r="C29" s="45"/>
+      <c r="D29" s="45"/>
+      <c r="E29" s="45"/>
     </row>
     <row r="30" spans="1:5">
-      <c r="A30" s="52"/>
-      <c r="B30" s="52"/>
-      <c r="C30" s="51"/>
-      <c r="D30" s="51"/>
-      <c r="E30" s="51"/>
+      <c r="A30" s="46"/>
+      <c r="B30" s="46"/>
+      <c r="C30" s="45"/>
+      <c r="D30" s="45"/>
+      <c r="E30" s="45"/>
     </row>
     <row r="31" spans="1:5">
-      <c r="A31" s="52"/>
-      <c r="B31" s="52"/>
-      <c r="C31" s="51"/>
-      <c r="D31" s="51"/>
-      <c r="E31" s="51"/>
+      <c r="A31" s="46"/>
+      <c r="B31" s="46"/>
+      <c r="C31" s="45"/>
+      <c r="D31" s="45"/>
+      <c r="E31" s="45"/>
     </row>
     <row r="32" spans="1:5">
-      <c r="A32" s="52"/>
-      <c r="B32" s="52"/>
-      <c r="C32" s="51"/>
-      <c r="D32" s="51"/>
-      <c r="E32" s="51"/>
+      <c r="A32" s="46"/>
+      <c r="B32" s="46"/>
+      <c r="C32" s="45"/>
+      <c r="D32" s="45"/>
+      <c r="E32" s="45"/>
     </row>
     <row r="33" spans="1:5">
-      <c r="A33" s="52"/>
-      <c r="B33" s="52"/>
-      <c r="C33" s="51"/>
-      <c r="D33" s="51"/>
-      <c r="E33" s="51"/>
+      <c r="A33" s="46"/>
+      <c r="B33" s="46"/>
+      <c r="C33" s="45"/>
+      <c r="D33" s="45"/>
+      <c r="E33" s="45"/>
     </row>
     <row r="34" spans="1:5">
-      <c r="A34" s="52"/>
-      <c r="B34" s="52"/>
-      <c r="C34" s="51"/>
-      <c r="D34" s="51"/>
-      <c r="E34" s="51"/>
+      <c r="A34" s="46"/>
+      <c r="B34" s="46"/>
+      <c r="C34" s="45"/>
+      <c r="D34" s="45"/>
+      <c r="E34" s="45"/>
     </row>
     <row r="35" spans="1:5">
-      <c r="A35" s="52"/>
-      <c r="B35" s="52"/>
-      <c r="C35" s="51"/>
-      <c r="D35" s="51"/>
-      <c r="E35" s="51"/>
+      <c r="A35" s="46"/>
+      <c r="B35" s="46"/>
+      <c r="C35" s="45"/>
+      <c r="D35" s="45"/>
+      <c r="E35" s="45"/>
     </row>
     <row r="36" spans="1:5">
-      <c r="A36" s="52"/>
-      <c r="B36" s="52"/>
-      <c r="C36" s="51"/>
-      <c r="D36" s="51"/>
-      <c r="E36" s="51"/>
+      <c r="A36" s="46"/>
+      <c r="B36" s="46"/>
+      <c r="C36" s="45"/>
+      <c r="D36" s="45"/>
+      <c r="E36" s="45"/>
     </row>
     <row r="37" spans="1:5">
-      <c r="A37" s="52"/>
-      <c r="B37" s="52"/>
-      <c r="C37" s="51"/>
-      <c r="D37" s="51"/>
-      <c r="E37" s="51"/>
+      <c r="A37" s="46"/>
+      <c r="B37" s="46"/>
+      <c r="C37" s="45"/>
+      <c r="D37" s="45"/>
+      <c r="E37" s="45"/>
     </row>
     <row r="38" spans="1:5">
-      <c r="A38" s="52"/>
-      <c r="B38" s="52"/>
-      <c r="C38" s="51"/>
-      <c r="D38" s="51"/>
-      <c r="E38" s="51"/>
+      <c r="A38" s="46"/>
+      <c r="B38" s="46"/>
+      <c r="C38" s="45"/>
+      <c r="D38" s="45"/>
+      <c r="E38" s="45"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -5833,7 +5765,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="48" t="s">
+      <c r="A1" s="42" t="s">
         <v>336</v>
       </c>
       <c r="B1" s="2" t="s">
@@ -5844,35 +5776,35 @@
       </c>
     </row>
     <row r="2" spans="1:3" ht="93" customHeight="1">
-      <c r="A2" s="50" t="s">
+      <c r="A2" s="44" t="s">
         <v>188</v>
       </c>
-      <c r="B2" s="49" t="s">
+      <c r="B2" s="43" t="s">
         <v>337</v>
       </c>
-      <c r="C2" s="49" t="s">
+      <c r="C2" s="43" t="s">
         <v>340</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="123.75" customHeight="1">
-      <c r="A3" s="50" t="s">
+      <c r="A3" s="44" t="s">
         <v>191</v>
       </c>
-      <c r="B3" s="49" t="s">
+      <c r="B3" s="43" t="s">
         <v>344</v>
       </c>
-      <c r="C3" s="49" t="s">
+      <c r="C3" s="43" t="s">
         <v>341</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="204">
-      <c r="A4" s="50" t="s">
+      <c r="A4" s="44" t="s">
         <v>306</v>
       </c>
-      <c r="B4" s="49" t="s">
+      <c r="B4" s="43" t="s">
         <v>343</v>
       </c>
-      <c r="C4" s="49" t="s">
+      <c r="C4" s="43" t="s">
         <v>341</v>
       </c>
     </row>
@@ -6004,11 +5936,11 @@
       </c>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="59"/>
-      <c r="B4" s="60"/>
-      <c r="C4" s="59"/>
-      <c r="D4" s="59"/>
-      <c r="E4" s="59"/>
+      <c r="A4" s="53"/>
+      <c r="B4" s="54"/>
+      <c r="C4" s="53"/>
+      <c r="D4" s="53"/>
+      <c r="E4" s="53"/>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="11" t="s">
@@ -6066,7 +5998,7 @@
       </c>
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
-      <c r="D9" s="58" t="s">
+      <c r="D9" s="52" t="s">
         <v>365</v>
       </c>
       <c r="E9" s="4"/>
@@ -6079,7 +6011,7 @@
         <v>367</v>
       </c>
       <c r="C10" s="4"/>
-      <c r="D10" s="58" t="s">
+      <c r="D10" s="52" t="s">
         <v>369</v>
       </c>
       <c r="E10" s="4"/>
@@ -6090,168 +6022,168 @@
       </c>
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
-      <c r="D11" s="58" t="s">
+      <c r="D11" s="52" t="s">
         <v>370</v>
       </c>
       <c r="E11" s="4"/>
     </row>
     <row r="12" spans="1:5">
-      <c r="A12" s="61"/>
-      <c r="B12" s="62"/>
-      <c r="C12" s="62"/>
-      <c r="D12" s="63"/>
-      <c r="E12" s="62"/>
+      <c r="A12" s="55"/>
+      <c r="B12" s="56"/>
+      <c r="C12" s="56"/>
+      <c r="D12" s="57"/>
+      <c r="E12" s="56"/>
     </row>
     <row r="13" spans="1:5" ht="409.5">
       <c r="A13" s="9" t="s">
         <v>371</v>
       </c>
       <c r="B13" s="4" t="s">
+        <v>389</v>
+      </c>
+      <c r="C13" s="9" t="s">
         <v>372</v>
       </c>
-      <c r="C13" s="9" t="s">
-        <v>373</v>
-      </c>
-      <c r="D13" s="58" t="s">
-        <v>376</v>
+      <c r="D13" s="52" t="s">
+        <v>375</v>
       </c>
       <c r="E13" s="4"/>
     </row>
     <row r="14" spans="1:5" ht="24">
       <c r="A14" s="9" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B14" s="4"/>
       <c r="C14" s="4"/>
-      <c r="D14" s="58" t="s">
-        <v>375</v>
+      <c r="D14" s="52" t="s">
+        <v>374</v>
       </c>
       <c r="E14" s="4"/>
     </row>
     <row r="15" spans="1:5">
-      <c r="A15" s="61"/>
-      <c r="B15" s="62"/>
-      <c r="C15" s="62"/>
-      <c r="D15" s="63"/>
-      <c r="E15" s="62"/>
+      <c r="A15" s="55"/>
+      <c r="B15" s="56"/>
+      <c r="C15" s="56"/>
+      <c r="D15" s="57"/>
+      <c r="E15" s="56"/>
     </row>
     <row r="16" spans="1:5" ht="168">
       <c r="A16" s="9" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B16" s="4" t="s">
+        <v>376</v>
+      </c>
+      <c r="C16" s="9" t="s">
         <v>377</v>
       </c>
-      <c r="C16" s="9" t="s">
-        <v>378</v>
-      </c>
-      <c r="D16" s="58" t="s">
-        <v>389</v>
+      <c r="D16" s="52" t="s">
+        <v>388</v>
       </c>
       <c r="E16" s="4"/>
     </row>
     <row r="17" spans="1:5" ht="24">
       <c r="A17" s="9" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B17" s="4"/>
       <c r="C17" s="4" t="s">
+        <v>380</v>
+      </c>
+      <c r="D17" s="52" t="s">
         <v>381</v>
       </c>
-      <c r="D17" s="58" t="s">
-        <v>382</v>
-      </c>
       <c r="E17" s="4"/>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="61"/>
-      <c r="B18" s="62"/>
-      <c r="C18" s="62"/>
-      <c r="D18" s="63"/>
-      <c r="E18" s="62"/>
+      <c r="A18" s="55"/>
+      <c r="B18" s="56"/>
+      <c r="C18" s="56"/>
+      <c r="D18" s="57"/>
+      <c r="E18" s="56"/>
     </row>
     <row r="19" spans="1:5" ht="192">
       <c r="A19" s="9" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B19" s="4" t="s">
+        <v>376</v>
+      </c>
+      <c r="C19" s="9" t="s">
         <v>377</v>
       </c>
-      <c r="C19" s="9" t="s">
-        <v>378</v>
-      </c>
-      <c r="D19" s="58" t="s">
-        <v>387</v>
+      <c r="D19" s="52" t="s">
+        <v>386</v>
       </c>
       <c r="E19" s="4"/>
     </row>
     <row r="20" spans="1:5" ht="24">
       <c r="A20" s="9" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B20" s="4"/>
       <c r="C20" s="4" t="s">
+        <v>380</v>
+      </c>
+      <c r="D20" s="52" t="s">
         <v>381</v>
       </c>
-      <c r="D20" s="58" t="s">
-        <v>382</v>
-      </c>
       <c r="E20" s="4"/>
     </row>
     <row r="21" spans="1:5">
-      <c r="A21" s="61"/>
-      <c r="B21" s="62"/>
-      <c r="C21" s="62"/>
-      <c r="D21" s="63"/>
-      <c r="E21" s="62"/>
+      <c r="A21" s="55"/>
+      <c r="B21" s="56"/>
+      <c r="C21" s="56"/>
+      <c r="D21" s="57"/>
+      <c r="E21" s="56"/>
     </row>
     <row r="22" spans="1:5" ht="192">
       <c r="A22" s="9" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B22" s="4" t="s">
+        <v>376</v>
+      </c>
+      <c r="C22" s="9" t="s">
         <v>377</v>
       </c>
-      <c r="C22" s="9" t="s">
-        <v>378</v>
-      </c>
-      <c r="D22" s="58" t="s">
-        <v>388</v>
+      <c r="D22" s="52" t="s">
+        <v>387</v>
       </c>
       <c r="E22" s="4"/>
     </row>
     <row r="23" spans="1:5" ht="24">
       <c r="A23" s="9" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B23" s="4"/>
       <c r="C23" s="4" t="s">
+        <v>380</v>
+      </c>
+      <c r="D23" s="52" t="s">
         <v>381</v>
       </c>
-      <c r="D23" s="58" t="s">
-        <v>382</v>
-      </c>
       <c r="E23" s="4"/>
     </row>
     <row r="24" spans="1:5">
-      <c r="A24" s="61"/>
-      <c r="B24" s="62"/>
-      <c r="C24" s="62"/>
-      <c r="D24" s="63"/>
-      <c r="E24" s="62"/>
+      <c r="A24" s="55"/>
+      <c r="B24" s="56"/>
+      <c r="C24" s="56"/>
+      <c r="D24" s="57"/>
+      <c r="E24" s="56"/>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="9"/>
       <c r="B25" s="4"/>
       <c r="C25" s="4"/>
-      <c r="D25" s="58"/>
+      <c r="D25" s="52"/>
       <c r="E25" s="4"/>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="9"/>
       <c r="B26" s="4"/>
       <c r="C26" s="4"/>
-      <c r="D26" s="58"/>
+      <c r="D26" s="52"/>
       <c r="E26" s="4"/>
     </row>
     <row r="27" spans="1:5">

--- a/internal_doc/03.开发设计/OM_web接口.xlsx
+++ b/internal_doc/03.开发设计/OM_web接口.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="6510" activeTab="7"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="6510" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="需求" sheetId="1" r:id="rId1"/>
@@ -282,7 +282,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="472" uniqueCount="390">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="482" uniqueCount="393">
   <si>
     <t>需求</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -2134,6 +2134,31 @@
   </si>
   <si>
     <t>notify task</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>agent更新DEL_HOST任务进度请求(agent-&gt;om)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>agent更新DEL_HOST任务进度响应(om-&gt;agent)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+    OM_BSON_FIELD_HOST_INFO:
+    [
+    {
+        OM_HOST_FIELD_NAME:"host",
+        OM_HOST_FIELD_IP:"ip"
+        OM_BSON_FIELD_HOST_USER:""
+        OM_BSON_FIELD_HOST_PASSWD:""
+        OM_BSON_FIELD_INSTALLPATH:""
+        OM_BSON_FIELD_HOST_SSHPORT:""
+    }
+    , ...
+    ]
+}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2546,6 +2571,74 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -2557,7 +2650,7 @@
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:sysClr val="window" lastClr="C7EDCC"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -5753,7 +5846,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="16.625" style="3" customWidth="1"/>
@@ -5775,7 +5868,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="93" customHeight="1">
+    <row r="2" spans="1:3" ht="192">
       <c r="A2" s="44" t="s">
         <v>188</v>
       </c>
@@ -5786,32 +5879,38 @@
         <v>340</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="123.75" customHeight="1">
+    <row r="3" spans="1:3" ht="168">
       <c r="A3" s="44" t="s">
-        <v>191</v>
+        <v>44</v>
       </c>
       <c r="B3" s="43" t="s">
-        <v>344</v>
+        <v>392</v>
       </c>
       <c r="C3" s="43" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="204">
       <c r="A4" s="44" t="s">
-        <v>306</v>
+        <v>191</v>
       </c>
       <c r="B4" s="43" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C4" s="43" t="s">
         <v>341</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="4"/>
-      <c r="B5" s="4"/>
-      <c r="C5" s="4"/>
+    <row r="5" spans="1:3" ht="204">
+      <c r="A5" s="44" t="s">
+        <v>306</v>
+      </c>
+      <c r="B5" s="43" t="s">
+        <v>343</v>
+      </c>
+      <c r="C5" s="43" t="s">
+        <v>341</v>
+      </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4"/>
@@ -5872,6 +5971,11 @@
       <c r="A17" s="4"/>
       <c r="B17" s="4"/>
       <c r="C17" s="4"/>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="4"/>
+      <c r="B18" s="4"/>
+      <c r="C18" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -5882,7 +5986,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="22.375" style="23" bestFit="1" customWidth="1"/>
@@ -6102,9 +6206,9 @@
       <c r="D18" s="57"/>
       <c r="E18" s="56"/>
     </row>
-    <row r="19" spans="1:5" ht="192">
+    <row r="19" spans="1:5" ht="168">
       <c r="A19" s="9" t="s">
-        <v>382</v>
+        <v>390</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>376</v>
@@ -6113,13 +6217,13 @@
         <v>377</v>
       </c>
       <c r="D19" s="52" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="E19" s="4"/>
     </row>
     <row r="20" spans="1:5" ht="24">
       <c r="A20" s="9" t="s">
-        <v>383</v>
+        <v>391</v>
       </c>
       <c r="B20" s="4"/>
       <c r="C20" s="4" t="s">
@@ -6139,7 +6243,7 @@
     </row>
     <row r="22" spans="1:5" ht="192">
       <c r="A22" s="9" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>376</v>
@@ -6148,13 +6252,13 @@
         <v>377</v>
       </c>
       <c r="D22" s="52" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="E22" s="4"/>
     </row>
     <row r="23" spans="1:5" ht="24">
       <c r="A23" s="9" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="B23" s="4"/>
       <c r="C23" s="4" t="s">
@@ -6172,33 +6276,68 @@
       <c r="D24" s="57"/>
       <c r="E24" s="56"/>
     </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="9"/>
-      <c r="B25" s="4"/>
-      <c r="C25" s="4"/>
-      <c r="D25" s="52"/>
+    <row r="25" spans="1:5" ht="192">
+      <c r="A25" s="9" t="s">
+        <v>384</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>376</v>
+      </c>
+      <c r="C25" s="9" t="s">
+        <v>377</v>
+      </c>
+      <c r="D25" s="52" t="s">
+        <v>387</v>
+      </c>
       <c r="E25" s="4"/>
     </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="9"/>
+    <row r="26" spans="1:5" ht="24">
+      <c r="A26" s="9" t="s">
+        <v>385</v>
+      </c>
       <c r="B26" s="4"/>
-      <c r="C26" s="4"/>
-      <c r="D26" s="52"/>
+      <c r="C26" s="4" t="s">
+        <v>380</v>
+      </c>
+      <c r="D26" s="52" t="s">
+        <v>381</v>
+      </c>
       <c r="E26" s="4"/>
     </row>
     <row r="27" spans="1:5">
-      <c r="A27" s="9"/>
-      <c r="B27" s="4"/>
-      <c r="C27" s="4"/>
-      <c r="D27" s="9"/>
-      <c r="E27" s="4"/>
+      <c r="A27" s="55"/>
+      <c r="B27" s="56"/>
+      <c r="C27" s="56"/>
+      <c r="D27" s="57"/>
+      <c r="E27" s="56"/>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="9"/>
       <c r="B28" s="4"/>
       <c r="C28" s="4"/>
-      <c r="D28" s="9"/>
+      <c r="D28" s="52"/>
       <c r="E28" s="4"/>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="9"/>
+      <c r="B29" s="4"/>
+      <c r="C29" s="4"/>
+      <c r="D29" s="52"/>
+      <c r="E29" s="4"/>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="9"/>
+      <c r="B30" s="4"/>
+      <c r="C30" s="4"/>
+      <c r="D30" s="9"/>
+      <c r="E30" s="4"/>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="9"/>
+      <c r="B31" s="4"/>
+      <c r="C31" s="4"/>
+      <c r="D31" s="9"/>
+      <c r="E31" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/internal_doc/03.开发设计/OM_web接口.xlsx
+++ b/internal_doc/03.开发设计/OM_web接口.xlsx
@@ -2151,6 +2151,7 @@
     {
         OM_HOST_FIELD_NAME:"host",
         OM_HOST_FIELD_IP:"ip"
+        OM_BSON_CLUSTER_NAME:""
         OM_BSON_FIELD_HOST_USER:""
         OM_BSON_FIELD_HOST_PASSWD:""
         OM_BSON_FIELD_INSTALLPATH:""
@@ -5879,7 +5880,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="168">
+    <row r="3" spans="1:3" ht="180">
       <c r="A3" s="44" t="s">
         <v>44</v>
       </c>
